--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1F9C274-5315-42F2-A13D-0FD4235EDEBF}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99560384-8675-4E90-92BA-AA4F27A1F8B2}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="106">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -99,9 +99,6 @@
     <t>Photo</t>
   </si>
   <si>
-    <t>Lim Boon Choon Stanley</t>
-  </si>
-  <si>
     <t>Chairman</t>
   </si>
   <si>
@@ -126,40 +123,7 @@
     <t>样本</t>
   </si>
   <si>
-    <t>Vice-Chairman</t>
-  </si>
-  <si>
     <t>副主席</t>
-  </si>
-  <si>
-    <t>Secretary</t>
-  </si>
-  <si>
-    <t>秘书</t>
-  </si>
-  <si>
-    <t>Vice-Secretary</t>
-  </si>
-  <si>
-    <t>副秘书</t>
-  </si>
-  <si>
-    <t>Treasurer</t>
-  </si>
-  <si>
-    <t>财政</t>
-  </si>
-  <si>
-    <t>Vice-Treasurer</t>
-  </si>
-  <si>
-    <t>副财政</t>
-  </si>
-  <si>
-    <t>Vice-Chairman Committee</t>
-  </si>
-  <si>
-    <t>副主席委员</t>
   </si>
   <si>
     <t>Sub-Committee (English)</t>
@@ -538,7 +502,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -549,24 +513,22 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -986,13 +948,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="5" width="22" customWidth="1"/>
+    <col min="4" max="4" width="33.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1013,353 +976,341 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="8">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D7" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="8">
-        <v>2</v>
-      </c>
-      <c r="B3" s="12" t="s">
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="8"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="8">
-        <v>3</v>
-      </c>
-      <c r="B4" s="12" t="s">
+      <c r="D8" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D9" s="10"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="8">
-        <v>4</v>
-      </c>
-      <c r="B5" s="12" t="s">
+      <c r="C10" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D10" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="8">
-        <v>5</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="E10" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="8"/>
-    </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="8">
-        <v>6</v>
-      </c>
-      <c r="B7" s="12" t="s">
+      <c r="D11" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C12" s="13"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="C13" s="13"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E7" s="8"/>
-    </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="12" t="s">
+      <c r="C14" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="D14" s="10"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="8"/>
-    </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="8">
-        <v>8</v>
-      </c>
-      <c r="B9" s="12" t="s">
+      <c r="C15" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="D15" s="10"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="8"/>
-    </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="8">
-        <v>9</v>
-      </c>
-      <c r="B10" s="12" t="s">
+      <c r="C16" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="D16" s="10"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="8"/>
-    </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="8">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12" t="s">
+      <c r="D17" s="10"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="4">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C18" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" s="8"/>
-    </row>
-    <row r="12" spans="1:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="8">
-        <v>11</v>
-      </c>
-      <c r="B12" s="12" t="s">
+      <c r="D18" s="10"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="8"/>
-    </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="8">
-        <v>12</v>
-      </c>
-      <c r="B13" s="12" t="s">
+      <c r="C19" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="8"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="8">
-        <v>13</v>
-      </c>
-      <c r="B14" s="12" t="s">
+      <c r="D19" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="8"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="8">
-        <v>14</v>
-      </c>
-      <c r="B15" s="12" t="s">
+      <c r="D20" s="10"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C21" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="8"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="8">
-        <v>15</v>
-      </c>
-      <c r="B16" s="12" t="s">
+      <c r="D21" s="10"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="4">
+        <v>21</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C22" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="8">
-        <v>16</v>
-      </c>
-      <c r="B17" s="12" t="s">
+      <c r="D22" s="10"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C23" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="8"/>
-    </row>
-    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="8">
-        <v>17</v>
-      </c>
-      <c r="B18" s="12" t="s">
+      <c r="D23" s="10"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="4">
+        <v>23</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C24" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="8"/>
-    </row>
-    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="8">
-        <v>18</v>
-      </c>
-      <c r="B19" s="12" t="s">
+      <c r="D24" s="10"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C25" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="8"/>
-    </row>
-    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="8">
-        <v>19</v>
-      </c>
-      <c r="B20" s="12" t="s">
+      <c r="D25" s="10"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="4">
+        <v>25</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C26" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="8"/>
-    </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="8">
-        <v>20</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="8"/>
-    </row>
-    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="8">
-        <v>21</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="8"/>
-    </row>
-    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="8">
-        <v>22</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="8"/>
-    </row>
-    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="8">
-        <v>23</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="8"/>
-    </row>
-    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="8">
-        <v>24</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="8"/>
-    </row>
-    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="8">
-        <v>25</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="8"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1381,7 +1332,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>20</v>
@@ -1390,10 +1341,10 @@
         <v>21</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>23</v>
@@ -1404,17 +1355,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -1422,16 +1375,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="F3" s="5"/>
     </row>
@@ -1440,17 +1393,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>36</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -1458,17 +1409,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>38</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -1476,17 +1425,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>40</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -1494,17 +1441,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>42</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="E7" s="5"/>
       <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -1512,17 +1457,15 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>44</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="E8" s="5"/>
       <c r="F8" s="5"/>
     </row>
   </sheetData>
@@ -1546,13 +1489,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>20</v>
@@ -1561,7 +1504,7 @@
         <v>21</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>23</v>
@@ -1569,85 +1512,85 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C2" s="5">
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="F2" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C3" s="5">
         <v>2</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C4" s="5">
         <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C5" s="5">
         <v>2</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="F5" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G5" s="5"/>
     </row>
@@ -1669,16 +1612,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -1686,13 +1629,13 @@
         <v>46263</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -1700,13 +1643,13 @@
         <v>46280</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1725,26 +1668,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1994,15 +1937,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
@@ -2011,6 +1945,15 @@
     <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2033,14 +1976,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2049,4 +1984,12 @@
     <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99560384-8675-4E90-92BA-AA4F27A1F8B2}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F00359DD-07EE-42F1-BC43-C3FCBE787531}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="105">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -250,9 +250,6 @@
   </si>
   <si>
     <t>林文俊</t>
-  </si>
-  <si>
-    <t>Chairman 会长</t>
   </si>
   <si>
     <t>Lim Soi Tee</t>
@@ -352,7 +349,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -391,11 +388,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -502,7 +494,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -519,14 +511,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -948,17 +939,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="33.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -969,13 +959,10 @@
         <v>21</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -985,332 +972,293 @@
       <c r="C2" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4">
         <v>21</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4">
         <v>23</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" s="10"/>
-      <c r="E26" s="4"/>
+      <c r="D26" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1441,10 +1389,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>61</v>
@@ -1457,10 +1405,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>61</v>
@@ -1937,6 +1885,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
@@ -1945,15 +1902,6 @@
     <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1976,6 +1924,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1984,12 +1940,4 @@
     <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F00359DD-07EE-42F1-BC43-C3FCBE787531}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{829E0F66-963C-4D2F-9019-11462E21D3E5}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="139">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -102,9 +102,6 @@
     <t>Chairman</t>
   </si>
   <si>
-    <t>stanley_lim.jpg</t>
-  </si>
-  <si>
     <t>Order</t>
   </si>
   <si>
@@ -123,9 +120,6 @@
     <t>样本</t>
   </si>
   <si>
-    <t>副主席</t>
-  </si>
-  <si>
     <t>Sub-Committee (English)</t>
   </si>
   <si>
@@ -210,9 +204,6 @@
     <t>黄献威</t>
   </si>
   <si>
-    <t>Vice Chairman Committee 副会长委员</t>
-  </si>
-  <si>
     <t>Goh Hock Kee</t>
   </si>
   <si>
@@ -231,9 +222,6 @@
     <t>王宝泉</t>
   </si>
   <si>
-    <t>Vice Chairman 第一副会长</t>
-  </si>
-  <si>
     <t>Koh Hock Siong BBM(L)</t>
   </si>
   <si>
@@ -340,6 +328,120 @@
   </si>
   <si>
     <t>张艺超</t>
+  </si>
+  <si>
+    <t>stanley.jpg</t>
+  </si>
+  <si>
+    <t>CherKimSeah.jpg</t>
+  </si>
+  <si>
+    <t>ChewGimCheong.jpg</t>
+  </si>
+  <si>
+    <t>GohHockKee.jpg</t>
+  </si>
+  <si>
+    <t>GohKenLai.jpg</t>
+  </si>
+  <si>
+    <t>KohKengGuan.jpg</t>
+  </si>
+  <si>
+    <t>LimSoiTee.jpg</t>
+  </si>
+  <si>
+    <t>NeoTianSiah.jpg</t>
+  </si>
+  <si>
+    <t>QuekChiaSeng.jpg</t>
+  </si>
+  <si>
+    <t>YapGuanTee.jpg</t>
+  </si>
+  <si>
+    <t>ZhangYiChao.jpg</t>
+  </si>
+  <si>
+    <t>Djoni.jpg</t>
+  </si>
+  <si>
+    <t>Fitri.jpg</t>
+  </si>
+  <si>
+    <t>Jie.jpg</t>
+  </si>
+  <si>
+    <t>Peter.jpg</t>
+  </si>
+  <si>
+    <t>Tony.jpg</t>
+  </si>
+  <si>
+    <t>William.jpg</t>
+  </si>
+  <si>
+    <t>Simon.jpg</t>
+  </si>
+  <si>
+    <t>Vincent.jpg</t>
+  </si>
+  <si>
+    <t>Eric.jpg</t>
+  </si>
+  <si>
+    <t>KohHockSiong.jpg</t>
+  </si>
+  <si>
+    <t>Ilman.jpg</t>
+  </si>
+  <si>
+    <t>Lawrence.jpg</t>
+  </si>
+  <si>
+    <t>Rosaline.jpg</t>
+  </si>
+  <si>
+    <t>Veron.jpg</t>
+  </si>
+  <si>
+    <t>第一副会长</t>
+  </si>
+  <si>
+    <t>Vice Chairman</t>
+  </si>
+  <si>
+    <t>副会长委员</t>
+  </si>
+  <si>
+    <t>Vice Chairman Committee</t>
+  </si>
+  <si>
+    <t>Stanley.jpg</t>
+  </si>
+  <si>
+    <t>Secretary</t>
+  </si>
+  <si>
+    <t>Vice Secretary</t>
+  </si>
+  <si>
+    <t>Treasurer</t>
+  </si>
+  <si>
+    <t>Vice Treasurer</t>
+  </si>
+  <si>
+    <t>秘书</t>
+  </si>
+  <si>
+    <t>副秘书</t>
+  </si>
+  <si>
+    <t>财政</t>
+  </si>
+  <si>
+    <t>副财政</t>
   </si>
 </sst>
 </file>
@@ -415,7 +517,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -490,11 +592,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D5DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D5DD"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -520,6 +633,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -967,109 +1081,125 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="4"/>
+        <v>54</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4"/>
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="4"/>
+        <v>58</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="4"/>
+        <v>64</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="4"/>
+        <v>66</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="4"/>
+        <v>68</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1077,188 +1207,220 @@
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="4"/>
+        <v>72</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="12" spans="1:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C13" s="12"/>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="4"/>
+        <v>76</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="4"/>
+        <v>78</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" s="4"/>
+        <v>80</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D18" s="4"/>
+        <v>84</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="4"/>
+        <v>86</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4">
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="4"/>
+        <v>90</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4">
         <v>21</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D22" s="4"/>
+        <v>92</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" s="4"/>
+        <v>94</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4">
         <v>23</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D25" s="4"/>
+        <v>98</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="4">
         <v>25</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>111</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1267,7 +1429,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1280,7 +1442,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>20</v>
@@ -1292,7 +1454,7 @@
         <v>22</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>23</v>
@@ -1303,19 +1465,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>25</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -1323,98 +1485,200 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="5"/>
+        <v>126</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+        <v>129</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+        <v>129</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+        <v>129</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+        <v>129</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="13">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="F9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="13">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="13">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C11" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="D11" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="13">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F12" t="s">
+        <v>124</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1437,13 +1701,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>20</v>
@@ -1452,7 +1716,7 @@
         <v>21</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>23</v>
@@ -1460,85 +1724,85 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C2" s="5">
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="F2" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C3" s="5">
         <v>2</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C4" s="5">
         <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C5" s="5">
         <v>2</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="F5" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G5" s="5"/>
     </row>
@@ -1560,16 +1824,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -1577,13 +1841,13 @@
         <v>46263</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -1591,13 +1855,13 @@
         <v>46280</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1616,26 +1880,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1885,15 +2149,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
@@ -1902,6 +2157,15 @@
     <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1924,14 +2188,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1940,4 +2196,12 @@
     <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,24 +8,37 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{829E0F66-963C-4D2F-9019-11462E21D3E5}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF8E275B-9681-4DE9-802A-F7E4AC116625}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
-    <sheet name="1_Committee" sheetId="2" r:id="rId2"/>
-    <sheet name="2_OfficeBearers" sheetId="3" r:id="rId3"/>
-    <sheet name="3_SubCommittees" sheetId="4" r:id="rId4"/>
-    <sheet name="4_Events" sheetId="5" r:id="rId5"/>
+    <sheet name="1_Events" sheetId="5" r:id="rId2"/>
+    <sheet name="2_Committee" sheetId="2" r:id="rId3"/>
+    <sheet name="3_OfficeBearers" sheetId="3" r:id="rId4"/>
+    <sheet name="4_SubCommittees" sheetId="4" r:id="rId5"/>
     <sheet name="Info" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="238">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -93,9 +106,6 @@
     <t>Name (中文)</t>
   </si>
   <si>
-    <t>Title</t>
-  </si>
-  <si>
     <t>Photo</t>
   </si>
   <si>
@@ -108,9 +118,6 @@
     <t>Title (English)</t>
   </si>
   <si>
-    <t>Title (中文)</t>
-  </si>
-  <si>
     <t>主席</t>
   </si>
   <si>
@@ -153,21 +160,6 @@
     <t>Event (中文)</t>
   </si>
   <si>
-    <t>Personnel In Charge</t>
-  </si>
-  <si>
-    <t>Charity Concert: Getai Glamour</t>
-  </si>
-  <si>
-    <t>慈善演唱会：歌台闪耀</t>
-  </si>
-  <si>
-    <t>Sample Event</t>
-  </si>
-  <si>
-    <t>样本活动</t>
-  </si>
-  <si>
     <t>Field</t>
   </si>
   <si>
@@ -442,6 +434,324 @@
   </si>
   <si>
     <t>副财政</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Programme/Fundraising</t>
+  </si>
+  <si>
+    <t>CNY Ration + Ang Bao</t>
+  </si>
+  <si>
+    <t>CNY Ration + Ang Bao Giving to AMS Beneficiaries</t>
+  </si>
+  <si>
+    <t>Programme</t>
+  </si>
+  <si>
+    <t>Ahmad Ibrahim CNY Engagement</t>
+  </si>
+  <si>
+    <t>Compliance/Ops</t>
+  </si>
+  <si>
+    <t>华报善堂 50 pax Elderly Engagement</t>
+  </si>
+  <si>
+    <t>Partnership/CSR</t>
+  </si>
+  <si>
+    <t>Elderly Outing (Chloe's Volunteer)</t>
+  </si>
+  <si>
+    <t>Hari Raya Puasa Ang Pao Distribution (AMS Muslims)</t>
+  </si>
+  <si>
+    <t>Hari Raya Puasa Lunch</t>
+  </si>
+  <si>
+    <t>Health Talk by TCM Physician</t>
+  </si>
+  <si>
+    <t>Governance</t>
+  </si>
+  <si>
+    <t>AGM &amp; Election of 10th Term Management Committee</t>
+  </si>
+  <si>
+    <t>Fundraising</t>
+  </si>
+  <si>
+    <t>AISS Engagement and Registration for Funerary Portrait Taking</t>
+  </si>
+  <si>
+    <t>Shine Dragon Boat Dumpling Festival Celebration</t>
+  </si>
+  <si>
+    <t>Charity Concert</t>
+  </si>
+  <si>
+    <t>Partnership</t>
+  </si>
+  <si>
+    <t>7th Month Fundraising Period (End)</t>
+  </si>
+  <si>
+    <t>Charity Concert at Tzu Chi</t>
+  </si>
+  <si>
+    <t>Information</t>
+  </si>
+  <si>
+    <t>New Year Ration Event (501 beneficiaries; Minister K Shanmugam attended)</t>
+  </si>
+  <si>
+    <t>新年物资派发活动（501名受惠者，尚穆根部长出席）</t>
+  </si>
+  <si>
+    <t>农历新年物资及红包派发（AMS受惠者）</t>
+  </si>
+  <si>
+    <t>CNY Dinner for 500 Elderly</t>
+  </si>
+  <si>
+    <t>500位乐龄人士新春晚宴</t>
+  </si>
+  <si>
+    <t>阿末依布拉欣新春交流活动</t>
+  </si>
+  <si>
+    <t>Revised TCM Fee Schedule Effective</t>
+  </si>
+  <si>
+    <t>中医收费标准调整生效</t>
+  </si>
+  <si>
+    <t>华报善堂50人乐龄交流活动</t>
+  </si>
+  <si>
+    <t>乐龄户外活动（Chloe义工队）</t>
+  </si>
+  <si>
+    <t>开斋节红包派发（AMS穆斯林受惠者）</t>
+  </si>
+  <si>
+    <t>开斋节午宴</t>
+  </si>
+  <si>
+    <t>中医师健康讲座</t>
+  </si>
+  <si>
+    <t>常年会员大会暨第十届管理委员会选举</t>
+  </si>
+  <si>
+    <t>By-election of Office Bearers (10th Term)</t>
+  </si>
+  <si>
+    <t>第十届职员补选</t>
+  </si>
+  <si>
+    <t>25th Anniversary Charity Dinner, Golf @ Orchid Country Club, Magazine Launch</t>
+  </si>
+  <si>
+    <t>25周年慈善晚宴、高尔夫球赛（胡姬乡村俱乐部）暨特刊推介</t>
+  </si>
+  <si>
+    <t>10th Term Management Committee Sworn In</t>
+  </si>
+  <si>
+    <t>第十届管理委员会宣誓就职</t>
+  </si>
+  <si>
+    <t>AISS交流活动暨寿像拍摄登记</t>
+  </si>
+  <si>
+    <t>Vesak Day Fundraising (Ubin Thai) – Day 1</t>
+  </si>
+  <si>
+    <t>卫塞节筹款（Ubin Thai）第一天</t>
+  </si>
+  <si>
+    <t>Vesak Day Fundraising (Ubin Thai) – Day 2</t>
+  </si>
+  <si>
+    <t>卫塞节筹款（Ubin Thai）第二天</t>
+  </si>
+  <si>
+    <t>Vesak Day Fundraising (Ubin Thai) – Day 3</t>
+  </si>
+  <si>
+    <t>卫塞节筹款（Ubin Thai）第三天</t>
+  </si>
+  <si>
+    <t>Vesak Day Fundraising (Ubin Thai) – Day 4</t>
+  </si>
+  <si>
+    <t>卫塞节筹款（Ubin Thai）第四天</t>
+  </si>
+  <si>
+    <t>端午节粽子庆祝活动</t>
+  </si>
+  <si>
+    <t>Morgan Stanley CSR + Funerary Portrait Taking</t>
+  </si>
+  <si>
+    <t>摩根士丹利企业社会责任活动暨寿像拍摄</t>
+  </si>
+  <si>
+    <t>Naval Base Secondary School Outing (Date Unconfirmed)</t>
+  </si>
+  <si>
+    <t>海军部中学户外活动（日期待定）</t>
+  </si>
+  <si>
+    <t>Asiatic Fire System CSR National Day Celebration (150 pax)</t>
+  </si>
+  <si>
+    <t>Asiatic Fire System企业社会责任国庆庆祝会（150人）</t>
+  </si>
+  <si>
+    <t>7th Month Fundraising Period (Start) – NHST Charity Auction &amp; Charity Dinner for Elderly</t>
+  </si>
+  <si>
+    <t>七月筹款期开始 – 慈善拍卖会暨乐龄慈善晚宴</t>
+  </si>
+  <si>
+    <t>TFE Ration Distribution (140 pax)</t>
+  </si>
+  <si>
+    <t>TFE物资派发（140人）</t>
+  </si>
+  <si>
+    <t>MWS Family Service Centre Family Wellness Day (Exhibition Booth)</t>
+  </si>
+  <si>
+    <t>卫理公会福利服务家庭服务中心家庭健康日（展位）</t>
+  </si>
+  <si>
+    <t>正罡玄门 Mid-Autumn Ration (200 pax)</t>
+  </si>
+  <si>
+    <t>正罡玄门中秋物资派发（200人）</t>
+  </si>
+  <si>
+    <t>七月筹款期结束</t>
+  </si>
+  <si>
+    <t>慈济慈善演唱会</t>
+  </si>
+  <si>
+    <t>Nine Emperor Gods Festival Fundraiser – Day 1</t>
+  </si>
+  <si>
+    <t>九皇爷诞筹款第一天</t>
+  </si>
+  <si>
+    <t>Nine Emperor Gods Festival Fundraiser – Day 2</t>
+  </si>
+  <si>
+    <t>九皇爷诞筹款第二天</t>
+  </si>
+  <si>
+    <t>Nine Emperor Gods Festival Fundraiser – Day 3</t>
+  </si>
+  <si>
+    <t>九皇爷诞筹款第三天</t>
+  </si>
+  <si>
+    <t>Charity Walk (Tentative)</t>
+  </si>
+  <si>
+    <t>慈善健走（暂定）</t>
+  </si>
+  <si>
+    <t>Deepavali Ang Pao Distribution (AMS Hindus)</t>
+  </si>
+  <si>
+    <t>屠妖节红包派发（AMS印族受惠者）</t>
+  </si>
+  <si>
+    <t>MS Project Ration Distribution (Date Unconfirmed)</t>
+  </si>
+  <si>
+    <t>MS项目物资派发（日期待定）</t>
+  </si>
+  <si>
+    <t>Sponsor a HUG Campaign (Physical Launch Closer to Christmas)</t>
+  </si>
+  <si>
+    <t>「认养一个拥抱」慈善运动（圣诞前实体推介）</t>
+  </si>
+  <si>
+    <t>New Year Ration</t>
+  </si>
+  <si>
+    <t>新年物资派发</t>
+  </si>
+  <si>
+    <t>农历新年物资及红包派发</t>
+  </si>
+  <si>
+    <t>CNY Dinner – CSR (JustCo or MS Project) – Day 1</t>
+  </si>
+  <si>
+    <t>新春晚宴 – 企业社会责任（JustCo或MS项目）第一天</t>
+  </si>
+  <si>
+    <t>CNY Dinner – CSR (JustCo or MS Project) – Day 2</t>
+  </si>
+  <si>
+    <t>新春晚宴 – 企业社会责任（JustCo或MS项目）第二天</t>
+  </si>
+  <si>
+    <t>CSR Partnership – Corporate / School</t>
+  </si>
+  <si>
+    <t>企业／学校社会责任合作</t>
+  </si>
+  <si>
+    <t>Hari Raya Puasa Ang Pao Distribution + Goodie Bag + Lunch</t>
+  </si>
+  <si>
+    <t>开斋节红包及礼包派发暨午宴</t>
+  </si>
+  <si>
+    <t>CSR Partnership – Corporate / School (Sunrise Walk)</t>
+  </si>
+  <si>
+    <t>企业／学校社会责任合作（日出健走）</t>
+  </si>
+  <si>
+    <t>Dragon Boat Festival Event (Actual Day 9 June)</t>
+  </si>
+  <si>
+    <t>端午节活动（实际节日为6月9日）</t>
+  </si>
+  <si>
+    <t>CSR Partnership – Corporate / School (National Day Celebration)</t>
+  </si>
+  <si>
+    <t>企业／学校社会责任合作（国庆庆祝）</t>
+  </si>
+  <si>
+    <t>7th Month Fundraising Period (Actual Day 16 Aug, covering 2–30 Aug)</t>
+  </si>
+  <si>
+    <t>七月筹款期（实际日期8月16日，涵盖8月2日至30日）</t>
+  </si>
+  <si>
+    <t>CSR Partnership – Corporate / School (Charity Concert)</t>
+  </si>
+  <si>
+    <t>企业／学校社会责任合作（慈善演唱会）</t>
+  </si>
+  <si>
+    <t>慈善演唱会</t>
+  </si>
+  <si>
+    <t>Title (Chinese)</t>
   </si>
 </sst>
 </file>
@@ -451,7 +761,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -498,6 +808,18 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -517,7 +839,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -603,11 +925,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D5DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D5DD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D5DD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -616,8 +951,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -633,7 +966,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -934,6 +1280,28 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="525" row="7">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{35DFA8DD-4C2F-4027-B6F7-80CB9B5FDB44}">
+  <we:reference id="WA200010725" version="1.0.0.1" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010725" version="1.0.0.1" store="WA200010725" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;02c0abc4-2cfb-4606-8b6f-f01025eea551&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A22"/>
@@ -1052,6 +1420,1180 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:E61"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="72.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="13">
+        <f>DATE(2026,1,1)</f>
+        <v>46023</v>
+      </c>
+      <c r="B2" s="14" t="str">
+        <f>TEXT($A2,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="13">
+        <f>DATE(2026,2,8)</f>
+        <v>46061</v>
+      </c>
+      <c r="B3" s="14" t="str">
+        <f>TEXT($A3,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="13">
+        <f>DATE(2026,2,26)</f>
+        <v>46079</v>
+      </c>
+      <c r="B4" s="14" t="str">
+        <f>TEXT($A4,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="13">
+        <f>DATE(2026,2,27)</f>
+        <v>46080</v>
+      </c>
+      <c r="B5" s="14" t="str">
+        <f>TEXT($A5,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="13">
+        <f>DATE(2026,3,2)</f>
+        <v>46083</v>
+      </c>
+      <c r="B6" s="14" t="str">
+        <f>TEXT($A6,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="13">
+        <f>DATE(2026,3,7)</f>
+        <v>46088</v>
+      </c>
+      <c r="B7" s="14" t="str">
+        <f>TEXT($A7,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="13">
+        <f>DATE(2026,3,20)</f>
+        <v>46101</v>
+      </c>
+      <c r="B8" s="14" t="str">
+        <f>TEXT($A8,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="13">
+        <f>DATE(2026,3,23)</f>
+        <v>46104</v>
+      </c>
+      <c r="B9" s="14" t="str">
+        <f>TEXT($A9,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="13">
+        <f>DATE(2026,3,24)</f>
+        <v>46105</v>
+      </c>
+      <c r="B10" s="14" t="str">
+        <f>TEXT($A10,"ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="13">
+        <f>DATE(2026,3,27)</f>
+        <v>46108</v>
+      </c>
+      <c r="B11" s="14" t="str">
+        <f>TEXT($A11,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="13">
+        <f>DATE(2026,4,20)</f>
+        <v>46132</v>
+      </c>
+      <c r="B12" s="14" t="str">
+        <f>TEXT($A12,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="13">
+        <f>DATE(2026,5,4)</f>
+        <v>46146</v>
+      </c>
+      <c r="B13" s="14" t="str">
+        <f>TEXT($A13,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="13">
+        <f>DATE(2026,5,15)</f>
+        <v>46157</v>
+      </c>
+      <c r="B14" s="14" t="str">
+        <f>TEXT($A14,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="13">
+        <f>DATE(2026,5,24)</f>
+        <v>46166</v>
+      </c>
+      <c r="B15" s="14" t="str">
+        <f>TEXT($A15,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="13">
+        <f>DATE(2026,5,25)</f>
+        <v>46167</v>
+      </c>
+      <c r="B16" s="14" t="str">
+        <f>TEXT($A16,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="13">
+        <f>DATE(2026,5,29)</f>
+        <v>46171</v>
+      </c>
+      <c r="B17" s="14" t="str">
+        <f>TEXT($A17,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="13">
+        <f>DATE(2026,5,30)</f>
+        <v>46172</v>
+      </c>
+      <c r="B18" s="14" t="str">
+        <f>TEXT($A18,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="13">
+        <f>DATE(2026,5,31)</f>
+        <v>46173</v>
+      </c>
+      <c r="B19" s="14" t="str">
+        <f>TEXT($A19,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="13">
+        <f>DATE(2026,6,1)</f>
+        <v>46174</v>
+      </c>
+      <c r="B20" s="14" t="str">
+        <f>TEXT($A20,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="13">
+        <f>DATE(2026,6,13)</f>
+        <v>46186</v>
+      </c>
+      <c r="B21" s="14" t="str">
+        <f>TEXT($A21,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="13">
+        <f>DATE(2026,7,3)</f>
+        <v>46206</v>
+      </c>
+      <c r="B22" s="14" t="str">
+        <f>TEXT($A22,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="13">
+        <f>DATE(2026,7,24)</f>
+        <v>46227</v>
+      </c>
+      <c r="B23" s="14" t="str">
+        <f>TEXT($A23,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="13">
+        <f>DATE(2026,8,1)</f>
+        <v>46235</v>
+      </c>
+      <c r="B24" s="14" t="str">
+        <f>TEXT($A24,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="13">
+        <f>DATE(2026,8,22)</f>
+        <v>46256</v>
+      </c>
+      <c r="B25" s="14" t="str">
+        <f>TEXT($A25,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="13">
+        <f>DATE(2026,9,4)</f>
+        <v>46269</v>
+      </c>
+      <c r="B26" s="14" t="str">
+        <f>TEXT($A26,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="13">
+        <f>DATE(2026,9,5)</f>
+        <v>46270</v>
+      </c>
+      <c r="B27" s="14" t="str">
+        <f>TEXT($A27,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="13">
+        <f>DATE(2026,9,19)</f>
+        <v>46284</v>
+      </c>
+      <c r="B28" s="14" t="str">
+        <f>TEXT($A28,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="13">
+        <f>DATE(2026,9,21)</f>
+        <v>46286</v>
+      </c>
+      <c r="B29" s="14" t="str">
+        <f>TEXT($A29,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="13">
+        <f>DATE(2026,10,10)</f>
+        <v>46305</v>
+      </c>
+      <c r="B30" s="14" t="str">
+        <f>TEXT($A30,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="13">
+        <f>DATE(2026,10,12)</f>
+        <v>46307</v>
+      </c>
+      <c r="B31" s="14" t="str">
+        <f>TEXT($A31,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="13">
+        <f>DATE(2026,10,13)</f>
+        <v>46308</v>
+      </c>
+      <c r="B32" s="14" t="str">
+        <f>TEXT($A32,"ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="13">
+        <f>DATE(2026,10,14)</f>
+        <v>46309</v>
+      </c>
+      <c r="B33" s="14" t="str">
+        <f>TEXT($A33,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" s="13">
+        <f>DATE(2026,10,31)</f>
+        <v>46326</v>
+      </c>
+      <c r="B34" s="14" t="str">
+        <f>TEXT($A34,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="13">
+        <f>DATE(2026,11,3)</f>
+        <v>46329</v>
+      </c>
+      <c r="B35" s="14" t="str">
+        <f>TEXT($A35,"ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="13">
+        <f>DATE(2026,11,10)</f>
+        <v>46336</v>
+      </c>
+      <c r="B36" s="14" t="str">
+        <f>TEXT($A36,"ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="13">
+        <f>DATE(2026,12,16)</f>
+        <v>46372</v>
+      </c>
+      <c r="B37" s="14" t="str">
+        <f>TEXT($A37,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" s="13">
+        <f>DATE(2027,1,1)</f>
+        <v>46388</v>
+      </c>
+      <c r="B38" s="14" t="str">
+        <f>TEXT($A38,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" s="13">
+        <f>DATE(2027,1,30)</f>
+        <v>46417</v>
+      </c>
+      <c r="B39" s="14" t="str">
+        <f>TEXT($A39,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" s="13">
+        <f>DATE(2027,2,18)</f>
+        <v>46436</v>
+      </c>
+      <c r="B40" s="14" t="str">
+        <f>TEXT($A40,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" s="13">
+        <f>DATE(2027,2,19)</f>
+        <v>46437</v>
+      </c>
+      <c r="B41" s="14" t="str">
+        <f>TEXT($A41,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="13">
+        <f>DATE(2027,3,19)</f>
+        <v>46465</v>
+      </c>
+      <c r="B42" s="14" t="str">
+        <f>TEXT($A42,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="13">
+        <f>DATE(2027,3,25)</f>
+        <v>46471</v>
+      </c>
+      <c r="B43" s="14" t="str">
+        <f>TEXT($A43,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" s="13">
+        <f>DATE(2027,4,3)</f>
+        <v>46480</v>
+      </c>
+      <c r="B44" s="14" t="str">
+        <f>TEXT($A44,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" s="13">
+        <f>DATE(2027,4,9)</f>
+        <v>46486</v>
+      </c>
+      <c r="B45" s="14" t="str">
+        <f>TEXT($A45,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" s="13">
+        <f>DATE(2027,5,19)</f>
+        <v>46526</v>
+      </c>
+      <c r="B46" s="14" t="str">
+        <f>TEXT($A46,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" s="13">
+        <f>DATE(2027,5,20)</f>
+        <v>46527</v>
+      </c>
+      <c r="B47" s="14" t="str">
+        <f>TEXT($A47,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" s="13">
+        <f>DATE(2027,5,21)</f>
+        <v>46528</v>
+      </c>
+      <c r="B48" s="14" t="str">
+        <f>TEXT($A48,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="13">
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
+      </c>
+      <c r="B49" s="14" t="str">
+        <f>TEXT($A49,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="13">
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
+      </c>
+      <c r="B50" s="14" t="str">
+        <f>TEXT($A50,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="13">
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
+      </c>
+      <c r="B51" s="14" t="str">
+        <f>TEXT($A51,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" s="13">
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
+      </c>
+      <c r="B52" s="14" t="str">
+        <f>TEXT($A52,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" s="13">
+        <f>DATE(2027,8,16)</f>
+        <v>46615</v>
+      </c>
+      <c r="B53" s="14" t="str">
+        <f>TEXT($A53,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" s="13">
+        <f>DATE(2027,8,20)</f>
+        <v>46619</v>
+      </c>
+      <c r="B54" s="14" t="str">
+        <f>TEXT($A54,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" s="13">
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
+      </c>
+      <c r="B55" s="14" t="str">
+        <f>TEXT($A55,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" s="13">
+        <f>DATE(2027,9,18)</f>
+        <v>46648</v>
+      </c>
+      <c r="B56" s="14" t="str">
+        <f>TEXT($A56,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" s="13">
+        <f>DATE(2027,10,1)</f>
+        <v>46661</v>
+      </c>
+      <c r="B57" s="14" t="str">
+        <f>TEXT($A57,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" s="13">
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
+      </c>
+      <c r="B58" s="14" t="str">
+        <f>TEXT($A58,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" s="13">
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
+      </c>
+      <c r="B59" s="14" t="str">
+        <f>TEXT($A59,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" s="13">
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
+      </c>
+      <c r="B60" s="14" t="str">
+        <f>TEXT($A60,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" s="13">
+        <f>DATE(2027,12,16)</f>
+        <v>46737</v>
+      </c>
+      <c r="B61" s="14" t="str">
+        <f>TEXT($A61,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1073,611 +2615,353 @@
         <v>21</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>54</v>
+      <c r="B2" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>56</v>
+      <c r="B3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>49</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>58</v>
+      <c r="B4" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>60</v>
+      <c r="B5" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>62</v>
+      <c r="B6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>64</v>
+      <c r="B7" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>66</v>
+      <c r="B8" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>68</v>
+      <c r="B9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>61</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>70</v>
+      <c r="B10" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>72</v>
+      <c r="B11" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="12"/>
+      <c r="B12" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="10"/>
       <c r="D12" s="4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="10"/>
       <c r="D13" s="4" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>76</v>
+      <c r="B14" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>78</v>
+      <c r="B15" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>71</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>80</v>
+      <c r="B16" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>82</v>
+      <c r="B17" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>84</v>
+      <c r="B18" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>77</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>86</v>
+      <c r="B19" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>88</v>
+      <c r="B20" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>81</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>90</v>
+      <c r="B21" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>83</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4">
         <v>21</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>92</v>
+      <c r="B22" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>94</v>
+      <c r="B23" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4">
         <v>23</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>96</v>
+      <c r="B24" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>98</v>
+      <c r="B25" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>91</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>100</v>
+      <c r="B26" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="13">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="F9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="13">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="F10" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="13">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="13">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="F12" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1686,6 +2970,266 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7" style="15" customWidth="1"/>
+    <col min="2" max="2" width="30" style="15" customWidth="1"/>
+    <col min="3" max="3" width="16" style="15" customWidth="1"/>
+    <col min="4" max="4" width="26" style="15" customWidth="1"/>
+    <col min="5" max="5" width="16" style="15" customWidth="1"/>
+    <col min="6" max="6" width="22" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="16">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="16">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="16">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="16">
+        <v>4</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="16">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="16">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="16">
+        <v>7</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="17">
+        <v>8</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="17">
+        <v>9</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="17">
+        <v>10</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="17">
+        <v>11</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1701,13 +3245,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>20</v>
@@ -1716,153 +3260,95 @@
         <v>21</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C2" s="5">
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C3" s="5">
         <v>2</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C4" s="5">
         <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C5" s="5">
         <v>2</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G5" s="5"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="6">
-        <v>46263</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="7">
-        <v>46280</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>29</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1880,26 +3366,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF8E275B-9681-4DE9-802A-F7E4AC116625}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C1C6EC9-DDDD-41CD-BA7D-AACE5E38B163}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="250">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -121,36 +121,18 @@
     <t>主席</t>
   </si>
   <si>
-    <t>Sample Name</t>
-  </si>
-  <si>
-    <t>样本</t>
-  </si>
-  <si>
     <t>Sub-Committee (English)</t>
   </si>
   <si>
     <t>Sub-Committee (中文)</t>
   </si>
   <si>
-    <t>Finance Sub-Committee</t>
-  </si>
-  <si>
-    <t>财务小组</t>
-  </si>
-  <si>
     <t>Chairperson</t>
   </si>
   <si>
     <t>Member</t>
   </si>
   <si>
-    <t>Events Sub-Committee</t>
-  </si>
-  <si>
-    <t>活动小组</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -262,9 +244,6 @@
     <t>黄洁滢</t>
   </si>
   <si>
-    <t>Ngi Ing Hou Lawrence</t>
-  </si>
-  <si>
     <t>吴荣豪</t>
   </si>
   <si>
@@ -388,6 +367,9 @@
     <t>Ilman.jpg</t>
   </si>
   <si>
+    <t>Cecil.jpg</t>
+  </si>
+  <si>
     <t>Lawrence.jpg</t>
   </si>
   <si>
@@ -442,9 +424,6 @@
     <t>Programme/Fundraising</t>
   </si>
   <si>
-    <t>CNY Ration + Ang Bao</t>
-  </si>
-  <si>
     <t>CNY Ration + Ang Bao Giving to AMS Beneficiaries</t>
   </si>
   <si>
@@ -490,9 +469,6 @@
     <t>Shine Dragon Boat Dumpling Festival Celebration</t>
   </si>
   <si>
-    <t>Charity Concert</t>
-  </si>
-  <si>
     <t>Partnership</t>
   </si>
   <si>
@@ -661,90 +637,48 @@
     <t>九皇爷诞筹款第三天</t>
   </si>
   <si>
-    <t>Charity Walk (Tentative)</t>
-  </si>
-  <si>
     <t>慈善健走（暂定）</t>
   </si>
   <si>
-    <t>Deepavali Ang Pao Distribution (AMS Hindus)</t>
-  </si>
-  <si>
     <t>屠妖节红包派发（AMS印族受惠者）</t>
   </si>
   <si>
-    <t>MS Project Ration Distribution (Date Unconfirmed)</t>
-  </si>
-  <si>
     <t>MS项目物资派发（日期待定）</t>
   </si>
   <si>
-    <t>Sponsor a HUG Campaign (Physical Launch Closer to Christmas)</t>
-  </si>
-  <si>
     <t>「认养一个拥抱」慈善运动（圣诞前实体推介）</t>
   </si>
   <si>
-    <t>New Year Ration</t>
-  </si>
-  <si>
     <t>新年物资派发</t>
   </si>
   <si>
     <t>农历新年物资及红包派发</t>
   </si>
   <si>
-    <t>CNY Dinner – CSR (JustCo or MS Project) – Day 1</t>
-  </si>
-  <si>
     <t>新春晚宴 – 企业社会责任（JustCo或MS项目）第一天</t>
   </si>
   <si>
-    <t>CNY Dinner – CSR (JustCo or MS Project) – Day 2</t>
-  </si>
-  <si>
     <t>新春晚宴 – 企业社会责任（JustCo或MS项目）第二天</t>
   </si>
   <si>
-    <t>CSR Partnership – Corporate / School</t>
-  </si>
-  <si>
     <t>企业／学校社会责任合作</t>
   </si>
   <si>
-    <t>Hari Raya Puasa Ang Pao Distribution + Goodie Bag + Lunch</t>
-  </si>
-  <si>
     <t>开斋节红包及礼包派发暨午宴</t>
   </si>
   <si>
-    <t>CSR Partnership – Corporate / School (Sunrise Walk)</t>
-  </si>
-  <si>
     <t>企业／学校社会责任合作（日出健走）</t>
   </si>
   <si>
-    <t>Dragon Boat Festival Event (Actual Day 9 June)</t>
-  </si>
-  <si>
     <t>端午节活动（实际节日为6月9日）</t>
   </si>
   <si>
-    <t>CSR Partnership – Corporate / School (National Day Celebration)</t>
-  </si>
-  <si>
     <t>企业／学校社会责任合作（国庆庆祝）</t>
   </si>
   <si>
-    <t>7th Month Fundraising Period (Actual Day 16 Aug, covering 2–30 Aug)</t>
-  </si>
-  <si>
     <t>七月筹款期（实际日期8月16日，涵盖8月2日至30日）</t>
   </si>
   <si>
-    <t>CSR Partnership – Corporate / School (Charity Concert)</t>
-  </si>
-  <si>
     <t>企业／学校社会责任合作（慈善演唱会）</t>
   </si>
   <si>
@@ -752,6 +686,108 @@
   </si>
   <si>
     <t>Title (Chinese)</t>
+  </si>
+  <si>
+    <t>[Tentative] Sponsor a HUG Campaign (Physical Launch Closer to Christmas)</t>
+  </si>
+  <si>
+    <t>[Tentative] MS Project Ration Distribution (Date Unconfirmed)</t>
+  </si>
+  <si>
+    <t>[Tentative] Deepavali Ang Pao Distribution (AMS Hindus)</t>
+  </si>
+  <si>
+    <t>[Tentative] Charity Walk</t>
+  </si>
+  <si>
+    <t>[Tentative] New Year Ration</t>
+  </si>
+  <si>
+    <t>[Tentative] CNY Ration + Ang Bao</t>
+  </si>
+  <si>
+    <t>[Tentative] CNY Dinner – CSR (JustCo or MS Project) – Day 1</t>
+  </si>
+  <si>
+    <t>[Tentative] CNY Dinner – CSR (JustCo or MS Project) – Day 2</t>
+  </si>
+  <si>
+    <t>[Tentative] CSR Partnership – Corporate / School</t>
+  </si>
+  <si>
+    <t>[Tentative] Hari Raya Puasa Ang Pao Distribution + Goodie Bag + Lunch</t>
+  </si>
+  <si>
+    <t>[Tentative] CSR Partnership – Corporate / School (Sunrise Walk)</t>
+  </si>
+  <si>
+    <t>[Tentative] Vesak Day Fundraising (Ubin Thai) – Day 1</t>
+  </si>
+  <si>
+    <t>[Tentative] Vesak Day Fundraising (Ubin Thai) – Day 2</t>
+  </si>
+  <si>
+    <t>[Tentative] Vesak Day Fundraising (Ubin Thai) – Day 3</t>
+  </si>
+  <si>
+    <t>[Tentative] Dragon Boat Festival Event (Actual Day 9 June)</t>
+  </si>
+  <si>
+    <t>[Tentative] CSR Partnership – Corporate / School (National Day Celebration)</t>
+  </si>
+  <si>
+    <t>[Tentative] 7th Month Fundraising Period (Actual Day 16 Aug, covering 2–30 Aug)</t>
+  </si>
+  <si>
+    <t>[Tentative] CSR Partnership – Corporate / School (Charity Concert)</t>
+  </si>
+  <si>
+    <t>[Tentative] Charity Concert</t>
+  </si>
+  <si>
+    <t>Dr Ngi Ing Hou Lawrence</t>
+  </si>
+  <si>
+    <t>Medical Committee</t>
+  </si>
+  <si>
+    <t>医药组</t>
+  </si>
+  <si>
+    <t>Activity Committee</t>
+  </si>
+  <si>
+    <t>活动组</t>
+  </si>
+  <si>
+    <t>Caring Heart Committee</t>
+  </si>
+  <si>
+    <t>爱心关怀组</t>
+  </si>
+  <si>
+    <t>Fund Raising Committee</t>
+  </si>
+  <si>
+    <t>募捐组</t>
+  </si>
+  <si>
+    <t>Volunteer Committee</t>
+  </si>
+  <si>
+    <t>义工组</t>
+  </si>
+  <si>
+    <t>Audit/Compliance Committee</t>
+  </si>
+  <si>
+    <t>审查组</t>
+  </si>
+  <si>
+    <t>Public Relations Committee</t>
+  </si>
+  <si>
+    <t>公关组</t>
   </si>
 </sst>
 </file>
@@ -821,7 +857,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -831,11 +867,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF142F63"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -942,7 +973,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -950,7 +981,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -980,6 +1010,10 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -995,6 +1029,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1432,1160 +1470,1160 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>154</v>
+      <c r="A1" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="13">
+      <c r="A2" s="12">
         <f>DATE(2026,1,1)</f>
         <v>46023</v>
       </c>
-      <c r="B2" s="14" t="str">
+      <c r="B2" s="13" t="str">
         <f>TEXT($A2,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>133</v>
+      <c r="C2" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="13">
+      <c r="A3" s="12">
         <f>DATE(2026,2,8)</f>
         <v>46061</v>
       </c>
-      <c r="B3" s="14" t="str">
+      <c r="B3" s="13" t="str">
         <f>TEXT($A3,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>133</v>
+      <c r="C3" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <f>DATE(2026,2,26)</f>
         <v>46079</v>
       </c>
-      <c r="B4" s="14" t="str">
+      <c r="B4" s="13" t="str">
         <f>TEXT($A4,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>136</v>
+      <c r="C4" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="13">
+      <c r="A5" s="12">
         <f>DATE(2026,2,27)</f>
         <v>46080</v>
       </c>
-      <c r="B5" s="14" t="str">
+      <c r="B5" s="13" t="str">
         <f>TEXT($A5,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>136</v>
+      <c r="C5" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="13">
+      <c r="A6" s="12">
         <f>DATE(2026,3,2)</f>
         <v>46083</v>
       </c>
-      <c r="B6" s="14" t="str">
+      <c r="B6" s="13" t="str">
         <f>TEXT($A6,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>138</v>
+      <c r="C6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="13">
+      <c r="A7" s="12">
         <f>DATE(2026,3,7)</f>
         <v>46088</v>
       </c>
-      <c r="B7" s="14" t="str">
+      <c r="B7" s="13" t="str">
         <f>TEXT($A7,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>136</v>
+      <c r="C7" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="13">
+      <c r="A8" s="12">
         <f>DATE(2026,3,20)</f>
         <v>46101</v>
       </c>
-      <c r="B8" s="14" t="str">
+      <c r="B8" s="13" t="str">
         <f>TEXT($A8,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>140</v>
+      <c r="C8" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="13">
+      <c r="A9" s="12">
         <f>DATE(2026,3,23)</f>
         <v>46104</v>
       </c>
-      <c r="B9" s="14" t="str">
+      <c r="B9" s="13" t="str">
         <f>TEXT($A9,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>136</v>
+      <c r="C9" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="13">
+      <c r="A10" s="12">
         <f>DATE(2026,3,24)</f>
         <v>46105</v>
       </c>
-      <c r="B10" s="14" t="str">
+      <c r="B10" s="13" t="str">
         <f>TEXT($A10,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="E10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>136</v>
       </c>
+      <c r="D10" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="13">
+      <c r="A11" s="12">
         <f>DATE(2026,3,27)</f>
         <v>46108</v>
       </c>
-      <c r="B11" s="14" t="str">
+      <c r="B11" s="13" t="str">
         <f>TEXT($A11,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>136</v>
+      <c r="C11" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="13">
+      <c r="A12" s="12">
         <f>DATE(2026,4,20)</f>
         <v>46132</v>
       </c>
-      <c r="B12" s="14" t="str">
+      <c r="B12" s="13" t="str">
         <f>TEXT($A12,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>145</v>
+      <c r="C12" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="13">
+      <c r="A13" s="12">
         <f>DATE(2026,5,4)</f>
         <v>46146</v>
       </c>
-      <c r="B13" s="14" t="str">
+      <c r="B13" s="13" t="str">
         <f>TEXT($A13,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>145</v>
+      <c r="C13" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="13">
+      <c r="A14" s="12">
         <f>DATE(2026,5,15)</f>
         <v>46157</v>
       </c>
-      <c r="B14" s="14" t="str">
+      <c r="B14" s="13" t="str">
         <f>TEXT($A14,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>147</v>
+      <c r="C14" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="13">
+      <c r="A15" s="12">
         <f>DATE(2026,5,24)</f>
         <v>46166</v>
       </c>
-      <c r="B15" s="14" t="str">
+      <c r="B15" s="13" t="str">
         <f>TEXT($A15,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>145</v>
+      <c r="C15" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="13">
+      <c r="A16" s="12">
         <f>DATE(2026,5,25)</f>
         <v>46167</v>
       </c>
-      <c r="B16" s="14" t="str">
+      <c r="B16" s="13" t="str">
         <f>TEXT($A16,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>136</v>
+      <c r="C16" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="13">
+      <c r="A17" s="12">
         <f>DATE(2026,5,29)</f>
         <v>46171</v>
       </c>
-      <c r="B17" s="14" t="str">
+      <c r="B17" s="13" t="str">
         <f>TEXT($A17,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>147</v>
+      <c r="C17" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="13">
+      <c r="A18" s="12">
         <f>DATE(2026,5,30)</f>
         <v>46172</v>
       </c>
-      <c r="B18" s="14" t="str">
+      <c r="B18" s="13" t="str">
         <f>TEXT($A18,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>147</v>
+      <c r="C18" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="13">
+      <c r="A19" s="12">
         <f>DATE(2026,5,31)</f>
         <v>46173</v>
       </c>
-      <c r="B19" s="14" t="str">
+      <c r="B19" s="13" t="str">
         <f>TEXT($A19,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>147</v>
+      <c r="C19" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="13">
+      <c r="A20" s="12">
         <f>DATE(2026,6,1)</f>
         <v>46174</v>
       </c>
-      <c r="B20" s="14" t="str">
+      <c r="B20" s="13" t="str">
         <f>TEXT($A20,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>147</v>
+      <c r="C20" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="13">
+      <c r="A21" s="12">
         <f>DATE(2026,6,13)</f>
         <v>46186</v>
       </c>
-      <c r="B21" s="14" t="str">
+      <c r="B21" s="13" t="str">
         <f>TEXT($A21,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>136</v>
+      <c r="C21" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="13">
+      <c r="A22" s="12">
         <f>DATE(2026,7,3)</f>
         <v>46206</v>
       </c>
-      <c r="B22" s="14" t="str">
+      <c r="B22" s="13" t="str">
         <f>TEXT($A22,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>140</v>
+      <c r="C22" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="13">
+      <c r="A23" s="12">
         <f>DATE(2026,7,24)</f>
         <v>46227</v>
       </c>
-      <c r="B23" s="14" t="str">
+      <c r="B23" s="13" t="str">
         <f>TEXT($A23,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>140</v>
+      <c r="C23" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="13">
+      <c r="A24" s="12">
         <f>DATE(2026,8,1)</f>
         <v>46235</v>
       </c>
-      <c r="B24" s="14" t="str">
+      <c r="B24" s="13" t="str">
         <f>TEXT($A24,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>140</v>
+      <c r="C24" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="13">
+      <c r="A25" s="12">
         <f>DATE(2026,8,22)</f>
         <v>46256</v>
       </c>
-      <c r="B25" s="14" t="str">
+      <c r="B25" s="13" t="str">
         <f>TEXT($A25,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>147</v>
+      <c r="C25" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="13">
+      <c r="A26" s="12">
         <f>DATE(2026,9,4)</f>
         <v>46269</v>
       </c>
-      <c r="B26" s="14" t="str">
+      <c r="B26" s="13" t="str">
         <f>TEXT($A26,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>136</v>
+      <c r="C26" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="13">
+      <c r="A27" s="12">
         <f>DATE(2026,9,5)</f>
         <v>46270</v>
       </c>
-      <c r="B27" s="14" t="str">
+      <c r="B27" s="13" t="str">
         <f>TEXT($A27,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C27" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>140</v>
+      <c r="C27" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="13">
+      <c r="A28" s="12">
         <f>DATE(2026,9,19)</f>
         <v>46284</v>
       </c>
-      <c r="B28" s="14" t="str">
+      <c r="B28" s="13" t="str">
         <f>TEXT($A28,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>151</v>
+      <c r="C28" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="13">
+      <c r="A29" s="12">
         <f>DATE(2026,9,21)</f>
         <v>46286</v>
       </c>
-      <c r="B29" s="14" t="str">
+      <c r="B29" s="13" t="str">
         <f>TEXT($A29,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>147</v>
+      <c r="C29" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="13">
+      <c r="A30" s="12">
         <f>DATE(2026,10,10)</f>
         <v>46305</v>
       </c>
-      <c r="B30" s="14" t="str">
+      <c r="B30" s="13" t="str">
         <f>TEXT($A30,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>147</v>
+      <c r="C30" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="13">
+      <c r="A31" s="12">
         <f>DATE(2026,10,12)</f>
         <v>46307</v>
       </c>
-      <c r="B31" s="14" t="str">
+      <c r="B31" s="13" t="str">
         <f>TEXT($A31,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>147</v>
+      <c r="C31" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="13">
+      <c r="A32" s="12">
         <f>DATE(2026,10,13)</f>
         <v>46308</v>
       </c>
-      <c r="B32" s="14" t="str">
+      <c r="B32" s="13" t="str">
         <f>TEXT($A32,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>147</v>
+      <c r="C32" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="13">
+      <c r="A33" s="12">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
       </c>
-      <c r="B33" s="14" t="str">
+      <c r="B33" s="13" t="str">
         <f>TEXT($A33,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C33" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>147</v>
+      <c r="C33" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="13">
+      <c r="A34" s="12">
         <f>DATE(2026,10,31)</f>
         <v>46326</v>
       </c>
-      <c r="B34" s="14" t="str">
+      <c r="B34" s="13" t="str">
         <f>TEXT($A34,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C34" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>147</v>
+      <c r="C34" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="13">
+      <c r="A35" s="12">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
       </c>
-      <c r="B35" s="14" t="str">
+      <c r="B35" s="13" t="str">
         <f>TEXT($A35,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C35" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>136</v>
+      <c r="C35" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="13">
+      <c r="A36" s="12">
         <f>DATE(2026,11,10)</f>
         <v>46336</v>
       </c>
-      <c r="B36" s="14" t="str">
+      <c r="B36" s="13" t="str">
         <f>TEXT($A36,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>136</v>
+      <c r="C36" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="13">
+      <c r="A37" s="12">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B37" s="14" t="str">
+      <c r="B37" s="13" t="str">
         <f>TEXT($A37,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>147</v>
+      <c r="C37" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="13">
+      <c r="A38" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B38" s="14" t="str">
+      <c r="B38" s="13" t="str">
         <f>TEXT($A38,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C38" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>133</v>
+      <c r="C38" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="13">
+      <c r="A39" s="12">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B39" s="14" t="str">
+      <c r="B39" s="13" t="str">
         <f>TEXT($A39,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C39" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>133</v>
+      <c r="C39" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="13">
+      <c r="A40" s="12">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B40" s="14" t="str">
+      <c r="B40" s="13" t="str">
         <f>TEXT($A40,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C40" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>140</v>
+      <c r="C40" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="13">
+      <c r="A41" s="12">
         <f>DATE(2027,2,19)</f>
         <v>46437</v>
       </c>
-      <c r="B41" s="14" t="str">
+      <c r="B41" s="13" t="str">
         <f>TEXT($A41,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C41" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>140</v>
+      <c r="C41" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="13">
+      <c r="A42" s="12">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B42" s="14" t="str">
+      <c r="B42" s="13" t="str">
         <f>TEXT($A42,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C42" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>140</v>
+      <c r="C42" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="13">
+      <c r="A43" s="12">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B43" s="14" t="str">
+      <c r="B43" s="13" t="str">
         <f>TEXT($A43,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C43" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="D43" s="12" t="s">
+      <c r="C43" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="E43" s="12" t="s">
-        <v>136</v>
+      <c r="D43" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="13">
+      <c r="A44" s="12">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
       </c>
-      <c r="B44" s="14" t="str">
+      <c r="B44" s="13" t="str">
         <f>TEXT($A44,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="D44" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>140</v>
+      <c r="D44" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="13">
+      <c r="A45" s="12">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
       </c>
-      <c r="B45" s="14" t="str">
+      <c r="B45" s="13" t="str">
         <f>TEXT($A45,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C45" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>140</v>
+      <c r="C45" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="13">
+      <c r="A46" s="12">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B46" s="14" t="str">
+      <c r="B46" s="13" t="str">
         <f>TEXT($A46,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C46" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="E46" s="12" t="s">
-        <v>147</v>
+      <c r="C46" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="13">
+      <c r="A47" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B47" s="14" t="str">
+      <c r="B47" s="13" t="str">
         <f>TEXT($A47,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C47" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>147</v>
+      <c r="C47" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="13">
+      <c r="A48" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
       </c>
-      <c r="B48" s="14" t="str">
+      <c r="B48" s="13" t="str">
         <f>TEXT($A48,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C48" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>147</v>
+      <c r="C48" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="13">
+      <c r="A49" s="12">
         <f>DATE(2027,5,28)</f>
         <v>46535</v>
       </c>
-      <c r="B49" s="14" t="str">
+      <c r="B49" s="13" t="str">
         <f>TEXT($A49,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C49" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>136</v>
+      <c r="C49" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="13">
+      <c r="A50" s="12">
         <f>DATE(2027,6,11)</f>
         <v>46549</v>
       </c>
-      <c r="B50" s="14" t="str">
+      <c r="B50" s="13" t="str">
         <f>TEXT($A50,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>140</v>
+      <c r="C50" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="13">
+      <c r="A51" s="12">
         <f>DATE(2027,7,9)</f>
         <v>46577</v>
       </c>
-      <c r="B51" s="14" t="str">
+      <c r="B51" s="13" t="str">
         <f>TEXT($A51,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C51" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E51" s="12" t="s">
-        <v>140</v>
+      <c r="C51" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="13">
+      <c r="A52" s="12">
         <f>DATE(2027,7,30)</f>
         <v>46598</v>
       </c>
-      <c r="B52" s="14" t="str">
+      <c r="B52" s="13" t="str">
         <f>TEXT($A52,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C52" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="D52" s="12" t="s">
+      <c r="C52" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="E52" s="12" t="s">
-        <v>140</v>
+      <c r="D52" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="13">
+      <c r="A53" s="12">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B53" s="14" t="str">
+      <c r="B53" s="13" t="str">
         <f>TEXT($A53,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="D53" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>147</v>
+      <c r="D53" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="13">
+      <c r="A54" s="12">
         <f>DATE(2027,8,20)</f>
         <v>46619</v>
       </c>
-      <c r="B54" s="14" t="str">
+      <c r="B54" s="13" t="str">
         <f>TEXT($A54,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C54" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>140</v>
+      <c r="C54" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="13">
+      <c r="A55" s="12">
         <f>DATE(2027,9,10)</f>
         <v>46640</v>
       </c>
-      <c r="B55" s="14" t="str">
+      <c r="B55" s="13" t="str">
         <f>TEXT($A55,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C55" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>140</v>
+      <c r="C55" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="13">
+      <c r="A56" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B56" s="14" t="str">
+      <c r="B56" s="13" t="str">
         <f>TEXT($A56,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C56" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>147</v>
+      <c r="C56" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="13">
+      <c r="A57" s="12">
         <f>DATE(2027,10,1)</f>
         <v>46661</v>
       </c>
-      <c r="B57" s="14" t="str">
+      <c r="B57" s="13" t="str">
         <f>TEXT($A57,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C57" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>140</v>
+      <c r="C57" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="13">
+      <c r="A58" s="12">
         <f>DATE(2027,10,15)</f>
         <v>46675</v>
       </c>
-      <c r="B58" s="14" t="str">
+      <c r="B58" s="13" t="str">
         <f>TEXT($A58,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C58" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>140</v>
+      <c r="C58" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="13">
+      <c r="A59" s="12">
         <f>DATE(2027,11,12)</f>
         <v>46703</v>
       </c>
-      <c r="B59" s="14" t="str">
+      <c r="B59" s="13" t="str">
         <f>TEXT($A59,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C59" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>140</v>
+      <c r="C59" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="13">
+      <c r="A60" s="12">
         <f>DATE(2027,11,26)</f>
         <v>46717</v>
       </c>
-      <c r="B60" s="14" t="str">
+      <c r="B60" s="13" t="str">
         <f>TEXT($A60,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C60" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>140</v>
+      <c r="C60" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" s="13">
+      <c r="A61" s="12">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B61" s="14" t="str">
+      <c r="B61" s="13" t="str">
         <f>TEXT($A61,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C61" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>147</v>
+      <c r="C61" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2622,346 +2660,346 @@
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>47</v>
+      <c r="B2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>49</v>
+      <c r="B3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>51</v>
+      <c r="B4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>53</v>
+      <c r="B5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>55</v>
+      <c r="B6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>57</v>
+      <c r="B7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>59</v>
+      <c r="B8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>61</v>
+      <c r="B9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>63</v>
+      <c r="B10" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>65</v>
+      <c r="B11" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="10"/>
+      <c r="B12" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="9"/>
       <c r="D12" s="4" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="10"/>
+      <c r="B13" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="9"/>
       <c r="D13" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>69</v>
+      <c r="B14" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>71</v>
+      <c r="B15" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>73</v>
+      <c r="B16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>75</v>
+      <c r="B17" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>77</v>
+      <c r="B18" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>79</v>
+      <c r="B19" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>81</v>
+      <c r="B20" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>83</v>
+      <c r="B21" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4">
         <v>21</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>85</v>
+      <c r="B22" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>87</v>
+      <c r="B23" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4">
         <v>23</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>89</v>
+      <c r="B24" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>82</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>91</v>
+      <c r="B25" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>93</v>
+      <c r="B26" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2974,13 +3012,13 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7" style="15" customWidth="1"/>
-    <col min="2" max="2" width="30" style="15" customWidth="1"/>
-    <col min="3" max="3" width="16" style="15" customWidth="1"/>
-    <col min="4" max="4" width="26" style="15" customWidth="1"/>
-    <col min="5" max="5" width="16" style="15" customWidth="1"/>
-    <col min="6" max="6" width="22" style="15" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="15"/>
+    <col min="1" max="1" width="7" style="14" customWidth="1"/>
+    <col min="2" max="2" width="30" style="14" customWidth="1"/>
+    <col min="3" max="3" width="16" style="14" customWidth="1"/>
+    <col min="4" max="4" width="26" style="14" customWidth="1"/>
+    <col min="5" max="5" width="16" style="14" customWidth="1"/>
+    <col min="6" max="6" width="22" style="14" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -2996,231 +3034,231 @@
       <c r="D1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="18" t="s">
-        <v>237</v>
+      <c r="E1" s="17" t="s">
+        <v>215</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="16">
+      <c r="A2" s="15">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="D2" s="16" t="s">
+      <c r="B2" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="15">
+        <v>2</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="15">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="15">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="15">
+        <v>5</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="15">
+        <v>6</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="15">
+        <v>7</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="16">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="16">
+        <v>9</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="16">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="16" t="s">
+      <c r="F10" s="14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="16">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="16">
-        <v>3</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="E4" s="16" t="s">
+      <c r="E11" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="16">
+        <v>11</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="F4" s="16" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="16">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="16">
-        <v>5</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="16">
-        <v>6</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="16">
-        <v>7</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="17">
-        <v>8</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="17">
-        <v>9</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" s="17" t="s">
+      <c r="E12" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="E10" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="17">
-        <v>10</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="F11" s="15" t="s">
+      <c r="F12" s="14" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="17">
-        <v>11</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -3231,124 +3269,519 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="C2" s="19">
+        <v>1</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="G2" s="18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" s="19">
+        <v>2</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="5">
+      <c r="G3" s="18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="19">
+        <v>3</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="C5" s="19">
+        <v>4</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="C6" s="19">
+        <v>5</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" s="19">
         <v>1</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="D7" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="C8" s="19">
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="D8" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" s="19">
         <v>1</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="D9" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="C10" s="19">
         <v>2</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="5"/>
+      <c r="D10" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="C11" s="19">
+        <v>1</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="19">
+        <v>2</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="C13" s="19">
+        <v>3</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="C14" s="19">
+        <v>4</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" s="19">
+        <v>1</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" s="19">
+        <v>2</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" s="19">
+        <v>1</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C18" s="19">
+        <v>2</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C19" s="19">
+        <v>3</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="C20" s="19">
+        <v>1</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="C21" s="19">
+        <v>2</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="C22" s="19">
+        <v>3</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>88</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3366,26 +3799,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C1C6EC9-DDDD-41CD-BA7D-AACE5E38B163}"/>
+  <xr:revisionPtr revIDLastSave="182" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66DD6999-85C0-44E5-ADEC-EA1298D67527}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -646,9 +646,6 @@
     <t>MS项目物资派发（日期待定）</t>
   </si>
   <si>
-    <t>「认养一个拥抱」慈善运动（圣诞前实体推介）</t>
-  </si>
-  <si>
     <t>新年物资派发</t>
   </si>
   <si>
@@ -788,6 +785,9 @@
   </si>
   <si>
     <t>公关组</t>
+  </si>
+  <si>
+    <t>「认捐拥抱・温暖长者」慈善运动（圣诞前实体推介）</t>
   </si>
 </sst>
 </file>
@@ -2104,7 +2104,7 @@
         <v>Sat</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>199</v>
@@ -2123,7 +2123,7 @@
         <v>Tue</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>200</v>
@@ -2142,7 +2142,7 @@
         <v>Tue</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>201</v>
@@ -2161,10 +2161,10 @@
         <v>Wed</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>202</v>
+        <v>215</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>249</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>140</v>
@@ -2180,10 +2180,10 @@
         <v>Fri</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>127</v>
@@ -2199,10 +2199,10 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>127</v>
@@ -2218,10 +2218,10 @@
         <v>Thu</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>133</v>
@@ -2237,10 +2237,10 @@
         <v>Fri</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E41" s="11" t="s">
         <v>133</v>
@@ -2256,10 +2256,10 @@
         <v>Fri</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>133</v>
@@ -2275,10 +2275,10 @@
         <v>Thu</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E43" s="11" t="s">
         <v>129</v>
@@ -2294,10 +2294,10 @@
         <v>Sat</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E44" s="11" t="s">
         <v>133</v>
@@ -2313,10 +2313,10 @@
         <v>Fri</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E45" s="11" t="s">
         <v>133</v>
@@ -2332,7 +2332,7 @@
         <v>Wed</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>169</v>
@@ -2351,7 +2351,7 @@
         <v>Thu</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>171</v>
@@ -2370,7 +2370,7 @@
         <v>Fri</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>173</v>
@@ -2389,10 +2389,10 @@
         <v>Fri</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>129</v>
@@ -2408,10 +2408,10 @@
         <v>Fri</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>133</v>
@@ -2427,10 +2427,10 @@
         <v>Fri</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>133</v>
@@ -2446,10 +2446,10 @@
         <v>Fri</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>133</v>
@@ -2465,10 +2465,10 @@
         <v>Mon</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>140</v>
@@ -2484,10 +2484,10 @@
         <v>Fri</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>133</v>
@@ -2503,10 +2503,10 @@
         <v>Fri</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>133</v>
@@ -2522,10 +2522,10 @@
         <v>Sat</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>140</v>
@@ -2541,10 +2541,10 @@
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>133</v>
@@ -2560,10 +2560,10 @@
         <v>Fri</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>133</v>
@@ -2579,10 +2579,10 @@
         <v>Fri</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E59" s="11" t="s">
         <v>133</v>
@@ -2598,10 +2598,10 @@
         <v>Fri</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>133</v>
@@ -2617,10 +2617,10 @@
         <v>Thu</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="D61" s="11" t="s">
-        <v>202</v>
+        <v>215</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>249</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>140</v>
@@ -2867,7 +2867,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>68</v>
@@ -3035,7 +3035,7 @@
         <v>25</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>22</v>
@@ -3306,10 +3306,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>236</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>237</v>
       </c>
       <c r="C2" s="19">
         <v>1</v>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>236</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>237</v>
       </c>
       <c r="C3" s="19">
         <v>2</v>
@@ -3350,16 +3350,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>236</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>237</v>
       </c>
       <c r="C4" s="19">
         <v>3</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E4" s="18" t="s">
         <v>68</v>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>236</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>237</v>
       </c>
       <c r="C5" s="19">
         <v>4</v>
@@ -3394,10 +3394,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>236</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>237</v>
       </c>
       <c r="C6" s="19">
         <v>5</v>
@@ -3417,10 +3417,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>238</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>239</v>
       </c>
       <c r="C7" s="19">
         <v>1</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>238</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>239</v>
       </c>
       <c r="C8" s="19">
         <v>2</v>
@@ -3463,10 +3463,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>240</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>241</v>
       </c>
       <c r="C9" s="19">
         <v>1</v>
@@ -3486,10 +3486,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>240</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>241</v>
       </c>
       <c r="C10" s="19">
         <v>2</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>242</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>243</v>
       </c>
       <c r="C11" s="19">
         <v>1</v>
@@ -3532,10 +3532,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>242</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>243</v>
       </c>
       <c r="C12" s="19">
         <v>2</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>242</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>243</v>
       </c>
       <c r="C13" s="19">
         <v>3</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="B14" s="18" t="s">
         <v>242</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>243</v>
       </c>
       <c r="C14" s="19">
         <v>4</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="B15" s="18" t="s">
         <v>244</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>245</v>
       </c>
       <c r="C15" s="19">
         <v>1</v>
@@ -3624,10 +3624,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="B16" s="18" t="s">
         <v>244</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>245</v>
       </c>
       <c r="C16" s="19">
         <v>2</v>
@@ -3647,10 +3647,10 @@
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="B17" s="18" t="s">
         <v>246</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>247</v>
       </c>
       <c r="C17" s="19">
         <v>1</v>
@@ -3670,10 +3670,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="B18" s="18" t="s">
         <v>246</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>247</v>
       </c>
       <c r="C18" s="19">
         <v>2</v>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="B19" s="18" t="s">
         <v>246</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>247</v>
       </c>
       <c r="C19" s="19">
         <v>3</v>
@@ -3716,10 +3716,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="B20" s="18" t="s">
         <v>248</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>249</v>
       </c>
       <c r="C20" s="19">
         <v>1</v>
@@ -3739,10 +3739,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>248</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>249</v>
       </c>
       <c r="C21" s="19">
         <v>2</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="B22" s="18" t="s">
         <v>248</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>249</v>
       </c>
       <c r="C22" s="19">
         <v>3</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66DD6999-85C0-44E5-ADEC-EA1298D67527}"/>
+  <xr:revisionPtr revIDLastSave="187" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0FC7D38-B85B-441E-9BA4-936AC6D2133E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="249">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -151,15 +151,9 @@
     <t>Last Updated</t>
   </si>
   <si>
-    <t>23 Jul 2026</t>
-  </si>
-  <si>
     <t>Footer Note</t>
   </si>
   <si>
-    <t>南凤福利协会 Nam Hong Welfare Service Society · For committee members' reference 仅供委员参考</t>
-  </si>
-  <si>
     <t>Cher Kim Seah</t>
   </si>
   <si>
@@ -788,6 +782,9 @@
   </si>
   <si>
     <t>「认捐拥抱・温暖长者」慈善运动（圣诞前实体推介）</t>
+  </si>
+  <si>
+    <t>南凤福利协会 Nam Hong Welfare Service Society · For committee members reference 仅供委员参考</t>
   </si>
 </sst>
 </file>
@@ -973,7 +970,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1004,15 +1001,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1029,10 +1027,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1474,7 +1468,7 @@
         <v>31</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>32</v>
@@ -1483,7 +1477,7 @@
         <v>33</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -1492,17 +1486,17 @@
         <v>46023</v>
       </c>
       <c r="B2" s="13" t="str">
-        <f>TEXT($A2,"ddd")</f>
+        <f t="shared" ref="B2:B33" si="0">TEXT($A2,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -1511,17 +1505,17 @@
         <v>46061</v>
       </c>
       <c r="B3" s="13" t="str">
-        <f>TEXT($A3,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -1530,17 +1524,17 @@
         <v>46079</v>
       </c>
       <c r="B4" s="13" t="str">
-        <f>TEXT($A4,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -1549,17 +1543,17 @@
         <v>46080</v>
       </c>
       <c r="B5" s="13" t="str">
-        <f>TEXT($A5,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -1568,17 +1562,17 @@
         <v>46083</v>
       </c>
       <c r="B6" s="13" t="str">
-        <f>TEXT($A6,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -1587,17 +1581,17 @@
         <v>46088</v>
       </c>
       <c r="B7" s="13" t="str">
-        <f>TEXT($A7,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -1606,17 +1600,17 @@
         <v>46101</v>
       </c>
       <c r="B8" s="13" t="str">
-        <f>TEXT($A8,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -1625,17 +1619,17 @@
         <v>46104</v>
       </c>
       <c r="B9" s="13" t="str">
-        <f>TEXT($A9,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -1644,17 +1638,17 @@
         <v>46105</v>
       </c>
       <c r="B10" s="13" t="str">
-        <f>TEXT($A10,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -1663,17 +1657,17 @@
         <v>46108</v>
       </c>
       <c r="B11" s="13" t="str">
-        <f>TEXT($A11,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -1682,17 +1676,17 @@
         <v>46132</v>
       </c>
       <c r="B12" s="13" t="str">
-        <f>TEXT($A12,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -1701,17 +1695,17 @@
         <v>46146</v>
       </c>
       <c r="B13" s="13" t="str">
-        <f>TEXT($A13,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -1720,17 +1714,17 @@
         <v>46157</v>
       </c>
       <c r="B14" s="13" t="str">
-        <f>TEXT($A14,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -1739,17 +1733,17 @@
         <v>46166</v>
       </c>
       <c r="B15" s="13" t="str">
-        <f>TEXT($A15,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -1758,17 +1752,17 @@
         <v>46167</v>
       </c>
       <c r="B16" s="13" t="str">
-        <f>TEXT($A16,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -1777,17 +1771,17 @@
         <v>46171</v>
       </c>
       <c r="B17" s="13" t="str">
-        <f>TEXT($A17,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -1796,17 +1790,17 @@
         <v>46172</v>
       </c>
       <c r="B18" s="13" t="str">
-        <f>TEXT($A18,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -1815,17 +1809,17 @@
         <v>46173</v>
       </c>
       <c r="B19" s="13" t="str">
-        <f>TEXT($A19,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -1834,17 +1828,17 @@
         <v>46174</v>
       </c>
       <c r="B20" s="13" t="str">
-        <f>TEXT($A20,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -1853,17 +1847,17 @@
         <v>46186</v>
       </c>
       <c r="B21" s="13" t="str">
-        <f>TEXT($A21,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -1872,17 +1866,17 @@
         <v>46206</v>
       </c>
       <c r="B22" s="13" t="str">
-        <f>TEXT($A22,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -1891,17 +1885,17 @@
         <v>46227</v>
       </c>
       <c r="B23" s="13" t="str">
-        <f>TEXT($A23,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -1910,17 +1904,17 @@
         <v>46235</v>
       </c>
       <c r="B24" s="13" t="str">
-        <f>TEXT($A24,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -1929,17 +1923,17 @@
         <v>46256</v>
       </c>
       <c r="B25" s="13" t="str">
-        <f>TEXT($A25,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -1948,17 +1942,17 @@
         <v>46269</v>
       </c>
       <c r="B26" s="13" t="str">
-        <f>TEXT($A26,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -1967,17 +1961,17 @@
         <v>46270</v>
       </c>
       <c r="B27" s="13" t="str">
-        <f>TEXT($A27,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -1986,17 +1980,17 @@
         <v>46284</v>
       </c>
       <c r="B28" s="13" t="str">
-        <f>TEXT($A28,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -2005,17 +1999,17 @@
         <v>46286</v>
       </c>
       <c r="B29" s="13" t="str">
-        <f>TEXT($A29,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -2024,17 +2018,17 @@
         <v>46305</v>
       </c>
       <c r="B30" s="13" t="str">
-        <f>TEXT($A30,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -2043,17 +2037,17 @@
         <v>46307</v>
       </c>
       <c r="B31" s="13" t="str">
-        <f>TEXT($A31,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -2062,17 +2056,17 @@
         <v>46308</v>
       </c>
       <c r="B32" s="13" t="str">
-        <f>TEXT($A32,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -2081,17 +2075,17 @@
         <v>46309</v>
       </c>
       <c r="B33" s="13" t="str">
-        <f>TEXT($A33,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -2100,17 +2094,17 @@
         <v>46326</v>
       </c>
       <c r="B34" s="13" t="str">
-        <f>TEXT($A34,"ddd")</f>
+        <f t="shared" ref="B34:B61" si="1">TEXT($A34,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C34" s="18" t="s">
-        <v>218</v>
+      <c r="C34" s="16" t="s">
+        <v>216</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -2119,17 +2113,17 @@
         <v>46329</v>
       </c>
       <c r="B35" s="13" t="str">
-        <f>TEXT($A35,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Tue</v>
       </c>
-      <c r="C35" s="18" t="s">
-        <v>217</v>
+      <c r="C35" s="16" t="s">
+        <v>215</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -2138,17 +2132,17 @@
         <v>46336</v>
       </c>
       <c r="B36" s="13" t="str">
-        <f>TEXT($A36,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Tue</v>
       </c>
-      <c r="C36" s="18" t="s">
-        <v>216</v>
+      <c r="C36" s="16" t="s">
+        <v>214</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -2157,17 +2151,17 @@
         <v>46372</v>
       </c>
       <c r="B37" s="13" t="str">
-        <f>TEXT($A37,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Wed</v>
       </c>
-      <c r="C37" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>249</v>
+      <c r="C37" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>247</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
@@ -2176,17 +2170,17 @@
         <v>46388</v>
       </c>
       <c r="B38" s="13" t="str">
-        <f>TEXT($A38,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
-      <c r="C38" s="18" t="s">
-        <v>219</v>
+      <c r="C38" s="16" t="s">
+        <v>217</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -2195,17 +2189,17 @@
         <v>46417</v>
       </c>
       <c r="B39" s="13" t="str">
-        <f>TEXT($A39,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -2214,17 +2208,17 @@
         <v>46436</v>
       </c>
       <c r="B40" s="13" t="str">
-        <f>TEXT($A40,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -2233,17 +2227,17 @@
         <v>46437</v>
       </c>
       <c r="B41" s="13" t="str">
-        <f>TEXT($A41,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
@@ -2252,17 +2246,17 @@
         <v>46465</v>
       </c>
       <c r="B42" s="13" t="str">
-        <f>TEXT($A42,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -2271,17 +2265,17 @@
         <v>46471</v>
       </c>
       <c r="B43" s="13" t="str">
-        <f>TEXT($A43,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -2290,17 +2284,17 @@
         <v>46480</v>
       </c>
       <c r="B44" s="13" t="str">
-        <f>TEXT($A44,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -2309,17 +2303,17 @@
         <v>46486</v>
       </c>
       <c r="B45" s="13" t="str">
-        <f>TEXT($A45,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
@@ -2328,17 +2322,17 @@
         <v>46526</v>
       </c>
       <c r="B46" s="13" t="str">
-        <f>TEXT($A46,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Wed</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -2347,17 +2341,17 @@
         <v>46527</v>
       </c>
       <c r="B47" s="13" t="str">
-        <f>TEXT($A47,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
@@ -2366,17 +2360,17 @@
         <v>46528</v>
       </c>
       <c r="B48" s="13" t="str">
-        <f>TEXT($A48,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
@@ -2385,17 +2379,17 @@
         <v>46535</v>
       </c>
       <c r="B49" s="13" t="str">
-        <f>TEXT($A49,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
@@ -2404,17 +2398,17 @@
         <v>46549</v>
       </c>
       <c r="B50" s="13" t="str">
-        <f>TEXT($A50,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
@@ -2423,17 +2417,17 @@
         <v>46577</v>
       </c>
       <c r="B51" s="13" t="str">
-        <f>TEXT($A51,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
@@ -2442,17 +2436,17 @@
         <v>46598</v>
       </c>
       <c r="B52" s="13" t="str">
-        <f>TEXT($A52,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
@@ -2461,17 +2455,17 @@
         <v>46615</v>
       </c>
       <c r="B53" s="13" t="str">
-        <f>TEXT($A53,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Mon</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
@@ -2480,17 +2474,17 @@
         <v>46619</v>
       </c>
       <c r="B54" s="13" t="str">
-        <f>TEXT($A54,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
@@ -2499,17 +2493,17 @@
         <v>46640</v>
       </c>
       <c r="B55" s="13" t="str">
-        <f>TEXT($A55,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
@@ -2518,17 +2512,17 @@
         <v>46648</v>
       </c>
       <c r="B56" s="13" t="str">
-        <f>TEXT($A56,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
@@ -2537,17 +2531,17 @@
         <v>46661</v>
       </c>
       <c r="B57" s="13" t="str">
-        <f>TEXT($A57,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
@@ -2556,17 +2550,17 @@
         <v>46675</v>
       </c>
       <c r="B58" s="13" t="str">
-        <f>TEXT($A58,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
@@ -2575,17 +2569,17 @@
         <v>46703</v>
       </c>
       <c r="B59" s="13" t="str">
-        <f>TEXT($A59,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
@@ -2594,17 +2588,17 @@
         <v>46717</v>
       </c>
       <c r="B60" s="13" t="str">
-        <f>TEXT($A60,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
@@ -2613,17 +2607,17 @@
         <v>46737</v>
       </c>
       <c r="B61" s="13" t="str">
-        <f>TEXT($A61,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>249</v>
+        <v>213</v>
+      </c>
+      <c r="D61" s="16" t="s">
+        <v>247</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2661,13 +2655,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2675,13 +2669,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2689,13 +2683,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2703,13 +2697,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2717,13 +2711,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2731,13 +2725,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2745,13 +2739,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2759,13 +2753,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2773,13 +2767,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2787,13 +2781,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -2801,11 +2795,11 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2813,11 +2807,11 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2825,13 +2819,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2839,13 +2833,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2853,13 +2847,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2867,13 +2861,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2881,13 +2875,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2895,13 +2889,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2909,13 +2903,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2923,13 +2917,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2937,13 +2931,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2951,13 +2945,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2965,13 +2959,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2979,13 +2973,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2993,13 +2987,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -3012,13 +3006,12 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7" style="14" customWidth="1"/>
-    <col min="2" max="2" width="30" style="14" customWidth="1"/>
-    <col min="3" max="3" width="16" style="14" customWidth="1"/>
-    <col min="4" max="4" width="26" style="14" customWidth="1"/>
-    <col min="5" max="5" width="16" style="14" customWidth="1"/>
-    <col min="6" max="6" width="22" style="14" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="14"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -3034,231 +3027,231 @@
       <c r="D1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="17" t="s">
-        <v>214</v>
+      <c r="E1" s="15" t="s">
+        <v>212</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="15">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="15" t="s">
+      <c r="D7" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="14">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="14">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="15">
-        <v>2</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="15">
-        <v>3</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="15">
-        <v>4</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="15">
-        <v>5</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="15">
-        <v>6</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="15">
-        <v>7</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="16">
-        <v>8</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" s="16" t="s">
+      <c r="E10" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="14">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E11" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="16">
-        <v>9</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" s="16" t="s">
+      <c r="F11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="14">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E12" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="F10" s="14" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="16">
-        <v>10</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="16">
-        <v>11</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>111</v>
+      <c r="F12" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3305,482 +3298,482 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="17">
+        <v>1</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" s="17">
+        <v>2</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="17">
+        <v>3</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="17">
+        <v>4</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="17">
+        <v>5</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B7" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C7" s="17">
         <v>1</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D7" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="C8" s="17">
+        <v>2</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="C9" s="17">
+        <v>1</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" s="17">
+        <v>2</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C11" s="17">
+        <v>1</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C12" s="17">
+        <v>2</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C13" s="17">
+        <v>3</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C14" s="17">
+        <v>4</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="C15" s="17">
+        <v>1</v>
+      </c>
+      <c r="D15" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E15" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F15" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="18" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="C3" s="19">
+      <c r="G15" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="C16" s="17">
         <v>2</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18" t="s">
+      <c r="D16" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="18" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="C4" s="19">
+      <c r="G16" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="C17" s="17">
+        <v>1</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="C18" s="17">
+        <v>2</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="C19" s="17">
         <v>3</v>
       </c>
-      <c r="D4" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="18" t="s">
+      <c r="D19" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="18" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="C5" s="19">
-        <v>4</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18" t="s">
+      <c r="G19" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C20" s="17">
+        <v>1</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C21" s="17">
+        <v>2</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="18" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="C6" s="19">
-        <v>5</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="18" t="s">
+      <c r="G21" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C22" s="17">
+        <v>3</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="18" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="C7" s="19">
-        <v>1</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="C8" s="19">
-        <v>2</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="C9" s="19">
-        <v>1</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="C10" s="19">
-        <v>2</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="C11" s="19">
-        <v>1</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="C12" s="19">
-        <v>2</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="C13" s="19">
-        <v>3</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="C14" s="19">
-        <v>4</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="C15" s="19">
-        <v>1</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="C16" s="19">
-        <v>2</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="E16" s="18" t="s">
+      <c r="G22" s="16" t="s">
         <v>86</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="C17" s="19">
-        <v>1</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="C18" s="19">
-        <v>2</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="C19" s="19">
-        <v>3</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="C20" s="19">
-        <v>1</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="C21" s="19">
-        <v>2</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="C22" s="19">
-        <v>3</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -3809,16 +3802,16 @@
       <c r="A2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>37</v>
+      <c r="B2" s="18">
+        <v>46229</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>39</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -4068,6 +4061,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
@@ -4076,15 +4078,6 @@
     <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4107,6 +4100,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4115,12 +4116,4 @@
     <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="187" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0FC7D38-B85B-441E-9BA4-936AC6D2133E}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E8EE138-7304-4329-B907-F584C4B159ED}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="250">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -785,6 +785,9 @@
   </si>
   <si>
     <t>南凤福利协会 Nam Hong Welfare Service Society · For committee members reference 仅供委员参考</t>
+  </si>
+  <si>
+    <t>26 07 2026</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +1012,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3802,8 +3805,8 @@
       <c r="A2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="18">
-        <v>46229</v>
+      <c r="B2" s="18" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -4061,15 +4064,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
@@ -4078,6 +4072,15 @@
     <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4100,14 +4103,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4116,4 +4111,12 @@
     <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="188" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E8EE138-7304-4329-B907-F584C4B159ED}"/>
+  <xr:revisionPtr revIDLastSave="190" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC73E805-A56F-447E-BC80-D9AA00447527}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -787,7 +787,7 @@
     <t>南凤福利协会 Nam Hong Welfare Service Society · For committee members reference 仅供委员参考</t>
   </si>
   <si>
-    <t>26 07 2026</t>
+    <t>26 July 2026</t>
   </si>
 </sst>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="190" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC73E805-A56F-447E-BC80-D9AA00447527}"/>
+  <xr:revisionPtr revIDLastSave="195" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F0E3EDC-B320-4508-A448-72B3B5501FFE}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -688,9 +688,6 @@
     <t>[Tentative] Deepavali Ang Pao Distribution (AMS Hindus)</t>
   </si>
   <si>
-    <t>[Tentative] Charity Walk</t>
-  </si>
-  <si>
     <t>[Tentative] New Year Ration</t>
   </si>
   <si>
@@ -788,6 +785,9 @@
   </si>
   <si>
     <t>26 July 2026</t>
+  </si>
+  <si>
+    <t>[Tentative] Charity Walk - postpone to April 2027</t>
   </si>
 </sst>
 </file>
@@ -2101,7 +2101,7 @@
         <v>Sat</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>197</v>
@@ -2161,7 +2161,7 @@
         <v>213</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>138</v>
@@ -2177,7 +2177,7 @@
         <v>Fri</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>200</v>
@@ -2196,7 +2196,7 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>201</v>
@@ -2215,7 +2215,7 @@
         <v>Thu</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>202</v>
@@ -2234,7 +2234,7 @@
         <v>Fri</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>203</v>
@@ -2253,7 +2253,7 @@
         <v>Fri</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>204</v>
@@ -2272,7 +2272,7 @@
         <v>Thu</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>205</v>
@@ -2291,7 +2291,7 @@
         <v>Sat</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>206</v>
@@ -2310,7 +2310,7 @@
         <v>Fri</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>204</v>
@@ -2329,7 +2329,7 @@
         <v>Wed</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>167</v>
@@ -2348,7 +2348,7 @@
         <v>Thu</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>169</v>
@@ -2367,7 +2367,7 @@
         <v>Fri</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>171</v>
@@ -2386,7 +2386,7 @@
         <v>Fri</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>207</v>
@@ -2405,7 +2405,7 @@
         <v>Fri</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D50" s="11" t="s">
         <v>204</v>
@@ -2424,7 +2424,7 @@
         <v>Fri</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D51" s="11" t="s">
         <v>204</v>
@@ -2443,7 +2443,7 @@
         <v>Fri</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D52" s="11" t="s">
         <v>208</v>
@@ -2462,7 +2462,7 @@
         <v>Mon</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D53" s="11" t="s">
         <v>209</v>
@@ -2481,7 +2481,7 @@
         <v>Fri</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D54" s="11" t="s">
         <v>210</v>
@@ -2500,7 +2500,7 @@
         <v>Fri</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D55" s="11" t="s">
         <v>204</v>
@@ -2519,7 +2519,7 @@
         <v>Sat</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D56" s="11" t="s">
         <v>211</v>
@@ -2538,7 +2538,7 @@
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D57" s="11" t="s">
         <v>204</v>
@@ -2557,7 +2557,7 @@
         <v>Fri</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>204</v>
@@ -2576,7 +2576,7 @@
         <v>Fri</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D59" s="11" t="s">
         <v>204</v>
@@ -2595,7 +2595,7 @@
         <v>Fri</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>204</v>
@@ -2617,7 +2617,7 @@
         <v>213</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>138</v>
@@ -2864,7 +2864,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>66</v>
@@ -3302,10 +3302,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>233</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>234</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>233</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>234</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -3346,16 +3346,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>233</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>234</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>66</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>233</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>234</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>233</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>234</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
@@ -3413,10 +3413,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>235</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>236</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>235</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>236</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>237</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>238</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>237</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>238</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>239</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>240</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -3528,10 +3528,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>239</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>240</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>239</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>240</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -3574,10 +3574,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>239</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>240</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>241</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>242</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -3620,10 +3620,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>241</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>242</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="B17" s="16" t="s">
         <v>243</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>244</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
@@ -3666,10 +3666,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>243</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>244</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -3689,10 +3689,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="B19" s="16" t="s">
         <v>243</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>244</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
@@ -3712,10 +3712,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B21" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B22" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -3806,7 +3806,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -3814,7 +3814,7 @@
         <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -3823,6 +3823,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4063,17 +4074,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -4084,6 +4084,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4102,17 +4113,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="195" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F0E3EDC-B320-4508-A448-72B3B5501FFE}"/>
+  <xr:revisionPtr revIDLastSave="197" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F05BDF63-9187-4F2A-B6CC-684A8B4BD20A}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="252">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -788,6 +788,12 @@
   </si>
   <si>
     <t>[Tentative] Charity Walk - postpone to April 2027</t>
+  </si>
+  <si>
+    <t>Password to open mobile page</t>
+  </si>
+  <si>
+    <t>NHWSS2026</t>
   </si>
 </sst>
 </file>
@@ -3786,7 +3792,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3815,6 +3821,14 @@
       </c>
       <c r="B3" s="4" t="s">
         <v>247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B4" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -3834,6 +3848,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4074,15 +4097,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4095,6 +4109,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4111,12 +4133,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="197" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F05BDF63-9187-4F2A-B6CC-684A8B4BD20A}"/>
+  <xr:revisionPtr revIDLastSave="215" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13432ACC-3AEE-40B3-A7F1-33618AC402AB}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="256">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -613,21 +613,12 @@
     <t>慈济慈善演唱会</t>
   </si>
   <si>
-    <t>Nine Emperor Gods Festival Fundraiser – Day 1</t>
-  </si>
-  <si>
     <t>九皇爷诞筹款第一天</t>
   </si>
   <si>
-    <t>Nine Emperor Gods Festival Fundraiser – Day 2</t>
-  </si>
-  <si>
     <t>九皇爷诞筹款第二天</t>
   </si>
   <si>
-    <t>Nine Emperor Gods Festival Fundraiser – Day 3</t>
-  </si>
-  <si>
     <t>九皇爷诞筹款第三天</t>
   </si>
   <si>
@@ -794,6 +785,27 @@
   </si>
   <si>
     <t>NHWSS2026</t>
+  </si>
+  <si>
+    <t>[Tentative] Nine Emperor Gods Festival Fundraiser – Day 1</t>
+  </si>
+  <si>
+    <t>[Tentative] Nine Emperor Gods Festival Fundraiser – Day 2</t>
+  </si>
+  <si>
+    <t>[Tentative] Nine Emperor Gods Festival Fundraiser – Day 3</t>
+  </si>
+  <si>
+    <t>元龙聖庙（关帝聖君兴诸众神诞）(理事：徐金声）</t>
+  </si>
+  <si>
+    <t>Temple Dinner - 元龙聖庙（关帝聖君兴诸众神诞）(Attendance: Cher Kim Seah, Agnes, Bryan, Kathy, Jin Hoa)</t>
+  </si>
+  <si>
+    <t>大牌137中元会 (理事：徐金声）</t>
+  </si>
+  <si>
+    <t>Lunar July month Zhong Yuan Festival - Block 137 Yishun Ring Road (Attendance: Cher Kim Seah, Agnes, Yan Yi)</t>
   </si>
 </sst>
 </file>
@@ -1462,7 +1474,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -1495,7 +1507,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="13" t="str">
-        <f t="shared" ref="B2:B33" si="0">TEXT($A2,"ddd")</f>
+        <f t="shared" ref="B2:B35" si="0">TEXT($A2,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -1928,132 +1940,132 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="12">
+        <f>DATE(2026,8,8)</f>
+        <v>46242</v>
+      </c>
+      <c r="B25" s="13" t="str">
+        <f>TEXT($A25,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="12">
+        <f>DATE(2026,8,14)</f>
+        <v>46248</v>
+      </c>
+      <c r="B26" s="13" t="str">
+        <f>TEXT($A26,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="12">
         <f>DATE(2026,8,22)</f>
         <v>46256</v>
-      </c>
-      <c r="B25" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Sat</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="12">
-        <f>DATE(2026,9,4)</f>
-        <v>46269</v>
-      </c>
-      <c r="B26" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Fri</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="12">
-        <f>DATE(2026,9,5)</f>
-        <v>46270</v>
       </c>
       <c r="B27" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="12">
+        <f>DATE(2026,9,4)</f>
+        <v>46269</v>
+      </c>
+      <c r="B28" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="12">
+        <f>DATE(2026,9,5)</f>
+        <v>46270</v>
+      </c>
+      <c r="B29" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="12">
         <f>DATE(2026,9,19)</f>
         <v>46284</v>
-      </c>
-      <c r="B28" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Sat</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="12">
-        <f>DATE(2026,9,21)</f>
-        <v>46286</v>
-      </c>
-      <c r="B29" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Mon</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="12">
-        <f>DATE(2026,10,10)</f>
-        <v>46305</v>
       </c>
       <c r="B30" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="12">
-        <f>DATE(2026,10,12)</f>
-        <v>46307</v>
+        <f>DATE(2026,9,21)</f>
+        <v>46286</v>
       </c>
       <c r="B31" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>191</v>
+        <v>142</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>138</v>
@@ -2061,398 +2073,398 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="12">
+        <f>DATE(2026,10,10)</f>
+        <v>46305</v>
+      </c>
+      <c r="B32" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="12">
+        <f>DATE(2026,10,12)</f>
+        <v>46307</v>
+      </c>
+      <c r="B33" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" s="12">
         <f>DATE(2026,10,13)</f>
         <v>46308</v>
       </c>
-      <c r="B32" s="13" t="str">
+      <c r="B34" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C32" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="E32" s="11" t="s">
+      <c r="C34" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E34" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="12">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="12">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
       </c>
-      <c r="B33" s="13" t="str">
+      <c r="B35" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C33" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="E33" s="11" t="s">
+      <c r="C35" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="E35" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="12">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="12">
         <f>DATE(2026,10,31)</f>
         <v>46326</v>
       </c>
-      <c r="B34" s="13" t="str">
-        <f t="shared" ref="B34:B61" si="1">TEXT($A34,"ddd")</f>
+      <c r="B36" s="13" t="str">
+        <f t="shared" ref="B36:B63" si="1">TEXT($A36,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C34" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="E34" s="11" t="s">
+      <c r="C36" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="E36" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="12">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="12">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
       </c>
-      <c r="B35" s="13" t="str">
+      <c r="B37" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Tue</v>
       </c>
-      <c r="C35" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="E35" s="11" t="s">
+      <c r="C37" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="E37" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="12">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" s="12">
         <f>DATE(2026,11,10)</f>
         <v>46336</v>
       </c>
-      <c r="B36" s="13" t="str">
+      <c r="B38" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Tue</v>
       </c>
-      <c r="C36" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="E36" s="11" t="s">
+      <c r="C38" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="E38" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="12">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" s="12">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B37" s="13" t="str">
+      <c r="B39" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Wed</v>
       </c>
-      <c r="C37" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="E37" s="11" t="s">
+      <c r="C39" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="12">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B38" s="13" t="str">
+      <c r="B40" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
-      <c r="C38" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="E38" s="11" t="s">
+      <c r="C40" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="E40" s="11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="12">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" s="12">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B39" s="13" t="str">
+      <c r="B41" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="C39" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="E39" s="11" t="s">
+      <c r="C41" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E41" s="11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="12">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="12">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B40" s="13" t="str">
+      <c r="B42" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
-      <c r="C40" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="E40" s="11" t="s">
+      <c r="C42" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="E42" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="12">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="12">
         <f>DATE(2027,2,19)</f>
         <v>46437</v>
       </c>
-      <c r="B41" s="13" t="str">
+      <c r="B43" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
-      <c r="C41" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="E41" s="11" t="s">
+      <c r="C43" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="E43" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="12">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" s="12">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B42" s="13" t="str">
+      <c r="B44" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
-      <c r="C42" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="E42" s="11" t="s">
+      <c r="C44" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E44" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="12">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" s="12">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B43" s="13" t="str">
+      <c r="B45" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
-      <c r="C43" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="E43" s="11" t="s">
+      <c r="C45" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E45" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="12">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" s="12">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
       </c>
-      <c r="B44" s="13" t="str">
+      <c r="B46" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="C44" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="E44" s="11" t="s">
+      <c r="C46" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E46" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="12">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" s="12">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
       </c>
-      <c r="B45" s="13" t="str">
+      <c r="B47" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
-      <c r="C45" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="E45" s="11" t="s">
+      <c r="C47" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E47" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="12">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" s="12">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B46" s="13" t="str">
+      <c r="B48" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Wed</v>
       </c>
-      <c r="C46" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="D46" s="11" t="s">
+      <c r="C48" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="D48" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E48" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="12">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B47" s="13" t="str">
+      <c r="B49" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
-      <c r="C47" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="D47" s="11" t="s">
+      <c r="C49" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="D49" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E49" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="12">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B48" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Fri</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
-      </c>
-      <c r="B49" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Fri</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
       </c>
       <c r="B50" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B51" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D51" s="11" t="s">
         <v>204</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="12">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B52" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>131</v>
@@ -2460,37 +2472,37 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="12">
-        <f>DATE(2027,8,16)</f>
-        <v>46615</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B53" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Mon</v>
+        <v>Fri</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="12">
-        <f>DATE(2027,8,20)</f>
-        <v>46619</v>
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
       </c>
       <c r="B54" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>131</v>
@@ -2498,56 +2510,56 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="12">
+        <f>DATE(2027,8,16)</f>
+        <v>46615</v>
+      </c>
+      <c r="B55" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Mon</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" s="12">
+        <f>DATE(2027,8,20)</f>
+        <v>46619</v>
+      </c>
+      <c r="B56" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Fri</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" s="12">
         <f>DATE(2027,9,10)</f>
         <v>46640</v>
-      </c>
-      <c r="B55" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Fri</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="12">
-        <f>DATE(2027,9,18)</f>
-        <v>46648</v>
-      </c>
-      <c r="B56" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Sat</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="12">
-        <f>DATE(2027,10,1)</f>
-        <v>46661</v>
       </c>
       <c r="B57" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>131</v>
@@ -2555,37 +2567,37 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="12">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
+        <f>DATE(2027,9,18)</f>
+        <v>46648</v>
       </c>
       <c r="B58" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Fri</v>
+        <v>Sat</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="12">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
+        <f>DATE(2027,10,1)</f>
+        <v>46661</v>
       </c>
       <c r="B59" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E59" s="11" t="s">
         <v>131</v>
@@ -2593,18 +2605,18 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
       </c>
       <c r="B60" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>131</v>
@@ -2612,20 +2624,58 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="12">
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
+      </c>
+      <c r="B61" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Fri</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" s="12">
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
+      </c>
+      <c r="B62" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Fri</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" s="12">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B61" s="13" t="str">
+      <c r="B63" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
-      <c r="C61" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="D61" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="E61" s="11" t="s">
+      <c r="C63" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="D63" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="E63" s="11" t="s">
         <v>138</v>
       </c>
     </row>
@@ -2870,7 +2920,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>66</v>
@@ -3037,7 +3087,7 @@
         <v>25</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>22</v>
@@ -3308,10 +3358,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -3331,10 +3381,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -3352,16 +3402,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>66</v>
@@ -3375,10 +3425,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -3396,10 +3446,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
@@ -3419,10 +3469,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
@@ -3442,10 +3492,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -3465,10 +3515,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
@@ -3488,10 +3538,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
@@ -3511,10 +3561,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -3534,10 +3584,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -3557,10 +3607,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -3580,10 +3630,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -3603,10 +3653,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -3626,10 +3676,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
@@ -3649,10 +3699,10 @@
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
@@ -3672,10 +3722,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -3695,10 +3745,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
@@ -3718,10 +3768,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
@@ -3741,10 +3791,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
@@ -3764,10 +3814,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -3812,7 +3862,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -3820,15 +3870,15 @@
         <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -3848,15 +3898,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4097,6 +4138,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4109,14 +4159,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4133,4 +4175,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="215" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13432ACC-3AEE-40B3-A7F1-33618AC402AB}"/>
+  <xr:revisionPtr revIDLastSave="217" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07EDF1A2-F731-4203-B0A9-979A64081F31}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -571,12 +571,6 @@
     <t>摩根士丹利企业社会责任活动暨寿像拍摄</t>
   </si>
   <si>
-    <t>Naval Base Secondary School Outing (Date Unconfirmed)</t>
-  </si>
-  <si>
-    <t>海军部中学户外活动（日期待定）</t>
-  </si>
-  <si>
     <t>Asiatic Fire System CSR National Day Celebration (150 pax)</t>
   </si>
   <si>
@@ -806,6 +800,12 @@
   </si>
   <si>
     <t>Lunar July month Zhong Yuan Festival - Block 137 Yishun Ring Road (Attendance: Cher Kim Seah, Agnes, Yan Yi)</t>
+  </si>
+  <si>
+    <t>Naval Base Secondary School Outing</t>
+  </si>
+  <si>
+    <t>海军部中学户外活动</t>
   </si>
 </sst>
 </file>
@@ -1910,10 +1910,10 @@
         <v>Fri</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>178</v>
+        <v>255</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>131</v>
@@ -1929,10 +1929,10 @@
         <v>Sat</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>131</v>
@@ -1948,10 +1948,10 @@
         <v>Sat</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>138</v>
@@ -1967,10 +1967,10 @@
         <v>Fri</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>138</v>
@@ -1986,10 +1986,10 @@
         <v>Sat</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>138</v>
@@ -2005,10 +2005,10 @@
         <v>Fri</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>127</v>
@@ -2024,10 +2024,10 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>131</v>
@@ -2043,10 +2043,10 @@
         <v>Sat</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>141</v>
@@ -2065,7 +2065,7 @@
         <v>142</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>138</v>
@@ -2084,7 +2084,7 @@
         <v>143</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>138</v>
@@ -2100,10 +2100,10 @@
         <v>Mon</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>138</v>
@@ -2119,10 +2119,10 @@
         <v>Tue</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>138</v>
@@ -2138,10 +2138,10 @@
         <v>Wed</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>138</v>
@@ -2157,10 +2157,10 @@
         <v>Sat</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>138</v>
@@ -2176,10 +2176,10 @@
         <v>Tue</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>127</v>
@@ -2195,10 +2195,10 @@
         <v>Tue</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>127</v>
@@ -2214,10 +2214,10 @@
         <v>Wed</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>138</v>
@@ -2233,10 +2233,10 @@
         <v>Fri</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>125</v>
@@ -2252,10 +2252,10 @@
         <v>Sat</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E41" s="11" t="s">
         <v>125</v>
@@ -2271,10 +2271,10 @@
         <v>Thu</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>131</v>
@@ -2290,10 +2290,10 @@
         <v>Fri</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E43" s="11" t="s">
         <v>131</v>
@@ -2309,10 +2309,10 @@
         <v>Fri</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E44" s="11" t="s">
         <v>131</v>
@@ -2328,10 +2328,10 @@
         <v>Thu</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E45" s="11" t="s">
         <v>127</v>
@@ -2347,10 +2347,10 @@
         <v>Sat</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>131</v>
@@ -2366,10 +2366,10 @@
         <v>Fri</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E47" s="11" t="s">
         <v>131</v>
@@ -2385,7 +2385,7 @@
         <v>Wed</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>167</v>
@@ -2404,7 +2404,7 @@
         <v>Thu</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>169</v>
@@ -2423,7 +2423,7 @@
         <v>Fri</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D50" s="11" t="s">
         <v>171</v>
@@ -2442,10 +2442,10 @@
         <v>Fri</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>127</v>
@@ -2461,10 +2461,10 @@
         <v>Fri</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>131</v>
@@ -2480,10 +2480,10 @@
         <v>Fri</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>131</v>
@@ -2499,10 +2499,10 @@
         <v>Fri</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>131</v>
@@ -2518,10 +2518,10 @@
         <v>Mon</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>138</v>
@@ -2537,10 +2537,10 @@
         <v>Fri</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>131</v>
@@ -2556,10 +2556,10 @@
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>131</v>
@@ -2575,10 +2575,10 @@
         <v>Sat</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>138</v>
@@ -2594,10 +2594,10 @@
         <v>Fri</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E59" s="11" t="s">
         <v>131</v>
@@ -2613,10 +2613,10 @@
         <v>Fri</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>131</v>
@@ -2632,10 +2632,10 @@
         <v>Fri</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>131</v>
@@ -2651,10 +2651,10 @@
         <v>Fri</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E62" s="11" t="s">
         <v>131</v>
@@ -2670,10 +2670,10 @@
         <v>Thu</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>138</v>
@@ -2920,7 +2920,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>66</v>
@@ -3087,7 +3087,7 @@
         <v>25</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>22</v>
@@ -3358,10 +3358,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -3381,10 +3381,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -3402,16 +3402,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>66</v>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
@@ -3469,10 +3469,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
@@ -3492,10 +3492,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -3515,10 +3515,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
@@ -3561,10 +3561,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -3584,10 +3584,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -3630,10 +3630,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -3653,10 +3653,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -3676,10 +3676,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
@@ -3722,10 +3722,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
@@ -3768,10 +3768,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
@@ -3814,10 +3814,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -3862,7 +3862,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -3870,15 +3870,15 @@
         <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="217" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07EDF1A2-F731-4203-B0A9-979A64081F31}"/>
+  <xr:revisionPtr revIDLastSave="312" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24497330-68BD-4E92-A7F8-C6174A469B21}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="273">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -466,9 +466,6 @@
     <t>Partnership</t>
   </si>
   <si>
-    <t>7th Month Fundraising Period (End)</t>
-  </si>
-  <si>
     <t>Charity Concert at Tzu Chi</t>
   </si>
   <si>
@@ -577,12 +574,6 @@
     <t>Asiatic Fire System企业社会责任国庆庆祝会（150人）</t>
   </si>
   <si>
-    <t>7th Month Fundraising Period (Start) – NHST Charity Auction &amp; Charity Dinner for Elderly</t>
-  </si>
-  <si>
-    <t>七月筹款期开始 – 慈善拍卖会暨乐龄慈善晚宴</t>
-  </si>
-  <si>
     <t>TFE Ration Distribution (140 pax)</t>
   </si>
   <si>
@@ -601,66 +592,9 @@
     <t>正罡玄门中秋物资派发（200人）</t>
   </si>
   <si>
-    <t>七月筹款期结束</t>
-  </si>
-  <si>
     <t>慈济慈善演唱会</t>
   </si>
   <si>
-    <t>九皇爷诞筹款第一天</t>
-  </si>
-  <si>
-    <t>九皇爷诞筹款第二天</t>
-  </si>
-  <si>
-    <t>九皇爷诞筹款第三天</t>
-  </si>
-  <si>
-    <t>慈善健走（暂定）</t>
-  </si>
-  <si>
-    <t>屠妖节红包派发（AMS印族受惠者）</t>
-  </si>
-  <si>
-    <t>MS项目物资派发（日期待定）</t>
-  </si>
-  <si>
-    <t>新年物资派发</t>
-  </si>
-  <si>
-    <t>农历新年物资及红包派发</t>
-  </si>
-  <si>
-    <t>新春晚宴 – 企业社会责任（JustCo或MS项目）第一天</t>
-  </si>
-  <si>
-    <t>新春晚宴 – 企业社会责任（JustCo或MS项目）第二天</t>
-  </si>
-  <si>
-    <t>企业／学校社会责任合作</t>
-  </si>
-  <si>
-    <t>开斋节红包及礼包派发暨午宴</t>
-  </si>
-  <si>
-    <t>企业／学校社会责任合作（日出健走）</t>
-  </si>
-  <si>
-    <t>端午节活动（实际节日为6月9日）</t>
-  </si>
-  <si>
-    <t>企业／学校社会责任合作（国庆庆祝）</t>
-  </si>
-  <si>
-    <t>七月筹款期（实际日期8月16日，涵盖8月2日至30日）</t>
-  </si>
-  <si>
-    <t>企业／学校社会责任合作（慈善演唱会）</t>
-  </si>
-  <si>
-    <t>慈善演唱会</t>
-  </si>
-  <si>
     <t>Title (Chinese)</t>
   </si>
   <si>
@@ -763,15 +697,9 @@
     <t>公关组</t>
   </si>
   <si>
-    <t>「认捐拥抱・温暖长者」慈善运动（圣诞前实体推介）</t>
-  </si>
-  <si>
     <t>南凤福利协会 Nam Hong Welfare Service Society · For committee members reference 仅供委员参考</t>
   </si>
   <si>
-    <t>26 July 2026</t>
-  </si>
-  <si>
     <t>[Tentative] Charity Walk - postpone to April 2027</t>
   </si>
   <si>
@@ -790,22 +718,145 @@
     <t>[Tentative] Nine Emperor Gods Festival Fundraiser – Day 3</t>
   </si>
   <si>
-    <t>元龙聖庙（关帝聖君兴诸众神诞）(理事：徐金声）</t>
-  </si>
-  <si>
     <t>Temple Dinner - 元龙聖庙（关帝聖君兴诸众神诞）(Attendance: Cher Kim Seah, Agnes, Bryan, Kathy, Jin Hoa)</t>
   </si>
   <si>
-    <t>大牌137中元会 (理事：徐金声）</t>
-  </si>
-  <si>
-    <t>Lunar July month Zhong Yuan Festival - Block 137 Yishun Ring Road (Attendance: Cher Kim Seah, Agnes, Yan Yi)</t>
-  </si>
-  <si>
     <t>Naval Base Secondary School Outing</t>
   </si>
   <si>
     <t>海军部中学户外活动</t>
+  </si>
+  <si>
+    <t>27 July 2026</t>
+  </si>
+  <si>
+    <t>[未确认] 九皇爷诞筹款第一天</t>
+  </si>
+  <si>
+    <t>[未确认] 九皇爷诞筹款第二天</t>
+  </si>
+  <si>
+    <t>[未确认] 九皇爷诞筹款第三天</t>
+  </si>
+  <si>
+    <t>[未确认] 慈善健走（暂定）</t>
+  </si>
+  <si>
+    <t>[未确认] 屠妖节红包派发（AMS印族受惠者）</t>
+  </si>
+  <si>
+    <t>[未确认] MS项目物资派发（日期待定）</t>
+  </si>
+  <si>
+    <t>[未确认] 「认捐拥抱・温暖长者」慈善运动（圣诞前实体推介）</t>
+  </si>
+  <si>
+    <t>[未确认] 新年物资派发</t>
+  </si>
+  <si>
+    <t>[未确认] 农历新年物资及红包派发</t>
+  </si>
+  <si>
+    <t>[未确认] 新春晚宴 – 企业社会责任（JustCo或MS项目）第一天</t>
+  </si>
+  <si>
+    <t>[未确认] 新春晚宴 – 企业社会责任（JustCo或MS项目）第二天</t>
+  </si>
+  <si>
+    <t>[未确认] 企业／学校社会责任合作</t>
+  </si>
+  <si>
+    <t>[未确认] 开斋节红包及礼包派发暨午宴</t>
+  </si>
+  <si>
+    <t>[未确认] 企业／学校社会责任合作（日出健走）</t>
+  </si>
+  <si>
+    <t>[未确认] 卫塞节筹款（Ubin Thai）第一天</t>
+  </si>
+  <si>
+    <t>[未确认] 卫塞节筹款（Ubin Thai）第二天</t>
+  </si>
+  <si>
+    <t>[未确认] 卫塞节筹款（Ubin Thai）第三天</t>
+  </si>
+  <si>
+    <t>[未确认] 端午节活动（实际节日为6月9日）</t>
+  </si>
+  <si>
+    <t>[未确认] 企业／学校社会责任合作（国庆庆祝）</t>
+  </si>
+  <si>
+    <t>[未确认] 七月筹款期（实际日期8月16日，涵盖8月2日至30日）</t>
+  </si>
+  <si>
+    <t>[未确认] 企业／学校社会责任合作（慈善演唱会）</t>
+  </si>
+  <si>
+    <t>[未确认] 慈善演唱会</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - Block 137 Yishun Ring Road (Attendance: Cher Kim Seah, Agnes, Yan Yi)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - YS ONE, 1 Yishun Street 23 (Attendance: Bryan, 丽菁, 丽丝和先生)</t>
+  </si>
+  <si>
+    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 7 Gambas Crescent, ARK@Gambas Level 2 (Attendance: Doran, Pei Yuen, Agnes, 晓晓)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - 724 Yishun Street 71 (Attendance: Chew Kim Cheong, Bryan, Kathy, 丽菁, 丽丝和先生)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - 561 Yishun Ring Road (Attendance: Cher Kim Seah, Yan Yi, Pei Yuen, Agnes, Kathy)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - Jurong Safra Pearl Garden Restaurant (Attendance: Neo Tian Siah, Kathy, Jin Hoa)</t>
+  </si>
+  <si>
+    <t>YS ONE 中元会&amp; 歌台 (代表：Bryan, 丽菁, 丽丝和先生）</t>
+  </si>
+  <si>
+    <t>[日期未确认] 方舟@岗巴士中元会 (代表：Doran, Pei Yuen, Agnes, 晓晓）</t>
+  </si>
+  <si>
+    <t>717 商店中元会 (代表：周锦昌, Bryan, Kathy, 丽菁, 丽丝和先生）</t>
+  </si>
+  <si>
+    <t>山顶师城杨艺中元会 (代表：梁天城, Kathy, Jin Hoa）</t>
+  </si>
+  <si>
+    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Attendance: Cher Kim Seah, Pei Yuen, Yan Yi)</t>
+  </si>
+  <si>
+    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Attendance: Cher Kim Seah, Doran, Bryan)</t>
+  </si>
+  <si>
+    <t>[日期未确认] 义顺镇商贩联合中元会歌台 (代表：徐金声, Doran, Bryan）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon (Attendance: Neo Tian Siah, NHWSS office staff, 5 front desk, 晓晓) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunar July (ZhongYuan Festival) - Blk 838 Yishun Street 81 (Attendance: Doran, Bryan, 丽菁, 丽丝和先生) </t>
+  </si>
+  <si>
+    <t>义顺南旺村中元会 (代表：Doran, Bryan, 丽菁, 丽丝和先生）</t>
+  </si>
+  <si>
+    <t>元龙聖庙（关帝聖君兴诸众神诞）(代表：徐金声, Agnes, Bryan, Kathy, Jin Hoa）。筹款活动包括义标。</t>
+  </si>
+  <si>
+    <t>大牌137中元会 (代表：徐金声,Agnes, Yan Yi）。筹款活动包括义标。</t>
+  </si>
+  <si>
+    <t>华报善堂中元会 (代表：徐金声, Yan Yi, Pei Yuen, Agnes, Kathy）。筹款活动包括义标。</t>
+  </si>
+  <si>
+    <t>[日期未确认] 义顺镇商贩联合中元会 (代表：徐金声, Pei Yuen, Yan Yi）。筹款活动包括义标。</t>
+  </si>
+  <si>
+    <t>南凤善堂中元会 (代表：梁天城,南凤福利协会员工，晓晓）。筹款活动包括义标。</t>
   </si>
 </sst>
 </file>
@@ -888,7 +939,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -987,11 +1038,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D5DD"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1033,6 +1093,8 @@
     <xf numFmtId="15" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1048,6 +1110,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1474,13 +1540,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="72.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="59.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1498,7 +1564,7 @@
         <v>33</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -1507,14 +1573,14 @@
         <v>46023</v>
       </c>
       <c r="B2" s="13" t="str">
-        <f t="shared" ref="B2:B35" si="0">TEXT($A2,"ddd")</f>
+        <f t="shared" ref="B2:B42" si="0">TEXT($A2,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>146</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>125</v>
@@ -1533,7 +1599,7 @@
         <v>126</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>125</v>
@@ -1549,10 +1615,10 @@
         <v>Thu</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>148</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>149</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>127</v>
@@ -1571,7 +1637,7 @@
         <v>128</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>127</v>
@@ -1587,10 +1653,10 @@
         <v>Mon</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>151</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>152</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>129</v>
@@ -1609,7 +1675,7 @@
         <v>130</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>127</v>
@@ -1628,7 +1694,7 @@
         <v>132</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>131</v>
@@ -1647,7 +1713,7 @@
         <v>133</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>127</v>
@@ -1666,7 +1732,7 @@
         <v>134</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>127</v>
@@ -1685,7 +1751,7 @@
         <v>135</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>127</v>
@@ -1704,7 +1770,7 @@
         <v>137</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>136</v>
@@ -1720,10 +1786,10 @@
         <v>Mon</v>
       </c>
       <c r="C13" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>159</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>160</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>136</v>
@@ -1739,10 +1805,10 @@
         <v>Fri</v>
       </c>
       <c r="C14" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>161</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>162</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>138</v>
@@ -1758,10 +1824,10 @@
         <v>Sun</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>163</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>164</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>136</v>
@@ -1780,7 +1846,7 @@
         <v>139</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>127</v>
@@ -1796,10 +1862,10 @@
         <v>Fri</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>166</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>167</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>138</v>
@@ -1815,10 +1881,10 @@
         <v>Sat</v>
       </c>
       <c r="C18" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>168</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>169</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>138</v>
@@ -1834,10 +1900,10 @@
         <v>Sun</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>138</v>
@@ -1853,10 +1919,10 @@
         <v>Mon</v>
       </c>
       <c r="C20" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>173</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>138</v>
@@ -1875,7 +1941,7 @@
         <v>140</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>127</v>
@@ -1891,10 +1957,10 @@
         <v>Fri</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>175</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>176</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>131</v>
@@ -1910,10 +1976,10 @@
         <v>Fri</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>131</v>
@@ -1929,10 +1995,10 @@
         <v>Sat</v>
       </c>
       <c r="C24" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>177</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>178</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>131</v>
@@ -1948,10 +2014,10 @@
         <v>Sat</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>250</v>
+        <v>226</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>268</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>138</v>
@@ -1967,10 +2033,10 @@
         <v>Fri</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="D26" s="11" t="s">
         <v>252</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>269</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>138</v>
@@ -1978,512 +2044,513 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="12">
-        <f>DATE(2026,8,22)</f>
-        <v>46256</v>
+        <f>DATE(2026,8,23)</f>
+        <v>46257</v>
       </c>
       <c r="B27" s="13" t="str">
+        <f>TEXT($A27,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="12">
+        <f>DATE(2026,8,26)</f>
+        <v>46260</v>
+      </c>
+      <c r="B28" s="13" t="str">
+        <f>TEXT($A28,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="12">
+        <f>DATE(2026,8,29)</f>
+        <v>46263</v>
+      </c>
+      <c r="B29" s="13" t="str">
+        <f>TEXT($A29,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="12">
+        <f>DATE(2026,9,1)</f>
+        <v>46266</v>
+      </c>
+      <c r="B30" s="13" t="str">
+        <f>TEXT($A30,"ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="12">
+        <f>DATE(2026,9,3)</f>
+        <v>46268</v>
+      </c>
+      <c r="B31" s="13" t="str">
+        <f>TEXT($A31,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="12">
+        <f>DATE(2026,9,3)</f>
+        <v>46268</v>
+      </c>
+      <c r="B32" s="13" t="str">
+        <f>TEXT($A32,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="12">
+        <f>DATE(2026,9,4)</f>
+        <v>46269</v>
+      </c>
+      <c r="B33" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="12">
+        <f>DATE(2026,9,5)</f>
+        <v>46270</v>
+      </c>
+      <c r="B34" s="13" t="str">
+        <f>TEXT($A34,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="12">
+        <f>DATE(2026,9,5)</f>
+        <v>46270</v>
+      </c>
+      <c r="B35" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D27" s="11" t="s">
+      <c r="C35" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="D35" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="12">
+        <f>DATE(2026,9,7)</f>
+        <v>46272</v>
+      </c>
+      <c r="B36" s="13" t="str">
+        <f>TEXT($A36,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="E36" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="12">
-        <f>DATE(2026,9,4)</f>
-        <v>46269</v>
-      </c>
-      <c r="B28" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Fri</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="12">
-        <f>DATE(2026,9,5)</f>
-        <v>46270</v>
-      </c>
-      <c r="B29" s="13" t="str">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="12">
+        <f>DATE(2026,9,9)</f>
+        <v>46274</v>
+      </c>
+      <c r="B37" s="13" t="str">
+        <f>TEXT($A37,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="12">
+        <f>DATE(2026,9,19)</f>
+        <v>46284</v>
+      </c>
+      <c r="B38" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C38" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D38" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="D29" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="12">
-        <f>DATE(2026,9,19)</f>
-        <v>46284</v>
-      </c>
-      <c r="B30" s="13" t="str">
+      <c r="E38" s="11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="12">
+        <f>DATE(2026,10,10)</f>
+        <v>46305</v>
+      </c>
+      <c r="B39" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="12">
-        <f>DATE(2026,9,21)</f>
-        <v>46286</v>
-      </c>
-      <c r="B31" s="13" t="str">
+      <c r="C39" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="12">
+        <f>DATE(2026,10,12)</f>
+        <v>46307</v>
+      </c>
+      <c r="B40" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C31" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="E31" s="11" t="s">
+      <c r="C40" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="E40" s="11" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="12">
-        <f>DATE(2026,10,10)</f>
-        <v>46305</v>
-      </c>
-      <c r="B32" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Sat</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="12">
-        <f>DATE(2026,10,12)</f>
-        <v>46307</v>
-      </c>
-      <c r="B33" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Mon</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="12">
+      <c r="G40" s="19"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="12">
         <f>DATE(2026,10,13)</f>
         <v>46308</v>
       </c>
-      <c r="B34" s="13" t="str">
+      <c r="B41" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C34" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="E34" s="11" t="s">
+      <c r="C41" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="E41" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="12">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="12">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
       </c>
-      <c r="B35" s="13" t="str">
+      <c r="B42" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C35" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="E35" s="11" t="s">
+      <c r="C42" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="E42" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="12">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="12">
         <f>DATE(2026,10,31)</f>
         <v>46326</v>
       </c>
-      <c r="B36" s="13" t="str">
-        <f t="shared" ref="B36:B63" si="1">TEXT($A36,"ddd")</f>
+      <c r="B43" s="13" t="str">
+        <f t="shared" ref="B43:B70" si="1">TEXT($A43,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C36" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="E36" s="11" t="s">
+      <c r="C43" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="E43" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="12">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" s="12">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
       </c>
-      <c r="B37" s="13" t="str">
+      <c r="B44" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Tue</v>
       </c>
-      <c r="C37" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="E37" s="11" t="s">
+      <c r="C44" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="E44" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="12">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="12">
         <f>DATE(2026,11,10)</f>
         <v>46336</v>
       </c>
-      <c r="B38" s="13" t="str">
+      <c r="B45" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Tue</v>
       </c>
-      <c r="C38" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="E38" s="11" t="s">
+      <c r="C45" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="E45" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="12">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" s="12">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B39" s="13" t="str">
+      <c r="B46" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Wed</v>
       </c>
-      <c r="C39" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="E39" s="11" t="s">
+      <c r="C46" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="E46" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="12">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
-      </c>
-      <c r="B40" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Fri</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="12">
-        <f>DATE(2027,1,30)</f>
-        <v>46417</v>
-      </c>
-      <c r="B41" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Sat</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="12">
-        <f>DATE(2027,2,18)</f>
-        <v>46436</v>
-      </c>
-      <c r="B42" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Thu</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="12">
-        <f>DATE(2027,2,19)</f>
-        <v>46437</v>
-      </c>
-      <c r="B43" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Fri</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="12">
-        <f>DATE(2027,3,19)</f>
-        <v>46465</v>
-      </c>
-      <c r="B44" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Fri</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="12">
-        <f>DATE(2027,3,25)</f>
-        <v>46471</v>
-      </c>
-      <c r="B45" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Thu</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="12">
-        <f>DATE(2027,4,3)</f>
-        <v>46480</v>
-      </c>
-      <c r="B46" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Sat</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="12">
-        <f>DATE(2027,4,9)</f>
-        <v>46486</v>
       </c>
       <c r="B47" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
-      <c r="C47" s="11" t="s">
-        <v>215</v>
+      <c r="C47" s="16" t="s">
+        <v>189</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="12">
-        <f>DATE(2027,5,19)</f>
-        <v>46526</v>
+        <f>DATE(2027,1,30)</f>
+        <v>46417</v>
       </c>
       <c r="B48" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Wed</v>
+        <v>Sat</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="12">
-        <f>DATE(2027,5,20)</f>
-        <v>46527</v>
+        <f>DATE(2027,2,18)</f>
+        <v>46436</v>
       </c>
       <c r="B49" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>169</v>
+        <v>239</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="12">
-        <f>DATE(2027,5,21)</f>
-        <v>46528</v>
+        <f>DATE(2027,2,19)</f>
+        <v>46437</v>
       </c>
       <c r="B50" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>171</v>
+        <v>240</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
+        <f>DATE(2027,3,19)</f>
+        <v>46465</v>
       </c>
       <c r="B51" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>202</v>
+        <v>241</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,3,25)</f>
+        <v>46471</v>
       </c>
       <c r="B52" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Fri</v>
+        <v>Thu</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,4,3)</f>
+        <v>46480</v>
       </c>
       <c r="B53" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Fri</v>
+        <v>Sat</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>199</v>
+        <v>243</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>131</v>
@@ -2491,18 +2558,18 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="12">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
+        <f>DATE(2027,4,9)</f>
+        <v>46486</v>
       </c>
       <c r="B54" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>131</v>
@@ -2510,18 +2577,18 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="12">
-        <f>DATE(2027,8,16)</f>
-        <v>46615</v>
+        <f>DATE(2027,5,19)</f>
+        <v>46526</v>
       </c>
       <c r="B55" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Mon</v>
+        <v>Wed</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>138</v>
@@ -2529,75 +2596,75 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="12">
-        <f>DATE(2027,8,20)</f>
-        <v>46619</v>
+        <f>DATE(2027,5,20)</f>
+        <v>46527</v>
       </c>
       <c r="B56" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Fri</v>
+        <v>Thu</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>205</v>
+        <v>245</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
+        <f>DATE(2027,5,21)</f>
+        <v>46528</v>
       </c>
       <c r="B57" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="12">
-        <f>DATE(2027,9,18)</f>
-        <v>46648</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B58" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Sat</v>
+        <v>Fri</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>206</v>
+        <v>247</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="12">
-        <f>DATE(2027,10,1)</f>
-        <v>46661</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B59" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>199</v>
+        <v>241</v>
       </c>
       <c r="E59" s="11" t="s">
         <v>131</v>
@@ -2605,18 +2672,18 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="12">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B60" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>199</v>
+        <v>241</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>131</v>
@@ -2624,18 +2691,18 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="12">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
       </c>
       <c r="B61" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>199</v>
+        <v>248</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>131</v>
@@ -2643,39 +2710,172 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="12">
+        <f>DATE(2027,8,16)</f>
+        <v>46615</v>
+      </c>
+      <c r="B62" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Mon</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" s="12">
+        <f>DATE(2027,8,20)</f>
+        <v>46619</v>
+      </c>
+      <c r="B63" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Fri</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" s="12">
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
+      </c>
+      <c r="B64" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Fri</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" s="12">
+        <f>DATE(2027,9,18)</f>
+        <v>46648</v>
+      </c>
+      <c r="B65" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Sat</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" s="12">
+        <f>DATE(2027,10,1)</f>
+        <v>46661</v>
+      </c>
+      <c r="B66" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Fri</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" s="12">
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
+      </c>
+      <c r="B67" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Fri</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" s="12">
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
+      </c>
+      <c r="B68" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Fri</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" s="12">
         <f>DATE(2027,11,26)</f>
         <v>46717</v>
       </c>
-      <c r="B62" s="13" t="str">
+      <c r="B69" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
-      <c r="C62" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="E62" s="11" t="s">
+      <c r="C69" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="E69" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="12">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" s="12">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B63" s="13" t="str">
+      <c r="B70" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
-      <c r="C63" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="D63" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="E63" s="11" t="s">
+      <c r="C70" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="E70" s="11" t="s">
         <v>138</v>
       </c>
     </row>
@@ -2920,7 +3120,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>66</v>
@@ -3087,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>22</v>
@@ -3358,10 +3558,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -3381,10 +3581,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -3402,16 +3602,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>66</v>
@@ -3425,10 +3625,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -3446,10 +3646,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
@@ -3469,10 +3669,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
@@ -3492,10 +3692,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -3515,10 +3715,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
@@ -3538,10 +3738,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
@@ -3561,10 +3761,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -3584,10 +3784,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -3607,10 +3807,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -3630,10 +3830,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -3653,10 +3853,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -3676,10 +3876,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
@@ -3699,10 +3899,10 @@
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
@@ -3722,10 +3922,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -3745,10 +3945,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
@@ -3768,10 +3968,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
@@ -3791,10 +3991,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
@@ -3814,10 +4014,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -3862,7 +4062,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -3870,15 +4070,15 @@
         <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="B4" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="312" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24497330-68BD-4E92-A7F8-C6174A469B21}"/>
+  <xr:revisionPtr revIDLastSave="314" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6075757D-6AC5-4560-B95E-12EF13BD4699}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -625,9 +625,6 @@
     <t>[Tentative] Hari Raya Puasa Ang Pao Distribution + Goodie Bag + Lunch</t>
   </si>
   <si>
-    <t>[Tentative] CSR Partnership – Corporate / School (Sunrise Walk)</t>
-  </si>
-  <si>
     <t>[Tentative] Vesak Day Fundraising (Ubin Thai) – Day 1</t>
   </si>
   <si>
@@ -857,6 +854,9 @@
   </si>
   <si>
     <t>南凤善堂中元会 (代表：梁天城,南凤福利协会员工，晓晓）。筹款活动包括义标。</t>
+  </si>
+  <si>
+    <t>[Tentative] CSR Partnership – Corporate / School (Charity Walk)</t>
   </si>
 </sst>
 </file>
@@ -1976,10 +1976,10 @@
         <v>Fri</v>
       </c>
       <c r="C23" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>227</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>228</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>131</v>
@@ -2014,10 +2014,10 @@
         <v>Sat</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>138</v>
@@ -2033,10 +2033,10 @@
         <v>Fri</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>138</v>
@@ -2052,10 +2052,10 @@
         <v>Sun</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>138</v>
@@ -2071,10 +2071,10 @@
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>138</v>
@@ -2090,10 +2090,10 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>138</v>
@@ -2109,10 +2109,10 @@
         <v>Tue</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>138</v>
@@ -2128,10 +2128,10 @@
         <v>Thu</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>138</v>
@@ -2147,10 +2147,10 @@
         <v>Thu</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>138</v>
@@ -2185,10 +2185,10 @@
         <v>Sat</v>
       </c>
       <c r="C34" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>263</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>264</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>138</v>
@@ -2223,10 +2223,10 @@
         <v>Mon</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>138</v>
@@ -2242,10 +2242,10 @@
         <v>Wed</v>
       </c>
       <c r="C37" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="D37" s="16" t="s">
         <v>266</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>267</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>138</v>
@@ -2253,12 +2253,12 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="12">
-        <f>DATE(2026,9,19)</f>
-        <v>46284</v>
+        <f>DATE(2026,9,20)</f>
+        <v>46285</v>
       </c>
       <c r="B38" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Sat</v>
+        <v>Sun</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>182</v>
@@ -2299,10 +2299,10 @@
         <v>Mon</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>138</v>
@@ -2319,10 +2319,10 @@
         <v>Tue</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E41" s="11" t="s">
         <v>138</v>
@@ -2338,10 +2338,10 @@
         <v>Wed</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>138</v>
@@ -2357,10 +2357,10 @@
         <v>Sat</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E43" s="11" t="s">
         <v>138</v>
@@ -2379,7 +2379,7 @@
         <v>188</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E44" s="11" t="s">
         <v>127</v>
@@ -2398,7 +2398,7 @@
         <v>187</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E45" s="11" t="s">
         <v>127</v>
@@ -2417,7 +2417,7 @@
         <v>186</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>138</v>
@@ -2436,7 +2436,7 @@
         <v>189</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E47" s="11" t="s">
         <v>125</v>
@@ -2455,7 +2455,7 @@
         <v>190</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E48" s="11" t="s">
         <v>125</v>
@@ -2474,7 +2474,7 @@
         <v>191</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>131</v>
@@ -2493,7 +2493,7 @@
         <v>192</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>131</v>
@@ -2512,7 +2512,7 @@
         <v>193</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>131</v>
@@ -2531,7 +2531,7 @@
         <v>194</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>127</v>
@@ -2546,11 +2546,11 @@
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="C53" s="11" t="s">
-        <v>195</v>
+      <c r="C53" s="16" t="s">
+        <v>272</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>131</v>
@@ -2569,7 +2569,7 @@
         <v>193</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>131</v>
@@ -2585,10 +2585,10 @@
         <v>Wed</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>138</v>
@@ -2604,10 +2604,10 @@
         <v>Thu</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>138</v>
@@ -2623,10 +2623,10 @@
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>138</v>
@@ -2642,10 +2642,10 @@
         <v>Fri</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>127</v>
@@ -2664,7 +2664,7 @@
         <v>193</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E59" s="11" t="s">
         <v>131</v>
@@ -2683,7 +2683,7 @@
         <v>193</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>131</v>
@@ -2699,10 +2699,10 @@
         <v>Fri</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>131</v>
@@ -2718,10 +2718,10 @@
         <v>Mon</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E62" s="11" t="s">
         <v>138</v>
@@ -2737,10 +2737,10 @@
         <v>Fri</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>131</v>
@@ -2759,7 +2759,7 @@
         <v>193</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E64" s="11" t="s">
         <v>131</v>
@@ -2775,10 +2775,10 @@
         <v>Sat</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>138</v>
@@ -2797,7 +2797,7 @@
         <v>193</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>131</v>
@@ -2816,7 +2816,7 @@
         <v>193</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E67" s="11" t="s">
         <v>131</v>
@@ -2835,7 +2835,7 @@
         <v>193</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E68" s="11" t="s">
         <v>131</v>
@@ -2854,7 +2854,7 @@
         <v>193</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>131</v>
@@ -2873,7 +2873,7 @@
         <v>186</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>138</v>
@@ -3120,7 +3120,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>66</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>205</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>206</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -3581,10 +3581,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>205</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>206</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -3602,16 +3602,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>205</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>206</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>66</v>
@@ -3625,10 +3625,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>205</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>206</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -3646,10 +3646,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>205</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>206</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
@@ -3669,10 +3669,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>207</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>208</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
@@ -3692,10 +3692,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>207</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>208</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>209</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>210</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
@@ -3738,10 +3738,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>209</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>210</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>211</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>212</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>211</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>212</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>211</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>212</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -3830,10 +3830,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>211</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>212</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>213</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>214</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -3876,10 +3876,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>213</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>214</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B17" s="16" t="s">
         <v>215</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>216</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>215</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>216</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -3945,10 +3945,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19" s="16" t="s">
         <v>215</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>216</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
@@ -3968,10 +3968,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
@@ -3991,10 +3991,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B21" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B22" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -4062,7 +4062,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -4070,15 +4070,15 @@
         <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B4" t="s">
         <v>221</v>
-      </c>
-      <c r="B4" t="s">
-        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="314" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6075757D-6AC5-4560-B95E-12EF13BD4699}"/>
+  <xr:revisionPtr revIDLastSave="317" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA4A2668-23A7-4D83-A4B2-010B9C6A062F}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -1051,7 +1051,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1093,8 +1093,7 @@
     <xf numFmtId="15" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1110,10 +1109,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2010,7 +2005,7 @@
         <v>46242</v>
       </c>
       <c r="B25" s="13" t="str">
-        <f>TEXT($A25,"ddd")</f>
+        <f t="shared" ref="B25:B33" si="1">TEXT($A25,"ddd")</f>
         <v>Sat</v>
       </c>
       <c r="C25" s="11" t="s">
@@ -2029,7 +2024,7 @@
         <v>46248</v>
       </c>
       <c r="B26" s="13" t="str">
-        <f>TEXT($A26,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
       <c r="C26" s="11" t="s">
@@ -2048,7 +2043,7 @@
         <v>46257</v>
       </c>
       <c r="B27" s="13" t="str">
-        <f>TEXT($A27,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Sun</v>
       </c>
       <c r="C27" s="11" t="s">
@@ -2067,13 +2062,13 @@
         <v>46260</v>
       </c>
       <c r="B28" s="13" t="str">
-        <f>TEXT($A28,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" t="s">
         <v>258</v>
       </c>
       <c r="E28" s="11" t="s">
@@ -2082,56 +2077,56 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="12">
+        <f>DATE(2026,8,28)</f>
+        <v>46262</v>
+      </c>
+      <c r="B29" s="13" t="str">
+        <f>TEXT($A29,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="12">
         <f>DATE(2026,8,29)</f>
         <v>46263</v>
       </c>
-      <c r="B29" s="13" t="str">
-        <f>TEXT($A29,"ddd")</f>
+      <c r="B30" s="13" t="str">
+        <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C30" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D30" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E30" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="12">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="12">
         <f>DATE(2026,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="B30" s="13" t="str">
-        <f>TEXT($A30,"ddd")</f>
+      <c r="B31" s="13" t="str">
+        <f t="shared" si="1"/>
         <v>Tue</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C31" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D31" s="16" t="s">
         <v>269</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="12">
-        <f>DATE(2026,9,3)</f>
-        <v>46268</v>
-      </c>
-      <c r="B31" s="13" t="str">
-        <f>TEXT($A31,"ddd")</f>
-        <v>Thu</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>260</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>138</v>
@@ -2143,14 +2138,14 @@
         <v>46268</v>
       </c>
       <c r="B32" s="13" t="str">
-        <f>TEXT($A32,"ddd")</f>
+        <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>270</v>
+        <v>256</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>260</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>138</v>
@@ -2158,21 +2153,21 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="12">
-        <f>DATE(2026,9,4)</f>
-        <v>46269</v>
+        <f>DATE(2026,9,3)</f>
+        <v>46268</v>
       </c>
       <c r="B33" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Fri</v>
+        <f t="shared" si="1"/>
+        <v>Thu</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>179</v>
+        <v>261</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>270</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -2353,7 +2348,7 @@
         <v>46326</v>
       </c>
       <c r="B43" s="13" t="str">
-        <f t="shared" ref="B43:B70" si="1">TEXT($A43,"ddd")</f>
+        <f t="shared" ref="B43:B70" si="2">TEXT($A43,"ddd")</f>
         <v>Sat</v>
       </c>
       <c r="C43" s="16" t="s">
@@ -2372,7 +2367,7 @@
         <v>46329</v>
       </c>
       <c r="B44" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
       <c r="C44" s="16" t="s">
@@ -2391,7 +2386,7 @@
         <v>46336</v>
       </c>
       <c r="B45" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
       <c r="C45" s="16" t="s">
@@ -2410,7 +2405,7 @@
         <v>46372</v>
       </c>
       <c r="B46" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
       <c r="C46" s="16" t="s">
@@ -2429,7 +2424,7 @@
         <v>46388</v>
       </c>
       <c r="B47" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C47" s="16" t="s">
@@ -2448,7 +2443,7 @@
         <v>46417</v>
       </c>
       <c r="B48" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
       <c r="C48" s="11" t="s">
@@ -2467,7 +2462,7 @@
         <v>46436</v>
       </c>
       <c r="B49" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
       <c r="C49" s="11" t="s">
@@ -2486,7 +2481,7 @@
         <v>46437</v>
       </c>
       <c r="B50" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C50" s="11" t="s">
@@ -2505,7 +2500,7 @@
         <v>46465</v>
       </c>
       <c r="B51" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C51" s="11" t="s">
@@ -2524,7 +2519,7 @@
         <v>46471</v>
       </c>
       <c r="B52" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
       <c r="C52" s="11" t="s">
@@ -2543,7 +2538,7 @@
         <v>46480</v>
       </c>
       <c r="B53" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
       <c r="C53" s="16" t="s">
@@ -2562,7 +2557,7 @@
         <v>46486</v>
       </c>
       <c r="B54" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C54" s="11" t="s">
@@ -2581,7 +2576,7 @@
         <v>46526</v>
       </c>
       <c r="B55" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
       <c r="C55" s="11" t="s">
@@ -2600,7 +2595,7 @@
         <v>46527</v>
       </c>
       <c r="B56" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
       <c r="C56" s="11" t="s">
@@ -2619,7 +2614,7 @@
         <v>46528</v>
       </c>
       <c r="B57" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
@@ -2638,7 +2633,7 @@
         <v>46535</v>
       </c>
       <c r="B58" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C58" s="11" t="s">
@@ -2657,7 +2652,7 @@
         <v>46549</v>
       </c>
       <c r="B59" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C59" s="11" t="s">
@@ -2676,7 +2671,7 @@
         <v>46577</v>
       </c>
       <c r="B60" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C60" s="11" t="s">
@@ -2695,7 +2690,7 @@
         <v>46598</v>
       </c>
       <c r="B61" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C61" s="11" t="s">
@@ -2714,7 +2709,7 @@
         <v>46615</v>
       </c>
       <c r="B62" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
       <c r="C62" s="11" t="s">
@@ -2733,7 +2728,7 @@
         <v>46619</v>
       </c>
       <c r="B63" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C63" s="11" t="s">
@@ -2752,7 +2747,7 @@
         <v>46640</v>
       </c>
       <c r="B64" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C64" s="11" t="s">
@@ -2771,7 +2766,7 @@
         <v>46648</v>
       </c>
       <c r="B65" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
       <c r="C65" s="11" t="s">
@@ -2790,7 +2785,7 @@
         <v>46661</v>
       </c>
       <c r="B66" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C66" s="11" t="s">
@@ -2809,7 +2804,7 @@
         <v>46675</v>
       </c>
       <c r="B67" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C67" s="11" t="s">
@@ -2828,7 +2823,7 @@
         <v>46703</v>
       </c>
       <c r="B68" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
@@ -2847,7 +2842,7 @@
         <v>46717</v>
       </c>
       <c r="B69" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
@@ -2866,7 +2861,7 @@
         <v>46737</v>
       </c>
       <c r="B70" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
       <c r="C70" s="11" t="s">
@@ -4098,6 +4093,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4338,15 +4342,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4359,6 +4354,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4375,12 +4378,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="317" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA4A2668-23A7-4D83-A4B2-010B9C6A062F}"/>
+  <xr:revisionPtr revIDLastSave="326" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F822D90-3F34-4875-98B2-711F8990CEDB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="275">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -857,6 +857,12 @@
   </si>
   <si>
     <t>[Tentative] CSR Partnership – Corporate / School (Charity Walk)</t>
+  </si>
+  <si>
+    <t>Chong Pang 61st National Day Dinner 2026, 7-10pm at Chong Pang 165 Hardcourt. (Attendance: William Tan, Bill Tan)</t>
+  </si>
+  <si>
+    <t>2026年中邦第61届国庆晚宴，晚上7点至10点。（代表：William Tan, Bill Tan）</t>
   </si>
 </sst>
 </file>
@@ -1535,7 +1541,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -1568,7 +1574,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="13" t="str">
-        <f t="shared" ref="B2:B42" si="0">TEXT($A2,"ddd")</f>
+        <f t="shared" ref="B2:B43" si="0">TEXT($A2,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -2005,7 +2011,7 @@
         <v>46242</v>
       </c>
       <c r="B25" s="13" t="str">
-        <f t="shared" ref="B25:B33" si="1">TEXT($A25,"ddd")</f>
+        <f t="shared" ref="B25:B34" si="1">TEXT($A25,"ddd")</f>
         <v>Sat</v>
       </c>
       <c r="C25" s="11" t="s">
@@ -2039,113 +2045,113 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="12">
+        <f>DATE(2026,8,15)</f>
+        <v>46249</v>
+      </c>
+      <c r="B27" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Sat</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="12">
         <f>DATE(2026,8,23)</f>
         <v>46257</v>
       </c>
-      <c r="B27" s="13" t="str">
+      <c r="B28" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sun</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C28" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D28" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E28" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="12">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="12">
         <f>DATE(2026,8,26)</f>
         <v>46260</v>
       </c>
-      <c r="B28" s="13" t="str">
+      <c r="B29" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Wed</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C29" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
         <v>258</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E29" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="12">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="12">
         <f>DATE(2026,8,28)</f>
         <v>46262</v>
       </c>
-      <c r="B29" s="13" t="str">
-        <f>TEXT($A29,"ddd")</f>
+      <c r="B30" s="13" t="str">
+        <f>TEXT($A30,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C30" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D30" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E30" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="12">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="12">
         <f>DATE(2026,8,29)</f>
         <v>46263</v>
       </c>
-      <c r="B30" s="13" t="str">
+      <c r="B31" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C31" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D31" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E31" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="12">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="12">
         <f>DATE(2026,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="B31" s="13" t="str">
+      <c r="B32" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Tue</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C32" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D32" s="16" t="s">
         <v>269</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="12">
-        <f>DATE(2026,9,3)</f>
-        <v>46268</v>
-      </c>
-      <c r="B32" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Thu</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>260</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>138</v>
@@ -2161,10 +2167,10 @@
         <v>Thu</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>270</v>
+        <v>256</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>260</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>138</v>
@@ -2172,18 +2178,18 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="12">
-        <f>DATE(2026,9,5)</f>
-        <v>46270</v>
+        <f>DATE(2026,9,3)</f>
+        <v>46268</v>
       </c>
       <c r="B34" s="13" t="str">
-        <f>TEXT($A34,"ddd")</f>
-        <v>Sat</v>
+        <f t="shared" si="1"/>
+        <v>Thu</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>263</v>
+        <v>261</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>270</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>138</v>
@@ -2195,205 +2201,205 @@
         <v>46270</v>
       </c>
       <c r="B35" s="13" t="str">
+        <f>TEXT($A35,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="12">
+        <f>DATE(2026,9,5)</f>
+        <v>46270</v>
+      </c>
+      <c r="B36" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C36" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D36" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E36" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="12">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="12">
         <f>DATE(2026,9,7)</f>
         <v>46272</v>
       </c>
-      <c r="B36" s="13" t="str">
-        <f>TEXT($A36,"ddd")</f>
+      <c r="B37" s="13" t="str">
+        <f>TEXT($A37,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C37" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D37" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E37" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="12">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="12">
         <f>DATE(2026,9,9)</f>
         <v>46274</v>
       </c>
-      <c r="B37" s="13" t="str">
-        <f>TEXT($A37,"ddd")</f>
+      <c r="B38" s="13" t="str">
+        <f>TEXT($A38,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C38" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D38" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E38" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="12">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="12">
         <f>DATE(2026,9,20)</f>
         <v>46285</v>
       </c>
-      <c r="B38" s="13" t="str">
+      <c r="B39" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C39" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D39" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E39" s="11" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="12">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="12">
         <f>DATE(2026,10,10)</f>
         <v>46305</v>
       </c>
-      <c r="B39" s="13" t="str">
+      <c r="B40" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C40" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D40" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E40" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="12">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="12">
         <f>DATE(2026,10,12)</f>
         <v>46307</v>
       </c>
-      <c r="B40" s="13" t="str">
+      <c r="B41" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C41" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D41" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E41" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G40" s="19"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="12">
+      <c r="G41" s="19"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="12">
         <f>DATE(2026,10,13)</f>
         <v>46308</v>
       </c>
-      <c r="B41" s="13" t="str">
+      <c r="B42" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C42" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D42" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E42" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" s="12">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="12">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
       </c>
-      <c r="B42" s="13" t="str">
+      <c r="B43" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C43" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D43" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E43" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="12">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" s="12">
         <f>DATE(2026,10,31)</f>
         <v>46326</v>
       </c>
-      <c r="B43" s="13" t="str">
-        <f t="shared" ref="B43:B70" si="2">TEXT($A43,"ddd")</f>
+      <c r="B44" s="13" t="str">
+        <f t="shared" ref="B44:B71" si="2">TEXT($A44,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C44" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D44" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E44" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="12">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="12">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
-      </c>
-      <c r="B44" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Tue</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="12">
-        <f>DATE(2026,11,10)</f>
-        <v>46336</v>
       </c>
       <c r="B45" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E45" s="11" t="s">
         <v>127</v>
@@ -2401,113 +2407,113 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="12">
+        <f>DATE(2026,11,10)</f>
+        <v>46336</v>
+      </c>
+      <c r="B46" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Tue</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="12">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B46" s="13" t="str">
+      <c r="B47" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C47" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D47" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E47" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="12">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B47" s="13" t="str">
+      <c r="B48" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C48" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D48" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E48" s="11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" s="12">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="12">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B48" s="13" t="str">
+      <c r="B49" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C49" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D49" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E49" s="11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="12">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="12">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B49" s="13" t="str">
+      <c r="B50" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C50" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D50" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E50" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="12">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="12">
         <f>DATE(2027,2,19)</f>
         <v>46437</v>
-      </c>
-      <c r="B50" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="12">
-        <f>DATE(2027,3,19)</f>
-        <v>46465</v>
       </c>
       <c r="B51" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>131</v>
@@ -2515,160 +2521,160 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="12">
+        <f>DATE(2027,3,19)</f>
+        <v>46465</v>
+      </c>
+      <c r="B52" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" s="12">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B52" s="13" t="str">
+      <c r="B53" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C53" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D53" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E53" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="12">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" s="12">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
       </c>
-      <c r="B53" s="13" t="str">
+      <c r="B54" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C54" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D54" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E54" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="12">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" s="12">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
       </c>
-      <c r="B54" s="13" t="str">
+      <c r="B55" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C55" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D55" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E55" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="12">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" s="12">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B55" s="13" t="str">
+      <c r="B56" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C56" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D56" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E56" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="12">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B56" s="13" t="str">
+      <c r="B57" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C57" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D57" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E57" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="12">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B57" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="E57" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
       </c>
       <c r="B58" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B59" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B60" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2686,18 +2692,18 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="12">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B61" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>131</v>
@@ -2705,56 +2711,56 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="12">
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
+      </c>
+      <c r="B62" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" s="12">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B62" s="13" t="str">
+      <c r="B63" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C63" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D63" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E63" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="12">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" s="12">
         <f>DATE(2027,8,20)</f>
         <v>46619</v>
-      </c>
-      <c r="B63" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A64" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
       </c>
       <c r="B64" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="E64" s="11" t="s">
         <v>131</v>
@@ -2762,46 +2768,46 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="12">
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
+      </c>
+      <c r="B65" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B65" s="13" t="str">
+      <c r="B66" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C66" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D66" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E66" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A66" s="12">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" s="12">
         <f>DATE(2027,10,1)</f>
         <v>46661</v>
-      </c>
-      <c r="B66" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A67" s="12">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
       </c>
       <c r="B67" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2819,8 +2825,8 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="12">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
       </c>
       <c r="B68" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2838,8 +2844,8 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
       </c>
       <c r="B69" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2857,20 +2863,39 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
+      </c>
+      <c r="B70" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" s="12">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B70" s="13" t="str">
+      <c r="B71" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C71" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="D70" s="16" t="s">
+      <c r="D71" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E71" s="11" t="s">
         <v>138</v>
       </c>
     </row>
@@ -4093,15 +4118,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4342,6 +4358,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4354,14 +4379,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4378,4 +4395,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="326" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F822D90-3F34-4875-98B2-711F8990CEDB}"/>
+  <xr:revisionPtr revIDLastSave="343" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F48E0D0-DFF4-4A2B-8F58-E6894380CD94}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="277">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -508,9 +508,6 @@
     <t>开斋节午宴</t>
   </si>
   <si>
-    <t>中医师健康讲座</t>
-  </si>
-  <si>
     <t>常年会员大会暨第十届管理委员会选举</t>
   </si>
   <si>
@@ -568,12 +565,6 @@
     <t>摩根士丹利企业社会责任活动暨寿像拍摄</t>
   </si>
   <si>
-    <t>Asiatic Fire System CSR National Day Celebration (150 pax)</t>
-  </si>
-  <si>
-    <t>Asiatic Fire System企业社会责任国庆庆祝会（150人）</t>
-  </si>
-  <si>
     <t>TFE Ration Distribution (140 pax)</t>
   </si>
   <si>
@@ -715,9 +706,6 @@
     <t>[Tentative] Nine Emperor Gods Festival Fundraiser – Day 3</t>
   </si>
   <si>
-    <t>Temple Dinner - 元龙聖庙（关帝聖君兴诸众神诞）(Attendance: Cher Kim Seah, Agnes, Bryan, Kathy, Jin Hoa)</t>
-  </si>
-  <si>
     <t>Naval Base Secondary School Outing</t>
   </si>
   <si>
@@ -793,24 +781,6 @@
     <t>[未确认] 慈善演唱会</t>
   </si>
   <si>
-    <t>Lunar July (ZhongYuan Festival) - Block 137 Yishun Ring Road (Attendance: Cher Kim Seah, Agnes, Yan Yi)</t>
-  </si>
-  <si>
-    <t>Lunar July (ZhongYuan Festival) - YS ONE, 1 Yishun Street 23 (Attendance: Bryan, 丽菁, 丽丝和先生)</t>
-  </si>
-  <si>
-    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 7 Gambas Crescent, ARK@Gambas Level 2 (Attendance: Doran, Pei Yuen, Agnes, 晓晓)</t>
-  </si>
-  <si>
-    <t>Lunar July (ZhongYuan Festival) - 724 Yishun Street 71 (Attendance: Chew Kim Cheong, Bryan, Kathy, 丽菁, 丽丝和先生)</t>
-  </si>
-  <si>
-    <t>Lunar July (ZhongYuan Festival) - 561 Yishun Ring Road (Attendance: Cher Kim Seah, Yan Yi, Pei Yuen, Agnes, Kathy)</t>
-  </si>
-  <si>
-    <t>Lunar July (ZhongYuan Festival) - Jurong Safra Pearl Garden Restaurant (Attendance: Neo Tian Siah, Kathy, Jin Hoa)</t>
-  </si>
-  <si>
     <t>YS ONE 中元会&amp; 歌台 (代表：Bryan, 丽菁, 丽丝和先生）</t>
   </si>
   <si>
@@ -823,21 +793,9 @@
     <t>山顶师城杨艺中元会 (代表：梁天城, Kathy, Jin Hoa）</t>
   </si>
   <si>
-    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Attendance: Cher Kim Seah, Pei Yuen, Yan Yi)</t>
-  </si>
-  <si>
-    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Attendance: Cher Kim Seah, Doran, Bryan)</t>
-  </si>
-  <si>
     <t>[日期未确认] 义顺镇商贩联合中元会歌台 (代表：徐金声, Doran, Bryan）</t>
   </si>
   <si>
-    <t xml:space="preserve">Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon (Attendance: Neo Tian Siah, NHWSS office staff, 5 front desk, 晓晓) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunar July (ZhongYuan Festival) - Blk 838 Yishun Street 81 (Attendance: Doran, Bryan, 丽菁, 丽丝和先生) </t>
-  </si>
-  <si>
     <t>义顺南旺村中元会 (代表：Doran, Bryan, 丽菁, 丽丝和先生）</t>
   </si>
   <si>
@@ -859,10 +817,58 @@
     <t>[Tentative] CSR Partnership – Corporate / School (Charity Walk)</t>
   </si>
   <si>
-    <t>Chong Pang 61st National Day Dinner 2026, 7-10pm at Chong Pang 165 Hardcourt. (Attendance: William Tan, Bill Tan)</t>
-  </si>
-  <si>
-    <t>2026年中邦第61届国庆晚宴，晚上7点至10点。（代表：William Tan, Bill Tan）</t>
+    <t>Asiatic Fire System CSR National Day Celebration (130 pax)</t>
+  </si>
+  <si>
+    <t>Asiatic Fire System企业社会责任国庆庆祝会（130人）</t>
+  </si>
+  <si>
+    <t>中医保健养生讲座 - 人老腿先衰</t>
+  </si>
+  <si>
+    <t>中医保健养生讲座 - 动养生 食养命</t>
+  </si>
+  <si>
+    <t>中医保健养生讲座 - 中药茶饮</t>
+  </si>
+  <si>
+    <t>2026年中邦第61届国庆晚宴，晚上7点至10点。（代表：陈浚纬, Bill Tan）</t>
+  </si>
+  <si>
+    <t>Temple Dinner - 元龙聖庙（关帝聖君兴诸众神诞）(Representative: Cher Kim Seah, Agnes, Bryan, Kathy, Jin Hoa)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - Block 137 Yishun Ring Road (Representative: Cher Kim Seah, Agnes, Yan Yi)</t>
+  </si>
+  <si>
+    <t>Chong Pang 61st National Day Dinner 2026, 7-10pm at Chong Pang 165 Hardcourt. (Representative: William Tan, Bill Tan)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - YS ONE, 1 Yishun Street 23 (Representative: Bryan, 丽菁, 丽丝和先生)</t>
+  </si>
+  <si>
+    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 7 Gambas Crescent, ARK@Gambas Level 2 (Representative: Doran, Pei Yuen, Agnes, 晓晓)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - 724 Yishun Street 71 (Representative: Chew Kim Cheong, Bryan, Kathy, 丽菁, 丽丝和先生)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - 561 Yishun Ring Road (Representative: Cher Kim Seah, Yan Yi, Pei Yuen, Agnes, Kathy)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - Jurong Safra Pearl Garden Restaurant (Representative: Neo Tian Siah, Kathy, Jin Hoa)</t>
+  </si>
+  <si>
+    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Pei Yuen, Yan Yi)</t>
+  </si>
+  <si>
+    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Doran, Bryan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon (Representative: Neo Tian Siah, NHWSS office staff, 5 front desk, 晓晓) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunar July (ZhongYuan Festival) - Blk 838 Yishun Street 81 (Representative: Doran, Bryan, 丽菁, 丽丝和先生) </t>
   </si>
 </sst>
 </file>
@@ -1541,7 +1547,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -1574,7 +1580,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="13" t="str">
-        <f t="shared" ref="B2:B43" si="0">TEXT($A2,"ddd")</f>
+        <f t="shared" ref="B2:B47" si="0">TEXT($A2,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -1751,8 +1757,8 @@
       <c r="C11" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>156</v>
+      <c r="D11" s="16" t="s">
+        <v>261</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>127</v>
@@ -1771,7 +1777,7 @@
         <v>137</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>136</v>
@@ -1787,10 +1793,10 @@
         <v>Mon</v>
       </c>
       <c r="C13" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>158</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>159</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>136</v>
@@ -1806,10 +1812,10 @@
         <v>Fri</v>
       </c>
       <c r="C14" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>160</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>161</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>138</v>
@@ -1825,10 +1831,10 @@
         <v>Sun</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>162</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>163</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>136</v>
@@ -1847,7 +1853,7 @@
         <v>139</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>127</v>
@@ -1863,10 +1869,10 @@
         <v>Fri</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>165</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>166</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>138</v>
@@ -1882,10 +1888,10 @@
         <v>Sat</v>
       </c>
       <c r="C18" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>167</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>168</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>138</v>
@@ -1901,10 +1907,10 @@
         <v>Sun</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>169</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>170</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>138</v>
@@ -1920,10 +1926,10 @@
         <v>Mon</v>
       </c>
       <c r="C20" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>171</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>172</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>138</v>
@@ -1931,208 +1937,208 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="12">
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
+      </c>
+      <c r="B21" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="12">
         <f>DATE(2026,6,13)</f>
         <v>46186</v>
       </c>
-      <c r="B21" s="13" t="str">
+      <c r="B22" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C22" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E21" s="11" t="s">
+      <c r="D22" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E22" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="12">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="12">
+        <f>DATE(2026,6,20)</f>
+        <v>46193</v>
+      </c>
+      <c r="B23" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="12">
         <f>DATE(2026,7,3)</f>
         <v>46206</v>
       </c>
-      <c r="B22" s="13" t="str">
+      <c r="B24" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C24" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="E22" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="12">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="12">
         <f>DATE(2026,7,24)</f>
         <v>46227</v>
       </c>
-      <c r="B23" s="13" t="str">
+      <c r="B25" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="E23" s="11" t="s">
+      <c r="C25" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="E25" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="12">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="12">
+        <f>DATE(2026,7,24)</f>
+        <v>46227</v>
+      </c>
+      <c r="B26" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="12">
+        <f>DATE(2026,7,25)</f>
+        <v>46228</v>
+      </c>
+      <c r="B27" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="12">
         <f>DATE(2026,8,1)</f>
         <v>46235</v>
       </c>
-      <c r="B24" s="13" t="str">
+      <c r="B28" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="E24" s="11" t="s">
+      <c r="C28" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="E28" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="12">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="12">
         <f>DATE(2026,8,8)</f>
         <v>46242</v>
       </c>
-      <c r="B25" s="13" t="str">
-        <f t="shared" ref="B25:B34" si="1">TEXT($A25,"ddd")</f>
+      <c r="B29" s="13" t="str">
+        <f t="shared" ref="B29:B38" si="1">TEXT($A29,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="E25" s="11" t="s">
+      <c r="C29" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="E29" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="12">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="12">
         <f>DATE(2026,8,14)</f>
         <v>46248</v>
       </c>
-      <c r="B26" s="13" t="str">
+      <c r="B30" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
-      <c r="C26" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="E26" s="11" t="s">
+      <c r="C30" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="12">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="12">
         <f>DATE(2026,8,15)</f>
         <v>46249</v>
-      </c>
-      <c r="B27" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Sat</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="12">
-        <f>DATE(2026,8,23)</f>
-        <v>46257</v>
-      </c>
-      <c r="B28" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Sun</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="12">
-        <f>DATE(2026,8,26)</f>
-        <v>46260</v>
-      </c>
-      <c r="B29" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Wed</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="D29" t="s">
-        <v>258</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="12">
-        <f>DATE(2026,8,28)</f>
-        <v>46262</v>
-      </c>
-      <c r="B30" s="13" t="str">
-        <f>TEXT($A30,"ddd")</f>
-        <v>Fri</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="12">
-        <f>DATE(2026,8,29)</f>
-        <v>46263</v>
       </c>
       <c r="B31" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>259</v>
+        <v>267</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>264</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>138</v>
@@ -2140,437 +2146,437 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="12">
+        <f>DATE(2026,8,23)</f>
+        <v>46257</v>
+      </c>
+      <c r="B32" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Sun</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="12">
+        <f>DATE(2026,8,26)</f>
+        <v>46260</v>
+      </c>
+      <c r="B33" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Wed</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D33" t="s">
+        <v>248</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="12">
+        <f>DATE(2026,8,28)</f>
+        <v>46262</v>
+      </c>
+      <c r="B34" s="13" t="str">
+        <f>TEXT($A34,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="12">
+        <f>DATE(2026,8,29)</f>
+        <v>46263</v>
+      </c>
+      <c r="B35" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Sat</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="12">
         <f>DATE(2026,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="B32" s="13" t="str">
+      <c r="B36" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Tue</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C36" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="D36" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="D32" s="16" t="s">
-        <v>269</v>
-      </c>
-      <c r="E32" s="11" t="s">
+      <c r="E36" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="12">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="12">
         <f>DATE(2026,9,3)</f>
         <v>46268</v>
       </c>
-      <c r="B33" s="13" t="str">
+      <c r="B37" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
-      <c r="C33" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="E33" s="11" t="s">
+      <c r="C37" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="E37" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="12">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="12">
         <f>DATE(2026,9,3)</f>
         <v>46268</v>
       </c>
-      <c r="B34" s="13" t="str">
+      <c r="B38" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
-      <c r="C34" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="E34" s="11" t="s">
+      <c r="C38" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="E38" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="12">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="12">
         <f>DATE(2026,9,5)</f>
         <v>46270</v>
       </c>
-      <c r="B35" s="13" t="str">
-        <f>TEXT($A35,"ddd")</f>
+      <c r="B39" s="13" t="str">
+        <f>TEXT($A39,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C35" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="E35" s="11" t="s">
+      <c r="C39" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="12">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="12">
         <f>DATE(2026,9,5)</f>
         <v>46270</v>
-      </c>
-      <c r="B36" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Sat</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="12">
-        <f>DATE(2026,9,7)</f>
-        <v>46272</v>
-      </c>
-      <c r="B37" s="13" t="str">
-        <f>TEXT($A37,"ddd")</f>
-        <v>Mon</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="12">
-        <f>DATE(2026,9,9)</f>
-        <v>46274</v>
-      </c>
-      <c r="B38" s="13" t="str">
-        <f>TEXT($A38,"ddd")</f>
-        <v>Wed</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="12">
-        <f>DATE(2026,9,20)</f>
-        <v>46285</v>
-      </c>
-      <c r="B39" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Sun</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="12">
-        <f>DATE(2026,10,10)</f>
-        <v>46305</v>
       </c>
       <c r="B40" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="12">
+        <f>DATE(2026,9,7)</f>
+        <v>46272</v>
+      </c>
+      <c r="B41" s="13" t="str">
+        <f>TEXT($A41,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="12">
+        <f>DATE(2026,9,9)</f>
+        <v>46274</v>
+      </c>
+      <c r="B42" s="13" t="str">
+        <f>TEXT($A42,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="12">
+        <f>DATE(2026,9,20)</f>
+        <v>46285</v>
+      </c>
+      <c r="B43" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" s="12">
+        <f>DATE(2026,10,10)</f>
+        <v>46305</v>
+      </c>
+      <c r="B44" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="12">
         <f>DATE(2026,10,12)</f>
         <v>46307</v>
       </c>
-      <c r="B41" s="13" t="str">
+      <c r="B45" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C41" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="E41" s="11" t="s">
+      <c r="C45" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E45" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G41" s="19"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" s="12">
+      <c r="G45" s="19"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" s="12">
         <f>DATE(2026,10,13)</f>
         <v>46308</v>
       </c>
-      <c r="B42" s="13" t="str">
+      <c r="B46" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C42" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="E42" s="11" t="s">
+      <c r="C46" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="E46" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="12">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="12">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
       </c>
-      <c r="B43" s="13" t="str">
+      <c r="B47" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C43" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="E43" s="11" t="s">
+      <c r="C47" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="E47" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="12">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" s="12">
         <f>DATE(2026,10,31)</f>
         <v>46326</v>
       </c>
-      <c r="B44" s="13" t="str">
-        <f t="shared" ref="B44:B71" si="2">TEXT($A44,"ddd")</f>
+      <c r="B48" s="13" t="str">
+        <f t="shared" ref="B48:B75" si="2">TEXT($A48,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C44" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="E44" s="11" t="s">
+      <c r="C48" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E48" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="12">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="12">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
       </c>
-      <c r="B45" s="13" t="str">
+      <c r="B49" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
-      <c r="C45" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="E45" s="11" t="s">
+      <c r="C49" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E49" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" s="12">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="12">
         <f>DATE(2026,11,10)</f>
         <v>46336</v>
       </c>
-      <c r="B46" s="13" t="str">
+      <c r="B50" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
-      <c r="C46" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="E46" s="11" t="s">
+      <c r="C50" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="E50" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="12">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="12">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B47" s="13" t="str">
+      <c r="B51" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C47" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="E47" s="11" t="s">
+      <c r="C51" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="E51" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" s="12">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
-      </c>
-      <c r="B48" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="12">
-        <f>DATE(2027,1,30)</f>
-        <v>46417</v>
-      </c>
-      <c r="B49" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Sat</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="12">
-        <f>DATE(2027,2,18)</f>
-        <v>46436</v>
-      </c>
-      <c r="B50" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="12">
-        <f>DATE(2027,2,19)</f>
-        <v>46437</v>
-      </c>
-      <c r="B51" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="12">
-        <f>DATE(2027,3,19)</f>
-        <v>46465</v>
       </c>
       <c r="B52" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C52" s="11" t="s">
-        <v>193</v>
+      <c r="C52" s="16" t="s">
+        <v>186</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="12">
-        <f>DATE(2027,3,25)</f>
-        <v>46471</v>
+        <f>DATE(2027,1,30)</f>
+        <v>46417</v>
       </c>
       <c r="B53" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Thu</v>
+        <v>Sat</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="12">
-        <f>DATE(2027,4,3)</f>
-        <v>46480</v>
+        <f>DATE(2027,2,18)</f>
+        <v>46436</v>
       </c>
       <c r="B54" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Sat</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>272</v>
+        <v>Thu</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>188</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>131</v>
@@ -2578,18 +2584,18 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="12">
-        <f>DATE(2027,4,9)</f>
-        <v>46486</v>
+        <f>DATE(2027,2,19)</f>
+        <v>46437</v>
       </c>
       <c r="B55" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>131</v>
@@ -2597,107 +2603,107 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="12">
-        <f>DATE(2027,5,19)</f>
-        <v>46526</v>
+        <f>DATE(2027,3,19)</f>
+        <v>46465</v>
       </c>
       <c r="B56" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Wed</v>
+        <v>Fri</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="12">
-        <f>DATE(2027,5,20)</f>
-        <v>46527</v>
+        <f>DATE(2027,3,25)</f>
+        <v>46471</v>
       </c>
       <c r="B57" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="12">
-        <f>DATE(2027,5,21)</f>
-        <v>46528</v>
+        <f>DATE(2027,4,3)</f>
+        <v>46480</v>
       </c>
       <c r="B58" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>197</v>
+        <v>Sat</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>258</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
+        <f>DATE(2027,4,9)</f>
+        <v>46486</v>
       </c>
       <c r="B59" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,5,19)</f>
+        <v>46526</v>
       </c>
       <c r="B60" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Wed</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,5,20)</f>
+        <v>46527</v>
       </c>
       <c r="B61" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Thu</v>
       </c>
       <c r="C61" s="11" t="s">
         <v>193</v>
@@ -2706,61 +2712,61 @@
         <v>240</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="12">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
+        <f>DATE(2027,5,21)</f>
+        <v>46528</v>
       </c>
       <c r="B62" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="12">
-        <f>DATE(2027,8,16)</f>
-        <v>46615</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B63" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Mon</v>
+        <v>Fri</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="12">
-        <f>DATE(2027,8,20)</f>
-        <v>46619</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B64" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="E64" s="11" t="s">
         <v>131</v>
@@ -2768,18 +2774,18 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B65" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>131</v>
@@ -2787,56 +2793,56 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="12">
-        <f>DATE(2027,9,18)</f>
-        <v>46648</v>
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
       </c>
       <c r="B66" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Sat</v>
+        <v>Fri</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="12">
-        <f>DATE(2027,10,1)</f>
-        <v>46661</v>
+        <f>DATE(2027,8,16)</f>
+        <v>46615</v>
       </c>
       <c r="B67" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Mon</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="12">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
+        <f>DATE(2027,8,20)</f>
+        <v>46619</v>
       </c>
       <c r="B68" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E68" s="11" t="s">
         <v>131</v>
@@ -2844,18 +2850,18 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="12">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
       </c>
       <c r="B69" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>131</v>
@@ -2863,39 +2869,115 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
+        <f>DATE(2027,9,18)</f>
+        <v>46648</v>
+      </c>
+      <c r="B70" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Sat</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" s="12">
+        <f>DATE(2027,10,1)</f>
+        <v>46661</v>
+      </c>
+      <c r="B71" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" s="12">
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
+      </c>
+      <c r="B72" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" s="12">
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
+      </c>
+      <c r="B73" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" s="12">
         <f>DATE(2027,11,26)</f>
         <v>46717</v>
       </c>
-      <c r="B70" s="13" t="str">
+      <c r="B74" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C70" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="D70" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="E70" s="11" t="s">
+      <c r="C74" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E74" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A71" s="12">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" s="12">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B71" s="13" t="str">
+      <c r="B75" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C71" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="E71" s="11" t="s">
+      <c r="C75" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D75" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="E75" s="11" t="s">
         <v>138</v>
       </c>
     </row>
@@ -3140,7 +3222,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>66</v>
@@ -3307,7 +3389,7 @@
         <v>25</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>22</v>
@@ -3578,10 +3660,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -3601,10 +3683,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -3622,16 +3704,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>66</v>
@@ -3645,10 +3727,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -3666,10 +3748,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
@@ -3689,10 +3771,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
@@ -3712,10 +3794,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -3735,10 +3817,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
@@ -3758,10 +3840,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
@@ -3781,10 +3863,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -3804,10 +3886,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -3827,10 +3909,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -3850,10 +3932,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -3873,10 +3955,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -3896,10 +3978,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
@@ -3919,10 +4001,10 @@
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
@@ -3942,10 +4024,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -3965,10 +4047,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
@@ -3988,10 +4070,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
@@ -4011,10 +4093,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
@@ -4034,10 +4116,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -4082,7 +4164,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -4090,15 +4172,15 @@
         <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -4118,6 +4200,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4358,15 +4449,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4379,6 +4461,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4395,12 +4485,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="343" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F48E0D0-DFF4-4A2B-8F58-E6894380CD94}"/>
+  <xr:revisionPtr revIDLastSave="350" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D1BB849-EA97-41A0-BB2F-E31F7080BAAB}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -835,12 +835,6 @@
     <t>2026年中邦第61届国庆晚宴，晚上7点至10点。（代表：陈浚纬, Bill Tan）</t>
   </si>
   <si>
-    <t>Temple Dinner - 元龙聖庙（关帝聖君兴诸众神诞）(Representative: Cher Kim Seah, Agnes, Bryan, Kathy, Jin Hoa)</t>
-  </si>
-  <si>
-    <t>Lunar July (ZhongYuan Festival) - Block 137 Yishun Ring Road (Representative: Cher Kim Seah, Agnes, Yan Yi)</t>
-  </si>
-  <si>
     <t>Chong Pang 61st National Day Dinner 2026, 7-10pm at Chong Pang 165 Hardcourt. (Representative: William Tan, Bill Tan)</t>
   </si>
   <si>
@@ -853,22 +847,28 @@
     <t>Lunar July (ZhongYuan Festival) - 724 Yishun Street 71 (Representative: Chew Kim Cheong, Bryan, Kathy, 丽菁, 丽丝和先生)</t>
   </si>
   <si>
-    <t>Lunar July (ZhongYuan Festival) - 561 Yishun Ring Road (Representative: Cher Kim Seah, Yan Yi, Pei Yuen, Agnes, Kathy)</t>
-  </si>
-  <si>
     <t>Lunar July (ZhongYuan Festival) - Jurong Safra Pearl Garden Restaurant (Representative: Neo Tian Siah, Kathy, Jin Hoa)</t>
   </si>
   <si>
-    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Pei Yuen, Yan Yi)</t>
-  </si>
-  <si>
     <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Doran, Bryan)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon (Representative: Neo Tian Siah, NHWSS office staff, 5 front desk, 晓晓) </t>
-  </si>
-  <si>
     <t xml:space="preserve">Lunar July (ZhongYuan Festival) - Blk 838 Yishun Street 81 (Representative: Doran, Bryan, 丽菁, 丽丝和先生) </t>
+  </si>
+  <si>
+    <t>Temple Dinner - 元龙聖庙（关帝聖君兴诸众神诞）(Representative: Cher Kim Seah, Agnes, Bryan, Kathy, Jin Hoa). Auction item included.</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - Block 137 Yishun Ring Road (Representative: Cher Kim Seah, Agnes, Yan Yi). Auction item included.</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - 561 Yishun Ring Road (Representative: Cher Kim Seah, Yan Yi, Pei Yuen, Agnes, Kathy). Auction item included.</t>
+  </si>
+  <si>
+    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Pei Yuen, Yan Yi). Auction item included.</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon (Representative: Neo Tian Siah, NHWSS office staff, 5 front desk, 晓晓). Auction item included.</t>
   </si>
 </sst>
 </file>
@@ -1552,7 +1552,7 @@
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="72.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="114.7265625" customWidth="1"/>
     <col min="4" max="4" width="59.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
   </cols>
@@ -2097,7 +2097,7 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>253</v>
@@ -2116,7 +2116,7 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="D30" s="16" t="s">
         <v>254</v>
@@ -2135,7 +2135,7 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>264</v>
@@ -2154,7 +2154,7 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>247</v>
@@ -2173,7 +2173,7 @@
         <v>Wed</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D33" t="s">
         <v>248</v>
@@ -2211,7 +2211,7 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>249</v>
@@ -2230,7 +2230,7 @@
         <v>Tue</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D36" s="16" t="s">
         <v>255</v>
@@ -2249,7 +2249,7 @@
         <v>Thu</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>250</v>
@@ -2268,7 +2268,7 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D38" s="16" t="s">
         <v>256</v>
@@ -2287,7 +2287,7 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>251</v>
@@ -2325,7 +2325,7 @@
         <v>Mon</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D41" s="16" t="s">
         <v>257</v>
@@ -2344,7 +2344,7 @@
         <v>Wed</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="D42" s="16" t="s">
         <v>252</v>
@@ -4200,15 +4200,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4449,6 +4440,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4461,14 +4461,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4485,4 +4477,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="350" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D1BB849-EA97-41A0-BB2F-E31F7080BAAB}"/>
+  <xr:revisionPtr revIDLastSave="365" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A000803B-3E5B-4E58-A395-2D2B786D9617}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="279">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -784,30 +784,15 @@
     <t>YS ONE 中元会&amp; 歌台 (代表：Bryan, 丽菁, 丽丝和先生）</t>
   </si>
   <si>
-    <t>[日期未确认] 方舟@岗巴士中元会 (代表：Doran, Pei Yuen, Agnes, 晓晓）</t>
-  </si>
-  <si>
-    <t>717 商店中元会 (代表：周锦昌, Bryan, Kathy, 丽菁, 丽丝和先生）</t>
-  </si>
-  <si>
     <t>山顶师城杨艺中元会 (代表：梁天城, Kathy, Jin Hoa）</t>
   </si>
   <si>
-    <t>[日期未确认] 义顺镇商贩联合中元会歌台 (代表：徐金声, Doran, Bryan）</t>
-  </si>
-  <si>
-    <t>义顺南旺村中元会 (代表：Doran, Bryan, 丽菁, 丽丝和先生）</t>
-  </si>
-  <si>
     <t>元龙聖庙（关帝聖君兴诸众神诞）(代表：徐金声, Agnes, Bryan, Kathy, Jin Hoa）。筹款活动包括义标。</t>
   </si>
   <si>
     <t>大牌137中元会 (代表：徐金声,Agnes, Yan Yi）。筹款活动包括义标。</t>
   </si>
   <si>
-    <t>华报善堂中元会 (代表：徐金声, Yan Yi, Pei Yuen, Agnes, Kathy）。筹款活动包括义标。</t>
-  </si>
-  <si>
     <t>[日期未确认] 义顺镇商贩联合中元会 (代表：徐金声, Pei Yuen, Yan Yi）。筹款活动包括义标。</t>
   </si>
   <si>
@@ -841,18 +826,9 @@
     <t>Lunar July (ZhongYuan Festival) - YS ONE, 1 Yishun Street 23 (Representative: Bryan, 丽菁, 丽丝和先生)</t>
   </si>
   <si>
-    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 7 Gambas Crescent, ARK@Gambas Level 2 (Representative: Doran, Pei Yuen, Agnes, 晓晓)</t>
-  </si>
-  <si>
-    <t>Lunar July (ZhongYuan Festival) - 724 Yishun Street 71 (Representative: Chew Kim Cheong, Bryan, Kathy, 丽菁, 丽丝和先生)</t>
-  </si>
-  <si>
     <t>Lunar July (ZhongYuan Festival) - Jurong Safra Pearl Garden Restaurant (Representative: Neo Tian Siah, Kathy, Jin Hoa)</t>
   </si>
   <si>
-    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Doran, Bryan)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lunar July (ZhongYuan Festival) - Blk 838 Yishun Street 81 (Representative: Doran, Bryan, 丽菁, 丽丝和先生) </t>
   </si>
   <si>
@@ -862,13 +838,43 @@
     <t>Lunar July (ZhongYuan Festival) - Block 137 Yishun Ring Road (Representative: Cher Kim Seah, Agnes, Yan Yi). Auction item included.</t>
   </si>
   <si>
-    <t>Lunar July (ZhongYuan Festival) - 561 Yishun Ring Road (Representative: Cher Kim Seah, Yan Yi, Pei Yuen, Agnes, Kathy). Auction item included.</t>
-  </si>
-  <si>
     <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Pei Yuen, Yan Yi). Auction item included.</t>
   </si>
   <si>
     <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon (Representative: Neo Tian Siah, NHWSS office staff, 5 front desk, 晓晓). Auction item included.</t>
+  </si>
+  <si>
+    <t>南凤善堂中元会.</t>
+  </si>
+  <si>
+    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 7 Gambas Crescent, ARK@Gambas Level 2 (Representative: Doran, Pei Yuen, Chi Hwee, 晓晓)</t>
+  </si>
+  <si>
+    <t>[日期未确认] 方舟@岗巴士中元会 (代表：Doran, Pei Yuen, Chee Hwee, 晓晓）</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - 724 Yishun Street 71 (Representative: Chew Kim Cheong, Kathy, 丽菁, 丽丝和先生)</t>
+  </si>
+  <si>
+    <t>717 商店中元会 (代表：周锦昌, Kathy, 丽菁, 丽丝和先生）</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - 561 Yishun Ring Road (Representative: Cher Kim Seah,Chi Hwee, Yan Yi, Agnes). Auction item included.</t>
+  </si>
+  <si>
+    <t>华报善堂中元会 (代表：徐金声, Chi Hwee, Yan Yi, Agnes, Jin Hoa）。筹款活动包括义标。</t>
+  </si>
+  <si>
+    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Doran, Pei Yuen)</t>
+  </si>
+  <si>
+    <t>[日期未确认] 义顺镇商贩联合中元会歌台 (代表：徐金声, Doran, Pei Yuen）</t>
+  </si>
+  <si>
+    <t>义顺南旺村中元会。普施祭祖法会。 (代表：Doran, Bryan, 丽菁, 丽丝和先生）</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon Temple Prayers</t>
   </si>
 </sst>
 </file>
@@ -1547,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -1580,7 +1586,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="13" t="str">
-        <f t="shared" ref="B2:B47" si="0">TEXT($A2,"ddd")</f>
+        <f t="shared" ref="B2:B48" si="0">TEXT($A2,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -1758,7 +1764,7 @@
         <v>135</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>127</v>
@@ -1948,7 +1954,7 @@
         <v>135</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>127</v>
@@ -1986,7 +1992,7 @@
         <v>135</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>127</v>
@@ -2043,7 +2049,7 @@
         <v>135</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>127</v>
@@ -2062,7 +2068,7 @@
         <v>135</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>127</v>
@@ -2078,10 +2084,10 @@
         <v>Sat</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>131</v>
@@ -2097,10 +2103,10 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>138</v>
@@ -2116,10 +2122,10 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>138</v>
@@ -2135,10 +2141,10 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>138</v>
@@ -2154,7 +2160,7 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>247</v>
@@ -2173,10 +2179,10 @@
         <v>Wed</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D33" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>138</v>
@@ -2211,10 +2217,10 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>138</v>
@@ -2230,10 +2236,10 @@
         <v>Tue</v>
       </c>
       <c r="C36" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="D36" s="16" t="s">
         <v>274</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>255</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>138</v>
@@ -2249,10 +2255,10 @@
         <v>Thu</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>138</v>
@@ -2268,10 +2274,10 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>138</v>
@@ -2287,10 +2293,10 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>138</v>
@@ -2325,10 +2331,10 @@
         <v>Mon</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E41" s="11" t="s">
         <v>138</v>
@@ -2336,171 +2342,171 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="12">
+        <f>DATE(2026,9,8)</f>
+        <v>46273</v>
+      </c>
+      <c r="B42" s="13" t="str">
+        <f>TEXT($A42,"ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="12">
         <f>DATE(2026,9,9)</f>
         <v>46274</v>
       </c>
-      <c r="B42" s="13" t="str">
-        <f>TEXT($A42,"ddd")</f>
+      <c r="B43" s="13" t="str">
+        <f>TEXT($A43,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C42" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="E42" s="11" t="s">
+      <c r="C43" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="E43" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="12">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" s="12">
         <f>DATE(2026,9,20)</f>
         <v>46285</v>
       </c>
-      <c r="B43" s="13" t="str">
+      <c r="B44" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C44" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D44" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E44" s="11" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="12">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="12">
         <f>DATE(2026,10,10)</f>
         <v>46305</v>
       </c>
-      <c r="B44" s="13" t="str">
+      <c r="B45" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C45" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D45" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E45" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="12">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" s="12">
         <f>DATE(2026,10,12)</f>
         <v>46307</v>
       </c>
-      <c r="B45" s="13" t="str">
+      <c r="B46" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C46" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D46" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E46" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G45" s="19"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" s="12">
+      <c r="G46" s="19"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="12">
         <f>DATE(2026,10,13)</f>
         <v>46308</v>
       </c>
-      <c r="B46" s="13" t="str">
+      <c r="B47" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C47" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D47" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E47" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="12">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" s="12">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
       </c>
-      <c r="B47" s="13" t="str">
+      <c r="B48" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C48" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D48" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E48" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" s="12">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="12">
         <f>DATE(2026,10,31)</f>
         <v>46326</v>
       </c>
-      <c r="B48" s="13" t="str">
-        <f t="shared" ref="B48:B75" si="2">TEXT($A48,"ddd")</f>
+      <c r="B49" s="13" t="str">
+        <f t="shared" ref="B49:B76" si="2">TEXT($A49,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C49" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D49" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E49" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="12">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="12">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
-      </c>
-      <c r="B49" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Tue</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="12">
-        <f>DATE(2026,11,10)</f>
-        <v>46336</v>
       </c>
       <c r="B50" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>127</v>
@@ -2508,113 +2514,113 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="12">
+        <f>DATE(2026,11,10)</f>
+        <v>46336</v>
+      </c>
+      <c r="B51" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Tue</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" s="12">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B51" s="13" t="str">
+      <c r="B52" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C52" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D52" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E52" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="12">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B52" s="13" t="str">
+      <c r="B53" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C53" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D53" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E53" s="11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="12">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" s="12">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B53" s="13" t="str">
+      <c r="B54" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C54" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D54" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E54" s="11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="12">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" s="12">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B54" s="13" t="str">
+      <c r="B55" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C55" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D55" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E55" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="12">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" s="12">
         <f>DATE(2027,2,19)</f>
         <v>46437</v>
-      </c>
-      <c r="B55" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="12">
-        <f>DATE(2027,3,19)</f>
-        <v>46465</v>
       </c>
       <c r="B56" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>131</v>
@@ -2622,160 +2628,160 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="12">
+        <f>DATE(2027,3,19)</f>
+        <v>46465</v>
+      </c>
+      <c r="B57" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" s="12">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B57" s="13" t="str">
+      <c r="B58" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C58" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D58" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E58" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="12">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" s="12">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
       </c>
-      <c r="B58" s="13" t="str">
+      <c r="B59" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C58" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="D58" s="11" t="s">
+      <c r="C59" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="D59" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E59" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="12">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" s="12">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
       </c>
-      <c r="B59" s="13" t="str">
+      <c r="B60" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C60" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D60" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E60" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="12">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" s="12">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B60" s="13" t="str">
+      <c r="B61" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C61" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D61" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E61" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" s="12">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B61" s="13" t="str">
+      <c r="B62" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C62" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D62" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E62" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" s="12">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B62" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="E62" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
       </c>
       <c r="B63" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B64" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B65" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2793,18 +2799,18 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="12">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B66" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>131</v>
@@ -2812,56 +2818,56 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="12">
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
+      </c>
+      <c r="B67" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" s="12">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B67" s="13" t="str">
+      <c r="B68" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C68" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D68" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="E67" s="11" t="s">
+      <c r="E68" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A68" s="12">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" s="12">
         <f>DATE(2027,8,20)</f>
         <v>46619</v>
-      </c>
-      <c r="B68" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="D68" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A69" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
       </c>
       <c r="B69" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>131</v>
@@ -2869,46 +2875,46 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
+      </c>
+      <c r="B70" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B70" s="13" t="str">
+      <c r="B71" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C71" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D71" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E71" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A71" s="12">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" s="12">
         <f>DATE(2027,10,1)</f>
         <v>46661</v>
-      </c>
-      <c r="B71" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="D71" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="E71" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A72" s="12">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
       </c>
       <c r="B72" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2926,8 +2932,8 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="12">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
       </c>
       <c r="B73" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2945,8 +2951,8 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
       </c>
       <c r="B74" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2964,20 +2970,39 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="12">
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
+      </c>
+      <c r="B75" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" s="12">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B75" s="13" t="str">
+      <c r="B76" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C76" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="D75" s="16" t="s">
+      <c r="D76" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="E76" s="11" t="s">
         <v>138</v>
       </c>
     </row>
@@ -4189,17 +4214,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4440,6 +4454,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -4450,17 +4475,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4479,6 +4493,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="365" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A000803B-3E5B-4E58-A395-2D2B786D9617}"/>
+  <xr:revisionPtr revIDLastSave="369" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{304DD191-79E1-48A8-A0E7-7F5071D74014}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -844,9 +844,6 @@
     <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon (Representative: Neo Tian Siah, NHWSS office staff, 5 front desk, 晓晓). Auction item included.</t>
   </si>
   <si>
-    <t>南凤善堂中元会.</t>
-  </si>
-  <si>
     <t>[Tentative date] Lunar July (ZhongYuan Festival) - 7 Gambas Crescent, ARK@Gambas Level 2 (Representative: Doran, Pei Yuen, Chi Hwee, 晓晓)</t>
   </si>
   <si>
@@ -871,10 +868,13 @@
     <t>[日期未确认] 义顺镇商贩联合中元会歌台 (代表：徐金声, Doran, Pei Yuen）</t>
   </si>
   <si>
-    <t>义顺南旺村中元会。普施祭祖法会。 (代表：Doran, Bryan, 丽菁, 丽丝和先生）</t>
-  </si>
-  <si>
-    <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon Temple Prayers</t>
+    <t>义顺南旺村中元会。(代表：Doran, Bryan, 丽菁, 丽丝和先生）</t>
+  </si>
+  <si>
+    <t>南凤善堂中元会晚宴（200人）</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon dinner (200 pax)</t>
   </si>
 </sst>
 </file>
@@ -2179,10 +2179,10 @@
         <v>Wed</v>
       </c>
       <c r="C33" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="D33" t="s">
         <v>269</v>
-      </c>
-      <c r="D33" t="s">
-        <v>270</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>138</v>
@@ -2217,10 +2217,10 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="D35" s="11" t="s">
         <v>271</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>272</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>138</v>
@@ -2236,10 +2236,10 @@
         <v>Tue</v>
       </c>
       <c r="C36" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="D36" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>274</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>138</v>
@@ -2293,10 +2293,10 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>275</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>276</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>138</v>
@@ -2353,7 +2353,7 @@
         <v>278</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>138</v>
@@ -2372,7 +2372,7 @@
         <v>263</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E43" s="11" t="s">
         <v>138</v>
@@ -4214,6 +4214,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4454,27 +4474,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4491,23 +4510,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="369" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{304DD191-79E1-48A8-A0E7-7F5071D74014}"/>
+  <xr:revisionPtr revIDLastSave="377" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7398130-92DE-41B3-AA40-FF7E1B9DE9CE}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,9 @@
     <sheet name="4_SubCommittees" sheetId="4" r:id="rId5"/>
     <sheet name="Info" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$77</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="281">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -875,6 +878,12 @@
   </si>
   <si>
     <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon dinner (200 pax)</t>
+  </si>
+  <si>
+    <t>咖啡老友，大牌110咖啡店，早上8点30分至9点30分</t>
+  </si>
+  <si>
+    <t>Kopi Kaki session at Blk 110 coffee shop, 830am to 930am</t>
   </si>
 </sst>
 </file>
@@ -1553,7 +1562,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G76"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -1586,7 +1596,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="13" t="str">
-        <f t="shared" ref="B2:B48" si="0">TEXT($A2,"ddd")</f>
+        <f t="shared" ref="B2:B49" si="0">TEXT($A2,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -2095,170 +2105,170 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="12">
+        <f>DATE(2026,8,5)</f>
+        <v>46239</v>
+      </c>
+      <c r="B29" s="13" t="str">
+        <f t="shared" ref="B29:B39" si="1">TEXT($A29,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="12">
         <f>DATE(2026,8,8)</f>
         <v>46242</v>
       </c>
-      <c r="B29" s="13" t="str">
-        <f t="shared" ref="B29:B38" si="1">TEXT($A29,"ddd")</f>
+      <c r="B30" s="13" t="str">
+        <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C30" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D30" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E30" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="12">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="12">
         <f>DATE(2026,8,14)</f>
         <v>46248</v>
       </c>
-      <c r="B30" s="13" t="str">
+      <c r="B31" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C31" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D31" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E31" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="12">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="12">
         <f>DATE(2026,8,15)</f>
         <v>46249</v>
       </c>
-      <c r="B31" s="13" t="str">
+      <c r="B32" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C32" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D32" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E32" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="12">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="12">
         <f>DATE(2026,8,23)</f>
         <v>46257</v>
       </c>
-      <c r="B32" s="13" t="str">
+      <c r="B33" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sun</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C33" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D33" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E33" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="12">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="12">
         <f>DATE(2026,8,26)</f>
         <v>46260</v>
       </c>
-      <c r="B33" s="13" t="str">
+      <c r="B34" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Wed</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C34" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>269</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E34" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="12">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="12">
         <f>DATE(2026,8,28)</f>
         <v>46262</v>
       </c>
-      <c r="B34" s="13" t="str">
-        <f>TEXT($A34,"ddd")</f>
+      <c r="B35" s="13" t="str">
+        <f>TEXT($A35,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C35" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D35" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E35" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="12">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="12">
         <f>DATE(2026,8,29)</f>
         <v>46263</v>
       </c>
-      <c r="B35" s="13" t="str">
+      <c r="B36" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C36" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D36" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E36" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="12">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="12">
         <f>DATE(2026,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="B36" s="13" t="str">
+      <c r="B37" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Tue</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C37" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D37" s="16" t="s">
         <v>273</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="12">
-        <f>DATE(2026,9,3)</f>
-        <v>46268</v>
-      </c>
-      <c r="B37" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Thu</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>248</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>138</v>
@@ -2274,10 +2284,10 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>251</v>
+        <v>262</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>248</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>138</v>
@@ -2285,18 +2295,18 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="12">
-        <f>DATE(2026,9,5)</f>
-        <v>46270</v>
+        <f>DATE(2026,9,3)</f>
+        <v>46268</v>
       </c>
       <c r="B39" s="13" t="str">
-        <f>TEXT($A39,"ddd")</f>
-        <v>Sat</v>
+        <f t="shared" si="1"/>
+        <v>Thu</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>275</v>
+        <v>266</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>251</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>138</v>
@@ -2308,224 +2318,224 @@
         <v>46270</v>
       </c>
       <c r="B40" s="13" t="str">
+        <f>TEXT($A40,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="12">
+        <f>DATE(2026,9,5)</f>
+        <v>46270</v>
+      </c>
+      <c r="B41" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C41" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D41" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E41" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="12">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="12">
         <f>DATE(2026,9,7)</f>
         <v>46272</v>
       </c>
-      <c r="B41" s="13" t="str">
-        <f>TEXT($A41,"ddd")</f>
+      <c r="B42" s="13" t="str">
+        <f>TEXT($A42,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C42" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D42" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E42" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" s="12">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="12">
         <f>DATE(2026,9,8)</f>
         <v>46273</v>
       </c>
-      <c r="B42" s="13" t="str">
-        <f>TEXT($A42,"ddd")</f>
+      <c r="B43" s="13" t="str">
+        <f>TEXT($A43,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C43" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D43" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E43" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="12">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" s="12">
         <f>DATE(2026,9,9)</f>
         <v>46274</v>
       </c>
-      <c r="B43" s="13" t="str">
-        <f>TEXT($A43,"ddd")</f>
+      <c r="B44" s="13" t="str">
+        <f>TEXT($A44,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C44" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D44" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E44" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="12">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="12">
         <f>DATE(2026,9,20)</f>
         <v>46285</v>
       </c>
-      <c r="B44" s="13" t="str">
+      <c r="B45" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C45" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D45" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E45" s="11" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="12">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" s="12">
         <f>DATE(2026,10,10)</f>
         <v>46305</v>
       </c>
-      <c r="B45" s="13" t="str">
+      <c r="B46" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C46" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D46" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E46" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" s="12">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="12">
         <f>DATE(2026,10,12)</f>
         <v>46307</v>
       </c>
-      <c r="B46" s="13" t="str">
+      <c r="B47" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C47" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D47" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E47" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G46" s="19"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="12">
+      <c r="G47" s="19"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" s="12">
         <f>DATE(2026,10,13)</f>
         <v>46308</v>
       </c>
-      <c r="B47" s="13" t="str">
+      <c r="B48" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C48" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D48" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E48" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" s="12">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="12">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
       </c>
-      <c r="B48" s="13" t="str">
+      <c r="B49" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C49" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D49" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E49" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="12">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="12">
         <f>DATE(2026,10,31)</f>
         <v>46326</v>
       </c>
-      <c r="B49" s="13" t="str">
-        <f t="shared" ref="B49:B76" si="2">TEXT($A49,"ddd")</f>
+      <c r="B50" s="13" t="str">
+        <f t="shared" ref="B50:B77" si="2">TEXT($A50,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C50" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D50" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E50" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="12">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="12">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
-      </c>
-      <c r="B50" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Tue</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="12">
-        <f>DATE(2026,11,10)</f>
-        <v>46336</v>
       </c>
       <c r="B51" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>127</v>
@@ -2533,113 +2543,113 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="12">
+        <f>DATE(2026,11,10)</f>
+        <v>46336</v>
+      </c>
+      <c r="B52" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Tue</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" s="12">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B52" s="13" t="str">
+      <c r="B53" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C53" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D53" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E53" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="12">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B53" s="13" t="str">
+      <c r="B54" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C54" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D54" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E54" s="11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="12">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" s="12">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B54" s="13" t="str">
+      <c r="B55" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C55" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D55" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E55" s="11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="12">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" s="12">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B55" s="13" t="str">
+      <c r="B56" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C56" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D56" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E56" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="12">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" s="12">
         <f>DATE(2027,2,19)</f>
         <v>46437</v>
-      </c>
-      <c r="B56" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="12">
-        <f>DATE(2027,3,19)</f>
-        <v>46465</v>
       </c>
       <c r="B57" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>131</v>
@@ -2647,160 +2657,160 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="12">
+        <f>DATE(2027,3,19)</f>
+        <v>46465</v>
+      </c>
+      <c r="B58" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" s="12">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B58" s="13" t="str">
+      <c r="B59" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C59" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D59" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E59" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="12">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" s="12">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
       </c>
-      <c r="B59" s="13" t="str">
+      <c r="B60" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="C60" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D60" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E60" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="12">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" s="12">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
       </c>
-      <c r="B60" s="13" t="str">
+      <c r="B61" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C61" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D61" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E61" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" s="12">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" s="12">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B61" s="13" t="str">
+      <c r="B62" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C62" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D62" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E62" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" s="12">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B62" s="13" t="str">
+      <c r="B63" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C63" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D63" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E63" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="12">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B63" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A64" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
       </c>
       <c r="B64" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B65" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B66" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2818,18 +2828,18 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="12">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B67" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E67" s="11" t="s">
         <v>131</v>
@@ -2837,56 +2847,56 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="12">
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
+      </c>
+      <c r="B68" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" s="12">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B68" s="13" t="str">
+      <c r="B69" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C69" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D69" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="E68" s="11" t="s">
+      <c r="E69" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A69" s="12">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" s="12">
         <f>DATE(2027,8,20)</f>
         <v>46619</v>
-      </c>
-      <c r="B69" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="E69" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A70" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
       </c>
       <c r="B70" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>131</v>
@@ -2894,46 +2904,46 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="12">
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
+      </c>
+      <c r="B71" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B71" s="13" t="str">
+      <c r="B72" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C72" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="D71" s="11" t="s">
+      <c r="D72" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="E71" s="11" t="s">
+      <c r="E72" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A72" s="12">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" s="12">
         <f>DATE(2027,10,1)</f>
         <v>46661</v>
-      </c>
-      <c r="B72" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="D72" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A73" s="12">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
       </c>
       <c r="B73" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2951,8 +2961,8 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="12">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
       </c>
       <c r="B74" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2970,8 +2980,8 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
       </c>
       <c r="B75" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2989,24 +2999,48 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="12">
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
+      </c>
+      <c r="B76" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" s="12">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B76" s="13" t="str">
+      <c r="B77" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C77" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="D76" s="16" t="s">
+      <c r="D77" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E77" s="11" t="s">
         <v>138</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E77" xr:uid="{00000000-0001-0000-0400-000000000000}">
+    <filterColumn colId="2">
+      <iconFilter iconSet="3Arrows"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4214,15 +4248,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
@@ -4231,6 +4256,15 @@
     <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4475,20 +4509,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
     <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="377" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7398130-92DE-41B3-AA40-FF7E1B9DE9CE}"/>
+  <xr:revisionPtr revIDLastSave="380" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77A123FC-8E73-4208-BCD1-ED2A22BBF5B4}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -601,9 +601,6 @@
     <t>[Tentative] Deepavali Ang Pao Distribution (AMS Hindus)</t>
   </si>
   <si>
-    <t>[Tentative] New Year Ration</t>
-  </si>
-  <si>
     <t>[Tentative] CNY Ration + Ang Bao</t>
   </si>
   <si>
@@ -884,6 +881,9 @@
   </si>
   <si>
     <t>Kopi Kaki session at Blk 110 coffee shop, 830am to 930am</t>
+  </si>
+  <si>
+    <t>[Tentative] New Year Ration. Wishing Tree</t>
   </si>
 </sst>
 </file>
@@ -1136,6 +1136,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1774,7 +1778,7 @@
         <v>135</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>127</v>
@@ -1964,7 +1968,7 @@
         <v>135</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>127</v>
@@ -2002,7 +2006,7 @@
         <v>135</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>127</v>
@@ -2037,10 +2041,10 @@
         <v>Fri</v>
       </c>
       <c r="C25" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>222</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>223</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>131</v>
@@ -2059,7 +2063,7 @@
         <v>135</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>127</v>
@@ -2078,7 +2082,7 @@
         <v>135</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>127</v>
@@ -2094,10 +2098,10 @@
         <v>Sat</v>
       </c>
       <c r="C28" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>254</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>255</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>131</v>
@@ -2113,10 +2117,10 @@
         <v>Wed</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>138</v>
@@ -2132,10 +2136,10 @@
         <v>Sat</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>138</v>
@@ -2151,10 +2155,10 @@
         <v>Fri</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>138</v>
@@ -2170,10 +2174,10 @@
         <v>Sat</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>138</v>
@@ -2189,10 +2193,10 @@
         <v>Sun</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>138</v>
@@ -2208,10 +2212,10 @@
         <v>Wed</v>
       </c>
       <c r="C34" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="D34" t="s">
         <v>268</v>
-      </c>
-      <c r="D34" t="s">
-        <v>269</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>138</v>
@@ -2246,10 +2250,10 @@
         <v>Sat</v>
       </c>
       <c r="C36" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>270</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>271</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>138</v>
@@ -2265,10 +2269,10 @@
         <v>Tue</v>
       </c>
       <c r="C37" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="D37" s="16" t="s">
         <v>272</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>273</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>138</v>
@@ -2284,10 +2288,10 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>138</v>
@@ -2303,10 +2307,10 @@
         <v>Thu</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>138</v>
@@ -2322,10 +2326,10 @@
         <v>Sat</v>
       </c>
       <c r="C40" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="D40" s="11" t="s">
         <v>274</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>275</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>138</v>
@@ -2360,10 +2364,10 @@
         <v>Mon</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>138</v>
@@ -2379,10 +2383,10 @@
         <v>Tue</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E43" s="11" t="s">
         <v>138</v>
@@ -2398,10 +2402,10 @@
         <v>Wed</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E44" s="11" t="s">
         <v>138</v>
@@ -2455,10 +2459,10 @@
         <v>Mon</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E47" s="11" t="s">
         <v>138</v>
@@ -2475,10 +2479,10 @@
         <v>Tue</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E48" s="11" t="s">
         <v>138</v>
@@ -2494,10 +2498,10 @@
         <v>Wed</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>138</v>
@@ -2513,10 +2517,10 @@
         <v>Sat</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>138</v>
@@ -2535,7 +2539,7 @@
         <v>185</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>127</v>
@@ -2554,7 +2558,7 @@
         <v>184</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>127</v>
@@ -2573,7 +2577,7 @@
         <v>183</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>138</v>
@@ -2589,10 +2593,10 @@
         <v>Fri</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>186</v>
+        <v>280</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>125</v>
@@ -2608,10 +2612,10 @@
         <v>Sat</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>125</v>
@@ -2627,10 +2631,10 @@
         <v>Thu</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>131</v>
@@ -2646,10 +2650,10 @@
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>131</v>
@@ -2665,10 +2669,10 @@
         <v>Fri</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>131</v>
@@ -2684,10 +2688,10 @@
         <v>Thu</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E59" s="11" t="s">
         <v>127</v>
@@ -2703,10 +2707,10 @@
         <v>Sat</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>131</v>
@@ -2722,10 +2726,10 @@
         <v>Fri</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>131</v>
@@ -2741,10 +2745,10 @@
         <v>Wed</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E62" s="11" t="s">
         <v>138</v>
@@ -2760,10 +2764,10 @@
         <v>Thu</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>138</v>
@@ -2779,10 +2783,10 @@
         <v>Fri</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E64" s="11" t="s">
         <v>138</v>
@@ -2798,10 +2802,10 @@
         <v>Fri</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>127</v>
@@ -2817,10 +2821,10 @@
         <v>Fri</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>131</v>
@@ -2836,10 +2840,10 @@
         <v>Fri</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E67" s="11" t="s">
         <v>131</v>
@@ -2855,10 +2859,10 @@
         <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E68" s="11" t="s">
         <v>131</v>
@@ -2874,10 +2878,10 @@
         <v>Mon</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>138</v>
@@ -2893,10 +2897,10 @@
         <v>Fri</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>131</v>
@@ -2912,10 +2916,10 @@
         <v>Fri</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>131</v>
@@ -2931,10 +2935,10 @@
         <v>Sat</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>138</v>
@@ -2950,10 +2954,10 @@
         <v>Fri</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E73" s="11" t="s">
         <v>131</v>
@@ -2969,10 +2973,10 @@
         <v>Fri</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E74" s="11" t="s">
         <v>131</v>
@@ -2988,10 +2992,10 @@
         <v>Fri</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E75" s="11" t="s">
         <v>131</v>
@@ -3007,10 +3011,10 @@
         <v>Fri</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E76" s="11" t="s">
         <v>131</v>
@@ -3029,7 +3033,7 @@
         <v>183</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E77" s="11" t="s">
         <v>138</v>
@@ -3281,7 +3285,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>66</v>
@@ -3719,10 +3723,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>201</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>202</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -3742,10 +3746,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>201</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>202</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -3763,16 +3767,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>201</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>202</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>66</v>
@@ -3786,10 +3790,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>201</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>202</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -3807,10 +3811,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>201</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>202</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
@@ -3830,10 +3834,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>203</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>204</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
@@ -3853,10 +3857,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>203</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>204</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -3876,10 +3880,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>205</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>206</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
@@ -3899,10 +3903,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>205</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>206</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
@@ -3922,10 +3926,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>207</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>208</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -3945,10 +3949,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>207</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>208</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -3968,10 +3972,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>207</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>208</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -3991,10 +3995,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>207</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>208</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -4014,10 +4018,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>209</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>210</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -4037,10 +4041,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>209</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>210</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
@@ -4060,10 +4064,10 @@
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B17" s="16" t="s">
         <v>211</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>212</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
@@ -4083,10 +4087,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>211</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>212</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -4106,10 +4110,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B19" s="16" t="s">
         <v>211</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>212</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
@@ -4129,10 +4133,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>213</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>214</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
@@ -4152,10 +4156,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B21" s="16" t="s">
         <v>213</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>214</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
@@ -4175,10 +4179,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B22" s="16" t="s">
         <v>213</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>214</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -4223,7 +4227,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -4231,15 +4235,15 @@
         <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" t="s">
         <v>217</v>
-      </c>
-      <c r="B4" t="s">
-        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -4259,15 +4263,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4508,6 +4503,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4520,14 +4524,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4544,4 +4540,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="380" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77A123FC-8E73-4208-BCD1-ED2A22BBF5B4}"/>
+  <xr:revisionPtr revIDLastSave="429" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92C05BDB-47B3-4425-8E78-92595D934202}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Info" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$76</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="279">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -418,9 +418,6 @@
     <t>Day</t>
   </si>
   <si>
-    <t>Programme/Fundraising</t>
-  </si>
-  <si>
     <t>CNY Ration + Ang Bao Giving to AMS Beneficiaries</t>
   </si>
   <si>
@@ -430,9 +427,6 @@
     <t>Ahmad Ibrahim CNY Engagement</t>
   </si>
   <si>
-    <t>Compliance/Ops</t>
-  </si>
-  <si>
     <t>华报善堂 50 pax Elderly Engagement</t>
   </si>
   <si>
@@ -466,9 +460,6 @@
     <t>Shine Dragon Boat Dumpling Festival Celebration</t>
   </si>
   <si>
-    <t>Partnership</t>
-  </si>
-  <si>
     <t>Charity Concert at Tzu Chi</t>
   </si>
   <si>
@@ -493,12 +484,6 @@
     <t>阿末依布拉欣新春交流活动</t>
   </si>
   <si>
-    <t>Revised TCM Fee Schedule Effective</t>
-  </si>
-  <si>
-    <t>中医收费标准调整生效</t>
-  </si>
-  <si>
     <t>华报善堂50人乐龄交流活动</t>
   </si>
   <si>
@@ -884,6 +869,15 @@
   </si>
   <si>
     <t>[Tentative] New Year Ration. Wishing Tree</t>
+  </si>
+  <si>
+    <t>Temple</t>
+  </si>
+  <si>
+    <t>Fundraising, Partnership/CSR</t>
+  </si>
+  <si>
+    <t>CC Invitation</t>
   </si>
 </sst>
 </file>
@@ -1136,10 +1130,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1567,7 +1557,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -1591,7 +1581,7 @@
         <v>33</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -1600,17 +1590,17 @@
         <v>46023</v>
       </c>
       <c r="B2" s="13" t="str">
-        <f t="shared" ref="B2:B49" si="0">TEXT($A2,"ddd")</f>
+        <f t="shared" ref="B2:B48" si="0">TEXT($A2,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -1623,13 +1613,13 @@
         <v>Sun</v>
       </c>
       <c r="C3" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>126</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -1642,13 +1632,13 @@
         <v>Thu</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -1661,162 +1651,162 @@
         <v>Fri</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
-        <f>DATE(2026,3,2)</f>
-        <v>46083</v>
+        <f>DATE(2026,3,7)</f>
+        <v>46088</v>
       </c>
       <c r="B6" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Sat</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
-        <f>DATE(2026,3,7)</f>
-        <v>46088</v>
+        <f>DATE(2026,3,20)</f>
+        <v>46101</v>
       </c>
       <c r="B7" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Sat</v>
+        <v>Fri</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>130</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="12">
-        <f>DATE(2026,3,20)</f>
-        <v>46101</v>
+        <f>DATE(2026,3,23)</f>
+        <v>46104</v>
       </c>
       <c r="B8" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Fri</v>
+        <v>Mon</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="12">
-        <f>DATE(2026,3,23)</f>
-        <v>46104</v>
+        <f>DATE(2026,3,24)</f>
+        <v>46105</v>
       </c>
       <c r="B9" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="12">
-        <f>DATE(2026,3,24)</f>
-        <v>46105</v>
+        <f>DATE(2026,3,27)</f>
+        <v>46108</v>
       </c>
       <c r="B10" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Tue</v>
+        <v>Fri</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>155</v>
+        <v>133</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>250</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="12">
-        <f>DATE(2026,3,27)</f>
-        <v>46108</v>
+        <f>DATE(2026,4,20)</f>
+        <v>46132</v>
       </c>
       <c r="B11" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Fri</v>
+        <v>Mon</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>255</v>
+      <c r="D11" s="11" t="s">
+        <v>151</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="12">
-        <f>DATE(2026,4,20)</f>
-        <v>46132</v>
+        <f>DATE(2026,5,4)</f>
+        <v>46146</v>
       </c>
       <c r="B12" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="12">
-        <f>DATE(2026,5,4)</f>
-        <v>46146</v>
+        <f>DATE(2026,5,15)</f>
+        <v>46157</v>
       </c>
       <c r="B13" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Fri</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>136</v>
@@ -1824,211 +1814,211 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="12">
-        <f>DATE(2026,5,15)</f>
-        <v>46157</v>
+        <f>DATE(2026,5,24)</f>
+        <v>46166</v>
       </c>
       <c r="B14" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Fri</v>
+        <v>Sun</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="12">
-        <f>DATE(2026,5,24)</f>
-        <v>46166</v>
+        <f>DATE(2026,5,25)</f>
+        <v>46167</v>
       </c>
       <c r="B15" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Sun</v>
+        <v>Mon</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="12">
-        <f>DATE(2026,5,25)</f>
-        <v>46167</v>
+        <f>DATE(2026,5,29)</f>
+        <v>46171</v>
       </c>
       <c r="B16" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Fri</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>127</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="12">
-        <f>DATE(2026,5,29)</f>
-        <v>46171</v>
+        <f>DATE(2026,5,30)</f>
+        <v>46172</v>
       </c>
       <c r="B17" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Fri</v>
+        <v>Sat</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="12">
-        <f>DATE(2026,5,30)</f>
-        <v>46172</v>
+        <f>DATE(2026,5,31)</f>
+        <v>46173</v>
       </c>
       <c r="B18" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Sat</v>
+        <v>Sun</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="12">
-        <f>DATE(2026,5,31)</f>
-        <v>46173</v>
+        <f>DATE(2026,6,1)</f>
+        <v>46174</v>
       </c>
       <c r="B19" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Sun</v>
+        <v>Mon</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="12">
-        <f>DATE(2026,6,1)</f>
-        <v>46174</v>
+        <f>DATE(2026,6,12)</f>
+        <v>46185</v>
       </c>
       <c r="B20" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Fri</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>171</v>
+        <v>133</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>251</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="12">
-        <f>DATE(2026,6,12)</f>
-        <v>46185</v>
+        <f>DATE(2026,6,13)</f>
+        <v>46186</v>
       </c>
       <c r="B21" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Fri</v>
+        <v>Sat</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>256</v>
+        <v>138</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>167</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="12">
-        <f>DATE(2026,6,13)</f>
-        <v>46186</v>
+        <f>DATE(2026,6,20)</f>
+        <v>46193</v>
       </c>
       <c r="B22" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>172</v>
+        <v>133</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>251</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="12">
-        <f>DATE(2026,6,20)</f>
-        <v>46193</v>
+        <f>DATE(2026,7,3)</f>
+        <v>46206</v>
       </c>
       <c r="B23" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Sat</v>
+        <v>Fri</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>256</v>
+        <v>168</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>169</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="12">
-        <f>DATE(2026,7,3)</f>
-        <v>46206</v>
+        <f>DATE(2026,7,24)</f>
+        <v>46227</v>
       </c>
       <c r="B24" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -2040,242 +2030,242 @@
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>222</v>
+      <c r="C25" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>252</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="12">
-        <f>DATE(2026,7,24)</f>
-        <v>46227</v>
+        <f>DATE(2026,7,25)</f>
+        <v>46228</v>
       </c>
       <c r="B26" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Fri</v>
+        <v>Sat</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="12">
-        <f>DATE(2026,7,25)</f>
-        <v>46228</v>
+        <f>DATE(2026,8,1)</f>
+        <v>46235</v>
       </c>
       <c r="B27" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>257</v>
+      <c r="C27" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>249</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="12">
-        <f>DATE(2026,8,1)</f>
-        <v>46235</v>
+        <f>DATE(2026,8,5)</f>
+        <v>46239</v>
       </c>
       <c r="B28" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Sat</v>
+        <f t="shared" ref="B28:B38" si="1">TEXT($A28,"ddd")</f>
+        <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>254</v>
+        <v>274</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>273</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>131</v>
+        <v>276</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="12">
-        <f>DATE(2026,8,5)</f>
-        <v>46239</v>
+        <f>DATE(2026,8,8)</f>
+        <v>46242</v>
       </c>
       <c r="B29" s="13" t="str">
-        <f t="shared" ref="B29:B39" si="1">TEXT($A29,"ddd")</f>
-        <v>Wed</v>
+        <f t="shared" si="1"/>
+        <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="12">
-        <f>DATE(2026,8,8)</f>
-        <v>46242</v>
+        <f>DATE(2026,8,14)</f>
+        <v>46248</v>
       </c>
       <c r="B30" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Sat</v>
+        <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="12">
-        <f>DATE(2026,8,14)</f>
-        <v>46248</v>
+        <f>DATE(2026,8,15)</f>
+        <v>46249</v>
       </c>
       <c r="B31" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Fri</v>
+        <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>138</v>
+        <v>278</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="12">
-        <f>DATE(2026,8,15)</f>
-        <v>46249</v>
+        <f>DATE(2026,8,23)</f>
+        <v>46257</v>
       </c>
       <c r="B32" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Sat</v>
+        <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>258</v>
+        <v>255</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>241</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="12">
-        <f>DATE(2026,8,23)</f>
-        <v>46257</v>
+        <f>DATE(2026,8,26)</f>
+        <v>46260</v>
       </c>
       <c r="B33" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Sun</v>
+        <v>Wed</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>246</v>
+        <v>262</v>
+      </c>
+      <c r="D33" t="s">
+        <v>263</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="12">
-        <f>DATE(2026,8,26)</f>
-        <v>46260</v>
+        <f>DATE(2026,8,28)</f>
+        <v>46262</v>
       </c>
       <c r="B34" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Wed</v>
+        <f>TEXT($A34,"ddd")</f>
+        <v>Fri</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D34" t="s">
-        <v>268</v>
+        <v>170</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>171</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="12">
-        <f>DATE(2026,8,28)</f>
-        <v>46262</v>
+        <f>DATE(2026,8,29)</f>
+        <v>46263</v>
       </c>
       <c r="B35" s="13" t="str">
-        <f>TEXT($A35,"ddd")</f>
-        <v>Fri</v>
+        <f t="shared" si="1"/>
+        <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>175</v>
+        <v>264</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>176</v>
+        <v>265</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>127</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="12">
-        <f>DATE(2026,8,29)</f>
-        <v>46263</v>
+        <f>DATE(2026,9,1)</f>
+        <v>46266</v>
       </c>
       <c r="B36" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Sat</v>
+        <v>Tue</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>270</v>
+        <v>266</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>267</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="12">
-        <f>DATE(2026,9,1)</f>
-        <v>46266</v>
+        <f>DATE(2026,9,3)</f>
+        <v>46268</v>
       </c>
       <c r="B37" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Tue</v>
+        <v>Thu</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>272</v>
+        <v>256</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>242</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
@@ -2288,32 +2278,32 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>247</v>
+        <v>260</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>245</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="12">
-        <f>DATE(2026,9,3)</f>
-        <v>46268</v>
+        <f>DATE(2026,9,5)</f>
+        <v>46270</v>
       </c>
       <c r="B39" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Thu</v>
+        <f>TEXT($A39,"ddd")</f>
+        <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>250</v>
+        <v>268</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>269</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
@@ -2322,725 +2312,706 @@
         <v>46270</v>
       </c>
       <c r="B40" s="13" t="str">
-        <f>TEXT($A40,"ddd")</f>
+        <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>273</v>
+        <v>172</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>274</v>
+        <v>173</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="12">
-        <f>DATE(2026,9,5)</f>
-        <v>46270</v>
+        <f>DATE(2026,9,7)</f>
+        <v>46272</v>
       </c>
       <c r="B41" s="13" t="str">
+        <f>TEXT($A41,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="12">
+        <f>DATE(2026,9,8)</f>
+        <v>46273</v>
+      </c>
+      <c r="B42" s="13" t="str">
+        <f>TEXT($A42,"ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="12">
+        <f>DATE(2026,9,9)</f>
+        <v>46274</v>
+      </c>
+      <c r="B43" s="13" t="str">
+        <f>TEXT($A43,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" s="12">
+        <f>DATE(2026,9,20)</f>
+        <v>46285</v>
+      </c>
+      <c r="B44" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="12">
+        <f>DATE(2026,10,10)</f>
+        <v>46305</v>
+      </c>
+      <c r="B45" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C41" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" s="12">
-        <f>DATE(2026,9,7)</f>
-        <v>46272</v>
-      </c>
-      <c r="B42" s="13" t="str">
-        <f>TEXT($A42,"ddd")</f>
-        <v>Mon</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="12">
-        <f>DATE(2026,9,8)</f>
-        <v>46273</v>
-      </c>
-      <c r="B43" s="13" t="str">
-        <f>TEXT($A43,"ddd")</f>
-        <v>Tue</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="12">
-        <f>DATE(2026,9,9)</f>
-        <v>46274</v>
-      </c>
-      <c r="B44" s="13" t="str">
-        <f>TEXT($A44,"ddd")</f>
-        <v>Wed</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="12">
-        <f>DATE(2026,9,20)</f>
-        <v>46285</v>
-      </c>
-      <c r="B45" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Sun</v>
-      </c>
       <c r="C45" s="11" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="12">
-        <f>DATE(2026,10,10)</f>
-        <v>46305</v>
+        <f>DATE(2026,10,12)</f>
+        <v>46307</v>
       </c>
       <c r="B46" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Sat</v>
+        <v>Mon</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>181</v>
+        <v>219</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>138</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="G46" s="19"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="12">
-        <f>DATE(2026,10,12)</f>
-        <v>46307</v>
+        <f>DATE(2026,10,13)</f>
+        <v>46308</v>
       </c>
       <c r="B47" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G47" s="19"/>
+        <v>276</v>
+      </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="12">
-        <f>DATE(2026,10,13)</f>
-        <v>46308</v>
+        <f>DATE(2026,10,14)</f>
+        <v>46309</v>
       </c>
       <c r="B48" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>Tue</v>
+        <v>Wed</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="12">
-        <f>DATE(2026,10,14)</f>
-        <v>46309</v>
+        <f>DATE(2026,10,31)</f>
+        <v>46326</v>
       </c>
       <c r="B49" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Wed</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>220</v>
+        <f t="shared" ref="B49:B76" si="2">TEXT($A49,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>210</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="12">
-        <f>DATE(2026,10,31)</f>
-        <v>46326</v>
+        <f>DATE(2026,11,3)</f>
+        <v>46329</v>
       </c>
       <c r="B50" s="13" t="str">
-        <f t="shared" ref="B50:B77" si="2">TEXT($A50,"ddd")</f>
-        <v>Sat</v>
+        <f t="shared" si="2"/>
+        <v>Tue</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="12">
-        <f>DATE(2026,11,3)</f>
-        <v>46329</v>
+        <f>DATE(2026,11,10)</f>
+        <v>46336</v>
       </c>
       <c r="B51" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="12">
-        <f>DATE(2026,11,10)</f>
-        <v>46336</v>
+        <f>DATE(2026,12,16)</f>
+        <v>46372</v>
       </c>
       <c r="B52" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Tue</v>
+        <v>Wed</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>229</v>
+        <v>178</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>225</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="12">
-        <f>DATE(2026,12,16)</f>
-        <v>46372</v>
+        <f>DATE(2027,1,1)</f>
+        <v>46388</v>
       </c>
       <c r="B53" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Wed</v>
+        <v>Fri</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>230</v>
+        <v>275</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>226</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="12">
-        <f>DATE(2027,1,1)</f>
-        <v>46388</v>
+        <f>DATE(2027,1,30)</f>
+        <v>46417</v>
       </c>
       <c r="B54" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>280</v>
+        <v>Sat</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>181</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="12">
-        <f>DATE(2027,1,30)</f>
-        <v>46417</v>
+        <f>DATE(2027,2,18)</f>
+        <v>46436</v>
       </c>
       <c r="B55" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Sat</v>
+        <v>Thu</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="12">
-        <f>DATE(2027,2,18)</f>
-        <v>46436</v>
+        <f>DATE(2027,2,19)</f>
+        <v>46437</v>
       </c>
       <c r="B56" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Thu</v>
+        <v>Fri</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="12">
-        <f>DATE(2027,2,19)</f>
-        <v>46437</v>
+        <f>DATE(2027,3,19)</f>
+        <v>46465</v>
       </c>
       <c r="B57" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="12">
-        <f>DATE(2027,3,19)</f>
-        <v>46465</v>
+        <f>DATE(2027,3,25)</f>
+        <v>46471</v>
       </c>
       <c r="B58" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Thu</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="12">
-        <f>DATE(2027,3,25)</f>
-        <v>46471</v>
+        <f>DATE(2027,4,3)</f>
+        <v>46480</v>
       </c>
       <c r="B59" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>190</v>
+        <v>Sat</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>247</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="12">
-        <f>DATE(2027,4,3)</f>
-        <v>46480</v>
+        <f>DATE(2027,4,9)</f>
+        <v>46486</v>
       </c>
       <c r="B60" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Sat</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>252</v>
+        <v>Fri</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>184</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>131</v>
+        <v>277</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="12">
-        <f>DATE(2027,4,9)</f>
-        <v>46486</v>
+        <f>DATE(2027,5,19)</f>
+        <v>46526</v>
       </c>
       <c r="B61" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Wed</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>131</v>
+        <v>276</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="12">
-        <f>DATE(2027,5,19)</f>
-        <v>46526</v>
+        <f>DATE(2027,5,20)</f>
+        <v>46527</v>
       </c>
       <c r="B62" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="12">
-        <f>DATE(2027,5,20)</f>
-        <v>46527</v>
+        <f>DATE(2027,5,21)</f>
+        <v>46528</v>
       </c>
       <c r="B63" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Thu</v>
+        <v>Fri</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="12">
-        <f>DATE(2027,5,21)</f>
-        <v>46528</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B64" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B65" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B66" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
       </c>
       <c r="B67" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="12">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
+        <f>DATE(2027,8,16)</f>
+        <v>46615</v>
       </c>
       <c r="B68" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Mon</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>131</v>
+        <v>276</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="12">
-        <f>DATE(2027,8,16)</f>
-        <v>46615</v>
+        <f>DATE(2027,8,20)</f>
+        <v>46619</v>
       </c>
       <c r="B69" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Mon</v>
+        <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
-        <f>DATE(2027,8,20)</f>
-        <v>46619</v>
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
       </c>
       <c r="B70" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
+        <f>DATE(2027,9,18)</f>
+        <v>46648</v>
       </c>
       <c r="B71" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Sat</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="12">
-        <f>DATE(2027,9,18)</f>
-        <v>46648</v>
+        <f>DATE(2027,10,1)</f>
+        <v>46661</v>
       </c>
       <c r="B72" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Sat</v>
+        <v>Fri</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="12">
-        <f>DATE(2027,10,1)</f>
-        <v>46661</v>
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
       </c>
       <c r="B73" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="12">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
       </c>
       <c r="B74" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="12">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
       </c>
       <c r="B75" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
+        <f>DATE(2027,12,16)</f>
+        <v>46737</v>
       </c>
       <c r="B76" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Thu</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>235</v>
+        <v>178</v>
+      </c>
+      <c r="D76" s="16" t="s">
+        <v>225</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A77" s="12">
-        <f>DATE(2027,12,16)</f>
-        <v>46737</v>
-      </c>
-      <c r="B77" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="D77" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="E77" s="11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E77" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E76" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
@@ -3285,7 +3256,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>66</v>
@@ -3452,7 +3423,7 @@
         <v>25</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>22</v>
@@ -3723,10 +3694,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -3746,10 +3717,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -3767,16 +3738,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>66</v>
@@ -3790,10 +3761,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -3811,10 +3782,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
@@ -3834,10 +3805,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
@@ -3857,10 +3828,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -3880,10 +3851,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
@@ -3903,10 +3874,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
@@ -3926,10 +3897,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -3949,10 +3920,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -3972,10 +3943,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -3995,10 +3966,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -4018,10 +3989,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -4041,10 +4012,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
@@ -4064,10 +4035,10 @@
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
@@ -4087,10 +4058,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -4110,10 +4081,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
@@ -4133,10 +4104,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
@@ -4156,10 +4127,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
@@ -4179,10 +4150,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -4227,7 +4198,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -4235,15 +4206,15 @@
         <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -4263,6 +4234,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4503,15 +4483,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4524,6 +4495,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4540,12 +4519,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="429" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92C05BDB-47B3-4425-8E78-92595D934202}"/>
+  <xr:revisionPtr revIDLastSave="440" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1670BA5-174A-4707-903A-56FA26A882E0}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Info" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$75</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="277">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -589,12 +589,6 @@
     <t>[Tentative] CNY Ration + Ang Bao</t>
   </si>
   <si>
-    <t>[Tentative] CNY Dinner – CSR (JustCo or MS Project) – Day 1</t>
-  </si>
-  <si>
-    <t>[Tentative] CNY Dinner – CSR (JustCo or MS Project) – Day 2</t>
-  </si>
-  <si>
     <t>[Tentative] CSR Partnership – Corporate / School</t>
   </si>
   <si>
@@ -727,12 +721,6 @@
     <t>[未确认] 农历新年物资及红包派发</t>
   </si>
   <si>
-    <t>[未确认] 新春晚宴 – 企业社会责任（JustCo或MS项目）第一天</t>
-  </si>
-  <si>
-    <t>[未确认] 新春晚宴 – 企业社会责任（JustCo或MS项目）第二天</t>
-  </si>
-  <si>
     <t>[未确认] 企业／学校社会责任合作</t>
   </si>
   <si>
@@ -878,6 +866,12 @@
   </si>
   <si>
     <t>CC Invitation</t>
+  </si>
+  <si>
+    <t>[Tentative] CNY Dinner – CSR (JustCo or MS Project) – either 18 Feb or 19 Feb</t>
+  </si>
+  <si>
+    <t>[未确认] 新春晚宴 – 企业社会责任（JustCo或MS项目）二月18日或二月19日</t>
   </si>
 </sst>
 </file>
@@ -1557,7 +1551,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -1600,7 +1594,7 @@
         <v>142</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -1638,7 +1632,7 @@
         <v>145</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -1749,7 +1743,7 @@
         <v>133</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>126</v>
@@ -1866,7 +1860,7 @@
         <v>160</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -1885,7 +1879,7 @@
         <v>162</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -1904,7 +1898,7 @@
         <v>164</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -1923,7 +1917,7 @@
         <v>166</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -1939,7 +1933,7 @@
         <v>133</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>126</v>
@@ -1977,7 +1971,7 @@
         <v>133</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>126</v>
@@ -2012,10 +2006,10 @@
         <v>Fri</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>129</v>
@@ -2034,7 +2028,7 @@
         <v>133</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>126</v>
@@ -2053,7 +2047,7 @@
         <v>133</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>126</v>
@@ -2069,10 +2063,10 @@
         <v>Sat</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>129</v>
@@ -2088,13 +2082,13 @@
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -2107,13 +2101,13 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -2126,13 +2120,13 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -2145,13 +2139,13 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -2164,13 +2158,13 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -2183,13 +2177,13 @@
         <v>Wed</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D33" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -2221,13 +2215,13 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -2240,13 +2234,13 @@
         <v>Tue</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -2259,13 +2253,13 @@
         <v>Thu</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
@@ -2278,13 +2272,13 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
@@ -2297,13 +2291,13 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
@@ -2335,13 +2329,13 @@
         <v>Mon</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
@@ -2354,13 +2348,13 @@
         <v>Tue</v>
       </c>
       <c r="C42" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="E42" s="11" t="s">
         <v>272</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
@@ -2373,13 +2367,13 @@
         <v>Wed</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
@@ -2430,13 +2424,13 @@
         <v>Mon</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G46" s="19"/>
     </row>
@@ -2450,13 +2444,13 @@
         <v>Tue</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
@@ -2469,13 +2463,13 @@
         <v>Wed</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
@@ -2484,14 +2478,14 @@
         <v>46326</v>
       </c>
       <c r="B49" s="13" t="str">
-        <f t="shared" ref="B49:B76" si="2">TEXT($A49,"ddd")</f>
+        <f t="shared" ref="B49:B75" si="2">TEXT($A49,"ddd")</f>
         <v>Sat</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>136</v>
@@ -2510,7 +2504,7 @@
         <v>180</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>126</v>
@@ -2529,7 +2523,7 @@
         <v>179</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>129</v>
@@ -2548,7 +2542,7 @@
         <v>178</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>136</v>
@@ -2564,10 +2558,10 @@
         <v>Fri</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>136</v>
@@ -2586,7 +2580,7 @@
         <v>181</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>126</v>
@@ -2602,29 +2596,29 @@
         <v>Thu</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>182</v>
+        <v>275</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>228</v>
+        <v>276</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>129</v>
+        <v>273</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="12">
-        <f>DATE(2027,2,19)</f>
-        <v>46437</v>
+        <f>DATE(2027,3,19)</f>
+        <v>46465</v>
       </c>
       <c r="B56" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>129</v>
@@ -2632,56 +2626,56 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="12">
-        <f>DATE(2027,3,19)</f>
-        <v>46465</v>
+        <f>DATE(2027,3,25)</f>
+        <v>46471</v>
       </c>
       <c r="B57" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Thu</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="12">
-        <f>DATE(2027,3,25)</f>
-        <v>46471</v>
+        <f>DATE(2027,4,3)</f>
+        <v>46480</v>
       </c>
       <c r="B58" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>185</v>
+        <v>Sat</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>243</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>126</v>
+        <v>273</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="12">
-        <f>DATE(2027,4,3)</f>
-        <v>46480</v>
+        <f>DATE(2027,4,9)</f>
+        <v>46486</v>
       </c>
       <c r="B59" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Sat</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>247</v>
+        <v>Fri</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>182</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="E59" s="11" t="s">
         <v>129</v>
@@ -2689,113 +2683,113 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="12">
-        <f>DATE(2027,4,9)</f>
-        <v>46486</v>
+        <f>DATE(2027,5,19)</f>
+        <v>46526</v>
       </c>
       <c r="B60" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Wed</v>
       </c>
       <c r="C60" s="11" t="s">
         <v>184</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="12">
-        <f>DATE(2027,5,19)</f>
-        <v>46526</v>
+        <f>DATE(2027,5,20)</f>
+        <v>46527</v>
       </c>
       <c r="B61" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="12">
-        <f>DATE(2027,5,20)</f>
-        <v>46527</v>
+        <f>DATE(2027,5,21)</f>
+        <v>46528</v>
       </c>
       <c r="B62" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Thu</v>
+        <v>Fri</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="12">
-        <f>DATE(2027,5,21)</f>
-        <v>46528</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B63" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>276</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B64" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B65" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>129</v>
@@ -2803,18 +2797,18 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
       </c>
       <c r="B66" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>129</v>
@@ -2822,56 +2816,56 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="12">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
+        <f>DATE(2027,8,16)</f>
+        <v>46615</v>
       </c>
       <c r="B67" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Mon</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>129</v>
+        <v>272</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="12">
-        <f>DATE(2027,8,16)</f>
-        <v>46615</v>
+        <f>DATE(2027,8,20)</f>
+        <v>46619</v>
       </c>
       <c r="B68" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Mon</v>
+        <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>276</v>
+        <v>129</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="12">
-        <f>DATE(2027,8,20)</f>
-        <v>46619</v>
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
       </c>
       <c r="B69" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>129</v>
@@ -2879,56 +2873,56 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
+        <f>DATE(2027,9,18)</f>
+        <v>46648</v>
       </c>
       <c r="B70" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Sat</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="12">
-        <f>DATE(2027,9,18)</f>
-        <v>46648</v>
+        <f>DATE(2027,10,1)</f>
+        <v>46661</v>
       </c>
       <c r="B71" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Sat</v>
+        <v>Fri</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="12">
-        <f>DATE(2027,10,1)</f>
-        <v>46661</v>
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
       </c>
       <c r="B72" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>129</v>
@@ -2936,18 +2930,18 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="12">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
       </c>
       <c r="B73" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E73" s="11" t="s">
         <v>129</v>
@@ -2955,18 +2949,18 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="12">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
       </c>
       <c r="B74" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E74" s="11" t="s">
         <v>129</v>
@@ -2974,44 +2968,25 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
+        <f>DATE(2027,12,16)</f>
+        <v>46737</v>
       </c>
       <c r="B75" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Thu</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D75" s="11" t="s">
-        <v>230</v>
+        <v>178</v>
+      </c>
+      <c r="D75" s="16" t="s">
+        <v>223</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A76" s="12">
-        <f>DATE(2027,12,16)</f>
-        <v>46737</v>
-      </c>
-      <c r="B76" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D76" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="E76" s="11" t="s">
         <v>136</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E76" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E75" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
@@ -3256,7 +3231,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>66</v>
@@ -3694,10 +3669,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -3717,10 +3692,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -3738,16 +3713,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>66</v>
@@ -3761,10 +3736,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -3782,10 +3757,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
@@ -3805,10 +3780,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
@@ -3828,10 +3803,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -3851,10 +3826,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
@@ -3874,10 +3849,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
@@ -3897,10 +3872,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -3920,10 +3895,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -3943,10 +3918,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -3966,10 +3941,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -3989,10 +3964,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -4012,10 +3987,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
@@ -4035,10 +4010,10 @@
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
@@ -4058,10 +4033,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -4081,10 +4056,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
@@ -4104,10 +4079,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
@@ -4127,10 +4102,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
@@ -4150,10 +4125,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -4198,7 +4173,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -4206,15 +4181,15 @@
         <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="440" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1670BA5-174A-4707-903A-56FA26A882E0}"/>
+  <xr:revisionPtr revIDLastSave="447" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14FD027E-61F0-4A90-A119-D35356982130}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Info" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$76</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="279">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -872,6 +872,12 @@
   </si>
   <si>
     <t>[未确认] 新春晚宴 – 企业社会责任（JustCo或MS项目）二月18日或二月19日</t>
+  </si>
+  <si>
+    <t>Wee Guan Construction CSR Mental Health Day (150 pax). 70 volunteers. Buffet, activities, goodie bag.</t>
+  </si>
+  <si>
+    <t>Wee Guan Construction 企业社会责任（150人）</t>
   </si>
 </sst>
 </file>
@@ -1551,7 +1557,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -1584,7 +1590,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="13" t="str">
-        <f t="shared" ref="B2:B48" si="0">TEXT($A2,"ddd")</f>
+        <f t="shared" ref="B2:B49" si="0">TEXT($A2,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -2397,389 +2403,389 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="12">
+        <f>DATE(2026,10,9)</f>
+        <v>46304</v>
+      </c>
+      <c r="B45" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" s="12">
         <f>DATE(2026,10,10)</f>
         <v>46305</v>
       </c>
-      <c r="B45" s="13" t="str">
+      <c r="B46" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C46" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D46" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E46" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" s="12">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="12">
         <f>DATE(2026,10,12)</f>
         <v>46307</v>
       </c>
-      <c r="B46" s="13" t="str">
+      <c r="B47" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C47" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D47" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E47" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="G46" s="19"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="12">
+      <c r="G47" s="19"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" s="12">
         <f>DATE(2026,10,13)</f>
         <v>46308</v>
       </c>
-      <c r="B47" s="13" t="str">
+      <c r="B48" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C48" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D48" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E48" s="11" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" s="12">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="12">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
       </c>
-      <c r="B48" s="13" t="str">
+      <c r="B49" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C49" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D49" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E49" s="11" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="12">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="12">
         <f>DATE(2026,10,31)</f>
         <v>46326</v>
       </c>
-      <c r="B49" s="13" t="str">
-        <f t="shared" ref="B49:B75" si="2">TEXT($A49,"ddd")</f>
+      <c r="B50" s="13" t="str">
+        <f t="shared" ref="B50:B76" si="2">TEXT($A50,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C50" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D50" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E50" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="12">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="12">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
-      </c>
-      <c r="B50" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Tue</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="12">
-        <f>DATE(2026,11,10)</f>
-        <v>46336</v>
       </c>
       <c r="B51" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="12">
+        <f>DATE(2026,11,10)</f>
+        <v>46336</v>
+      </c>
+      <c r="B52" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Tue</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" s="12">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B52" s="13" t="str">
+      <c r="B53" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C53" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D53" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E53" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="12">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B53" s="13" t="str">
+      <c r="B54" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C54" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D54" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E54" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="12">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" s="12">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B54" s="13" t="str">
+      <c r="B55" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C55" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D55" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E55" s="11" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="12">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" s="12">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B55" s="13" t="str">
+      <c r="B56" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C56" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D56" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E56" s="11" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="12">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" s="12">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B56" s="13" t="str">
+      <c r="B57" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C57" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D57" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E57" s="11" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="12">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" s="12">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B57" s="13" t="str">
+      <c r="B58" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C58" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D58" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E58" s="11" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="12">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" s="12">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
       </c>
-      <c r="B58" s="13" t="str">
+      <c r="B59" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C59" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D59" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E59" s="11" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="12">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" s="12">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
       </c>
-      <c r="B59" s="13" t="str">
+      <c r="B60" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C60" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D60" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E60" s="11" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="12">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" s="12">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B60" s="13" t="str">
+      <c r="B61" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C61" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D61" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E61" s="11" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" s="12">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B61" s="13" t="str">
+      <c r="B62" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C62" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D62" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E62" s="11" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" s="12">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B62" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="E62" s="11" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
       </c>
       <c r="B63" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>126</v>
+        <v>272</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B64" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B65" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2797,18 +2803,18 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="12">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B66" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>129</v>
@@ -2816,56 +2822,56 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="12">
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
+      </c>
+      <c r="B67" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" s="12">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B67" s="13" t="str">
+      <c r="B68" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C68" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D68" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="E67" s="11" t="s">
+      <c r="E68" s="11" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A68" s="12">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" s="12">
         <f>DATE(2027,8,20)</f>
         <v>46619</v>
-      </c>
-      <c r="B68" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="D68" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A69" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
       </c>
       <c r="B69" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>129</v>
@@ -2873,46 +2879,46 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
+      </c>
+      <c r="B70" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B70" s="13" t="str">
+      <c r="B71" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C71" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D71" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E71" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A71" s="12">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" s="12">
         <f>DATE(2027,10,1)</f>
         <v>46661</v>
-      </c>
-      <c r="B71" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D71" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="E71" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A72" s="12">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
       </c>
       <c r="B72" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2930,8 +2936,8 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="12">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
       </c>
       <c r="B73" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2949,8 +2955,8 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
       </c>
       <c r="B74" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2968,25 +2974,44 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="12">
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
+      </c>
+      <c r="B75" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" s="12">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B75" s="13" t="str">
+      <c r="B76" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C76" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D75" s="16" t="s">
+      <c r="D76" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="E76" s="11" t="s">
         <v>136</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E75" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E76" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="447" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14FD027E-61F0-4A90-A119-D35356982130}"/>
+  <xr:revisionPtr revIDLastSave="448" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25AFC097-57CA-4392-AB2D-CC60467B44D2}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -691,9 +691,6 @@
     <t>海军部中学户外活动</t>
   </si>
   <si>
-    <t>27 July 2026</t>
-  </si>
-  <si>
     <t>[未确认] 九皇爷诞筹款第一天</t>
   </si>
   <si>
@@ -878,6 +875,9 @@
   </si>
   <si>
     <t>Wee Guan Construction 企业社会责任（150人）</t>
+  </si>
+  <si>
+    <t>3 August 2026</t>
   </si>
 </sst>
 </file>
@@ -1749,7 +1749,7 @@
         <v>133</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>126</v>
@@ -1866,7 +1866,7 @@
         <v>160</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -1885,7 +1885,7 @@
         <v>162</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -1904,7 +1904,7 @@
         <v>164</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -1923,7 +1923,7 @@
         <v>166</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -1939,7 +1939,7 @@
         <v>133</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>126</v>
@@ -1977,7 +1977,7 @@
         <v>133</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>126</v>
@@ -2034,7 +2034,7 @@
         <v>133</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>126</v>
@@ -2053,7 +2053,7 @@
         <v>133</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>126</v>
@@ -2069,10 +2069,10 @@
         <v>Sat</v>
       </c>
       <c r="C27" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>244</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>245</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>129</v>
@@ -2088,13 +2088,13 @@
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -2107,13 +2107,13 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -2126,13 +2126,13 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -2145,13 +2145,13 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -2164,13 +2164,13 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -2183,13 +2183,13 @@
         <v>Wed</v>
       </c>
       <c r="C33" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="D33" t="s">
         <v>258</v>
       </c>
-      <c r="D33" t="s">
-        <v>259</v>
-      </c>
       <c r="E33" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -2221,13 +2221,13 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="D35" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="D35" s="11" t="s">
-        <v>261</v>
-      </c>
       <c r="E35" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -2240,13 +2240,13 @@
         <v>Tue</v>
       </c>
       <c r="C36" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D36" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="D36" s="16" t="s">
-        <v>263</v>
-      </c>
       <c r="E36" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -2259,13 +2259,13 @@
         <v>Thu</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
@@ -2278,13 +2278,13 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
@@ -2297,13 +2297,13 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="D39" s="11" t="s">
-        <v>265</v>
-      </c>
       <c r="E39" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
@@ -2335,13 +2335,13 @@
         <v>Mon</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
@@ -2354,13 +2354,13 @@
         <v>Tue</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
@@ -2373,13 +2373,13 @@
         <v>Wed</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
@@ -2411,10 +2411,10 @@
         <v>Fri</v>
       </c>
       <c r="C45" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D45" s="11" t="s">
         <v>277</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>278</v>
       </c>
       <c r="E45" s="11" t="s">
         <v>129</v>
@@ -2452,10 +2452,10 @@
         <v>211</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G47" s="19"/>
     </row>
@@ -2472,10 +2472,10 @@
         <v>212</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
@@ -2491,10 +2491,10 @@
         <v>213</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
@@ -2510,7 +2510,7 @@
         <v>208</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>136</v>
@@ -2529,7 +2529,7 @@
         <v>180</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>126</v>
@@ -2548,7 +2548,7 @@
         <v>179</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>129</v>
@@ -2567,7 +2567,7 @@
         <v>178</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>136</v>
@@ -2583,10 +2583,10 @@
         <v>Fri</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>136</v>
@@ -2605,7 +2605,7 @@
         <v>181</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>126</v>
@@ -2621,13 +2621,13 @@
         <v>Thu</v>
       </c>
       <c r="C56" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="D56" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="D56" s="11" t="s">
-        <v>276</v>
-      </c>
       <c r="E56" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
@@ -2643,7 +2643,7 @@
         <v>182</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>129</v>
@@ -2662,7 +2662,7 @@
         <v>183</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>126</v>
@@ -2678,13 +2678,13 @@
         <v>Sat</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
@@ -2700,7 +2700,7 @@
         <v>182</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>129</v>
@@ -2719,10 +2719,10 @@
         <v>184</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
@@ -2738,10 +2738,10 @@
         <v>185</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
@@ -2757,10 +2757,10 @@
         <v>186</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
@@ -2776,7 +2776,7 @@
         <v>187</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E64" s="11" t="s">
         <v>126</v>
@@ -2795,7 +2795,7 @@
         <v>182</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>129</v>
@@ -2814,7 +2814,7 @@
         <v>182</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>129</v>
@@ -2833,7 +2833,7 @@
         <v>188</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E67" s="11" t="s">
         <v>129</v>
@@ -2852,10 +2852,10 @@
         <v>189</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
@@ -2871,7 +2871,7 @@
         <v>190</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>129</v>
@@ -2890,7 +2890,7 @@
         <v>182</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>129</v>
@@ -2909,7 +2909,7 @@
         <v>191</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>136</v>
@@ -2928,7 +2928,7 @@
         <v>182</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>129</v>
@@ -2947,7 +2947,7 @@
         <v>182</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E73" s="11" t="s">
         <v>129</v>
@@ -2966,7 +2966,7 @@
         <v>182</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E74" s="11" t="s">
         <v>129</v>
@@ -2985,7 +2985,7 @@
         <v>182</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E75" s="11" t="s">
         <v>129</v>
@@ -3004,7 +3004,7 @@
         <v>178</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E76" s="11" t="s">
         <v>136</v>
@@ -4198,7 +4198,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>216</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">

--- a/data.xlsx
+++ b/data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="448" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25AFC097-57CA-4392-AB2D-CC60467B44D2}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -4234,15 +4234,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4483,6 +4474,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4495,14 +4495,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4519,4 +4511,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="448" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25AFC097-57CA-4392-AB2D-CC60467B44D2}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="448" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25AFC097-57CA-4392-AB2D-CC60467B44D2}"/>
+  <xr:revisionPtr revIDLastSave="449" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB694869-43B7-43B8-9608-4A98E28FBB32}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -2094,7 +2094,7 @@
         <v>268</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>271</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -4234,6 +4234,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4474,15 +4483,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4495,6 +4495,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4511,12 +4519,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="449" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB694869-43B7-43B8-9608-4A98E28FBB32}"/>
+  <xr:revisionPtr revIDLastSave="463" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFBF7FDA-766B-40A1-817C-9B064714A02E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -790,51 +790,15 @@
     <t>2026年中邦第61届国庆晚宴，晚上7点至10点。（代表：陈浚纬, Bill Tan）</t>
   </si>
   <si>
-    <t>Chong Pang 61st National Day Dinner 2026, 7-10pm at Chong Pang 165 Hardcourt. (Representative: William Tan, Bill Tan)</t>
-  </si>
-  <si>
-    <t>Lunar July (ZhongYuan Festival) - YS ONE, 1 Yishun Street 23 (Representative: Bryan, 丽菁, 丽丝和先生)</t>
-  </si>
-  <si>
-    <t>Lunar July (ZhongYuan Festival) - Jurong Safra Pearl Garden Restaurant (Representative: Neo Tian Siah, Kathy, Jin Hoa)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunar July (ZhongYuan Festival) - Blk 838 Yishun Street 81 (Representative: Doran, Bryan, 丽菁, 丽丝和先生) </t>
-  </si>
-  <si>
-    <t>Temple Dinner - 元龙聖庙（关帝聖君兴诸众神诞）(Representative: Cher Kim Seah, Agnes, Bryan, Kathy, Jin Hoa). Auction item included.</t>
-  </si>
-  <si>
-    <t>Lunar July (ZhongYuan Festival) - Block 137 Yishun Ring Road (Representative: Cher Kim Seah, Agnes, Yan Yi). Auction item included.</t>
-  </si>
-  <si>
-    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Pei Yuen, Yan Yi). Auction item included.</t>
-  </si>
-  <si>
-    <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon (Representative: Neo Tian Siah, NHWSS office staff, 5 front desk, 晓晓). Auction item included.</t>
-  </si>
-  <si>
-    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 7 Gambas Crescent, ARK@Gambas Level 2 (Representative: Doran, Pei Yuen, Chi Hwee, 晓晓)</t>
-  </si>
-  <si>
     <t>[日期未确认] 方舟@岗巴士中元会 (代表：Doran, Pei Yuen, Chee Hwee, 晓晓）</t>
   </si>
   <si>
-    <t>Lunar July (ZhongYuan Festival) - 724 Yishun Street 71 (Representative: Chew Kim Cheong, Kathy, 丽菁, 丽丝和先生)</t>
-  </si>
-  <si>
     <t>717 商店中元会 (代表：周锦昌, Kathy, 丽菁, 丽丝和先生）</t>
   </si>
   <si>
-    <t>Lunar July (ZhongYuan Festival) - 561 Yishun Ring Road (Representative: Cher Kim Seah,Chi Hwee, Yan Yi, Agnes). Auction item included.</t>
-  </si>
-  <si>
     <t>华报善堂中元会 (代表：徐金声, Chi Hwee, Yan Yi, Agnes, Jin Hoa）。筹款活动包括义标。</t>
   </si>
   <si>
-    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Doran, Pei Yuen)</t>
-  </si>
-  <si>
     <t>[日期未确认] 义顺镇商贩联合中元会歌台 (代表：徐金声, Doran, Pei Yuen）</t>
   </si>
   <si>
@@ -844,9 +808,6 @@
     <t>南凤善堂中元会晚宴（200人）</t>
   </si>
   <si>
-    <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon dinner (200 pax)</t>
-  </si>
-  <si>
     <t>咖啡老友，大牌110咖啡店，早上8点30分至9点30分</t>
   </si>
   <si>
@@ -878,6 +839,45 @@
   </si>
   <si>
     <t>3 August 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temple Dinner - 元龙聖庙（关帝聖君兴诸众神诞）(Representative: Cher Kim Seah, Agnes, Bryan, Kathy, Jin Hoa - all to arrive by 7pm). Auction item included. </t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - Block 137 Yishun Ring Road (Representative: Cher Kim Seah, Agnes, Yan Yi - all to arrive by 7pm). Auction item included.</t>
+  </si>
+  <si>
+    <t>Chong Pang 61st National Day Dinner 2026, 7-10pm at Chong Pang 165 Hardcourt. (Representative: William Tan, Bill Tan - all to arrive by 7pm)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - YS ONE, 1 Yishun Street 23 (Representative: Bryan, 丽菁, 丽丝和先生 - all to arrive by 7pm)</t>
+  </si>
+  <si>
+    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 7 Gambas Crescent, ARK@Gambas Level 2 (Representative: Doran, Pei Yuen, Chi Hwee, 晓晓 - all to arrive by 7pm)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - 724 Yishun Street 71 (Representative: Chew Kim Cheong, Kathy, 丽菁, 丽丝和先生 - all to arrive by 7pm)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - 561 Yishun Ring Road (Representative: Cher Kim Seah,Chi Hwee, Yan Yi, Agnes - all to arrive by 7pm). Auction item included.</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - Jurong Safra Pearl Garden Restaurant (Representative: Neo Tian Siah, Kathy, Jin Hoa - all to arrive by 7pm)</t>
+  </si>
+  <si>
+    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Pei Yuen, Yan Yi - all to arrive by 7pm). Auction item included.</t>
+  </si>
+  <si>
+    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Doran, Pei Yuen - all to arrive by 7pm)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon (Representative: Neo Tian Siah, NHWSS office staff, 5 front desk, 晓晓 - all to arrive by 7pm). Auction item included.</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon dinner (200 pax) - all to arrive by 7pm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunar July (ZhongYuan Festival) - Blk 838 Yishun Street 81 (Representative: Doran, Bryan, 丽菁, 丽丝和先生 - all to arrive by 7pm) </t>
   </si>
 </sst>
 </file>
@@ -1866,7 +1866,7 @@
         <v>160</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -1885,7 +1885,7 @@
         <v>162</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -1904,7 +1904,7 @@
         <v>164</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -1923,7 +1923,7 @@
         <v>166</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -2088,10 +2088,10 @@
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>126</v>
@@ -2107,13 +2107,13 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>238</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -2126,13 +2126,13 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="D30" s="16" t="s">
         <v>239</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -2145,13 +2145,13 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>248</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -2164,13 +2164,13 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>236</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -2183,13 +2183,13 @@
         <v>Wed</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="D33" t="s">
+        <v>249</v>
+      </c>
+      <c r="E33" s="11" t="s">
         <v>258</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -2221,13 +2221,13 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -2240,13 +2240,13 @@
         <v>Tue</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -2259,13 +2259,13 @@
         <v>Thu</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>237</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
@@ -2278,13 +2278,13 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="D38" s="16" t="s">
         <v>240</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
@@ -2297,13 +2297,13 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
@@ -2335,13 +2335,13 @@
         <v>Mon</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="D41" s="16" t="s">
         <v>241</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
@@ -2354,13 +2354,13 @@
         <v>Tue</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
@@ -2373,13 +2373,13 @@
         <v>Wed</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
@@ -2411,10 +2411,10 @@
         <v>Fri</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="E45" s="11" t="s">
         <v>129</v>
@@ -2455,7 +2455,7 @@
         <v>216</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="G47" s="19"/>
     </row>
@@ -2475,7 +2475,7 @@
         <v>217</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
@@ -2494,7 +2494,7 @@
         <v>218</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
@@ -2583,7 +2583,7 @@
         <v>Fri</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="D54" s="11" t="s">
         <v>223</v>
@@ -2621,13 +2621,13 @@
         <v>Thu</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
@@ -2684,7 +2684,7 @@
         <v>227</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
@@ -2722,7 +2722,7 @@
         <v>228</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
@@ -2741,7 +2741,7 @@
         <v>229</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
@@ -2760,7 +2760,7 @@
         <v>230</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
@@ -2855,7 +2855,7 @@
         <v>233</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
@@ -4198,7 +4198,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -4234,15 +4234,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4483,6 +4474,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4495,14 +4495,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4519,4 +4511,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="463" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFBF7FDA-766B-40A1-817C-9B064714A02E}"/>
+  <xr:revisionPtr revIDLastSave="472" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B9A1738-E816-4E70-AA8F-FFAD42B4FA8C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Info" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$77</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="280">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -823,9 +823,6 @@
     <t>Fundraising, Partnership/CSR</t>
   </si>
   <si>
-    <t>CC Invitation</t>
-  </si>
-  <si>
     <t>[Tentative] CNY Dinner – CSR (JustCo or MS Project) – either 18 Feb or 19 Feb</t>
   </si>
   <si>
@@ -878,6 +875,12 @@
   </si>
   <si>
     <t xml:space="preserve">Lunar July (ZhongYuan Festival) - Blk 838 Yishun Street 81 (Representative: Doran, Bryan, 丽菁, 丽丝和先生 - all to arrive by 7pm) </t>
+  </si>
+  <si>
+    <t>Invitation</t>
+  </si>
+  <si>
+    <t>North West District Meeting and Council Appointment Ceremony 2026. 6pm-9pm. (Representative: Jin Hoa)</t>
   </si>
 </sst>
 </file>
@@ -1557,7 +1560,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -1590,7 +1593,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="13" t="str">
-        <f t="shared" ref="B2:B49" si="0">TEXT($A2,"ddd")</f>
+        <f t="shared" ref="B2:B50" si="0">TEXT($A2,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -2107,7 +2110,7 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>238</v>
@@ -2126,7 +2129,7 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D30" s="16" t="s">
         <v>239</v>
@@ -2145,13 +2148,13 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>248</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -2164,7 +2167,7 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>236</v>
@@ -2183,7 +2186,7 @@
         <v>Wed</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D33" t="s">
         <v>249</v>
@@ -2221,7 +2224,7 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>250</v>
@@ -2240,7 +2243,7 @@
         <v>Tue</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D36" s="16" t="s">
         <v>251</v>
@@ -2259,7 +2262,7 @@
         <v>Thu</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>237</v>
@@ -2278,7 +2281,7 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D38" s="16" t="s">
         <v>240</v>
@@ -2297,7 +2300,7 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>252</v>
@@ -2335,7 +2338,7 @@
         <v>Mon</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D41" s="16" t="s">
         <v>241</v>
@@ -2354,7 +2357,7 @@
         <v>Tue</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D42" s="16" t="s">
         <v>254</v>
@@ -2373,7 +2376,7 @@
         <v>Wed</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D43" s="16" t="s">
         <v>253</v>
@@ -2384,427 +2387,425 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="12">
+        <f>DATE(2026,9,18)</f>
+        <v>46283</v>
+      </c>
+      <c r="B44" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="12">
         <f>DATE(2026,9,20)</f>
         <v>46285</v>
       </c>
-      <c r="B44" s="13" t="str">
+      <c r="B45" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C45" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D45" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E45" s="11" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="12">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" s="12">
         <f>DATE(2026,10,9)</f>
         <v>46304</v>
       </c>
-      <c r="B45" s="13" t="str">
+      <c r="B46" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C46" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="D46" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="D45" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="E45" s="11" t="s">
+      <c r="E46" s="11" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" s="12">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="12">
         <f>DATE(2026,10,10)</f>
         <v>46305</v>
       </c>
-      <c r="B46" s="13" t="str">
+      <c r="B47" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C47" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D47" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E47" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="12">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" s="12">
         <f>DATE(2026,10,12)</f>
         <v>46307</v>
       </c>
-      <c r="B47" s="13" t="str">
+      <c r="B48" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C48" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D48" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E48" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="G47" s="19"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" s="12">
+      <c r="G48" s="19"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="12">
         <f>DATE(2026,10,13)</f>
         <v>46308</v>
       </c>
-      <c r="B48" s="13" t="str">
+      <c r="B49" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C49" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D49" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E49" s="11" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="12">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="12">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
       </c>
-      <c r="B49" s="13" t="str">
+      <c r="B50" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C50" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D50" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E50" s="11" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="12">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="12">
         <f>DATE(2026,10,31)</f>
         <v>46326</v>
       </c>
-      <c r="B50" s="13" t="str">
-        <f t="shared" ref="B50:B76" si="2">TEXT($A50,"ddd")</f>
+      <c r="B51" s="13" t="str">
+        <f t="shared" ref="B51:B77" si="2">TEXT($A51,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C51" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D51" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E51" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="12">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" s="12">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
-      </c>
-      <c r="B51" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Tue</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="12">
-        <f>DATE(2026,11,10)</f>
-        <v>46336</v>
       </c>
       <c r="B52" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="12">
+        <f>DATE(2026,11,10)</f>
+        <v>46336</v>
+      </c>
+      <c r="B53" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Tue</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" s="12">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B53" s="13" t="str">
+      <c r="B54" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C54" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D54" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E54" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="12">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B54" s="13" t="str">
+      <c r="B55" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C55" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D55" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E55" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="12">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" s="12">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B55" s="13" t="str">
+      <c r="B56" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C56" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D56" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E56" s="11" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="12">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" s="12">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B56" s="13" t="str">
+      <c r="B57" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C57" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="D57" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="D56" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="E56" s="11" t="s">
+      <c r="E57" s="11" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="12">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" s="12">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B57" s="13" t="str">
+      <c r="B58" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C58" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D58" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E58" s="11" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="12">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" s="12">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B58" s="13" t="str">
+      <c r="B59" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C59" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D59" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E59" s="11" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="12">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" s="12">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
       </c>
-      <c r="B59" s="13" t="str">
+      <c r="B60" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="C60" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D60" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E60" s="11" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="12">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" s="12">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
       </c>
-      <c r="B60" s="13" t="str">
+      <c r="B61" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C61" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D61" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E61" s="11" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" s="12">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" s="12">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B61" s="13" t="str">
+      <c r="B62" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C62" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D62" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E62" s="11" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" s="12">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B62" s="13" t="str">
+      <c r="B63" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C63" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D63" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E63" s="11" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="12">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B63" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A64" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
       </c>
       <c r="B64" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>126</v>
+        <v>258</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B65" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B66" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2822,18 +2823,18 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="12">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B67" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E67" s="11" t="s">
         <v>129</v>
@@ -2841,56 +2842,56 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="12">
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
+      </c>
+      <c r="B68" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" s="12">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B68" s="13" t="str">
+      <c r="B69" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C69" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D69" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="E68" s="11" t="s">
+      <c r="E69" s="11" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A69" s="12">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" s="12">
         <f>DATE(2027,8,20)</f>
         <v>46619</v>
-      </c>
-      <c r="B69" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="E69" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A70" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
       </c>
       <c r="B70" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>129</v>
@@ -2898,46 +2899,46 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="12">
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
+      </c>
+      <c r="B71" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B71" s="13" t="str">
+      <c r="B72" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C72" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="D71" s="11" t="s">
+      <c r="D72" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="E71" s="11" t="s">
+      <c r="E72" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A72" s="12">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" s="12">
         <f>DATE(2027,10,1)</f>
         <v>46661</v>
-      </c>
-      <c r="B72" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D72" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A73" s="12">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
       </c>
       <c r="B73" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2955,8 +2956,8 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="12">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
       </c>
       <c r="B74" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2974,8 +2975,8 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
       </c>
       <c r="B75" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2993,25 +2994,44 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="12">
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
+      </c>
+      <c r="B76" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" s="12">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B76" s="13" t="str">
+      <c r="B77" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C77" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D76" s="16" t="s">
+      <c r="D77" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E77" s="11" t="s">
         <v>136</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E76" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E77" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
@@ -4198,7 +4218,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -4234,6 +4254,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4474,15 +4503,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4495,6 +4515,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4511,12 +4539,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="472" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B9A1738-E816-4E70-AA8F-FFAD42B4FA8C}"/>
+  <xr:revisionPtr revIDLastSave="474" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2E0FBF8-51CE-4FDA-B38B-97C4386C05B0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -823,6 +823,9 @@
     <t>Fundraising, Partnership/CSR</t>
   </si>
   <si>
+    <t>CC Invitation</t>
+  </si>
+  <si>
     <t>[Tentative] CNY Dinner – CSR (JustCo or MS Project) – either 18 Feb or 19 Feb</t>
   </si>
   <si>
@@ -875,9 +878,6 @@
   </si>
   <si>
     <t xml:space="preserve">Lunar July (ZhongYuan Festival) - Blk 838 Yishun Street 81 (Representative: Doran, Bryan, 丽菁, 丽丝和先生 - all to arrive by 7pm) </t>
-  </si>
-  <si>
-    <t>Invitation</t>
   </si>
   <si>
     <t>North West District Meeting and Council Appointment Ceremony 2026. 6pm-9pm. (Representative: Jin Hoa)</t>
@@ -2110,7 +2110,7 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>238</v>
@@ -2129,7 +2129,7 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D30" s="16" t="s">
         <v>239</v>
@@ -2148,13 +2148,13 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>248</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -2167,7 +2167,7 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>236</v>
@@ -2186,7 +2186,7 @@
         <v>Wed</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D33" t="s">
         <v>249</v>
@@ -2224,7 +2224,7 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>250</v>
@@ -2243,7 +2243,7 @@
         <v>Tue</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D36" s="16" t="s">
         <v>251</v>
@@ -2262,7 +2262,7 @@
         <v>Thu</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>237</v>
@@ -2281,7 +2281,7 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D38" s="16" t="s">
         <v>240</v>
@@ -2300,7 +2300,7 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>252</v>
@@ -2338,7 +2338,7 @@
         <v>Mon</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D41" s="16" t="s">
         <v>241</v>
@@ -2357,7 +2357,7 @@
         <v>Tue</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D42" s="16" t="s">
         <v>254</v>
@@ -2376,7 +2376,7 @@
         <v>Wed</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D43" s="16" t="s">
         <v>253</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="11" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
@@ -2431,10 +2431,10 @@
         <v>Fri</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>129</v>
@@ -2641,10 +2641,10 @@
         <v>Thu</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>259</v>
@@ -4218,7 +4218,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="474" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2E0FBF8-51CE-4FDA-B38B-97C4386C05B0}"/>
+  <xr:revisionPtr revIDLastSave="476" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E6604B9-4288-4B83-B3C3-FDF1C6D712B7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -823,9 +823,6 @@
     <t>Fundraising, Partnership/CSR</t>
   </si>
   <si>
-    <t>CC Invitation</t>
-  </si>
-  <si>
     <t>[Tentative] CNY Dinner – CSR (JustCo or MS Project) – either 18 Feb or 19 Feb</t>
   </si>
   <si>
@@ -881,6 +878,9 @@
   </si>
   <si>
     <t>North West District Meeting and Council Appointment Ceremony 2026. 6pm-9pm. (Representative: Jin Hoa)</t>
+  </si>
+  <si>
+    <t>Govt. Agency Invitation</t>
   </si>
 </sst>
 </file>
@@ -2110,7 +2110,7 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>238</v>
@@ -2129,7 +2129,7 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D30" s="16" t="s">
         <v>239</v>
@@ -2148,13 +2148,13 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>248</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -2167,7 +2167,7 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>236</v>
@@ -2186,7 +2186,7 @@
         <v>Wed</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D33" t="s">
         <v>249</v>
@@ -2224,7 +2224,7 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>250</v>
@@ -2243,7 +2243,7 @@
         <v>Tue</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D36" s="16" t="s">
         <v>251</v>
@@ -2262,7 +2262,7 @@
         <v>Thu</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>237</v>
@@ -2281,7 +2281,7 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D38" s="16" t="s">
         <v>240</v>
@@ -2300,7 +2300,7 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>252</v>
@@ -2338,7 +2338,7 @@
         <v>Mon</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D41" s="16" t="s">
         <v>241</v>
@@ -2357,7 +2357,7 @@
         <v>Tue</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D42" s="16" t="s">
         <v>254</v>
@@ -2376,7 +2376,7 @@
         <v>Wed</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D43" s="16" t="s">
         <v>253</v>
@@ -2395,11 +2395,11 @@
         <v>Fri</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="11" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
@@ -2431,10 +2431,10 @@
         <v>Fri</v>
       </c>
       <c r="C46" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="D46" s="11" t="s">
         <v>263</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>264</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>129</v>
@@ -2641,10 +2641,10 @@
         <v>Thu</v>
       </c>
       <c r="C57" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="D57" s="11" t="s">
         <v>261</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>262</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>259</v>
@@ -4218,7 +4218,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -4254,15 +4254,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4503,6 +4494,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4515,14 +4515,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4539,4 +4531,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="476" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E6604B9-4288-4B83-B3C3-FDF1C6D712B7}"/>
+  <xr:revisionPtr revIDLastSave="485" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D77CA27-EB0B-4BB2-8B86-D3D57942512A}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Info" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$78</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="282">
   <si>
     <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
   </si>
@@ -829,9 +829,6 @@
     <t>[未确认] 新春晚宴 – 企业社会责任（JustCo或MS项目）二月18日或二月19日</t>
   </si>
   <si>
-    <t>Wee Guan Construction CSR Mental Health Day (150 pax). 70 volunteers. Buffet, activities, goodie bag.</t>
-  </si>
-  <si>
     <t>Wee Guan Construction 企业社会责任（150人）</t>
   </si>
   <si>
@@ -881,6 +878,15 @@
   </si>
   <si>
     <t>Govt. Agency Invitation</t>
+  </si>
+  <si>
+    <t>Wee Guan Construction CSR Mental Health Day (150 pax). 70 volunteers. Buffet, activities, goodie bag. 9am to 1pm.</t>
+  </si>
+  <si>
+    <t>Building Nee Soon Together | Invitation to Dialogue Session</t>
+  </si>
+  <si>
+    <t>Building Nee Soon Together | Invitation to Dialogue Session. Location: Nee Soon South Community Club (30 Yishun Street 81, Singapore 768455). Format: Dialogue with Mr K. Shanmugam, Senior Minister, Coordinating Minister for National Security, Minister for Home Affairs and Advisors to Nee Soon GRC’s GROS. 3 to 6pm. (Representative: Stanley, Jin Hoa)</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1081,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1118,6 +1124,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1560,7 +1569,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -1593,7 +1602,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="13" t="str">
-        <f t="shared" ref="B2:B50" si="0">TEXT($A2,"ddd")</f>
+        <f t="shared" ref="B2:B51" si="0">TEXT($A2,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -2110,7 +2119,7 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>238</v>
@@ -2129,7 +2138,7 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D30" s="16" t="s">
         <v>239</v>
@@ -2148,13 +2157,13 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>248</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -2167,7 +2176,7 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>236</v>
@@ -2176,7 +2185,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="12">
         <f>DATE(2026,8,26)</f>
         <v>46260</v>
@@ -2186,7 +2195,7 @@
         <v>Wed</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D33" t="s">
         <v>249</v>
@@ -2195,7 +2204,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="12">
         <f>DATE(2026,8,28)</f>
         <v>46262</v>
@@ -2214,7 +2223,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="12">
         <f>DATE(2026,8,29)</f>
         <v>46263</v>
@@ -2224,7 +2233,7 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>250</v>
@@ -2233,7 +2242,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="12">
         <f>DATE(2026,9,1)</f>
         <v>46266</v>
@@ -2243,7 +2252,7 @@
         <v>Tue</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D36" s="16" t="s">
         <v>251</v>
@@ -2252,7 +2261,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="12">
         <f>DATE(2026,9,3)</f>
         <v>46268</v>
@@ -2262,7 +2271,7 @@
         <v>Thu</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>237</v>
@@ -2271,7 +2280,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="12">
         <f>DATE(2026,9,3)</f>
         <v>46268</v>
@@ -2281,7 +2290,7 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D38" s="16" t="s">
         <v>240</v>
@@ -2290,7 +2299,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="12">
         <f>DATE(2026,9,5)</f>
         <v>46270</v>
@@ -2300,7 +2309,7 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>252</v>
@@ -2309,7 +2318,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="12">
         <f>DATE(2026,9,5)</f>
         <v>46270</v>
@@ -2328,7 +2337,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="12">
         <f>DATE(2026,9,7)</f>
         <v>46272</v>
@@ -2338,7 +2347,7 @@
         <v>Mon</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D41" s="16" t="s">
         <v>241</v>
@@ -2347,7 +2356,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="12">
         <f>DATE(2026,9,8)</f>
         <v>46273</v>
@@ -2357,7 +2366,7 @@
         <v>Tue</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D42" s="16" t="s">
         <v>254</v>
@@ -2366,7 +2375,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="12">
         <f>DATE(2026,9,9)</f>
         <v>46274</v>
@@ -2376,7 +2385,7 @@
         <v>Wed</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D43" s="16" t="s">
         <v>253</v>
@@ -2385,7 +2394,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="12">
         <f>DATE(2026,9,18)</f>
         <v>46283</v>
@@ -2395,14 +2404,14 @@
         <v>Fri</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="11" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="12">
         <f>DATE(2026,9,20)</f>
         <v>46285</v>
@@ -2421,7 +2430,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="12">
         <f>DATE(2026,10,9)</f>
         <v>46304</v>
@@ -2431,400 +2440,400 @@
         <v>Fri</v>
       </c>
       <c r="C46" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="D46" s="11" t="s">
         <v>262</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>263</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" ht="38.5" x14ac:dyDescent="0.35">
       <c r="A47" s="12">
+        <f>DATE(2026,10,9)</f>
+        <v>46304</v>
+      </c>
+      <c r="B47" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" s="12">
         <f>DATE(2026,10,10)</f>
         <v>46305</v>
       </c>
-      <c r="B47" s="13" t="str">
+      <c r="B48" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C48" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D48" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E48" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" s="12">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" s="12">
         <f>DATE(2026,10,12)</f>
         <v>46307</v>
       </c>
-      <c r="B48" s="13" t="str">
+      <c r="B49" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C49" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D49" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E49" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="G48" s="19"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="12">
+      <c r="G49" s="19"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" s="12">
         <f>DATE(2026,10,13)</f>
         <v>46308</v>
       </c>
-      <c r="B49" s="13" t="str">
+      <c r="B50" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C50" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D50" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E50" s="11" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="12">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" s="12">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
       </c>
-      <c r="B50" s="13" t="str">
+      <c r="B51" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C51" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D51" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E51" s="11" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="12">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" s="12">
         <f>DATE(2026,10,31)</f>
         <v>46326</v>
       </c>
-      <c r="B51" s="13" t="str">
-        <f t="shared" ref="B51:B77" si="2">TEXT($A51,"ddd")</f>
+      <c r="B52" s="13" t="str">
+        <f t="shared" ref="B52:B78" si="2">TEXT($A52,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C52" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D52" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E52" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="12">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" s="12">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
-      </c>
-      <c r="B52" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Tue</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="12">
-        <f>DATE(2026,11,10)</f>
-        <v>46336</v>
       </c>
       <c r="B53" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
       <c r="C53" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54" s="12">
+        <f>DATE(2026,11,10)</f>
+        <v>46336</v>
+      </c>
+      <c r="B54" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Tue</v>
+      </c>
+      <c r="C54" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D54" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E54" s="11" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="12">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55" s="12">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B54" s="13" t="str">
+      <c r="B55" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C55" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="D54" s="16" t="s">
+      <c r="D55" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E55" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="12">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B55" s="13" t="str">
+      <c r="B56" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C56" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D56" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E56" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="12">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" s="12">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B56" s="13" t="str">
+      <c r="B57" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C57" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D57" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E57" s="11" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="12">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58" s="12">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B57" s="13" t="str">
+      <c r="B58" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C58" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D58" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E58" s="11" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="12">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" s="12">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B58" s="13" t="str">
+      <c r="B59" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C59" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D59" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E59" s="11" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="12">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" s="12">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B59" s="13" t="str">
+      <c r="B60" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C60" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D60" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E60" s="11" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="12">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" s="12">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
       </c>
-      <c r="B60" s="13" t="str">
+      <c r="B61" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="C61" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D61" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E61" s="11" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" s="12">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" s="12">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
       </c>
-      <c r="B61" s="13" t="str">
+      <c r="B62" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C62" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D62" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E62" s="11" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" s="12">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" s="12">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B62" s="13" t="str">
+      <c r="B63" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C63" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D63" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E63" s="11" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="12">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B63" s="13" t="str">
+      <c r="B64" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C64" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D64" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E64" s="11" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A64" s="12">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B64" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D64" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A65" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
       </c>
       <c r="B65" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>126</v>
+        <v>258</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B66" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B67" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2842,18 +2851,18 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="12">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B68" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E68" s="11" t="s">
         <v>129</v>
@@ -2861,56 +2870,56 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="12">
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
+      </c>
+      <c r="B69" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" s="12">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B69" s="13" t="str">
+      <c r="B70" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C70" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D70" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="E70" s="11" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A70" s="12">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" s="12">
         <f>DATE(2027,8,20)</f>
         <v>46619</v>
-      </c>
-      <c r="B70" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="D70" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="E70" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A71" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
       </c>
       <c r="B71" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>129</v>
@@ -2918,46 +2927,46 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="12">
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
+      </c>
+      <c r="B72" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B72" s="13" t="str">
+      <c r="B73" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C73" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="D72" s="11" t="s">
+      <c r="D73" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="E72" s="11" t="s">
+      <c r="E73" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A73" s="12">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" s="12">
         <f>DATE(2027,10,1)</f>
         <v>46661</v>
-      </c>
-      <c r="B73" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A74" s="12">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
       </c>
       <c r="B74" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2975,8 +2984,8 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="12">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
       </c>
       <c r="B75" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2994,8 +3003,8 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
       </c>
       <c r="B76" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3013,25 +3022,44 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="12">
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
+      </c>
+      <c r="B77" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" s="12">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B77" s="13" t="str">
+      <c r="B78" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C78" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D77" s="16" t="s">
+      <c r="D78" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="E77" s="11" t="s">
+      <c r="E78" s="11" t="s">
         <v>136</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E77" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E78" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
@@ -4218,7 +4246,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -4254,6 +4282,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4494,15 +4531,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4515,6 +4543,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4531,12 +4567,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="485" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D77CA27-EB0B-4BB2-8B86-D3D57942512A}"/>
+  <xr:revisionPtr revIDLastSave="486" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DBD88AB-5425-4621-81D6-D016A924F630}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,9 +43,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="282">
   <si>
-    <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会委员手册数据文件</t>
-  </si>
-  <si>
     <t>HOW THIS WORKS</t>
   </si>
   <si>
@@ -382,9 +379,6 @@
     <t>Vice Chairman</t>
   </si>
   <si>
-    <t>副会长委员</t>
-  </si>
-  <si>
     <t>Vice Chairman Committee</t>
   </si>
   <si>
@@ -496,9 +490,6 @@
     <t>开斋节午宴</t>
   </si>
   <si>
-    <t>常年会员大会暨第十届管理委员会选举</t>
-  </si>
-  <si>
     <t>By-election of Office Bearers (10th Term)</t>
   </si>
   <si>
@@ -514,9 +505,6 @@
     <t>10th Term Management Committee Sworn In</t>
   </si>
   <si>
-    <t>第十届管理委员会宣誓就职</t>
-  </si>
-  <si>
     <t>AISS交流活动暨寿像拍摄登记</t>
   </si>
   <si>
@@ -664,9 +652,6 @@
     <t>公关组</t>
   </si>
   <si>
-    <t>南凤福利协会 Nam Hong Welfare Service Society · For committee members reference 仅供委员参考</t>
-  </si>
-  <si>
     <t>[Tentative] Charity Walk - postpone to April 2027</t>
   </si>
   <si>
@@ -887,6 +872,21 @@
   </si>
   <si>
     <t>Building Nee Soon Together | Invitation to Dialogue Session. Location: Nee Soon South Community Club (30 Yishun Street 81, Singapore 768455). Format: Dialogue with Mr K. Shanmugam, Senior Minister, Coordinating Minister for National Security, Minister for Home Affairs and Advisors to Nee Soon GRC’s GROS. 3 to 6pm. (Representative: Stanley, Jin Hoa)</t>
+  </si>
+  <si>
+    <t>NHWSS COMMITTEE HANDBOOK — DATA FILE  南凤福利协会理事手册数据文件</t>
+  </si>
+  <si>
+    <t>常年会员大会暨第十届管理理事会选举</t>
+  </si>
+  <si>
+    <t>第十届管理理事会宣誓就职</t>
+  </si>
+  <si>
+    <t>副会长理事</t>
+  </si>
+  <si>
+    <t>南凤福利协会 Nam Hong Welfare Service Society · For committee members reference 仅供理事参考</t>
   </si>
 </sst>
 </file>
@@ -1459,7 +1459,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -1467,17 +1467,17 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
@@ -1485,62 +1485,62 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
@@ -1548,17 +1548,17 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1581,19 +1581,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>33</v>
-      </c>
       <c r="E1" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -1606,13 +1606,13 @@
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -1625,13 +1625,13 @@
         <v>Sun</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -1644,13 +1644,13 @@
         <v>Thu</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -1663,13 +1663,13 @@
         <v>Fri</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -1682,13 +1682,13 @@
         <v>Sat</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -1701,13 +1701,13 @@
         <v>Fri</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -1720,13 +1720,13 @@
         <v>Mon</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -1739,13 +1739,13 @@
         <v>Tue</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -1758,13 +1758,13 @@
         <v>Fri</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -1777,13 +1777,13 @@
         <v>Mon</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>151</v>
+        <v>278</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -1796,13 +1796,13 @@
         <v>Mon</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -1815,13 +1815,13 @@
         <v>Fri</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -1834,13 +1834,13 @@
         <v>Sun</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>157</v>
+        <v>279</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -1853,13 +1853,13 @@
         <v>Mon</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -1872,13 +1872,13 @@
         <v>Fri</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -1891,13 +1891,13 @@
         <v>Sat</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -1910,13 +1910,13 @@
         <v>Sun</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -1929,13 +1929,13 @@
         <v>Mon</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -1948,13 +1948,13 @@
         <v>Fri</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -1967,13 +1967,13 @@
         <v>Sat</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -1986,13 +1986,13 @@
         <v>Sat</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -2005,13 +2005,13 @@
         <v>Fri</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -2024,13 +2024,13 @@
         <v>Fri</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -2043,13 +2043,13 @@
         <v>Fri</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -2062,13 +2062,13 @@
         <v>Sat</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -2081,13 +2081,13 @@
         <v>Sat</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -2100,13 +2100,13 @@
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -2119,13 +2119,13 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -2138,13 +2138,13 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -2157,13 +2157,13 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -2176,13 +2176,13 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -2195,13 +2195,13 @@
         <v>Wed</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="D33" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -2214,13 +2214,13 @@
         <v>Fri</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -2233,13 +2233,13 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -2252,13 +2252,13 @@
         <v>Tue</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -2271,13 +2271,13 @@
         <v>Thu</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
@@ -2290,13 +2290,13 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -2309,13 +2309,13 @@
         <v>Sat</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -2328,13 +2328,13 @@
         <v>Sat</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -2347,13 +2347,13 @@
         <v>Mon</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
@@ -2366,13 +2366,13 @@
         <v>Tue</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -2385,13 +2385,13 @@
         <v>Wed</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="D43" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="E43" s="11" t="s">
         <v>253</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -2404,11 +2404,11 @@
         <v>Fri</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="11" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -2421,13 +2421,13 @@
         <v>Sun</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
@@ -2440,13 +2440,13 @@
         <v>Fri</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="38.5" x14ac:dyDescent="0.35">
@@ -2459,13 +2459,13 @@
         <v>Fri</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
@@ -2478,13 +2478,13 @@
         <v>Sat</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -2497,13 +2497,13 @@
         <v>Mon</v>
       </c>
       <c r="C49" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D49" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="D49" s="11" t="s">
-        <v>216</v>
-      </c>
       <c r="E49" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G49" s="19"/>
     </row>
@@ -2517,13 +2517,13 @@
         <v>Tue</v>
       </c>
       <c r="C50" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="D50" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="D50" s="11" t="s">
-        <v>217</v>
-      </c>
       <c r="E50" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -2536,13 +2536,13 @@
         <v>Wed</v>
       </c>
       <c r="C51" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="D51" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D51" s="11" t="s">
-        <v>218</v>
-      </c>
       <c r="E51" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -2555,13 +2555,13 @@
         <v>Sat</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -2574,13 +2574,13 @@
         <v>Tue</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -2593,13 +2593,13 @@
         <v>Tue</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -2612,13 +2612,13 @@
         <v>Wed</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -2631,13 +2631,13 @@
         <v>Fri</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -2650,13 +2650,13 @@
         <v>Sat</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -2669,13 +2669,13 @@
         <v>Thu</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
@@ -2688,13 +2688,13 @@
         <v>Fri</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -2707,13 +2707,13 @@
         <v>Thu</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -2726,13 +2726,13 @@
         <v>Sat</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -2745,13 +2745,13 @@
         <v>Fri</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -2764,13 +2764,13 @@
         <v>Wed</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -2783,13 +2783,13 @@
         <v>Thu</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
@@ -2802,13 +2802,13 @@
         <v>Fri</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
@@ -2821,13 +2821,13 @@
         <v>Fri</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
@@ -2840,13 +2840,13 @@
         <v>Fri</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
@@ -2859,13 +2859,13 @@
         <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
@@ -2878,13 +2878,13 @@
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
@@ -2897,13 +2897,13 @@
         <v>Mon</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
@@ -2916,13 +2916,13 @@
         <v>Fri</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
@@ -2935,13 +2935,13 @@
         <v>Fri</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
@@ -2954,13 +2954,13 @@
         <v>Sat</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
@@ -2973,13 +2973,13 @@
         <v>Fri</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
@@ -2992,13 +2992,13 @@
         <v>Fri</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
@@ -3011,13 +3011,13 @@
         <v>Fri</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
@@ -3030,13 +3030,13 @@
         <v>Fri</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
@@ -3049,13 +3049,13 @@
         <v>Thu</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -3081,16 +3081,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3098,13 +3098,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>39</v>
-      </c>
       <c r="D2" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3112,13 +3112,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="D3" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3126,13 +3126,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>43</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3140,13 +3140,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="D5" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3154,13 +3154,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="D6" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3168,13 +3168,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="D7" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3182,13 +3182,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>51</v>
-      </c>
       <c r="D8" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3196,13 +3196,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="D9" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3210,13 +3210,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>55</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3224,13 +3224,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="D11" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3238,11 +3238,11 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3250,11 +3250,11 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3262,13 +3262,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="D14" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3276,13 +3276,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>63</v>
-      </c>
       <c r="D15" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3290,13 +3290,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>65</v>
-      </c>
       <c r="D16" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3304,13 +3304,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3318,13 +3318,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="D18" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3332,13 +3332,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="D19" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3346,13 +3346,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>72</v>
-      </c>
       <c r="D20" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3360,13 +3360,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>74</v>
-      </c>
       <c r="D21" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3374,13 +3374,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="D22" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3388,13 +3388,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>78</v>
-      </c>
       <c r="D23" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3402,13 +3402,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>80</v>
-      </c>
       <c r="D24" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3416,13 +3416,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>82</v>
-      </c>
       <c r="D25" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3430,13 +3430,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>84</v>
-      </c>
       <c r="D26" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -3459,22 +3459,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -3482,19 +3482,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="D2" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -3502,19 +3502,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>49</v>
-      </c>
       <c r="D3" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -3522,19 +3522,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>113</v>
+        <v>280</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -3542,19 +3542,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="D5" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>113</v>
+        <v>280</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -3562,19 +3562,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="D6" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>113</v>
+        <v>280</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -3582,19 +3582,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="D7" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>113</v>
+        <v>280</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -3602,19 +3602,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="D8" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>113</v>
+        <v>280</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -3622,19 +3622,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" t="s">
         <v>79</v>
       </c>
-      <c r="C9" t="s">
-        <v>80</v>
-      </c>
       <c r="D9" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -3642,19 +3642,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" t="s">
         <v>75</v>
       </c>
-      <c r="C10" t="s">
-        <v>76</v>
-      </c>
       <c r="D10" s="14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -3662,19 +3662,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
         <v>73</v>
       </c>
-      <c r="C11" t="s">
-        <v>74</v>
-      </c>
       <c r="D11" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -3682,19 +3682,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="C12" t="s">
-        <v>68</v>
-      </c>
       <c r="D12" s="14" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -3719,504 +3719,504 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>28</v>
-      </c>
       <c r="C1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>21</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
       </c>
       <c r="D2" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="16" t="s">
-        <v>43</v>
-      </c>
       <c r="F2" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E3" s="16"/>
       <c r="F3" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
       </c>
       <c r="D6" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="16" t="s">
-        <v>68</v>
-      </c>
       <c r="F6" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
       </c>
       <c r="D7" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="16" t="s">
-        <v>72</v>
-      </c>
       <c r="F7" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
       </c>
       <c r="D8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="16" t="s">
-        <v>53</v>
-      </c>
       <c r="F8" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
       </c>
       <c r="D9" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E9" s="16" t="s">
-        <v>78</v>
-      </c>
       <c r="F9" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
       </c>
       <c r="D10" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="16" t="s">
-        <v>82</v>
-      </c>
       <c r="F10" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
       </c>
       <c r="D11" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="F11" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
       </c>
       <c r="D12" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="16" t="s">
-        <v>63</v>
-      </c>
       <c r="F12" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
       </c>
       <c r="D13" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="16" t="s">
-        <v>41</v>
-      </c>
       <c r="F13" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
       </c>
       <c r="D14" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="16" t="s">
-        <v>39</v>
-      </c>
       <c r="F14" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
       </c>
       <c r="D15" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="16" t="s">
-        <v>45</v>
-      </c>
       <c r="F15" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
       </c>
       <c r="D16" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="16" t="s">
-        <v>84</v>
-      </c>
       <c r="F16" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
       </c>
       <c r="D17" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="16" t="s">
-        <v>65</v>
-      </c>
       <c r="F17" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
       </c>
       <c r="D18" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="16" t="s">
-        <v>76</v>
-      </c>
       <c r="F18" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
       </c>
       <c r="D19" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E19" s="16" t="s">
-        <v>78</v>
-      </c>
       <c r="F19" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
       </c>
       <c r="D20" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="16" t="s">
-        <v>72</v>
-      </c>
       <c r="F20" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
       </c>
       <c r="D21" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="16" t="s">
-        <v>84</v>
-      </c>
       <c r="F21" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
       </c>
       <c r="D22" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="16" t="s">
-        <v>39</v>
-      </c>
       <c r="F22" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -4235,34 +4235,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>207</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -4282,15 +4282,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4531,6 +4522,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4543,14 +4543,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4567,4 +4559,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="486" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DBD88AB-5425-4621-81D6-D016A924F630}"/>
+  <xr:revisionPtr revIDLastSave="494" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{807CD7A4-AB09-4D3E-82FB-93F9455594AC}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Info" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$79</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="284">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -887,6 +887,12 @@
   </si>
   <si>
     <t>南凤福利协会 Nam Hong Welfare Service Society · For committee members reference 仅供理事参考</t>
+  </si>
+  <si>
+    <t>中邦，健康之歌。 八月二十九日，早上9点30分至中午12点30分。医师梁芷维健康讲座 - 动养生，食养命。</t>
+  </si>
+  <si>
+    <t>Songs of Health. Chong Pang Zone. Blk 108, Yishun Ring Road #01-301. 9.30am to 12.30pm (Representative: Physician Leong Chin Mee - Health Talk)</t>
   </si>
 </sst>
 </file>
@@ -1569,7 +1575,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -1602,7 +1608,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="13" t="str">
-        <f t="shared" ref="B2:B51" si="0">TEXT($A2,"ddd")</f>
+        <f t="shared" ref="B2:B52" si="0">TEXT($A2,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -2096,7 +2102,7 @@
         <v>46239</v>
       </c>
       <c r="B28" s="13" t="str">
-        <f t="shared" ref="B28:B38" si="1">TEXT($A28,"ddd")</f>
+        <f t="shared" ref="B28:B39" si="1">TEXT($A28,"ddd")</f>
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
@@ -2233,48 +2239,48 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>245</v>
+        <v>282</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="12">
+        <f>DATE(2026,8,29)</f>
+        <v>46263</v>
+      </c>
+      <c r="B36" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Sat</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="12">
         <f>DATE(2026,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="B36" s="13" t="str">
+      <c r="B37" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Tue</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C37" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D37" s="16" t="s">
         <v>246</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="12">
-        <f>DATE(2026,9,3)</f>
-        <v>46268</v>
-      </c>
-      <c r="B37" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Thu</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>232</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>253</v>
@@ -2290,10 +2296,10 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>235</v>
+        <v>266</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>232</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>253</v>
@@ -2301,18 +2307,18 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="12">
-        <f>DATE(2026,9,5)</f>
-        <v>46270</v>
+        <f>DATE(2026,9,3)</f>
+        <v>46268</v>
       </c>
       <c r="B39" s="13" t="str">
-        <f>TEXT($A39,"ddd")</f>
-        <v>Sat</v>
+        <f t="shared" si="1"/>
+        <v>Thu</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>247</v>
+        <v>267</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>235</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>253</v>
@@ -2324,132 +2330,132 @@
         <v>46270</v>
       </c>
       <c r="B40" s="13" t="str">
+        <f>TEXT($A40,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" s="12">
+        <f>DATE(2026,9,5)</f>
+        <v>46270</v>
+      </c>
+      <c r="B41" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C41" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D41" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E41" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="12">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="12">
         <f>DATE(2026,9,7)</f>
         <v>46272</v>
       </c>
-      <c r="B41" s="13" t="str">
-        <f>TEXT($A41,"ddd")</f>
+      <c r="B42" s="13" t="str">
+        <f>TEXT($A42,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C42" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D42" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E42" s="11" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="12">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="12">
         <f>DATE(2026,9,8)</f>
         <v>46273</v>
       </c>
-      <c r="B42" s="13" t="str">
-        <f>TEXT($A42,"ddd")</f>
+      <c r="B43" s="13" t="str">
+        <f>TEXT($A43,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C43" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D43" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E43" s="11" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="12">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" s="12">
         <f>DATE(2026,9,9)</f>
         <v>46274</v>
       </c>
-      <c r="B43" s="13" t="str">
-        <f>TEXT($A43,"ddd")</f>
+      <c r="B44" s="13" t="str">
+        <f>TEXT($A44,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C44" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D44" s="16" t="s">
         <v>248</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E44" s="11" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="12">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" s="12">
         <f>DATE(2026,9,18)</f>
         <v>46283</v>
       </c>
-      <c r="B44" s="13" t="str">
+      <c r="B45" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C45" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11" t="s">
+      <c r="D45" s="11"/>
+      <c r="E45" s="11" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="12">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" s="12">
         <f>DATE(2026,9,20)</f>
         <v>46285</v>
       </c>
-      <c r="B45" s="13" t="str">
+      <c r="B46" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C46" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D46" s="11" t="s">
         <v>171</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="12">
-        <f>DATE(2026,10,9)</f>
-        <v>46304</v>
-      </c>
-      <c r="B46" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Fri</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>257</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="38.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="12">
         <f>DATE(2026,10,9)</f>
         <v>46304</v>
@@ -2458,401 +2464,401 @@
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C47" s="20" t="s">
+      <c r="C47" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="12">
+        <f>DATE(2026,10,9)</f>
+        <v>46304</v>
+      </c>
+      <c r="B48" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="C48" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D48" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E48" s="11" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="12">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" s="12">
         <f>DATE(2026,10,10)</f>
         <v>46305</v>
       </c>
-      <c r="B48" s="13" t="str">
+      <c r="B49" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C49" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D49" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E49" s="11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49" s="12">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" s="12">
         <f>DATE(2026,10,12)</f>
         <v>46307</v>
       </c>
-      <c r="B49" s="13" t="str">
+      <c r="B50" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C50" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D50" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E50" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="G49" s="19"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A50" s="12">
+      <c r="G50" s="19"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" s="12">
         <f>DATE(2026,10,13)</f>
         <v>46308</v>
       </c>
-      <c r="B50" s="13" t="str">
+      <c r="B51" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C51" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D51" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E51" s="11" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A51" s="12">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" s="12">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
       </c>
-      <c r="B51" s="13" t="str">
+      <c r="B52" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C52" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D52" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E52" s="11" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52" s="12">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" s="12">
         <f>DATE(2026,10,31)</f>
         <v>46326</v>
       </c>
-      <c r="B52" s="13" t="str">
-        <f t="shared" ref="B52:B78" si="2">TEXT($A52,"ddd")</f>
+      <c r="B53" s="13" t="str">
+        <f t="shared" ref="B53:B79" si="2">TEXT($A53,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C53" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D53" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E53" s="11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" s="12">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54" s="12">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
-      </c>
-      <c r="B53" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Tue</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" s="12">
-        <f>DATE(2026,11,10)</f>
-        <v>46336</v>
       </c>
       <c r="B54" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="12">
+        <f>DATE(2026,11,10)</f>
+        <v>46336</v>
+      </c>
+      <c r="B55" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Tue</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56" s="12">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B55" s="13" t="str">
+      <c r="B56" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C56" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="D55" s="16" t="s">
+      <c r="D56" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E56" s="11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56" s="12">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B56" s="13" t="str">
+      <c r="B57" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="C57" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D57" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E57" s="11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A57" s="12">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58" s="12">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B57" s="13" t="str">
+      <c r="B58" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C58" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D58" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E58" s="11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A58" s="12">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" s="12">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B58" s="13" t="str">
+      <c r="B59" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C59" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D59" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E59" s="11" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A59" s="12">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" s="12">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B59" s="13" t="str">
+      <c r="B60" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C60" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D60" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E60" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A60" s="12">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" s="12">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B60" s="13" t="str">
+      <c r="B61" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C61" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D61" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E61" s="11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61" s="12">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" s="12">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
       </c>
-      <c r="B61" s="13" t="str">
+      <c r="B62" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C62" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D62" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E62" s="11" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A62" s="12">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" s="12">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
       </c>
-      <c r="B62" s="13" t="str">
+      <c r="B63" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C63" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D63" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E63" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A63" s="12">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" s="12">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B63" s="13" t="str">
+      <c r="B64" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C64" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D64" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E64" s="11" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A64" s="12">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B64" s="13" t="str">
+      <c r="B65" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C65" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D65" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="E65" s="11" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A65" s="12">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B65" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D65" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A66" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
       </c>
       <c r="B66" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>124</v>
+        <v>253</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B67" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B68" s="13" t="str">
         <f t="shared" si="2"/>
@@ -2870,18 +2876,18 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="12">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B69" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>127</v>
@@ -2889,56 +2895,56 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
+      </c>
+      <c r="B70" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" s="12">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B70" s="13" t="str">
+      <c r="B71" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C71" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D71" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E71" s="11" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A71" s="12">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" s="12">
         <f>DATE(2027,8,20)</f>
         <v>46619</v>
-      </c>
-      <c r="B71" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D71" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="E71" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A72" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
       </c>
       <c r="B72" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>127</v>
@@ -2946,46 +2952,46 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="12">
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
+      </c>
+      <c r="B73" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B73" s="13" t="str">
+      <c r="B74" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C74" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="D73" s="11" t="s">
+      <c r="D74" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="E74" s="11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A74" s="12">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" s="12">
         <f>DATE(2027,10,1)</f>
         <v>46661</v>
-      </c>
-      <c r="B74" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D74" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="E74" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A75" s="12">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
       </c>
       <c r="B75" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3003,8 +3009,8 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="12">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
       </c>
       <c r="B76" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3022,8 +3028,8 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
       </c>
       <c r="B77" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3041,25 +3047,44 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="12">
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
+      </c>
+      <c r="B78" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" s="12">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B78" s="13" t="str">
+      <c r="B79" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="C79" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="D78" s="16" t="s">
+      <c r="D79" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="E78" s="11" t="s">
+      <c r="E79" s="11" t="s">
         <v>134</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E78" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E79" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
@@ -4282,6 +4307,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4522,15 +4556,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4543,6 +4568,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4559,12 +4592,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="494" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{807CD7A4-AB09-4D3E-82FB-93F9455594AC}"/>
+  <xr:revisionPtr revIDLastSave="517" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C9D9629-D6BB-429F-A9A1-51B1DE05D439}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Info" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$81</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="287">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -745,9 +745,6 @@
     <t>元龙聖庙（关帝聖君兴诸众神诞）(代表：徐金声, Agnes, Bryan, Kathy, Jin Hoa）。筹款活动包括义标。</t>
   </si>
   <si>
-    <t>大牌137中元会 (代表：徐金声,Agnes, Yan Yi）。筹款活动包括义标。</t>
-  </si>
-  <si>
     <t>[日期未确认] 义顺镇商贩联合中元会 (代表：徐金声, Pei Yuen, Yan Yi）。筹款活动包括义标。</t>
   </si>
   <si>
@@ -775,9 +772,6 @@
     <t>2026年中邦第61届国庆晚宴，晚上7点至10点。（代表：陈浚纬, Bill Tan）</t>
   </si>
   <si>
-    <t>[日期未确认] 方舟@岗巴士中元会 (代表：Doran, Pei Yuen, Chee Hwee, 晓晓）</t>
-  </si>
-  <si>
     <t>717 商店中元会 (代表：周锦昌, Kathy, 丽菁, 丽丝和先生）</t>
   </si>
   <si>
@@ -823,18 +817,12 @@
     <t xml:space="preserve">Temple Dinner - 元龙聖庙（关帝聖君兴诸众神诞）(Representative: Cher Kim Seah, Agnes, Bryan, Kathy, Jin Hoa - all to arrive by 7pm). Auction item included. </t>
   </si>
   <si>
-    <t>Lunar July (ZhongYuan Festival) - Block 137 Yishun Ring Road (Representative: Cher Kim Seah, Agnes, Yan Yi - all to arrive by 7pm). Auction item included.</t>
-  </si>
-  <si>
     <t>Chong Pang 61st National Day Dinner 2026, 7-10pm at Chong Pang 165 Hardcourt. (Representative: William Tan, Bill Tan - all to arrive by 7pm)</t>
   </si>
   <si>
     <t>Lunar July (ZhongYuan Festival) - YS ONE, 1 Yishun Street 23 (Representative: Bryan, 丽菁, 丽丝和先生 - all to arrive by 7pm)</t>
   </si>
   <si>
-    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 7 Gambas Crescent, ARK@Gambas Level 2 (Representative: Doran, Pei Yuen, Chi Hwee, 晓晓 - all to arrive by 7pm)</t>
-  </si>
-  <si>
     <t>Lunar July (ZhongYuan Festival) - 724 Yishun Street 71 (Representative: Chew Kim Cheong, Kathy, 丽菁, 丽丝和先生 - all to arrive by 7pm)</t>
   </si>
   <si>
@@ -893,6 +881,27 @@
   </si>
   <si>
     <t>Songs of Health. Chong Pang Zone. Blk 108, Yishun Ring Road #01-301. 9.30am to 12.30pm (Representative: Physician Leong Chin Mee - Health Talk)</t>
+  </si>
+  <si>
+    <t>Kopi Kaki session at [location TBA], 830am to 930am</t>
+  </si>
+  <si>
+    <t>咖啡老友 【地址未定】早上8点30分至9点30分</t>
+  </si>
+  <si>
+    <t>Charity Governance Conference 2026. 9.30am to 3.30pm. Raffles City Convention Centre. Conference 9.30am - 12pm, Workshop 2pm - 3.30pm. (Attendees: GMO staff)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - 7 Gambas Crescent, ARK@Gambas Level 2 (Representative: Doran, Pei Yuen, Chi Hwee, Agnes - all to arrive by 7pm)</t>
+  </si>
+  <si>
+    <t>方舟@岗巴士中元会 (代表：Doran, Pei Yuen, Chi Hwee, Agnes）</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - Block 139 Yishun Ring Road (Representative: Cher Kim Seah, Agnes, Yan Yi, Kathy - all to arrive by 7pm). Auction item included.</t>
+  </si>
+  <si>
+    <t>大牌139中元会 (代表：徐金声,Agnes, Yan Yi, Kathy）。筹款活动包括义标。</t>
   </si>
 </sst>
 </file>
@@ -902,7 +911,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -960,6 +969,14 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1084,10 +1101,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1133,8 +1151,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1465,7 +1485,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -1575,7 +1595,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -1608,7 +1628,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="13" t="str">
-        <f t="shared" ref="B2:B52" si="0">TEXT($A2,"ddd")</f>
+        <f t="shared" ref="B2:B54" si="0">TEXT($A2,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -1767,7 +1787,7 @@
         <v>131</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>124</v>
@@ -1786,7 +1806,7 @@
         <v>133</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>132</v>
@@ -1843,7 +1863,7 @@
         <v>153</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>132</v>
@@ -1884,7 +1904,7 @@
         <v>156</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -1903,7 +1923,7 @@
         <v>158</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -1922,7 +1942,7 @@
         <v>160</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -1941,7 +1961,7 @@
         <v>162</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -1957,7 +1977,7 @@
         <v>131</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>124</v>
@@ -1995,7 +2015,7 @@
         <v>131</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>124</v>
@@ -2052,7 +2072,7 @@
         <v>131</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>124</v>
@@ -2071,7 +2091,7 @@
         <v>131</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>124</v>
@@ -2087,10 +2107,10 @@
         <v>Sat</v>
       </c>
       <c r="C27" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>238</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>239</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>127</v>
@@ -2106,10 +2126,10 @@
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>124</v>
@@ -2125,13 +2145,13 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>233</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -2144,13 +2164,13 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -2163,13 +2183,13 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -2182,51 +2202,51 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>231</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="12">
-        <f>DATE(2026,8,26)</f>
-        <v>46260</v>
+        <f>DATE(2026,8,28)</f>
+        <v>46262</v>
       </c>
       <c r="B33" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Wed</v>
+        <f>TEXT($A33,"ddd")</f>
+        <v>Fri</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="D33" t="s">
-        <v>244</v>
+        <v>166</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>167</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>253</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="12">
-        <f>DATE(2026,8,28)</f>
-        <v>46262</v>
+        <f>DATE(2026,8,29)</f>
+        <v>46263</v>
       </c>
       <c r="B34" s="13" t="str">
-        <f>TEXT($A34,"ddd")</f>
-        <v>Fri</v>
+        <f t="shared" si="1"/>
+        <v>Sat</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>166</v>
+        <v>279</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>167</v>
+        <v>278</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>127</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -2239,32 +2259,32 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>282</v>
+        <v>243</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="12">
-        <f>DATE(2026,8,29)</f>
-        <v>46263</v>
+        <f>DATE(2026,8,31)</f>
+        <v>46265</v>
       </c>
       <c r="B36" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Sat</v>
+        <f>TEXT($A36,"ddd")</f>
+        <v>Mon</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>245</v>
+        <v>283</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>284</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -2277,13 +2297,13 @@
         <v>Tue</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
@@ -2296,13 +2316,13 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>232</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -2315,13 +2335,13 @@
         <v>Thu</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -2334,13 +2354,13 @@
         <v>Sat</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -2372,13 +2392,13 @@
         <v>Mon</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -2391,13 +2411,13 @@
         <v>Tue</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -2410,503 +2430,501 @@
         <v>Wed</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="12">
+        <f>DATE(2026,9,15)</f>
+        <v>46280</v>
+      </c>
+      <c r="B45" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="D45" s="16"/>
+      <c r="E45" s="11" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" s="12">
+        <f>DATE(2026,9,16)</f>
+        <v>46281</v>
+      </c>
+      <c r="B46" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" s="12">
         <f>DATE(2026,9,18)</f>
         <v>46283</v>
-      </c>
-      <c r="B45" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Fri</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="12">
-        <f>DATE(2026,9,20)</f>
-        <v>46285</v>
-      </c>
-      <c r="B46" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Sun</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="12">
-        <f>DATE(2026,10,9)</f>
-        <v>46304</v>
       </c>
       <c r="B47" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>257</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="D47" s="11"/>
       <c r="E47" s="11" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" s="12">
+        <f>DATE(2026,9,20)</f>
+        <v>46285</v>
+      </c>
+      <c r="B48" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="E48" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="38.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="12">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" s="12">
         <f>DATE(2026,10,9)</f>
         <v>46304</v>
       </c>
-      <c r="B48" s="13" t="str">
+      <c r="B49" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C48" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49" s="12">
+      <c r="C49" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="12">
+        <f>DATE(2026,10,9)</f>
+        <v>46304</v>
+      </c>
+      <c r="B50" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>272</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" s="12">
         <f>DATE(2026,10,10)</f>
         <v>46305</v>
       </c>
-      <c r="B49" s="13" t="str">
+      <c r="B51" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C51" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D51" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E51" s="11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A50" s="12">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" s="12">
         <f>DATE(2026,10,12)</f>
         <v>46307</v>
       </c>
-      <c r="B50" s="13" t="str">
+      <c r="B52" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C52" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D52" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="E50" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="G50" s="19"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A51" s="12">
+      <c r="E52" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="G52" s="19"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" s="12">
         <f>DATE(2026,10,13)</f>
         <v>46308</v>
       </c>
-      <c r="B51" s="13" t="str">
+      <c r="B53" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C53" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D53" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="E51" s="11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52" s="12">
+      <c r="E53" s="11" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54" s="12">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
       </c>
-      <c r="B52" s="13" t="str">
+      <c r="B54" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C54" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D54" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="E52" s="11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" s="12">
+      <c r="E54" s="11" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55" s="12">
         <f>DATE(2026,10,31)</f>
         <v>46326</v>
       </c>
-      <c r="B53" s="13" t="str">
-        <f t="shared" ref="B53:B79" si="2">TEXT($A53,"ddd")</f>
+      <c r="B55" s="13" t="str">
+        <f t="shared" ref="B55:B81" si="2">TEXT($A55,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C55" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D55" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E55" s="11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" s="12">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56" s="12">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
       </c>
-      <c r="B54" s="13" t="str">
+      <c r="B56" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C56" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D56" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E56" s="11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A55" s="12">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" s="12">
         <f>DATE(2026,11,10)</f>
         <v>46336</v>
       </c>
-      <c r="B55" s="13" t="str">
+      <c r="B57" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C57" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D57" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E57" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56" s="12">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58" s="12">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B56" s="13" t="str">
+      <c r="B58" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="C58" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="D56" s="16" t="s">
+      <c r="D58" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E58" s="11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A57" s="12">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B57" s="13" t="str">
+      <c r="B59" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C57" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="D57" s="11" t="s">
+      <c r="C59" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="D59" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E59" s="11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A58" s="12">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" s="12">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B58" s="13" t="str">
+      <c r="B60" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C60" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D60" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E60" s="11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A59" s="12">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" s="12">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
-      </c>
-      <c r="B59" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="E59" s="11" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A60" s="12">
-        <f>DATE(2027,3,19)</f>
-        <v>46465</v>
-      </c>
-      <c r="B60" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D60" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="E60" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61" s="12">
-        <f>DATE(2027,3,25)</f>
-        <v>46471</v>
       </c>
       <c r="B61" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>179</v>
+        <v>253</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>221</v>
+        <v>254</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>124</v>
+        <v>252</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="12">
+        <f>DATE(2027,3,19)</f>
+        <v>46465</v>
+      </c>
+      <c r="B62" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" s="12">
+        <f>DATE(2027,3,25)</f>
+        <v>46471</v>
+      </c>
+      <c r="B63" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Thu</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" s="12">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
       </c>
-      <c r="B62" s="13" t="str">
+      <c r="B64" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C62" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="D62" s="11" t="s">
+      <c r="C64" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="D64" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="E62" s="11" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A63" s="12">
+      <c r="E64" s="11" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" s="12">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
       </c>
-      <c r="B63" s="13" t="str">
+      <c r="B65" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C65" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D65" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E65" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A64" s="12">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" s="12">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B64" s="13" t="str">
+      <c r="B66" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C66" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D66" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="E64" s="11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A65" s="12">
+      <c r="E66" s="11" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B65" s="13" t="str">
+      <c r="B67" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C67" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D67" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="E65" s="11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A66" s="12">
+      <c r="E67" s="11" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B66" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A67" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
-      </c>
-      <c r="B67" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="D67" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A68" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
       </c>
       <c r="B68" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>127</v>
+        <v>251</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B69" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B70" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>127</v>
@@ -2914,37 +2932,37 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="12">
-        <f>DATE(2027,8,16)</f>
-        <v>46615</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B71" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Mon</v>
+        <v>Fri</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>253</v>
+        <v>127</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="12">
-        <f>DATE(2027,8,20)</f>
-        <v>46619</v>
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
       </c>
       <c r="B72" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>127</v>
@@ -2952,46 +2970,46 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="12">
+        <f>DATE(2027,8,16)</f>
+        <v>46615</v>
+      </c>
+      <c r="B73" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Mon</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" s="12">
+        <f>DATE(2027,8,20)</f>
+        <v>46619</v>
+      </c>
+      <c r="B74" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" s="12">
         <f>DATE(2027,9,10)</f>
         <v>46640</v>
-      </c>
-      <c r="B73" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A74" s="12">
-        <f>DATE(2027,9,18)</f>
-        <v>46648</v>
-      </c>
-      <c r="B74" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Sat</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D74" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="E74" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A75" s="12">
-        <f>DATE(2027,10,1)</f>
-        <v>46661</v>
       </c>
       <c r="B75" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3009,27 +3027,27 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="12">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
+        <f>DATE(2027,9,18)</f>
+        <v>46648</v>
       </c>
       <c r="B76" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Sat</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="12">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
+        <f>DATE(2027,10,1)</f>
+        <v>46661</v>
       </c>
       <c r="B77" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3047,8 +3065,8 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
       </c>
       <c r="B78" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3066,29 +3084,70 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="12">
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
+      </c>
+      <c r="B79" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" s="12">
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
+      </c>
+      <c r="B80" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81" s="12">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B79" s="13" t="str">
+      <c r="B81" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="C81" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="D79" s="16" t="s">
+      <c r="D81" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="E79" s="11" t="s">
+      <c r="E81" s="11" t="s">
         <v>134</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E79" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E81" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="D36" r:id="rId1" xr:uid="{DF6FA8D1-34EA-46D0-A461-22B2F51DB446}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3556,7 +3615,7 @@
         <v>112</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>95</v>
@@ -3576,7 +3635,7 @@
         <v>112</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>88</v>
@@ -3596,7 +3655,7 @@
         <v>112</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>104</v>
@@ -3616,7 +3675,7 @@
         <v>112</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>90</v>
@@ -3636,7 +3695,7 @@
         <v>112</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>92</v>
@@ -4271,7 +4330,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -4279,7 +4338,7 @@
         <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -4307,15 +4366,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4556,6 +4606,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
@@ -4568,14 +4627,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4592,4 +4643,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10731"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="517" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C9D9629-D6BB-429F-A9A1-51B1DE05D439}"/>
+  <xr:revisionPtr revIDLastSave="519" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A48DE50-5F12-6D41-B5B1-D4E7557135ED}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$81</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="289">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -898,10 +898,10 @@
     <t>方舟@岗巴士中元会 (代表：Doran, Pei Yuen, Chi Hwee, Agnes）</t>
   </si>
   <si>
-    <t>Lunar July (ZhongYuan Festival) - Block 139 Yishun Ring Road (Representative: Cher Kim Seah, Agnes, Yan Yi, Kathy - all to arrive by 7pm). Auction item included.</t>
-  </si>
-  <si>
-    <t>大牌139中元会 (代表：徐金声,Agnes, Yan Yi, Kathy）。筹款活动包括义标。</t>
+    <t>Lunar July (ZhongYuan Festival) - Block 139 Yishun Ring Road (Representative: Cher Kim Seah, 梁医师, Yan Yi, Kathy - all to arrive by 7pm). Auction item included.</t>
+  </si>
+  <si>
+    <t>大牌139中元会 (代表：徐金声,梁医师, Yan Yi, Kathy）。筹款活动包括义标。</t>
   </si>
 </sst>
 </file>
@@ -1478,111 +1478,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="108" customWidth="1"/>
+    <col min="1" max="1" width="108.01953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
@@ -1596,16 +1596,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:G81"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="114.7265625" customWidth="1"/>
-    <col min="4" max="4" width="59.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="114.74609375" customWidth="1"/>
+    <col min="4" max="4" width="59.45703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.04296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>30</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="12">
         <f>DATE(2026,1,1)</f>
         <v>46023</v>
@@ -1641,7 +1641,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <f>DATE(2026,2,8)</f>
         <v>46061</v>
@@ -1660,7 +1660,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <f>DATE(2026,2,26)</f>
         <v>46079</v>
@@ -1679,7 +1679,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <f>DATE(2026,2,27)</f>
         <v>46080</v>
@@ -1698,7 +1698,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <f>DATE(2026,3,7)</f>
         <v>46088</v>
@@ -1717,7 +1717,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <f>DATE(2026,3,20)</f>
         <v>46101</v>
@@ -1736,7 +1736,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <f>DATE(2026,3,23)</f>
         <v>46104</v>
@@ -1755,7 +1755,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <f>DATE(2026,3,24)</f>
         <v>46105</v>
@@ -1774,7 +1774,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <f>DATE(2026,3,27)</f>
         <v>46108</v>
@@ -1793,7 +1793,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <f>DATE(2026,4,20)</f>
         <v>46132</v>
@@ -1812,7 +1812,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <f>DATE(2026,5,4)</f>
         <v>46146</v>
@@ -1831,7 +1831,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <f>DATE(2026,5,15)</f>
         <v>46157</v>
@@ -1850,7 +1850,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <f>DATE(2026,5,24)</f>
         <v>46166</v>
@@ -1869,7 +1869,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <f>DATE(2026,5,25)</f>
         <v>46167</v>
@@ -1888,7 +1888,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <f>DATE(2026,5,29)</f>
         <v>46171</v>
@@ -1907,7 +1907,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <f>DATE(2026,5,30)</f>
         <v>46172</v>
@@ -1926,7 +1926,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <f>DATE(2026,5,31)</f>
         <v>46173</v>
@@ -1945,7 +1945,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <f>DATE(2026,6,1)</f>
         <v>46174</v>
@@ -1964,7 +1964,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <f>DATE(2026,6,12)</f>
         <v>46185</v>
@@ -1983,7 +1983,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <f>DATE(2026,6,13)</f>
         <v>46186</v>
@@ -2002,7 +2002,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <f>DATE(2026,6,20)</f>
         <v>46193</v>
@@ -2021,7 +2021,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <f>DATE(2026,7,3)</f>
         <v>46206</v>
@@ -2040,7 +2040,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <f>DATE(2026,7,24)</f>
         <v>46227</v>
@@ -2059,7 +2059,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <f>DATE(2026,7,24)</f>
         <v>46227</v>
@@ -2078,7 +2078,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <f>DATE(2026,7,25)</f>
         <v>46228</v>
@@ -2097,7 +2097,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <f>DATE(2026,8,1)</f>
         <v>46235</v>
@@ -2116,7 +2116,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <f>DATE(2026,8,5)</f>
         <v>46239</v>
@@ -2135,7 +2135,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <f>DATE(2026,8,8)</f>
         <v>46242</v>
@@ -2154,7 +2154,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <f>DATE(2026,8,14)</f>
         <v>46248</v>
@@ -2173,7 +2173,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <f>DATE(2026,8,15)</f>
         <v>46249</v>
@@ -2192,7 +2192,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <f>DATE(2026,8,23)</f>
         <v>46257</v>
@@ -2211,7 +2211,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <f>DATE(2026,8,28)</f>
         <v>46262</v>
@@ -2230,7 +2230,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <f>DATE(2026,8,29)</f>
         <v>46263</v>
@@ -2249,7 +2249,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <f>DATE(2026,8,29)</f>
         <v>46263</v>
@@ -2268,7 +2268,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <f>DATE(2026,8,31)</f>
         <v>46265</v>
@@ -2287,7 +2287,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <f>DATE(2026,9,1)</f>
         <v>46266</v>
@@ -2306,7 +2306,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <f>DATE(2026,9,3)</f>
         <v>46268</v>
@@ -2325,7 +2325,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <f>DATE(2026,9,3)</f>
         <v>46268</v>
@@ -2344,7 +2344,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <f>DATE(2026,9,5)</f>
         <v>46270</v>
@@ -2363,7 +2363,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <f>DATE(2026,9,5)</f>
         <v>46270</v>
@@ -2382,7 +2382,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <f>DATE(2026,9,7)</f>
         <v>46272</v>
@@ -2401,7 +2401,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <f>DATE(2026,9,8)</f>
         <v>46273</v>
@@ -2420,7 +2420,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <f>DATE(2026,9,9)</f>
         <v>46274</v>
@@ -2439,7 +2439,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <f>DATE(2026,9,15)</f>
         <v>46280</v>
@@ -2456,7 +2456,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <f>DATE(2026,9,16)</f>
         <v>46281</v>
@@ -2475,7 +2475,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <f>DATE(2026,9,18)</f>
         <v>46283</v>
@@ -2492,7 +2492,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <f>DATE(2026,9,20)</f>
         <v>46285</v>
@@ -2511,7 +2511,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <f>DATE(2026,10,9)</f>
         <v>46304</v>
@@ -2530,7 +2530,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="38.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" ht="36" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <f>DATE(2026,10,9)</f>
         <v>46304</v>
@@ -2549,7 +2549,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <f>DATE(2026,10,10)</f>
         <v>46305</v>
@@ -2568,7 +2568,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <f>DATE(2026,10,12)</f>
         <v>46307</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="G52" s="19"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <f>DATE(2026,10,13)</f>
         <v>46308</v>
@@ -2607,7 +2607,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
@@ -2626,7 +2626,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <f>DATE(2026,10,31)</f>
         <v>46326</v>
@@ -2645,7 +2645,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
@@ -2664,7 +2664,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <f>DATE(2026,11,10)</f>
         <v>46336</v>
@@ -2683,7 +2683,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
@@ -2702,7 +2702,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
@@ -2721,7 +2721,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
@@ -2740,7 +2740,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
@@ -2759,7 +2759,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
@@ -2778,7 +2778,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
@@ -2797,7 +2797,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
@@ -2816,7 +2816,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
@@ -2835,7 +2835,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
@@ -2854,7 +2854,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
@@ -2873,7 +2873,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
@@ -2892,7 +2892,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <f>DATE(2027,5,28)</f>
         <v>46535</v>
@@ -2911,7 +2911,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <f>DATE(2027,6,11)</f>
         <v>46549</v>
@@ -2930,7 +2930,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <f>DATE(2027,7,9)</f>
         <v>46577</v>
@@ -2949,7 +2949,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <f>DATE(2027,7,30)</f>
         <v>46598</v>
@@ -2968,7 +2968,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
@@ -2987,7 +2987,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <f>DATE(2027,8,20)</f>
         <v>46619</v>
@@ -3006,7 +3006,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <f>DATE(2027,9,10)</f>
         <v>46640</v>
@@ -3025,7 +3025,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
@@ -3044,7 +3044,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <f>DATE(2027,10,1)</f>
         <v>46661</v>
@@ -3063,7 +3063,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <f>DATE(2027,10,15)</f>
         <v>46675</v>
@@ -3082,7 +3082,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <f>DATE(2027,11,12)</f>
         <v>46703</v>
@@ -3101,7 +3101,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <f>DATE(2027,11,26)</f>
         <v>46717</v>
@@ -3120,7 +3120,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
@@ -3155,15 +3155,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="1" max="1" width="6.05078125" customWidth="1"/>
+    <col min="2" max="2" width="29.99609375" customWidth="1"/>
+    <col min="3" max="3" width="16.0078125" customWidth="1"/>
+    <col min="4" max="4" width="22.05859375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -3247,7 +3247,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -3369,7 +3369,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -3467,7 +3467,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -3531,17 +3531,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="1" max="1" width="6.9921875" customWidth="1"/>
+    <col min="2" max="2" width="29.99609375" customWidth="1"/>
+    <col min="3" max="3" width="16.0078125" customWidth="1"/>
+    <col min="4" max="4" width="25.9609375" customWidth="1"/>
+    <col min="5" max="5" width="16.0078125" customWidth="1"/>
+    <col min="6" max="6" width="22.05859375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
@@ -3561,7 +3561,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3621,7 +3621,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="14">
         <v>8</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="14">
         <v>9</v>
       </c>
@@ -3741,7 +3741,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="14">
         <v>10</v>
       </c>
@@ -3761,7 +3761,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="14">
         <v>11</v>
       </c>
@@ -3790,18 +3790,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.078125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.63671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.78125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.8046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.02734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.91796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>26</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
         <v>189</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
         <v>189</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
         <v>189</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
         <v>189</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
         <v>189</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
         <v>191</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="16" t="s">
         <v>191</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
         <v>193</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="16" t="s">
         <v>193</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="16" t="s">
         <v>195</v>
       </c>
@@ -4050,7 +4050,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
         <v>195</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
         <v>195</v>
       </c>
@@ -4096,7 +4096,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
         <v>195</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="16" t="s">
         <v>197</v>
       </c>
@@ -4142,7 +4142,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="16" t="s">
         <v>197</v>
       </c>
@@ -4165,7 +4165,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>199</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
         <v>199</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
         <v>199</v>
       </c>
@@ -4234,7 +4234,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
         <v>201</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
         <v>201</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
         <v>201</v>
       </c>
@@ -4311,13 +4311,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="90" customWidth="1"/>
+    <col min="1" max="1" width="16.0078125" customWidth="1"/>
+    <col min="2" max="2" width="89.99609375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>33</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>35</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>36</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>204</v>
       </c>
@@ -4355,14 +4355,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4607,21 +4605,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4631,24 +4628,23 @@
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
     <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="519" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A48DE50-5F12-6D41-B5B1-D4E7557135ED}"/>
+  <xr:revisionPtr revIDLastSave="521" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2D31F92-5CDD-40EF-B946-FA98D7219CD6}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="288">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -902,6 +902,9 @@
   </si>
   <si>
     <t>大牌139中元会 (代表：徐金声,梁医师, Yan Yi, Kathy）。筹款活动包括义标。</t>
+  </si>
+  <si>
+    <t>[Tentative] CSR Partnership – Corporate / School - Singapore Flyer (suggestion)</t>
   </si>
 </sst>
 </file>
@@ -1478,111 +1481,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="108.01953125" customWidth="1"/>
+    <col min="1" max="1" width="108" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
@@ -1596,16 +1599,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:G81"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="114.74609375" customWidth="1"/>
-    <col min="4" max="4" width="59.45703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.04296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="114.7265625" customWidth="1"/>
+    <col min="4" max="4" width="59.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>30</v>
       </c>
@@ -1622,7 +1625,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="12">
         <f>DATE(2026,1,1)</f>
         <v>46023</v>
@@ -1641,7 +1644,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="12">
         <f>DATE(2026,2,8)</f>
         <v>46061</v>
@@ -1660,7 +1663,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="12">
         <f>DATE(2026,2,26)</f>
         <v>46079</v>
@@ -1679,7 +1682,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="12">
         <f>DATE(2026,2,27)</f>
         <v>46080</v>
@@ -1698,7 +1701,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
         <f>DATE(2026,3,7)</f>
         <v>46088</v>
@@ -1717,7 +1720,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
         <f>DATE(2026,3,20)</f>
         <v>46101</v>
@@ -1736,7 +1739,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="12">
         <f>DATE(2026,3,23)</f>
         <v>46104</v>
@@ -1755,7 +1758,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="12">
         <f>DATE(2026,3,24)</f>
         <v>46105</v>
@@ -1774,7 +1777,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="12">
         <f>DATE(2026,3,27)</f>
         <v>46108</v>
@@ -1793,7 +1796,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="12">
         <f>DATE(2026,4,20)</f>
         <v>46132</v>
@@ -1812,7 +1815,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="12">
         <f>DATE(2026,5,4)</f>
         <v>46146</v>
@@ -1831,7 +1834,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="12">
         <f>DATE(2026,5,15)</f>
         <v>46157</v>
@@ -1850,7 +1853,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="12">
         <f>DATE(2026,5,24)</f>
         <v>46166</v>
@@ -1869,7 +1872,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="12">
         <f>DATE(2026,5,25)</f>
         <v>46167</v>
@@ -1888,7 +1891,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="12">
         <f>DATE(2026,5,29)</f>
         <v>46171</v>
@@ -1907,7 +1910,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="12">
         <f>DATE(2026,5,30)</f>
         <v>46172</v>
@@ -1926,7 +1929,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="12">
         <f>DATE(2026,5,31)</f>
         <v>46173</v>
@@ -1945,7 +1948,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="12">
         <f>DATE(2026,6,1)</f>
         <v>46174</v>
@@ -1964,7 +1967,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="12">
         <f>DATE(2026,6,12)</f>
         <v>46185</v>
@@ -1983,7 +1986,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="12">
         <f>DATE(2026,6,13)</f>
         <v>46186</v>
@@ -2002,7 +2005,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="12">
         <f>DATE(2026,6,20)</f>
         <v>46193</v>
@@ -2021,7 +2024,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="12">
         <f>DATE(2026,7,3)</f>
         <v>46206</v>
@@ -2040,7 +2043,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="12">
         <f>DATE(2026,7,24)</f>
         <v>46227</v>
@@ -2059,7 +2062,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="12">
         <f>DATE(2026,7,24)</f>
         <v>46227</v>
@@ -2078,7 +2081,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="12">
         <f>DATE(2026,7,25)</f>
         <v>46228</v>
@@ -2097,7 +2100,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="12">
         <f>DATE(2026,8,1)</f>
         <v>46235</v>
@@ -2116,7 +2119,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="12">
         <f>DATE(2026,8,5)</f>
         <v>46239</v>
@@ -2135,7 +2138,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="12">
         <f>DATE(2026,8,8)</f>
         <v>46242</v>
@@ -2154,7 +2157,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="12">
         <f>DATE(2026,8,14)</f>
         <v>46248</v>
@@ -2173,7 +2176,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="12">
         <f>DATE(2026,8,15)</f>
         <v>46249</v>
@@ -2192,7 +2195,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="12">
         <f>DATE(2026,8,23)</f>
         <v>46257</v>
@@ -2211,7 +2214,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="12">
         <f>DATE(2026,8,28)</f>
         <v>46262</v>
@@ -2230,7 +2233,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="12">
         <f>DATE(2026,8,29)</f>
         <v>46263</v>
@@ -2249,7 +2252,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="12">
         <f>DATE(2026,8,29)</f>
         <v>46263</v>
@@ -2268,7 +2271,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="12">
         <f>DATE(2026,8,31)</f>
         <v>46265</v>
@@ -2287,7 +2290,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="12">
         <f>DATE(2026,9,1)</f>
         <v>46266</v>
@@ -2306,7 +2309,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="12">
         <f>DATE(2026,9,3)</f>
         <v>46268</v>
@@ -2325,7 +2328,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="12">
         <f>DATE(2026,9,3)</f>
         <v>46268</v>
@@ -2344,7 +2347,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="12">
         <f>DATE(2026,9,5)</f>
         <v>46270</v>
@@ -2363,7 +2366,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="12">
         <f>DATE(2026,9,5)</f>
         <v>46270</v>
@@ -2382,7 +2385,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="12">
         <f>DATE(2026,9,7)</f>
         <v>46272</v>
@@ -2401,7 +2404,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="12">
         <f>DATE(2026,9,8)</f>
         <v>46273</v>
@@ -2420,7 +2423,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="12">
         <f>DATE(2026,9,9)</f>
         <v>46274</v>
@@ -2439,7 +2442,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="12">
         <f>DATE(2026,9,15)</f>
         <v>46280</v>
@@ -2456,7 +2459,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="12">
         <f>DATE(2026,9,16)</f>
         <v>46281</v>
@@ -2475,7 +2478,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="12">
         <f>DATE(2026,9,18)</f>
         <v>46283</v>
@@ -2492,7 +2495,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="12">
         <f>DATE(2026,9,20)</f>
         <v>46285</v>
@@ -2511,7 +2514,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="12">
         <f>DATE(2026,10,9)</f>
         <v>46304</v>
@@ -2530,7 +2533,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="36" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" ht="38.5" x14ac:dyDescent="0.35">
       <c r="A50" s="12">
         <f>DATE(2026,10,9)</f>
         <v>46304</v>
@@ -2549,7 +2552,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="12">
         <f>DATE(2026,10,10)</f>
         <v>46305</v>
@@ -2568,7 +2571,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="12">
         <f>DATE(2026,10,12)</f>
         <v>46307</v>
@@ -2588,7 +2591,7 @@
       </c>
       <c r="G52" s="19"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="12">
         <f>DATE(2026,10,13)</f>
         <v>46308</v>
@@ -2607,7 +2610,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="12">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
@@ -2626,7 +2629,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="12">
         <f>DATE(2026,10,31)</f>
         <v>46326</v>
@@ -2645,7 +2648,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="12">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
@@ -2664,7 +2667,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="12">
         <f>DATE(2026,11,10)</f>
         <v>46336</v>
@@ -2683,7 +2686,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="12">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
@@ -2702,7 +2705,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
@@ -2721,7 +2724,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="12">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
@@ -2740,7 +2743,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="12">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
@@ -2759,7 +2762,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="12">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
@@ -2778,7 +2781,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="12">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
@@ -2797,7 +2800,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="12">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
@@ -2816,7 +2819,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="12">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
@@ -2835,7 +2838,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="12">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
@@ -2854,7 +2857,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
@@ -2873,7 +2876,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
@@ -2892,7 +2895,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="12">
         <f>DATE(2027,5,28)</f>
         <v>46535</v>
@@ -2911,7 +2914,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
         <f>DATE(2027,6,11)</f>
         <v>46549</v>
@@ -2921,7 +2924,7 @@
         <v>Fri</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>178</v>
+        <v>287</v>
       </c>
       <c r="D70" s="11" t="s">
         <v>220</v>
@@ -2930,7 +2933,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="12">
         <f>DATE(2027,7,9)</f>
         <v>46577</v>
@@ -2949,7 +2952,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="12">
         <f>DATE(2027,7,30)</f>
         <v>46598</v>
@@ -2968,7 +2971,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="12">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
@@ -2987,7 +2990,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="12">
         <f>DATE(2027,8,20)</f>
         <v>46619</v>
@@ -3006,7 +3009,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="12">
         <f>DATE(2027,9,10)</f>
         <v>46640</v>
@@ -3025,7 +3028,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
@@ -3044,7 +3047,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="12">
         <f>DATE(2027,10,1)</f>
         <v>46661</v>
@@ -3063,7 +3066,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="12">
         <f>DATE(2027,10,15)</f>
         <v>46675</v>
@@ -3082,7 +3085,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="12">
         <f>DATE(2027,11,12)</f>
         <v>46703</v>
@@ -3101,7 +3104,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="12">
         <f>DATE(2027,11,26)</f>
         <v>46717</v>
@@ -3120,7 +3123,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="12">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
@@ -3155,15 +3158,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.05078125" customWidth="1"/>
-    <col min="2" max="2" width="29.99609375" customWidth="1"/>
-    <col min="3" max="3" width="16.0078125" customWidth="1"/>
-    <col min="4" max="4" width="22.05859375" customWidth="1"/>
+    <col min="1" max="1" width="6.08984375" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="22.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
@@ -3177,7 +3180,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3191,7 +3194,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3205,7 +3208,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3219,7 +3222,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -3233,7 +3236,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -3247,7 +3250,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3261,7 +3264,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -3275,7 +3278,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -3289,7 +3292,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -3303,7 +3306,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -3317,7 +3320,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -3329,7 +3332,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -3341,7 +3344,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -3355,7 +3358,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -3369,7 +3372,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -3383,7 +3386,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -3397,7 +3400,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -3411,7 +3414,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -3425,7 +3428,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -3439,7 +3442,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -3453,7 +3456,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -3467,7 +3470,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -3481,7 +3484,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -3495,7 +3498,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -3509,7 +3512,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -3531,17 +3534,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.9921875" customWidth="1"/>
-    <col min="2" max="2" width="29.99609375" customWidth="1"/>
-    <col min="3" max="3" width="16.0078125" customWidth="1"/>
-    <col min="4" max="4" width="25.9609375" customWidth="1"/>
-    <col min="5" max="5" width="16.0078125" customWidth="1"/>
-    <col min="6" max="6" width="22.05859375" customWidth="1"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="22.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
@@ -3561,7 +3564,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3581,7 +3584,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3601,7 +3604,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3621,7 +3624,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -3641,7 +3644,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -3661,7 +3664,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3681,7 +3684,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -3701,7 +3704,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="14">
         <v>8</v>
       </c>
@@ -3721,7 +3724,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="14">
         <v>9</v>
       </c>
@@ -3741,7 +3744,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="14">
         <v>10</v>
       </c>
@@ -3761,7 +3764,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="14">
         <v>11</v>
       </c>
@@ -3790,18 +3793,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.078125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.63671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.78125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.8046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.02734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.91796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>26</v>
       </c>
@@ -3824,7 +3827,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>189</v>
       </c>
@@ -3847,7 +3850,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
         <v>189</v>
       </c>
@@ -3868,7 +3871,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
         <v>189</v>
       </c>
@@ -3891,7 +3894,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
         <v>189</v>
       </c>
@@ -3912,7 +3915,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>189</v>
       </c>
@@ -3935,7 +3938,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>191</v>
       </c>
@@ -3958,7 +3961,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
         <v>191</v>
       </c>
@@ -3981,7 +3984,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
         <v>193</v>
       </c>
@@ -4004,7 +4007,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
         <v>193</v>
       </c>
@@ -4027,7 +4030,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
         <v>195</v>
       </c>
@@ -4050,7 +4053,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
         <v>195</v>
       </c>
@@ -4073,7 +4076,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
         <v>195</v>
       </c>
@@ -4096,7 +4099,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
         <v>195</v>
       </c>
@@ -4119,7 +4122,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
         <v>197</v>
       </c>
@@ -4142,7 +4145,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
         <v>197</v>
       </c>
@@ -4165,7 +4168,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
         <v>199</v>
       </c>
@@ -4188,7 +4191,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
         <v>199</v>
       </c>
@@ -4211,7 +4214,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
         <v>199</v>
       </c>
@@ -4234,7 +4237,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
         <v>201</v>
       </c>
@@ -4257,7 +4260,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
         <v>201</v>
       </c>
@@ -4280,7 +4283,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
         <v>201</v>
       </c>
@@ -4311,13 +4314,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.0078125" customWidth="1"/>
-    <col min="2" max="2" width="89.99609375" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>33</v>
       </c>
@@ -4325,7 +4328,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>35</v>
       </c>
@@ -4333,7 +4336,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>36</v>
       </c>
@@ -4341,7 +4344,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>204</v>
       </c>
@@ -4355,15 +4358,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4604,6 +4598,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4616,14 +4619,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4632,6 +4627,21 @@
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
     <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="521" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2D31F92-5CDD-40EF-B946-FA98D7219CD6}"/>
+  <xr:revisionPtr revIDLastSave="526" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B50AFE15-2D39-472E-81D8-498BBB415743}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -454,9 +454,6 @@
     <t>Shine Dragon Boat Dumpling Festival Celebration</t>
   </si>
   <si>
-    <t>Charity Concert at Tzu Chi</t>
-  </si>
-  <si>
     <t>Information</t>
   </si>
   <si>
@@ -559,9 +556,6 @@
     <t>正罡玄门中秋物资派发（200人）</t>
   </si>
   <si>
-    <t>慈济慈善演唱会</t>
-  </si>
-  <si>
     <t>Title (Chinese)</t>
   </si>
   <si>
@@ -905,6 +899,12 @@
   </si>
   <si>
     <t>[Tentative] CSR Partnership – Corporate / School - Singapore Flyer (suggestion)</t>
+  </si>
+  <si>
+    <t>Nam Hong Charity Concert 2026 (Location: Tzu Chi Humanistic Youth Centre)</t>
+  </si>
+  <si>
+    <t>南凤慈济慈善演唱会2026</t>
   </si>
 </sst>
 </file>
@@ -1488,7 +1488,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -1622,7 +1622,7 @@
         <v>32</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -1635,10 +1635,10 @@
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>139</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>140</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>127</v>
@@ -1657,7 +1657,7 @@
         <v>123</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>124</v>
@@ -1673,10 +1673,10 @@
         <v>Thu</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>142</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>143</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>134</v>
@@ -1695,7 +1695,7 @@
         <v>125</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>124</v>
@@ -1714,7 +1714,7 @@
         <v>126</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>124</v>
@@ -1733,7 +1733,7 @@
         <v>128</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>127</v>
@@ -1752,7 +1752,7 @@
         <v>129</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>124</v>
@@ -1771,7 +1771,7 @@
         <v>130</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>124</v>
@@ -1790,7 +1790,7 @@
         <v>131</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>124</v>
@@ -1809,7 +1809,7 @@
         <v>133</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>132</v>
@@ -1825,10 +1825,10 @@
         <v>Mon</v>
       </c>
       <c r="C12" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>149</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>150</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>132</v>
@@ -1844,10 +1844,10 @@
         <v>Fri</v>
       </c>
       <c r="C13" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>151</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>152</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>134</v>
@@ -1863,10 +1863,10 @@
         <v>Sun</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>132</v>
@@ -1885,7 +1885,7 @@
         <v>135</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>124</v>
@@ -1901,13 +1901,13 @@
         <v>Fri</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>156</v>
-      </c>
       <c r="E16" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -1920,13 +1920,13 @@
         <v>Sat</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>158</v>
-      </c>
       <c r="E17" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -1939,13 +1939,13 @@
         <v>Sun</v>
       </c>
       <c r="C18" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D18" s="11" t="s">
-        <v>160</v>
-      </c>
       <c r="E18" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -1958,13 +1958,13 @@
         <v>Mon</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>162</v>
-      </c>
       <c r="E19" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -1980,7 +1980,7 @@
         <v>131</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>124</v>
@@ -1999,7 +1999,7 @@
         <v>136</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>124</v>
@@ -2018,7 +2018,7 @@
         <v>131</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>124</v>
@@ -2034,10 +2034,10 @@
         <v>Fri</v>
       </c>
       <c r="C23" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>164</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>165</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>127</v>
@@ -2053,10 +2053,10 @@
         <v>Fri</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>127</v>
@@ -2075,7 +2075,7 @@
         <v>131</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>124</v>
@@ -2094,7 +2094,7 @@
         <v>131</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>124</v>
@@ -2110,10 +2110,10 @@
         <v>Sat</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>127</v>
@@ -2129,10 +2129,10 @@
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>124</v>
@@ -2148,13 +2148,13 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -2167,13 +2167,13 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -2186,13 +2186,13 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -2205,13 +2205,13 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -2224,10 +2224,10 @@
         <v>Fri</v>
       </c>
       <c r="C33" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>166</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>167</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>127</v>
@@ -2243,13 +2243,13 @@
         <v>Sat</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -2262,13 +2262,13 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -2281,13 +2281,13 @@
         <v>Mon</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -2300,13 +2300,13 @@
         <v>Tue</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
@@ -2319,13 +2319,13 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -2338,13 +2338,13 @@
         <v>Thu</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -2357,13 +2357,13 @@
         <v>Sat</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -2376,10 +2376,10 @@
         <v>Sat</v>
       </c>
       <c r="C41" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D41" s="11" t="s">
         <v>168</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>169</v>
       </c>
       <c r="E41" s="11" t="s">
         <v>127</v>
@@ -2395,13 +2395,13 @@
         <v>Mon</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -2414,13 +2414,13 @@
         <v>Tue</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -2433,13 +2433,13 @@
         <v>Wed</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -2452,11 +2452,11 @@
         <v>Tue</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
@@ -2469,13 +2469,13 @@
         <v>Wed</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -2488,11 +2488,11 @@
         <v>Fri</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D47" s="11"/>
       <c r="E47" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
@@ -2505,10 +2505,10 @@
         <v>Sun</v>
       </c>
       <c r="C48" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D48" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="E48" s="11" t="s">
         <v>127</v>
@@ -2524,10 +2524,10 @@
         <v>Fri</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>127</v>
@@ -2543,13 +2543,13 @@
         <v>Fri</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -2562,10 +2562,10 @@
         <v>Sat</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>137</v>
+        <v>286</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>172</v>
+        <v>287</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>134</v>
@@ -2581,13 +2581,13 @@
         <v>Mon</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G52" s="19"/>
     </row>
@@ -2601,13 +2601,13 @@
         <v>Tue</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -2620,13 +2620,13 @@
         <v>Wed</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -2639,10 +2639,10 @@
         <v>Sat</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>134</v>
@@ -2658,10 +2658,10 @@
         <v>Tue</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>124</v>
@@ -2677,10 +2677,10 @@
         <v>Tue</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>127</v>
@@ -2696,10 +2696,10 @@
         <v>Wed</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>134</v>
@@ -2715,10 +2715,10 @@
         <v>Fri</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E59" s="11" t="s">
         <v>134</v>
@@ -2734,10 +2734,10 @@
         <v>Sat</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>124</v>
@@ -2753,13 +2753,13 @@
         <v>Thu</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -2772,10 +2772,10 @@
         <v>Fri</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E62" s="11" t="s">
         <v>127</v>
@@ -2791,10 +2791,10 @@
         <v>Thu</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>124</v>
@@ -2810,13 +2810,13 @@
         <v>Sat</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
@@ -2829,10 +2829,10 @@
         <v>Fri</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>127</v>
@@ -2848,13 +2848,13 @@
         <v>Wed</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
@@ -2867,13 +2867,13 @@
         <v>Thu</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
@@ -2886,13 +2886,13 @@
         <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
@@ -2905,10 +2905,10 @@
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>124</v>
@@ -2924,10 +2924,10 @@
         <v>Fri</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>127</v>
@@ -2943,10 +2943,10 @@
         <v>Fri</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>127</v>
@@ -2962,10 +2962,10 @@
         <v>Fri</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>127</v>
@@ -2981,13 +2981,13 @@
         <v>Mon</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
@@ -3000,10 +3000,10 @@
         <v>Fri</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E74" s="11" t="s">
         <v>127</v>
@@ -3019,10 +3019,10 @@
         <v>Fri</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E75" s="11" t="s">
         <v>127</v>
@@ -3038,10 +3038,10 @@
         <v>Sat</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E76" s="11" t="s">
         <v>134</v>
@@ -3057,10 +3057,10 @@
         <v>Fri</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E77" s="11" t="s">
         <v>127</v>
@@ -3076,10 +3076,10 @@
         <v>Fri</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E78" s="11" t="s">
         <v>127</v>
@@ -3095,10 +3095,10 @@
         <v>Fri</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E79" s="11" t="s">
         <v>127</v>
@@ -3114,10 +3114,10 @@
         <v>Fri</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E80" s="11" t="s">
         <v>127</v>
@@ -3133,10 +3133,10 @@
         <v>Thu</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>134</v>
@@ -3391,7 +3391,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>65</v>
@@ -3558,7 +3558,7 @@
         <v>24</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>21</v>
@@ -3618,7 +3618,7 @@
         <v>112</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>95</v>
@@ -3638,7 +3638,7 @@
         <v>112</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>88</v>
@@ -3658,7 +3658,7 @@
         <v>112</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>104</v>
@@ -3678,7 +3678,7 @@
         <v>112</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>90</v>
@@ -3698,7 +3698,7 @@
         <v>112</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>92</v>
@@ -3829,10 +3829,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -3852,10 +3852,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -3873,16 +3873,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>65</v>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -3917,10 +3917,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
@@ -3940,10 +3940,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -3986,10 +3986,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
@@ -4009,10 +4009,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
@@ -4032,10 +4032,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -4055,10 +4055,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -4078,10 +4078,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -4101,10 +4101,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -4124,10 +4124,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -4147,10 +4147,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
@@ -4193,10 +4193,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -4216,10 +4216,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
@@ -4239,10 +4239,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -4333,7 +4333,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -4341,15 +4341,15 @@
         <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -4358,6 +4358,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100075DF30E65B6EF43A4A87751785D6134" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bb82854400ecd26b0783e1c1c0c001ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3" xmlns:ns3="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e524ce3f3da87e709475b3d7b1de4709" ns2:_="" ns3:_="">
     <xsd:import namespace="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
@@ -4598,15 +4607,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4619,6 +4619,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E40BF6C7-2D4E-4A6F-80DC-45FE9A6AC6EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4638,14 +4646,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="526" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B50AFE15-2D39-472E-81D8-498BBB415743}"/>
+  <xr:revisionPtr revIDLastSave="588" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8BBCDB3-DC6F-442D-90B4-651C48763A98}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="2_Committee" sheetId="2" r:id="rId3"/>
     <sheet name="3_OfficeBearers" sheetId="3" r:id="rId4"/>
     <sheet name="4_SubCommittees" sheetId="4" r:id="rId5"/>
-    <sheet name="Info" sheetId="6" r:id="rId6"/>
+    <sheet name="5_Employees" sheetId="7" r:id="rId6"/>
+    <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$81</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="436">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -229,9 +230,6 @@
     <t>Ng Chuan Seng (Tony)</t>
   </si>
   <si>
-    <t>黄泉森</t>
-  </si>
-  <si>
     <t>Ng Jie Ying (Cecil) PBM</t>
   </si>
   <si>
@@ -905,6 +903,453 @@
   </si>
   <si>
     <t>南凤慈济慈善演唱会2026</t>
+  </si>
+  <si>
+    <t>黄泉盛</t>
+  </si>
+  <si>
+    <t>Wong Jin Hoa</t>
+  </si>
+  <si>
+    <t>黄子豪</t>
+  </si>
+  <si>
+    <t>Kathy Koh</t>
+  </si>
+  <si>
+    <t>Aceline Wong</t>
+  </si>
+  <si>
+    <t>Agnes Lew</t>
+  </si>
+  <si>
+    <t>Bryan Cheo</t>
+  </si>
+  <si>
+    <t>Chan Yin Yee</t>
+  </si>
+  <si>
+    <t>Xu Jingyi</t>
+  </si>
+  <si>
+    <t>Lim Chi Hwee</t>
+  </si>
+  <si>
+    <t>Crystal Lee</t>
+  </si>
+  <si>
+    <t>Cheng Pei Yuen</t>
+  </si>
+  <si>
+    <t>Doran Hooi</t>
+  </si>
+  <si>
+    <t>Alicia Lee</t>
+  </si>
+  <si>
+    <t>Cheong Keong Eng</t>
+  </si>
+  <si>
+    <t>Eh Siok Teng</t>
+  </si>
+  <si>
+    <t>Vivian Goh</t>
+  </si>
+  <si>
+    <t>Lee Bon Teck</t>
+  </si>
+  <si>
+    <t>Leong Chin Mee</t>
+  </si>
+  <si>
+    <t>Low Soon Meng</t>
+  </si>
+  <si>
+    <t>Lu Yuehong</t>
+  </si>
+  <si>
+    <t>Ong Choe Jang</t>
+  </si>
+  <si>
+    <t>Puah Mei Chia</t>
+  </si>
+  <si>
+    <t>Tan Gek Hee</t>
+  </si>
+  <si>
+    <t>Yap Ai Mee</t>
+  </si>
+  <si>
+    <t>Ang Geok Chin</t>
+  </si>
+  <si>
+    <t>Ang Lay Siew</t>
+  </si>
+  <si>
+    <t>Chung Wai Yee</t>
+  </si>
+  <si>
+    <t>Carol Lim</t>
+  </si>
+  <si>
+    <t>Low Yoke Want</t>
+  </si>
+  <si>
+    <t>Ng Poh Cheng</t>
+  </si>
+  <si>
+    <t>Sam Geok Lan</t>
+  </si>
+  <si>
+    <t>Wong Lai Chee</t>
+  </si>
+  <si>
+    <t>Woo Bee Choo</t>
+  </si>
+  <si>
+    <t>许玉鵰</t>
+  </si>
+  <si>
+    <t>黄馨仪</t>
+  </si>
+  <si>
+    <t>刘秀亮</t>
+  </si>
+  <si>
+    <t>朱展弘</t>
+  </si>
+  <si>
+    <t>曾燕仪</t>
+  </si>
+  <si>
+    <t>许静仪</t>
+  </si>
+  <si>
+    <t>林子惠</t>
+  </si>
+  <si>
+    <t>李恩慧</t>
+  </si>
+  <si>
+    <t>曾琣云</t>
+  </si>
+  <si>
+    <t>许健辉</t>
+  </si>
+  <si>
+    <t>李恩菁</t>
+  </si>
+  <si>
+    <t>钟秉融</t>
+  </si>
+  <si>
+    <t>余淑婷</t>
+  </si>
+  <si>
+    <t>吴泋瑮</t>
+  </si>
+  <si>
+    <t>李文德</t>
+  </si>
+  <si>
+    <t>梁芷维</t>
+  </si>
+  <si>
+    <t>刘顺明</t>
+  </si>
+  <si>
+    <t>鹿月红</t>
+  </si>
+  <si>
+    <t>翁楚璋</t>
+  </si>
+  <si>
+    <t>潘媚佳</t>
+  </si>
+  <si>
+    <t>陈玉枝</t>
+  </si>
+  <si>
+    <t>叶艾美</t>
+  </si>
+  <si>
+    <t>洪玉珍</t>
+  </si>
+  <si>
+    <t>洪丽銹</t>
+  </si>
+  <si>
+    <t>曾惠仪</t>
+  </si>
+  <si>
+    <t>林语晴</t>
+  </si>
+  <si>
+    <t>刘玉云</t>
+  </si>
+  <si>
+    <t>黄宝清</t>
+  </si>
+  <si>
+    <t>岑玉兰</t>
+  </si>
+  <si>
+    <t>黄丽珠</t>
+  </si>
+  <si>
+    <t>吴美珠</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>执行董事</t>
+  </si>
+  <si>
+    <t>Assistant General Manager</t>
+  </si>
+  <si>
+    <t>副经理</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>会计</t>
+  </si>
+  <si>
+    <t>Donor Caring Officer</t>
+  </si>
+  <si>
+    <t>Fundraising &amp; Events Officer</t>
+  </si>
+  <si>
+    <t>Caring Heart Officer</t>
+  </si>
+  <si>
+    <t>Marketing Communication Executive</t>
+  </si>
+  <si>
+    <t>Events And Social Media Officer</t>
+  </si>
+  <si>
+    <t>Team Officer (HR/Finance/Admin)</t>
+  </si>
+  <si>
+    <t>Team Officer (TCM/Caring Heart)</t>
+  </si>
+  <si>
+    <t>Team Officer (Communication/Event)</t>
+  </si>
+  <si>
+    <t>Team Officer (Finance/IT/Board)</t>
+  </si>
+  <si>
+    <t>TCM Physician</t>
+  </si>
+  <si>
+    <t>医师</t>
+  </si>
+  <si>
+    <t>TCM Clinic Assistant</t>
+  </si>
+  <si>
+    <t>诊所助理</t>
+  </si>
+  <si>
+    <t>.jpg</t>
+  </si>
+  <si>
+    <t>jinhoa</t>
+  </si>
+  <si>
+    <t>kathy</t>
+  </si>
+  <si>
+    <t>aceline</t>
+  </si>
+  <si>
+    <t>agnes</t>
+  </si>
+  <si>
+    <t>bryan</t>
+  </si>
+  <si>
+    <t>yinyee</t>
+  </si>
+  <si>
+    <t>jingyi</t>
+  </si>
+  <si>
+    <t>chihwee</t>
+  </si>
+  <si>
+    <t>crystal</t>
+  </si>
+  <si>
+    <t>peiyuen</t>
+  </si>
+  <si>
+    <t>doran</t>
+  </si>
+  <si>
+    <t>alicia</t>
+  </si>
+  <si>
+    <t>keongeng</t>
+  </si>
+  <si>
+    <t>siokteng</t>
+  </si>
+  <si>
+    <t>vivian</t>
+  </si>
+  <si>
+    <t>bonteck</t>
+  </si>
+  <si>
+    <t>chinmee</t>
+  </si>
+  <si>
+    <t>soonmeng</t>
+  </si>
+  <si>
+    <t>yuehong</t>
+  </si>
+  <si>
+    <t>choejang</t>
+  </si>
+  <si>
+    <t>meichia</t>
+  </si>
+  <si>
+    <t>gekhee</t>
+  </si>
+  <si>
+    <t>aimee</t>
+  </si>
+  <si>
+    <t>geokchin</t>
+  </si>
+  <si>
+    <t>laysiew</t>
+  </si>
+  <si>
+    <t>waiyee</t>
+  </si>
+  <si>
+    <t>carol</t>
+  </si>
+  <si>
+    <t>yokewant</t>
+  </si>
+  <si>
+    <t>pohcheng</t>
+  </si>
+  <si>
+    <t>geoklan</t>
+  </si>
+  <si>
+    <t>laichee</t>
+  </si>
+  <si>
+    <t>beechoo</t>
   </si>
 </sst>
 </file>
@@ -914,7 +1359,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -977,6 +1422,17 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="DengXian"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1108,7 +1564,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1155,6 +1611,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1488,7 +1949,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -1598,7 +2059,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -1608,12 +2069,12 @@
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>30</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>31</v>
@@ -1622,10 +2083,10 @@
         <v>32</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="12">
         <f>DATE(2026,1,1)</f>
         <v>46023</v>
@@ -1635,16 +2096,19 @@
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>139</v>
-      </c>
       <c r="E2" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+      <c r="H2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="12">
         <f>DATE(2026,2,8)</f>
         <v>46061</v>
@@ -1654,16 +2118,19 @@
         <v>Sun</v>
       </c>
       <c r="C3" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="H3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="12">
         <f>DATE(2026,2,26)</f>
         <v>46079</v>
@@ -1673,16 +2140,19 @@
         <v>Thu</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>142</v>
-      </c>
       <c r="E4" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+      <c r="H4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="12">
         <f>DATE(2026,2,27)</f>
         <v>46080</v>
@@ -1692,16 +2162,19 @@
         <v>Fri</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+      <c r="H5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
         <f>DATE(2026,3,7)</f>
         <v>46088</v>
@@ -1711,16 +2184,19 @@
         <v>Sat</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+      <c r="H6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
         <f>DATE(2026,3,20)</f>
         <v>46101</v>
@@ -1730,16 +2206,19 @@
         <v>Fri</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+      <c r="H7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="12">
         <f>DATE(2026,3,23)</f>
         <v>46104</v>
@@ -1749,16 +2228,19 @@
         <v>Mon</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+      <c r="H8" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="12">
         <f>DATE(2026,3,24)</f>
         <v>46105</v>
@@ -1768,16 +2250,16 @@
         <v>Tue</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="12">
         <f>DATE(2026,3,27)</f>
         <v>46108</v>
@@ -1787,16 +2269,16 @@
         <v>Fri</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="12">
         <f>DATE(2026,4,20)</f>
         <v>46132</v>
@@ -1806,16 +2288,16 @@
         <v>Mon</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="12">
         <f>DATE(2026,5,4)</f>
         <v>46146</v>
@@ -1825,16 +2307,16 @@
         <v>Mon</v>
       </c>
       <c r="C12" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>149</v>
-      </c>
       <c r="E12" s="11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="12">
         <f>DATE(2026,5,15)</f>
         <v>46157</v>
@@ -1844,16 +2326,16 @@
         <v>Fri</v>
       </c>
       <c r="C13" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>151</v>
-      </c>
       <c r="E13" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="12">
         <f>DATE(2026,5,24)</f>
         <v>46166</v>
@@ -1863,16 +2345,16 @@
         <v>Sun</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="12">
         <f>DATE(2026,5,25)</f>
         <v>46167</v>
@@ -1882,16 +2364,16 @@
         <v>Mon</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="12">
         <f>DATE(2026,5,29)</f>
         <v>46171</v>
@@ -1901,13 +2383,13 @@
         <v>Fri</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>155</v>
-      </c>
       <c r="E16" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -1920,13 +2402,13 @@
         <v>Sat</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>157</v>
-      </c>
       <c r="E17" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -1939,13 +2421,13 @@
         <v>Sun</v>
       </c>
       <c r="C18" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="11" t="s">
-        <v>159</v>
-      </c>
       <c r="E18" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -1958,13 +2440,13 @@
         <v>Mon</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>161</v>
-      </c>
       <c r="E19" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -1977,13 +2459,13 @@
         <v>Fri</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -1996,13 +2478,13 @@
         <v>Sat</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -2015,13 +2497,13 @@
         <v>Sat</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -2034,13 +2516,13 @@
         <v>Fri</v>
       </c>
       <c r="C23" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="D23" s="11" t="s">
-        <v>164</v>
-      </c>
       <c r="E23" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -2053,13 +2535,13 @@
         <v>Fri</v>
       </c>
       <c r="C24" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>208</v>
-      </c>
       <c r="E24" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -2072,13 +2554,13 @@
         <v>Fri</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -2091,13 +2573,13 @@
         <v>Sat</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -2110,13 +2592,13 @@
         <v>Sat</v>
       </c>
       <c r="C27" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="D27" s="11" t="s">
-        <v>236</v>
-      </c>
       <c r="E27" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -2129,13 +2611,13 @@
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -2148,13 +2630,13 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -2167,13 +2649,13 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="D30" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="D30" s="16" t="s">
-        <v>284</v>
-      </c>
       <c r="E30" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -2186,13 +2668,13 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -2205,13 +2687,13 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -2224,13 +2706,13 @@
         <v>Fri</v>
       </c>
       <c r="C33" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="D33" s="11" t="s">
-        <v>166</v>
-      </c>
       <c r="E33" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -2243,13 +2725,13 @@
         <v>Sat</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -2262,13 +2744,13 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -2281,13 +2763,13 @@
         <v>Mon</v>
       </c>
       <c r="C36" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="D36" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="D36" s="21" t="s">
-        <v>282</v>
-      </c>
       <c r="E36" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -2300,13 +2782,13 @@
         <v>Tue</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
@@ -2319,13 +2801,13 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -2338,13 +2820,13 @@
         <v>Thu</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -2357,13 +2839,13 @@
         <v>Sat</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -2376,13 +2858,13 @@
         <v>Sat</v>
       </c>
       <c r="C41" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="D41" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D41" s="11" t="s">
-        <v>168</v>
-      </c>
       <c r="E41" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
@@ -2395,13 +2877,13 @@
         <v>Mon</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -2414,13 +2896,13 @@
         <v>Tue</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -2433,13 +2915,13 @@
         <v>Wed</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -2452,11 +2934,11 @@
         <v>Tue</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
@@ -2469,13 +2951,13 @@
         <v>Wed</v>
       </c>
       <c r="C46" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="D46" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="D46" s="16" t="s">
-        <v>279</v>
-      </c>
       <c r="E46" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -2488,11 +2970,11 @@
         <v>Fri</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D47" s="11"/>
       <c r="E47" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
@@ -2505,13 +2987,13 @@
         <v>Sun</v>
       </c>
       <c r="C48" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D48" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="D48" s="11" t="s">
-        <v>170</v>
-      </c>
       <c r="E48" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -2524,13 +3006,13 @@
         <v>Fri</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="38.5" x14ac:dyDescent="0.35">
@@ -2543,13 +3025,13 @@
         <v>Fri</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -2562,13 +3044,13 @@
         <v>Sat</v>
       </c>
       <c r="C51" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="D51" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="D51" s="11" t="s">
-        <v>287</v>
-      </c>
       <c r="E51" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -2581,13 +3063,13 @@
         <v>Mon</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G52" s="19"/>
     </row>
@@ -2601,13 +3083,13 @@
         <v>Tue</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -2620,13 +3102,13 @@
         <v>Wed</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -2639,13 +3121,13 @@
         <v>Sat</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -2658,13 +3140,13 @@
         <v>Tue</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -2677,13 +3159,13 @@
         <v>Tue</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -2696,13 +3178,13 @@
         <v>Wed</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
@@ -2715,13 +3197,13 @@
         <v>Fri</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -2734,13 +3216,13 @@
         <v>Sat</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -2753,13 +3235,13 @@
         <v>Thu</v>
       </c>
       <c r="C61" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="D61" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="D61" s="11" t="s">
-        <v>252</v>
-      </c>
       <c r="E61" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -2772,13 +3254,13 @@
         <v>Fri</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -2791,13 +3273,13 @@
         <v>Thu</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -2810,13 +3292,13 @@
         <v>Sat</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
@@ -2829,13 +3311,13 @@
         <v>Fri</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
@@ -2848,13 +3330,13 @@
         <v>Wed</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
@@ -2867,13 +3349,13 @@
         <v>Thu</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
@@ -2886,13 +3368,13 @@
         <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
@@ -2905,13 +3387,13 @@
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
@@ -2924,13 +3406,13 @@
         <v>Fri</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
@@ -2943,13 +3425,13 @@
         <v>Fri</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
@@ -2962,13 +3444,13 @@
         <v>Fri</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
@@ -2981,13 +3463,13 @@
         <v>Mon</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
@@ -3000,13 +3482,13 @@
         <v>Fri</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
@@ -3019,13 +3501,13 @@
         <v>Fri</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
@@ -3038,13 +3520,13 @@
         <v>Sat</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
@@ -3057,13 +3539,13 @@
         <v>Fri</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
@@ -3076,13 +3558,13 @@
         <v>Fri</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
@@ -3095,13 +3577,13 @@
         <v>Fri</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
@@ -3114,13 +3596,13 @@
         <v>Fri</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
@@ -3133,13 +3615,13 @@
         <v>Thu</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -3191,7 +3673,7 @@
         <v>38</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3205,7 +3687,7 @@
         <v>40</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3219,7 +3701,7 @@
         <v>42</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3233,7 +3715,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3247,7 +3729,7 @@
         <v>46</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3261,7 +3743,7 @@
         <v>48</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3275,7 +3757,7 @@
         <v>50</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3289,7 +3771,7 @@
         <v>52</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3303,7 +3785,7 @@
         <v>54</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3317,7 +3799,7 @@
         <v>56</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3329,7 +3811,7 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3341,7 +3823,7 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3355,7 +3837,7 @@
         <v>60</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3366,10 +3848,10 @@
         <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>62</v>
+        <v>287</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3377,13 +3859,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>64</v>
-      </c>
       <c r="D16" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3391,13 +3873,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3405,13 +3887,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>67</v>
-      </c>
       <c r="D18" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3419,13 +3901,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="D19" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3433,13 +3915,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="D20" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3447,13 +3929,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>73</v>
-      </c>
       <c r="D21" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3461,13 +3943,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>75</v>
-      </c>
       <c r="D22" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3475,13 +3957,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="D23" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3489,13 +3971,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>79</v>
-      </c>
       <c r="D24" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3503,13 +3985,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>81</v>
-      </c>
       <c r="D25" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3517,13 +3999,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>83</v>
-      </c>
       <c r="D26" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -3558,7 +4040,7 @@
         <v>24</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>21</v>
@@ -3581,7 +4063,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -3595,13 +4077,13 @@
         <v>48</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -3615,13 +4097,13 @@
         <v>42</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -3635,13 +4117,13 @@
         <v>46</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -3655,13 +4137,13 @@
         <v>50</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -3675,13 +4157,13 @@
         <v>56</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -3689,19 +4171,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="D8" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -3709,19 +4191,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" t="s">
         <v>78</v>
       </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
       <c r="D9" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -3729,19 +4211,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
         <v>74</v>
       </c>
-      <c r="C10" t="s">
-        <v>75</v>
-      </c>
       <c r="D10" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -3749,19 +4231,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" t="s">
         <v>72</v>
       </c>
-      <c r="C11" t="s">
-        <v>73</v>
-      </c>
       <c r="D11" s="14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -3769,19 +4251,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s">
         <v>66</v>
       </c>
-      <c r="C12" t="s">
-        <v>67</v>
-      </c>
       <c r="D12" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -3829,10 +4311,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>187</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>188</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -3847,15 +4329,15 @@
         <v>28</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>187</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>188</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -3868,38 +4350,38 @@
         <v>29</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>187</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>188</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F4" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>187</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>188</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -3912,61 +4394,61 @@
         <v>29</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>187</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>188</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
       </c>
       <c r="D6" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>67</v>
       </c>
       <c r="F6" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>189</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>190</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
       </c>
       <c r="D7" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>70</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>71</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>28</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>189</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>190</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -3981,61 +4463,61 @@
         <v>29</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>191</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>192</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
       </c>
       <c r="D9" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>76</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>77</v>
       </c>
       <c r="F9" s="16" t="s">
         <v>28</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>191</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>192</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
       </c>
       <c r="D10" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>80</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>81</v>
       </c>
       <c r="F10" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>193</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>194</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -4050,15 +4532,15 @@
         <v>28</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>193</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>194</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -4067,21 +4549,21 @@
         <v>61</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>62</v>
+        <v>287</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>193</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>194</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -4096,15 +4578,15 @@
         <v>29</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>193</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>194</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -4119,15 +4601,15 @@
         <v>29</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>195</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>196</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -4142,153 +4624,153 @@
         <v>28</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>195</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>196</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
       </c>
       <c r="D16" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="16" t="s">
         <v>82</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>83</v>
       </c>
       <c r="F16" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B17" s="16" t="s">
         <v>197</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>198</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
       </c>
       <c r="D17" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>63</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>64</v>
       </c>
       <c r="F17" s="16" t="s">
         <v>28</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>197</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>198</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
       </c>
       <c r="D18" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="16" t="s">
         <v>74</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>75</v>
       </c>
       <c r="F18" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" s="16" t="s">
         <v>197</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>198</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
       </c>
       <c r="D19" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>76</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>77</v>
       </c>
       <c r="F19" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>199</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>200</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
       </c>
       <c r="D20" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="16" t="s">
         <v>70</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>71</v>
       </c>
       <c r="F20" s="16" t="s">
         <v>28</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B21" s="16" t="s">
         <v>199</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>200</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
       </c>
       <c r="D21" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="16" t="s">
         <v>82</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>83</v>
       </c>
       <c r="F21" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22" s="16" t="s">
         <v>199</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>200</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -4303,7 +4785,7 @@
         <v>29</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -4312,6 +4794,892 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC0465A6-3A26-40AA-B771-10510B3DEE98}">
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="35.81640625" customWidth="1"/>
+    <col min="5" max="5" width="22.7265625" customWidth="1"/>
+    <col min="6" max="6" width="22.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="F2" s="4" t="str">
+        <f>G2&amp;H2</f>
+        <v>jinhoa.jpg</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>404</v>
+      </c>
+      <c r="H2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>387</v>
+      </c>
+      <c r="F3" s="4" t="str">
+        <f t="shared" ref="F3:F33" si="0">G3&amp;H3</f>
+        <v>kathy.jpg</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>405</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>388</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="F4" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>aceline.jpg</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="E5" s="25"/>
+      <c r="F5" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>agnes.jpg</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>407</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>391</v>
+      </c>
+      <c r="E6" s="25"/>
+      <c r="F6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>bryan.jpg</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="E7" s="25"/>
+      <c r="F7" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>yinyee.jpg</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>409</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="E8" s="25"/>
+      <c r="F8" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>jingyi.jpg</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>410</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="22" t="s">
+        <v>359</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="E9" s="25"/>
+      <c r="F9" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>chihwee.jpg</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>411</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>395</v>
+      </c>
+      <c r="E10" s="25"/>
+      <c r="F10" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>crystal.jpg</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>412</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>396</v>
+      </c>
+      <c r="E11" s="25"/>
+      <c r="F11" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>peiyuen.jpg</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>413</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="22" t="s">
+        <v>362</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>397</v>
+      </c>
+      <c r="E12" s="25"/>
+      <c r="F12" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>doran.jpg</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="22" t="s">
+        <v>363</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>398</v>
+      </c>
+      <c r="E13" s="25"/>
+      <c r="F13" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>alicia.jpg</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="F14" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>keongeng.jpg</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>416</v>
+      </c>
+      <c r="H14" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="F15" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>siokteng.jpg</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>417</v>
+      </c>
+      <c r="H15" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="F16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>vivian.jpg</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>418</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="F17" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>bonteck.jpg</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>419</v>
+      </c>
+      <c r="H17" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="F18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>chinmee.jpg</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>420</v>
+      </c>
+      <c r="H18" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="22" t="s">
+        <v>369</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>306</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="F19" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>soonmeng.jpg</v>
+      </c>
+      <c r="G19" s="24" t="s">
+        <v>421</v>
+      </c>
+      <c r="H19" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="F20" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>yuehong.jpg</v>
+      </c>
+      <c r="G20" s="24" t="s">
+        <v>422</v>
+      </c>
+      <c r="H20" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="F21" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>choejang.jpg</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>423</v>
+      </c>
+      <c r="H21" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="22" t="s">
+        <v>372</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="F22" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>meichia.jpg</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>424</v>
+      </c>
+      <c r="H22" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="22" t="s">
+        <v>373</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="F23" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>gekhee.jpg</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>425</v>
+      </c>
+      <c r="H23" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="22" t="s">
+        <v>374</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="F24" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>aimee.jpg</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>426</v>
+      </c>
+      <c r="H24" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="22" t="s">
+        <v>375</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="F25" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geokchin.jpg</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>427</v>
+      </c>
+      <c r="H25" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="22" t="s">
+        <v>376</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="F26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laysiew.jpg</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>428</v>
+      </c>
+      <c r="H26" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="22" t="s">
+        <v>377</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="F27" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>waiyee.jpg</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>429</v>
+      </c>
+      <c r="H27" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="22" t="s">
+        <v>378</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="F28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>carol.jpg</v>
+      </c>
+      <c r="G28" s="24" t="s">
+        <v>430</v>
+      </c>
+      <c r="H28" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="22" t="s">
+        <v>379</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="F29" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>yokewant.jpg</v>
+      </c>
+      <c r="G29" s="24" t="s">
+        <v>431</v>
+      </c>
+      <c r="H29" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="22" t="s">
+        <v>380</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="F30" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>pohcheng.jpg</v>
+      </c>
+      <c r="G30" s="24" t="s">
+        <v>432</v>
+      </c>
+      <c r="H30" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="22" t="s">
+        <v>381</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="F31" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geoklan.jpg</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>433</v>
+      </c>
+      <c r="H31" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="22" t="s">
+        <v>382</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>350</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="F32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laichee.jpg</v>
+      </c>
+      <c r="G32" s="24" t="s">
+        <v>434</v>
+      </c>
+      <c r="H32" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="F33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>beechoo.jpg</v>
+      </c>
+      <c r="G33" s="24" t="s">
+        <v>435</v>
+      </c>
+      <c r="H33" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4333,7 +5701,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -4341,15 +5709,15 @@
         <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" t="s">
         <v>202</v>
-      </c>
-      <c r="B4" t="s">
-        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -4358,12 +5726,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4608,20 +5978,23 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4647,14 +6020,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="588" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8BBCDB3-DC6F-442D-90B4-651C48763A98}"/>
+  <xr:revisionPtr revIDLastSave="589" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AA757D9-3822-407C-AFD7-54E03C502152}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="435">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -801,9 +801,6 @@
   </si>
   <si>
     <t>Wee Guan Construction 企业社会责任（150人）</t>
-  </si>
-  <si>
-    <t>3 August 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Temple Dinner - 元龙聖庙（关帝聖君兴诸众神诞）(Representative: Cher Kim Seah, Agnes, Bryan, Kathy, Jin Hoa - all to arrive by 7pm). Auction item included. </t>
@@ -1564,7 +1561,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1612,9 +1609,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1949,7 +1943,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -2215,7 +2209,7 @@
         <v>126</v>
       </c>
       <c r="H7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -2291,7 +2285,7 @@
         <v>132</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>131</v>
@@ -2348,7 +2342,7 @@
         <v>151</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>131</v>
@@ -2630,7 +2624,7 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>230</v>
@@ -2649,10 +2643,10 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="D30" s="16" t="s">
         <v>282</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>283</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>248</v>
@@ -2668,13 +2662,13 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>239</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -2687,7 +2681,7 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>228</v>
@@ -2725,13 +2719,13 @@
         <v>Sat</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -2744,7 +2738,7 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>240</v>
@@ -2763,10 +2757,10 @@
         <v>Mon</v>
       </c>
       <c r="C36" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="D36" s="21" t="s">
         <v>280</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>281</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>248</v>
@@ -2782,7 +2776,7 @@
         <v>Tue</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D37" s="16" t="s">
         <v>241</v>
@@ -2801,7 +2795,7 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>229</v>
@@ -2820,7 +2814,7 @@
         <v>Thu</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D39" s="16" t="s">
         <v>231</v>
@@ -2839,7 +2833,7 @@
         <v>Sat</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>242</v>
@@ -2877,7 +2871,7 @@
         <v>Mon</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D42" s="16" t="s">
         <v>232</v>
@@ -2896,7 +2890,7 @@
         <v>Tue</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D43" s="16" t="s">
         <v>244</v>
@@ -2915,7 +2909,7 @@
         <v>Wed</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D44" s="16" t="s">
         <v>243</v>
@@ -2934,11 +2928,11 @@
         <v>Tue</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
@@ -2951,13 +2945,13 @@
         <v>Wed</v>
       </c>
       <c r="C46" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D46" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="D46" s="16" t="s">
-        <v>278</v>
-      </c>
       <c r="E46" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -2970,11 +2964,11 @@
         <v>Fri</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D47" s="11"/>
       <c r="E47" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
@@ -3006,7 +3000,7 @@
         <v>Fri</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>252</v>
@@ -3025,13 +3019,13 @@
         <v>Fri</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -3044,10 +3038,10 @@
         <v>Sat</v>
       </c>
       <c r="C51" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="D51" s="11" t="s">
         <v>285</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>286</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>133</v>
@@ -3406,7 +3400,7 @@
         <v>Fri</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D70" s="11" t="s">
         <v>217</v>
@@ -3848,7 +3842,7 @@
         <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>98</v>
@@ -4100,7 +4094,7 @@
         <v>111</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>94</v>
@@ -4120,7 +4114,7 @@
         <v>111</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>87</v>
@@ -4140,7 +4134,7 @@
         <v>111</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>103</v>
@@ -4160,7 +4154,7 @@
         <v>111</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>89</v>
@@ -4180,7 +4174,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>91</v>
@@ -4549,7 +4543,7 @@
         <v>61</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>29</v>
@@ -4828,848 +4822,839 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="B2" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="B2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C2" t="s">
         <v>288</v>
       </c>
-      <c r="C2" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E2" t="s">
         <v>384</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>385</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>G2&amp;H2</f>
         <v>jinhoa.jpg</v>
       </c>
-      <c r="G2" s="24" t="s">
-        <v>404</v>
+      <c r="G2" t="s">
+        <v>403</v>
       </c>
       <c r="H2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>353</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="D3" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D3" t="s">
+        <v>385</v>
+      </c>
+      <c r="E3" t="s">
         <v>386</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>387</v>
       </c>
       <c r="F3" s="4" t="str">
         <f t="shared" ref="F3:F33" si="0">G3&amp;H3</f>
         <v>kathy.jpg</v>
       </c>
-      <c r="G3" s="24" t="s">
-        <v>405</v>
-      </c>
-      <c r="H3" s="25" t="s">
-        <v>403</v>
+      <c r="G3" t="s">
+        <v>404</v>
+      </c>
+      <c r="H3" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>354</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>291</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>322</v>
-      </c>
-      <c r="D4" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="B4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D4" t="s">
+        <v>387</v>
+      </c>
+      <c r="E4" t="s">
         <v>388</v>
       </c>
-      <c r="E4" s="25" t="s">
-        <v>389</v>
-      </c>
       <c r="F4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aceline.jpg</v>
       </c>
-      <c r="G4" s="24" t="s">
-        <v>406</v>
-      </c>
-      <c r="H4" s="25" t="s">
-        <v>403</v>
+      <c r="G4" t="s">
+        <v>405</v>
+      </c>
+      <c r="H4" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>292</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>390</v>
-      </c>
-      <c r="E5" s="25"/>
+        <v>354</v>
+      </c>
+      <c r="B5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C5" t="s">
+        <v>322</v>
+      </c>
+      <c r="D5" t="s">
+        <v>389</v>
+      </c>
       <c r="F5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>agnes.jpg</v>
       </c>
-      <c r="G5" s="24" t="s">
-        <v>407</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>403</v>
+      <c r="G5" t="s">
+        <v>406</v>
+      </c>
+      <c r="H5" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>391</v>
-      </c>
-      <c r="E6" s="25"/>
+        <v>355</v>
+      </c>
+      <c r="B6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D6" t="s">
+        <v>390</v>
+      </c>
       <c r="F6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bryan.jpg</v>
       </c>
-      <c r="G6" s="24" t="s">
-        <v>408</v>
-      </c>
-      <c r="H6" s="25" t="s">
-        <v>403</v>
+      <c r="G6" t="s">
+        <v>407</v>
+      </c>
+      <c r="H6" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>357</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>294</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>325</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>392</v>
-      </c>
-      <c r="E7" s="25"/>
+        <v>356</v>
+      </c>
+      <c r="B7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C7" t="s">
+        <v>324</v>
+      </c>
+      <c r="D7" t="s">
+        <v>391</v>
+      </c>
       <c r="F7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yinyee.jpg</v>
       </c>
-      <c r="G7" s="24" t="s">
-        <v>409</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>403</v>
+      <c r="G7" t="s">
+        <v>408</v>
+      </c>
+      <c r="H7" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
-        <v>358</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>393</v>
-      </c>
-      <c r="E8" s="25"/>
+        <v>357</v>
+      </c>
+      <c r="B8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" t="s">
+        <v>325</v>
+      </c>
+      <c r="D8" t="s">
+        <v>392</v>
+      </c>
       <c r="F8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>jingyi.jpg</v>
       </c>
-      <c r="G8" s="24" t="s">
-        <v>410</v>
-      </c>
-      <c r="H8" s="25" t="s">
-        <v>403</v>
+      <c r="G8" t="s">
+        <v>409</v>
+      </c>
+      <c r="H8" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
-        <v>359</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>327</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>394</v>
-      </c>
-      <c r="E9" s="25"/>
+        <v>358</v>
+      </c>
+      <c r="B9" t="s">
+        <v>295</v>
+      </c>
+      <c r="C9" t="s">
+        <v>326</v>
+      </c>
+      <c r="D9" t="s">
+        <v>393</v>
+      </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chihwee.jpg</v>
       </c>
-      <c r="G9" s="24" t="s">
-        <v>411</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>403</v>
+      <c r="G9" t="s">
+        <v>410</v>
+      </c>
+      <c r="H9" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
-        <v>360</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>328</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>395</v>
-      </c>
-      <c r="E10" s="25"/>
+        <v>359</v>
+      </c>
+      <c r="B10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C10" t="s">
+        <v>327</v>
+      </c>
+      <c r="D10" t="s">
+        <v>394</v>
+      </c>
       <c r="F10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>crystal.jpg</v>
       </c>
-      <c r="G10" s="24" t="s">
-        <v>412</v>
-      </c>
-      <c r="H10" s="25" t="s">
-        <v>403</v>
+      <c r="G10" t="s">
+        <v>411</v>
+      </c>
+      <c r="H10" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
-        <v>361</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>329</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>396</v>
-      </c>
-      <c r="E11" s="25"/>
+        <v>360</v>
+      </c>
+      <c r="B11" t="s">
+        <v>297</v>
+      </c>
+      <c r="C11" t="s">
+        <v>328</v>
+      </c>
+      <c r="D11" t="s">
+        <v>395</v>
+      </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>peiyuen.jpg</v>
       </c>
-      <c r="G11" s="24" t="s">
-        <v>413</v>
-      </c>
-      <c r="H11" s="25" t="s">
-        <v>403</v>
+      <c r="G11" t="s">
+        <v>412</v>
+      </c>
+      <c r="H11" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>330</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>397</v>
-      </c>
-      <c r="E12" s="25"/>
+        <v>361</v>
+      </c>
+      <c r="B12" t="s">
+        <v>298</v>
+      </c>
+      <c r="C12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D12" t="s">
+        <v>396</v>
+      </c>
       <c r="F12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>doran.jpg</v>
       </c>
-      <c r="G12" s="24" t="s">
-        <v>414</v>
-      </c>
-      <c r="H12" s="25" t="s">
-        <v>403</v>
+      <c r="G12" t="s">
+        <v>413</v>
+      </c>
+      <c r="H12" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
-        <v>363</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>331</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>398</v>
-      </c>
-      <c r="E13" s="25"/>
+        <v>362</v>
+      </c>
+      <c r="B13" t="s">
+        <v>299</v>
+      </c>
+      <c r="C13" t="s">
+        <v>330</v>
+      </c>
+      <c r="D13" t="s">
+        <v>397</v>
+      </c>
       <c r="F13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>alicia.jpg</v>
       </c>
-      <c r="G13" s="24" t="s">
-        <v>415</v>
-      </c>
-      <c r="H13" s="25" t="s">
-        <v>403</v>
+      <c r="G13" t="s">
+        <v>414</v>
+      </c>
+      <c r="H13" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
-        <v>364</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>301</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>332</v>
-      </c>
-      <c r="D14" s="25" t="s">
+        <v>363</v>
+      </c>
+      <c r="B14" t="s">
+        <v>300</v>
+      </c>
+      <c r="C14" t="s">
+        <v>331</v>
+      </c>
+      <c r="D14" t="s">
+        <v>398</v>
+      </c>
+      <c r="E14" t="s">
         <v>399</v>
       </c>
-      <c r="E14" s="25" t="s">
-        <v>400</v>
-      </c>
       <c r="F14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>keongeng.jpg</v>
       </c>
-      <c r="G14" s="24" t="s">
-        <v>416</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>403</v>
+      <c r="G14" t="s">
+        <v>415</v>
+      </c>
+      <c r="H14" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
-        <v>365</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>302</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>333</v>
-      </c>
-      <c r="D15" s="25" t="s">
+        <v>364</v>
+      </c>
+      <c r="B15" t="s">
+        <v>301</v>
+      </c>
+      <c r="C15" t="s">
+        <v>332</v>
+      </c>
+      <c r="D15" t="s">
+        <v>398</v>
+      </c>
+      <c r="E15" t="s">
         <v>399</v>
       </c>
-      <c r="E15" s="25" t="s">
-        <v>400</v>
-      </c>
       <c r="F15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>siokteng.jpg</v>
       </c>
-      <c r="G15" s="24" t="s">
-        <v>417</v>
-      </c>
-      <c r="H15" s="25" t="s">
-        <v>403</v>
+      <c r="G15" t="s">
+        <v>416</v>
+      </c>
+      <c r="H15" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
-        <v>366</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>303</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>334</v>
-      </c>
-      <c r="D16" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="B16" t="s">
+        <v>302</v>
+      </c>
+      <c r="C16" t="s">
+        <v>333</v>
+      </c>
+      <c r="D16" t="s">
+        <v>398</v>
+      </c>
+      <c r="E16" t="s">
         <v>399</v>
       </c>
-      <c r="E16" s="25" t="s">
-        <v>400</v>
-      </c>
       <c r="F16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>vivian.jpg</v>
       </c>
-      <c r="G16" s="24" t="s">
-        <v>418</v>
-      </c>
-      <c r="H16" s="25" t="s">
-        <v>403</v>
+      <c r="G16" t="s">
+        <v>417</v>
+      </c>
+      <c r="H16" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
-        <v>367</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>335</v>
-      </c>
-      <c r="D17" s="25" t="s">
+        <v>366</v>
+      </c>
+      <c r="B17" t="s">
+        <v>303</v>
+      </c>
+      <c r="C17" t="s">
+        <v>334</v>
+      </c>
+      <c r="D17" t="s">
+        <v>398</v>
+      </c>
+      <c r="E17" t="s">
         <v>399</v>
       </c>
-      <c r="E17" s="25" t="s">
-        <v>400</v>
-      </c>
       <c r="F17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bonteck.jpg</v>
       </c>
-      <c r="G17" s="24" t="s">
-        <v>419</v>
-      </c>
-      <c r="H17" s="25" t="s">
-        <v>403</v>
+      <c r="G17" t="s">
+        <v>418</v>
+      </c>
+      <c r="H17" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
-        <v>368</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="D18" s="25" t="s">
+        <v>367</v>
+      </c>
+      <c r="B18" t="s">
+        <v>304</v>
+      </c>
+      <c r="C18" t="s">
+        <v>335</v>
+      </c>
+      <c r="D18" t="s">
+        <v>398</v>
+      </c>
+      <c r="E18" t="s">
         <v>399</v>
       </c>
-      <c r="E18" s="25" t="s">
-        <v>400</v>
-      </c>
       <c r="F18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chinmee.jpg</v>
       </c>
-      <c r="G18" s="24" t="s">
-        <v>420</v>
-      </c>
-      <c r="H18" s="25" t="s">
-        <v>403</v>
+      <c r="G18" t="s">
+        <v>419</v>
+      </c>
+      <c r="H18" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
-        <v>369</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>306</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>337</v>
-      </c>
-      <c r="D19" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="B19" t="s">
+        <v>305</v>
+      </c>
+      <c r="C19" t="s">
+        <v>336</v>
+      </c>
+      <c r="D19" t="s">
+        <v>398</v>
+      </c>
+      <c r="E19" t="s">
         <v>399</v>
       </c>
-      <c r="E19" s="25" t="s">
-        <v>400</v>
-      </c>
       <c r="F19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>soonmeng.jpg</v>
       </c>
-      <c r="G19" s="24" t="s">
-        <v>421</v>
-      </c>
-      <c r="H19" s="25" t="s">
-        <v>403</v>
+      <c r="G19" t="s">
+        <v>420</v>
+      </c>
+      <c r="H19" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
-        <v>370</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>338</v>
-      </c>
-      <c r="D20" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="B20" t="s">
+        <v>306</v>
+      </c>
+      <c r="C20" t="s">
+        <v>337</v>
+      </c>
+      <c r="D20" t="s">
+        <v>398</v>
+      </c>
+      <c r="E20" t="s">
         <v>399</v>
       </c>
-      <c r="E20" s="25" t="s">
-        <v>400</v>
-      </c>
       <c r="F20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yuehong.jpg</v>
       </c>
-      <c r="G20" s="24" t="s">
-        <v>422</v>
-      </c>
-      <c r="H20" s="25" t="s">
-        <v>403</v>
+      <c r="G20" t="s">
+        <v>421</v>
+      </c>
+      <c r="H20" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
-        <v>371</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="D21" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="B21" t="s">
+        <v>307</v>
+      </c>
+      <c r="C21" t="s">
+        <v>338</v>
+      </c>
+      <c r="D21" t="s">
+        <v>398</v>
+      </c>
+      <c r="E21" t="s">
         <v>399</v>
       </c>
-      <c r="E21" s="25" t="s">
-        <v>400</v>
-      </c>
       <c r="F21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>choejang.jpg</v>
       </c>
-      <c r="G21" s="24" t="s">
-        <v>423</v>
-      </c>
-      <c r="H21" s="25" t="s">
-        <v>403</v>
+      <c r="G21" t="s">
+        <v>422</v>
+      </c>
+      <c r="H21" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
-        <v>372</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>340</v>
-      </c>
-      <c r="D22" s="25" t="s">
+        <v>371</v>
+      </c>
+      <c r="B22" t="s">
+        <v>308</v>
+      </c>
+      <c r="C22" t="s">
+        <v>339</v>
+      </c>
+      <c r="D22" t="s">
+        <v>398</v>
+      </c>
+      <c r="E22" t="s">
         <v>399</v>
       </c>
-      <c r="E22" s="25" t="s">
-        <v>400</v>
-      </c>
       <c r="F22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>meichia.jpg</v>
       </c>
-      <c r="G22" s="24" t="s">
-        <v>424</v>
-      </c>
-      <c r="H22" s="25" t="s">
-        <v>403</v>
+      <c r="G22" t="s">
+        <v>423</v>
+      </c>
+      <c r="H22" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
-        <v>373</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>341</v>
-      </c>
-      <c r="D23" s="25" t="s">
+        <v>372</v>
+      </c>
+      <c r="B23" t="s">
+        <v>309</v>
+      </c>
+      <c r="C23" t="s">
+        <v>340</v>
+      </c>
+      <c r="D23" t="s">
+        <v>398</v>
+      </c>
+      <c r="E23" t="s">
         <v>399</v>
       </c>
-      <c r="E23" s="25" t="s">
-        <v>400</v>
-      </c>
       <c r="F23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>gekhee.jpg</v>
       </c>
-      <c r="G23" s="24" t="s">
-        <v>425</v>
-      </c>
-      <c r="H23" s="25" t="s">
-        <v>403</v>
+      <c r="G23" t="s">
+        <v>424</v>
+      </c>
+      <c r="H23" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
-        <v>374</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>311</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>342</v>
-      </c>
-      <c r="D24" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="B24" t="s">
+        <v>310</v>
+      </c>
+      <c r="C24" t="s">
+        <v>341</v>
+      </c>
+      <c r="D24" t="s">
+        <v>398</v>
+      </c>
+      <c r="E24" t="s">
         <v>399</v>
       </c>
-      <c r="E24" s="25" t="s">
-        <v>400</v>
-      </c>
       <c r="F24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aimee.jpg</v>
       </c>
-      <c r="G24" s="24" t="s">
-        <v>426</v>
-      </c>
-      <c r="H24" s="25" t="s">
-        <v>403</v>
+      <c r="G24" t="s">
+        <v>425</v>
+      </c>
+      <c r="H24" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>375</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>312</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>343</v>
-      </c>
-      <c r="D25" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="B25" t="s">
+        <v>311</v>
+      </c>
+      <c r="C25" t="s">
+        <v>342</v>
+      </c>
+      <c r="D25" t="s">
+        <v>400</v>
+      </c>
+      <c r="E25" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="E25" s="26" t="s">
+      <c r="F25" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geokchin.jpg</v>
+      </c>
+      <c r="G25" t="s">
+        <v>426</v>
+      </c>
+      <c r="H25" t="s">
         <v>402</v>
-      </c>
-      <c r="F25" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>geokchin.jpg</v>
-      </c>
-      <c r="G25" s="24" t="s">
-        <v>427</v>
-      </c>
-      <c r="H25" s="25" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>376</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>313</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>344</v>
-      </c>
-      <c r="D26" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="B26" t="s">
+        <v>312</v>
+      </c>
+      <c r="C26" t="s">
+        <v>343</v>
+      </c>
+      <c r="D26" t="s">
+        <v>400</v>
+      </c>
+      <c r="E26" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="E26" s="26" t="s">
+      <c r="F26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laysiew.jpg</v>
+      </c>
+      <c r="G26" t="s">
+        <v>427</v>
+      </c>
+      <c r="H26" t="s">
         <v>402</v>
-      </c>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>laysiew.jpg</v>
-      </c>
-      <c r="G26" s="24" t="s">
-        <v>428</v>
-      </c>
-      <c r="H26" s="25" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
-        <v>377</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>345</v>
-      </c>
-      <c r="D27" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="B27" t="s">
+        <v>313</v>
+      </c>
+      <c r="C27" t="s">
+        <v>344</v>
+      </c>
+      <c r="D27" t="s">
+        <v>400</v>
+      </c>
+      <c r="E27" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="E27" s="26" t="s">
+      <c r="F27" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>waiyee.jpg</v>
+      </c>
+      <c r="G27" t="s">
+        <v>428</v>
+      </c>
+      <c r="H27" t="s">
         <v>402</v>
-      </c>
-      <c r="F27" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>waiyee.jpg</v>
-      </c>
-      <c r="G27" s="24" t="s">
-        <v>429</v>
-      </c>
-      <c r="H27" s="25" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
-        <v>378</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>315</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>346</v>
-      </c>
-      <c r="D28" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="B28" t="s">
+        <v>314</v>
+      </c>
+      <c r="C28" t="s">
+        <v>345</v>
+      </c>
+      <c r="D28" t="s">
+        <v>400</v>
+      </c>
+      <c r="E28" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="E28" s="26" t="s">
+      <c r="F28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>carol.jpg</v>
+      </c>
+      <c r="G28" t="s">
+        <v>429</v>
+      </c>
+      <c r="H28" t="s">
         <v>402</v>
-      </c>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>carol.jpg</v>
-      </c>
-      <c r="G28" s="24" t="s">
-        <v>430</v>
-      </c>
-      <c r="H28" s="25" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
-        <v>379</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="D29" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="B29" t="s">
+        <v>315</v>
+      </c>
+      <c r="C29" t="s">
+        <v>346</v>
+      </c>
+      <c r="D29" t="s">
+        <v>400</v>
+      </c>
+      <c r="E29" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="E29" s="26" t="s">
+      <c r="F29" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>yokewant.jpg</v>
+      </c>
+      <c r="G29" t="s">
+        <v>430</v>
+      </c>
+      <c r="H29" t="s">
         <v>402</v>
-      </c>
-      <c r="F29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>yokewant.jpg</v>
-      </c>
-      <c r="G29" s="24" t="s">
-        <v>431</v>
-      </c>
-      <c r="H29" s="25" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
-        <v>380</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="D30" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="B30" t="s">
+        <v>316</v>
+      </c>
+      <c r="C30" t="s">
+        <v>347</v>
+      </c>
+      <c r="D30" t="s">
+        <v>400</v>
+      </c>
+      <c r="E30" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="E30" s="26" t="s">
+      <c r="F30" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>pohcheng.jpg</v>
+      </c>
+      <c r="G30" t="s">
+        <v>431</v>
+      </c>
+      <c r="H30" t="s">
         <v>402</v>
-      </c>
-      <c r="F30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>pohcheng.jpg</v>
-      </c>
-      <c r="G30" s="24" t="s">
-        <v>432</v>
-      </c>
-      <c r="H30" s="25" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
-        <v>381</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>349</v>
-      </c>
-      <c r="D31" s="25" t="s">
+        <v>380</v>
+      </c>
+      <c r="B31" t="s">
+        <v>317</v>
+      </c>
+      <c r="C31" t="s">
+        <v>348</v>
+      </c>
+      <c r="D31" t="s">
+        <v>400</v>
+      </c>
+      <c r="E31" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="E31" s="26" t="s">
+      <c r="F31" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geoklan.jpg</v>
+      </c>
+      <c r="G31" t="s">
+        <v>432</v>
+      </c>
+      <c r="H31" t="s">
         <v>402</v>
-      </c>
-      <c r="F31" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>geoklan.jpg</v>
-      </c>
-      <c r="G31" s="24" t="s">
-        <v>433</v>
-      </c>
-      <c r="H31" s="25" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
-        <v>382</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>350</v>
-      </c>
-      <c r="D32" s="25" t="s">
+        <v>381</v>
+      </c>
+      <c r="B32" t="s">
+        <v>318</v>
+      </c>
+      <c r="C32" t="s">
+        <v>349</v>
+      </c>
+      <c r="D32" t="s">
+        <v>400</v>
+      </c>
+      <c r="E32" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="E32" s="26" t="s">
+      <c r="F32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laichee.jpg</v>
+      </c>
+      <c r="G32" t="s">
+        <v>433</v>
+      </c>
+      <c r="H32" t="s">
         <v>402</v>
-      </c>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>laichee.jpg</v>
-      </c>
-      <c r="G32" s="24" t="s">
-        <v>434</v>
-      </c>
-      <c r="H32" s="25" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>383</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>351</v>
-      </c>
-      <c r="D33" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="B33" t="s">
+        <v>319</v>
+      </c>
+      <c r="C33" t="s">
+        <v>350</v>
+      </c>
+      <c r="D33" t="s">
+        <v>400</v>
+      </c>
+      <c r="E33" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="E33" s="26" t="s">
+      <c r="F33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>beechoo.jpg</v>
+      </c>
+      <c r="G33" t="s">
+        <v>434</v>
+      </c>
+      <c r="H33" t="s">
         <v>402</v>
-      </c>
-      <c r="F33" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>beechoo.jpg</v>
-      </c>
-      <c r="G33" s="24" t="s">
-        <v>435</v>
-      </c>
-      <c r="H33" s="25" t="s">
-        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -5700,8 +5685,9 @@
       <c r="A2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>253</v>
+      <c r="B2" s="18">
+        <f ca="1">TODAY()</f>
+        <v>46251</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -5709,7 +5695,7 @@
         <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -5726,14 +5712,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5978,23 +5962,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6020,9 +6001,14 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="589" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AA757D9-3822-407C-AFD7-54E03C502152}"/>
+  <xr:revisionPtr revIDLastSave="694" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A633333-D661-4E54-B797-A99088FCAB75}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$80</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="481">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -644,9 +644,6 @@
     <t>公关组</t>
   </si>
   <si>
-    <t>[Tentative] Charity Walk - postpone to April 2027</t>
-  </si>
-  <si>
     <t>Password to open mobile page</t>
   </si>
   <si>
@@ -677,9 +674,6 @@
     <t>[未确认] 九皇爷诞筹款第三天</t>
   </si>
   <si>
-    <t>[未确认] 慈善健走（暂定）</t>
-  </si>
-  <si>
     <t>[未确认] 屠妖节红包派发（AMS印族受惠者）</t>
   </si>
   <si>
@@ -1347,6 +1341,150 @@
   </si>
   <si>
     <t>beechoo</t>
+  </si>
+  <si>
+    <t>calendar</t>
+  </si>
+  <si>
+    <t>New Year Ration</t>
+  </si>
+  <si>
+    <t>Shine Dragon Boat</t>
+  </si>
+  <si>
+    <t>Temple Dinner - 元龙聖庙</t>
+  </si>
+  <si>
+    <t>CNY Ration</t>
+  </si>
+  <si>
+    <t>CNY Dinner</t>
+  </si>
+  <si>
+    <t>Elderly Outing</t>
+  </si>
+  <si>
+    <t>Health Talk</t>
+  </si>
+  <si>
+    <t>School - Ahmad Ibrahim</t>
+  </si>
+  <si>
+    <t>华报善堂</t>
+  </si>
+  <si>
+    <t>Kopi Kaki</t>
+  </si>
+  <si>
+    <t>Hari Raya Lunch</t>
+  </si>
+  <si>
+    <t>Hari Raya Ang Pao</t>
+  </si>
+  <si>
+    <t>Ubin Thai</t>
+  </si>
+  <si>
+    <t>By-election</t>
+  </si>
+  <si>
+    <t>25th Anniversary</t>
+  </si>
+  <si>
+    <t>AGM</t>
+  </si>
+  <si>
+    <t>Members sworn-in</t>
+  </si>
+  <si>
+    <t>Corporate - AISS, Funerary portriat</t>
+  </si>
+  <si>
+    <t>Corporate - Morgan Stanley, Funerary Portrait</t>
+  </si>
+  <si>
+    <t>School - Naval Base</t>
+  </si>
+  <si>
+    <t>Corporate - Asistic Fire System</t>
+  </si>
+  <si>
+    <t>中元会 - Blk 139</t>
+  </si>
+  <si>
+    <t>中元会 - YS One</t>
+  </si>
+  <si>
+    <t>Chong Pang 61st National Day Dinner</t>
+  </si>
+  <si>
+    <t>Corporate - TFE</t>
+  </si>
+  <si>
+    <t>中元会 - Blk 724</t>
+  </si>
+  <si>
+    <t>中元会 - ARK@Gambas</t>
+  </si>
+  <si>
+    <t>中元会 - Blk 561</t>
+  </si>
+  <si>
+    <t>中元会 - Jurong Safra</t>
+  </si>
+  <si>
+    <t>中元会 - Blk 104</t>
+  </si>
+  <si>
+    <t>MWS Family Wellness</t>
+  </si>
+  <si>
+    <t>中元会 - 南凤善堂</t>
+  </si>
+  <si>
+    <t>中元会 - Blk 838</t>
+  </si>
+  <si>
+    <t>Charity Conference</t>
+  </si>
+  <si>
+    <t>North West District Meeting</t>
+  </si>
+  <si>
+    <t>Corporate - 正罡玄门</t>
+  </si>
+  <si>
+    <t>Corporate - Wee Guan</t>
+  </si>
+  <si>
+    <t>Nee Soon CC dialogue with MP</t>
+  </si>
+  <si>
+    <t>Charity Concert</t>
+  </si>
+  <si>
+    <t>九皇爷</t>
+  </si>
+  <si>
+    <t>CSR Partnership</t>
+  </si>
+  <si>
+    <t>Deepavali Ang Pao</t>
+  </si>
+  <si>
+    <t>Corporate - MS Project</t>
+  </si>
+  <si>
+    <t>Sponsor a HUG</t>
+  </si>
+  <si>
+    <t>7th Month Fundraising</t>
+  </si>
+  <si>
+    <t>Corporate - Charity Walk</t>
+  </si>
+  <si>
+    <t>Dragon Board Festival</t>
   </si>
 </sst>
 </file>
@@ -1561,7 +1699,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1610,6 +1748,11 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1943,7 +2086,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -2053,7 +2196,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -2079,6 +2222,9 @@
       <c r="E1" s="10" t="s">
         <v>136</v>
       </c>
+      <c r="F1" s="24" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="12">
@@ -2098,6 +2244,9 @@
       <c r="E2" s="11" t="s">
         <v>126</v>
       </c>
+      <c r="F2" s="25" t="s">
+        <v>434</v>
+      </c>
       <c r="H2" t="s">
         <v>126</v>
       </c>
@@ -2120,6 +2269,9 @@
       <c r="E3" s="11" t="s">
         <v>123</v>
       </c>
+      <c r="F3" s="25" t="s">
+        <v>437</v>
+      </c>
       <c r="H3" t="s">
         <v>123</v>
       </c>
@@ -2142,6 +2294,9 @@
       <c r="E4" s="11" t="s">
         <v>133</v>
       </c>
+      <c r="F4" s="25" t="s">
+        <v>438</v>
+      </c>
       <c r="H4" t="s">
         <v>133</v>
       </c>
@@ -2164,6 +2319,9 @@
       <c r="E5" s="11" t="s">
         <v>123</v>
       </c>
+      <c r="F5" s="25" t="s">
+        <v>441</v>
+      </c>
       <c r="H5" t="s">
         <v>131</v>
       </c>
@@ -2186,8 +2344,11 @@
       <c r="E6" s="11" t="s">
         <v>123</v>
       </c>
+      <c r="F6" s="25" t="s">
+        <v>442</v>
+      </c>
       <c r="H6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -2208,8 +2369,11 @@
       <c r="E7" s="11" t="s">
         <v>126</v>
       </c>
+      <c r="F7" s="25" t="s">
+        <v>439</v>
+      </c>
       <c r="H7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -2230,8 +2394,11 @@
       <c r="E8" s="11" t="s">
         <v>123</v>
       </c>
+      <c r="F8" s="25" t="s">
+        <v>445</v>
+      </c>
       <c r="H8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -2252,6 +2419,9 @@
       <c r="E9" s="11" t="s">
         <v>123</v>
       </c>
+      <c r="F9" s="25" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="12">
@@ -2266,10 +2436,13 @@
         <v>130</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>123</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -2285,10 +2458,13 @@
         <v>132</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>131</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -2309,6 +2485,9 @@
       <c r="E12" s="11" t="s">
         <v>131</v>
       </c>
+      <c r="F12" s="25" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="12">
@@ -2328,6 +2507,9 @@
       <c r="E13" s="11" t="s">
         <v>133</v>
       </c>
+      <c r="F13" s="25" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="12">
@@ -2342,10 +2524,13 @@
         <v>151</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>131</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -2366,6 +2551,9 @@
       <c r="E15" s="11" t="s">
         <v>123</v>
       </c>
+      <c r="F15" s="25" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="12">
@@ -2383,10 +2571,13 @@
         <v>154</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="12">
         <f>DATE(2026,5,30)</f>
         <v>46172</v>
@@ -2402,10 +2593,13 @@
         <v>156</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="12">
         <f>DATE(2026,5,31)</f>
         <v>46173</v>
@@ -2421,10 +2615,13 @@
         <v>158</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="12">
         <f>DATE(2026,6,1)</f>
         <v>46174</v>
@@ -2440,10 +2637,13 @@
         <v>160</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="12">
         <f>DATE(2026,6,12)</f>
         <v>46185</v>
@@ -2456,13 +2656,16 @@
         <v>130</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F20" s="25" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="12">
         <f>DATE(2026,6,13)</f>
         <v>46186</v>
@@ -2480,8 +2683,11 @@
       <c r="E21" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F21" s="25" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="12">
         <f>DATE(2026,6,20)</f>
         <v>46193</v>
@@ -2494,13 +2700,16 @@
         <v>130</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F22" s="25" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="12">
         <f>DATE(2026,7,3)</f>
         <v>46206</v>
@@ -2518,8 +2727,11 @@
       <c r="E23" s="11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F23" s="25" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="12">
         <f>DATE(2026,7,24)</f>
         <v>46227</v>
@@ -2529,16 +2741,19 @@
         <v>Fri</v>
       </c>
       <c r="C24" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>206</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>207</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F24" s="25" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="12">
         <f>DATE(2026,7,24)</f>
         <v>46227</v>
@@ -2551,13 +2766,16 @@
         <v>130</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F25" s="25" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="12">
         <f>DATE(2026,7,25)</f>
         <v>46228</v>
@@ -2570,13 +2788,16 @@
         <v>130</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F26" s="25" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="12">
         <f>DATE(2026,8,1)</f>
         <v>46235</v>
@@ -2586,16 +2807,19 @@
         <v>Sat</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F27" s="25" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="12">
         <f>DATE(2026,8,5)</f>
         <v>46239</v>
@@ -2605,16 +2829,19 @@
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F28" s="25" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="12">
         <f>DATE(2026,8,8)</f>
         <v>46242</v>
@@ -2624,16 +2851,19 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F29" s="25" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="12">
         <f>DATE(2026,8,14)</f>
         <v>46248</v>
@@ -2643,16 +2873,19 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F30" s="25" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="12">
         <f>DATE(2026,8,15)</f>
         <v>46249</v>
@@ -2662,16 +2895,19 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="12">
         <f>DATE(2026,8,23)</f>
         <v>46257</v>
@@ -2681,16 +2917,19 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F32" s="25" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="12">
         <f>DATE(2026,8,28)</f>
         <v>46262</v>
@@ -2708,8 +2947,11 @@
       <c r="E33" s="11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F33" s="25" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="12">
         <f>DATE(2026,8,29)</f>
         <v>46263</v>
@@ -2719,16 +2961,19 @@
         <v>Sat</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="12">
         <f>DATE(2026,8,29)</f>
         <v>46263</v>
@@ -2738,16 +2983,19 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F35" s="25" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="12">
         <f>DATE(2026,8,31)</f>
         <v>46265</v>
@@ -2757,16 +3005,19 @@
         <v>Mon</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F36" s="25" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="12">
         <f>DATE(2026,9,1)</f>
         <v>46266</v>
@@ -2776,16 +3027,19 @@
         <v>Tue</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F37" s="25" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="12">
         <f>DATE(2026,9,3)</f>
         <v>46268</v>
@@ -2795,16 +3049,19 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="12">
         <f>DATE(2026,9,3)</f>
         <v>46268</v>
@@ -2814,16 +3071,19 @@
         <v>Thu</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F39" s="25" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="12">
         <f>DATE(2026,9,5)</f>
         <v>46270</v>
@@ -2833,16 +3093,19 @@
         <v>Sat</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F40" s="25" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="12">
         <f>DATE(2026,9,5)</f>
         <v>46270</v>
@@ -2860,8 +3123,11 @@
       <c r="E41" s="11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F41" s="25" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="12">
         <f>DATE(2026,9,7)</f>
         <v>46272</v>
@@ -2871,16 +3137,19 @@
         <v>Mon</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F42" s="25" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="12">
         <f>DATE(2026,9,8)</f>
         <v>46273</v>
@@ -2890,16 +3159,19 @@
         <v>Tue</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F43" s="25" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="12">
         <f>DATE(2026,9,9)</f>
         <v>46274</v>
@@ -2909,16 +3181,19 @@
         <v>Wed</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F44" s="25" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="12">
         <f>DATE(2026,9,15)</f>
         <v>46280</v>
@@ -2928,14 +3203,17 @@
         <v>Tue</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="11" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+      <c r="F45" s="25" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="12">
         <f>DATE(2026,9,16)</f>
         <v>46281</v>
@@ -2945,16 +3223,19 @@
         <v>Wed</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+      <c r="F46" s="25" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="12">
         <f>DATE(2026,9,18)</f>
         <v>46283</v>
@@ -2964,14 +3245,17 @@
         <v>Fri</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D47" s="11"/>
       <c r="E47" s="11" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+      <c r="F47" s="25" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="12">
         <f>DATE(2026,9,20)</f>
         <v>46285</v>
@@ -2988,6 +3272,9 @@
       </c>
       <c r="E48" s="11" t="s">
         <v>126</v>
+      </c>
+      <c r="F48" s="25" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -3000,13 +3287,16 @@
         <v>Fri</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>126</v>
+      </c>
+      <c r="F49" s="25" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="38.5" x14ac:dyDescent="0.35">
@@ -3019,13 +3309,16 @@
         <v>Fri</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>265</v>
+        <v>263</v>
+      </c>
+      <c r="F50" s="25" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -3038,13 +3331,16 @@
         <v>Sat</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>133</v>
+      </c>
+      <c r="F51" s="25" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -3057,13 +3353,16 @@
         <v>Mon</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
+      </c>
+      <c r="F52" s="25" t="s">
+        <v>473</v>
       </c>
       <c r="G52" s="19"/>
     </row>
@@ -3077,13 +3376,16 @@
         <v>Tue</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
+      </c>
+      <c r="F53" s="25" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -3096,437 +3398,506 @@
         <v>Wed</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
+      </c>
+      <c r="F54" s="25" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="12">
-        <f>DATE(2026,10,31)</f>
-        <v>46326</v>
+        <f>DATE(2026,11,3)</f>
+        <v>46329</v>
       </c>
       <c r="B55" s="13" t="str">
-        <f t="shared" ref="B55:B81" si="2">TEXT($A55,"ddd")</f>
-        <v>Sat</v>
+        <f t="shared" ref="B55:B80" si="2">TEXT($A55,"ddd")</f>
+        <v>Tue</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>133</v>
+        <v>123</v>
+      </c>
+      <c r="F55" s="25" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="12">
-        <f>DATE(2026,11,3)</f>
-        <v>46329</v>
+        <f>DATE(2026,11,10)</f>
+        <v>46336</v>
       </c>
       <c r="B56" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>123</v>
+        <v>126</v>
+      </c>
+      <c r="F56" s="25" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="12">
-        <f>DATE(2026,11,10)</f>
-        <v>46336</v>
+        <f>DATE(2026,12,16)</f>
+        <v>46372</v>
       </c>
       <c r="B57" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Tue</v>
+        <v>Wed</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>213</v>
+        <v>171</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>212</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>126</v>
+        <v>133</v>
+      </c>
+      <c r="F57" s="25" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="12">
-        <f>DATE(2026,12,16)</f>
-        <v>46372</v>
+        <f>DATE(2027,1,1)</f>
+        <v>46388</v>
       </c>
       <c r="B58" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Wed</v>
+        <v>Fri</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>214</v>
+        <v>245</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>213</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>133</v>
       </c>
+      <c r="F58" s="25" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="12">
-        <f>DATE(2027,1,1)</f>
-        <v>46388</v>
+        <f>DATE(2027,1,30)</f>
+        <v>46417</v>
       </c>
       <c r="B59" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>247</v>
+        <v>Sat</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>174</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>133</v>
+        <v>123</v>
+      </c>
+      <c r="F59" s="25" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="12">
-        <f>DATE(2027,1,30)</f>
-        <v>46417</v>
+        <f>DATE(2027,2,18)</f>
+        <v>46436</v>
       </c>
       <c r="B60" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Sat</v>
+        <v>Thu</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>174</v>
+        <v>248</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>123</v>
+        <v>247</v>
+      </c>
+      <c r="F60" s="26" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="12">
-        <f>DATE(2027,2,18)</f>
-        <v>46436</v>
+        <f>DATE(2027,3,19)</f>
+        <v>46465</v>
       </c>
       <c r="B61" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Thu</v>
+        <v>Fri</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>249</v>
+        <v>126</v>
+      </c>
+      <c r="F61" s="26" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="12">
-        <f>DATE(2027,3,19)</f>
-        <v>46465</v>
+        <f>DATE(2027,3,25)</f>
+        <v>46471</v>
       </c>
       <c r="B62" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Thu</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>126</v>
+        <v>123</v>
+      </c>
+      <c r="F62" s="26" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="12">
-        <f>DATE(2027,3,25)</f>
-        <v>46471</v>
+        <f>DATE(2027,4,3)</f>
+        <v>46480</v>
       </c>
       <c r="B63" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>176</v>
+        <v>Sat</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>123</v>
+        <v>247</v>
+      </c>
+      <c r="F63" s="26" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="12">
-        <f>DATE(2027,4,3)</f>
-        <v>46480</v>
+        <f>DATE(2027,4,9)</f>
+        <v>46486</v>
       </c>
       <c r="B64" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Sat</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>233</v>
+        <v>Fri</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>175</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+      <c r="F64" s="26" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="12">
-        <f>DATE(2027,4,9)</f>
-        <v>46486</v>
+        <f>DATE(2027,5,19)</f>
+        <v>46526</v>
       </c>
       <c r="B65" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Wed</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F65" s="26" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="12">
-        <f>DATE(2027,5,19)</f>
-        <v>46526</v>
+        <f>DATE(2027,5,20)</f>
+        <v>46527</v>
       </c>
       <c r="B66" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F66" s="26" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="12">
-        <f>DATE(2027,5,20)</f>
-        <v>46527</v>
+        <f>DATE(2027,5,21)</f>
+        <v>46528</v>
       </c>
       <c r="B67" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Thu</v>
+        <v>Fri</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F67" s="26" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="12">
-        <f>DATE(2027,5,21)</f>
-        <v>46528</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B68" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+      <c r="F68" s="26" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B69" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>180</v>
+        <v>281</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+      <c r="F69" s="26" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B70" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>283</v>
+        <v>175</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F70" s="26" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
       </c>
       <c r="B71" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F71" s="26" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="12">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
+        <f>DATE(2027,8,16)</f>
+        <v>46615</v>
       </c>
       <c r="B72" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Mon</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+      <c r="F72" s="26" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="12">
-        <f>DATE(2027,8,16)</f>
-        <v>46615</v>
+        <f>DATE(2027,8,20)</f>
+        <v>46619</v>
       </c>
       <c r="B73" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Mon</v>
+        <v>Fri</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+      <c r="F73" s="26" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="12">
-        <f>DATE(2027,8,20)</f>
-        <v>46619</v>
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
       </c>
       <c r="B74" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="E74" s="11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F74" s="26" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
+        <f>DATE(2027,9,18)</f>
+        <v>46648</v>
       </c>
       <c r="B75" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Sat</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+      <c r="F75" s="26" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="12">
-        <f>DATE(2027,9,18)</f>
-        <v>46648</v>
+        <f>DATE(2027,10,1)</f>
+        <v>46661</v>
       </c>
       <c r="B76" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Sat</v>
+        <v>Fri</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+      <c r="F76" s="26" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="12">
-        <f>DATE(2027,10,1)</f>
-        <v>46661</v>
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
       </c>
       <c r="B77" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3536,16 +3907,19 @@
         <v>175</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E77" s="11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F77" s="26" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="12">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
       </c>
       <c r="B78" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3555,16 +3929,19 @@
         <v>175</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E78" s="11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F78" s="26" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="12">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
       </c>
       <c r="B79" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3574,52 +3951,39 @@
         <v>175</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E79" s="11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F79" s="26" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
+        <f>DATE(2027,12,16)</f>
+        <v>46737</v>
       </c>
       <c r="B80" s="13" t="str">
         <f t="shared" si="2"/>
-        <v>Fri</v>
+        <v>Thu</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="D80" s="11" t="s">
-        <v>217</v>
+        <v>171</v>
+      </c>
+      <c r="D80" s="16" t="s">
+        <v>212</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A81" s="12">
-        <f>DATE(2027,12,16)</f>
-        <v>46737</v>
-      </c>
-      <c r="B81" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Thu</v>
-      </c>
-      <c r="C81" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="D81" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="E81" s="11" t="s">
         <v>133</v>
       </c>
+      <c r="F80" s="26" t="s">
+        <v>477</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E81" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E80" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
@@ -3842,7 +4206,7 @@
         <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>98</v>
@@ -4094,7 +4458,7 @@
         <v>111</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>94</v>
@@ -4114,7 +4478,7 @@
         <v>111</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>87</v>
@@ -4134,7 +4498,7 @@
         <v>111</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>103</v>
@@ -4154,7 +4518,7 @@
         <v>111</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>89</v>
@@ -4174,7 +4538,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>91</v>
@@ -4543,7 +4907,7 @@
         <v>61</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>29</v>
@@ -4822,839 +5186,839 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>G2&amp;H2</f>
         <v>jinhoa.jpg</v>
       </c>
       <c r="G2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F3" s="4" t="str">
         <f t="shared" ref="F3:F33" si="0">G3&amp;H3</f>
         <v>kathy.jpg</v>
       </c>
       <c r="G3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aceline.jpg</v>
       </c>
       <c r="G4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="H4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>agnes.jpg</v>
       </c>
       <c r="G5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H5" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bryan.jpg</v>
       </c>
       <c r="G6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yinyee.jpg</v>
       </c>
       <c r="G7" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H7" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B8" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D8" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>jingyi.jpg</v>
       </c>
       <c r="G8" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H8" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D9" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chihwee.jpg</v>
       </c>
       <c r="G9" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H9" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B10" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C10" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D10" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>crystal.jpg</v>
       </c>
       <c r="G10" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B11" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C11" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D11" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>peiyuen.jpg</v>
       </c>
       <c r="G11" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H11" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>doran.jpg</v>
       </c>
       <c r="G12" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H12" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B13" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D13" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>alicia.jpg</v>
       </c>
       <c r="G13" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H13" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C14" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D14" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E14" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>keongeng.jpg</v>
       </c>
       <c r="G14" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H14" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C15" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E15" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>siokteng.jpg</v>
       </c>
       <c r="G15" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H15" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B16" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C16" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D16" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E16" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>vivian.jpg</v>
       </c>
       <c r="G16" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H16" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B17" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C17" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D17" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E17" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bonteck.jpg</v>
       </c>
       <c r="G17" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H17" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B18" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C18" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D18" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E18" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chinmee.jpg</v>
       </c>
       <c r="G18" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H18" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B19" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C19" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D19" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E19" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>soonmeng.jpg</v>
       </c>
       <c r="G19" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H19" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B20" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C20" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D20" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E20" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yuehong.jpg</v>
       </c>
       <c r="G20" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H20" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B21" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C21" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D21" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E21" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>choejang.jpg</v>
       </c>
       <c r="G21" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H21" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B22" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C22" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D22" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E22" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>meichia.jpg</v>
       </c>
       <c r="G22" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H22" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B23" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C23" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D23" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E23" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>gekhee.jpg</v>
       </c>
       <c r="G23" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H23" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B24" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C24" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D24" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E24" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aimee.jpg</v>
       </c>
       <c r="G24" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H24" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B25" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C25" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D25" t="s">
+        <v>398</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="F25" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geokchin.jpg</v>
+      </c>
+      <c r="G25" t="s">
+        <v>424</v>
+      </c>
+      <c r="H25" t="s">
         <v>400</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>401</v>
-      </c>
-      <c r="F25" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>geokchin.jpg</v>
-      </c>
-      <c r="G25" t="s">
-        <v>426</v>
-      </c>
-      <c r="H25" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B26" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D26" t="s">
+        <v>398</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="F26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laysiew.jpg</v>
+      </c>
+      <c r="G26" t="s">
+        <v>425</v>
+      </c>
+      <c r="H26" t="s">
         <v>400</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>401</v>
-      </c>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>laysiew.jpg</v>
-      </c>
-      <c r="G26" t="s">
-        <v>427</v>
-      </c>
-      <c r="H26" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B27" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C27" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D27" t="s">
+        <v>398</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="F27" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>waiyee.jpg</v>
+      </c>
+      <c r="G27" t="s">
+        <v>426</v>
+      </c>
+      <c r="H27" t="s">
         <v>400</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>401</v>
-      </c>
-      <c r="F27" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>waiyee.jpg</v>
-      </c>
-      <c r="G27" t="s">
-        <v>428</v>
-      </c>
-      <c r="H27" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B28" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C28" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D28" t="s">
+        <v>398</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="F28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>carol.jpg</v>
+      </c>
+      <c r="G28" t="s">
+        <v>427</v>
+      </c>
+      <c r="H28" t="s">
         <v>400</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>401</v>
-      </c>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>carol.jpg</v>
-      </c>
-      <c r="G28" t="s">
-        <v>429</v>
-      </c>
-      <c r="H28" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B29" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C29" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D29" t="s">
+        <v>398</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="F29" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>yokewant.jpg</v>
+      </c>
+      <c r="G29" t="s">
+        <v>428</v>
+      </c>
+      <c r="H29" t="s">
         <v>400</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>401</v>
-      </c>
-      <c r="F29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>yokewant.jpg</v>
-      </c>
-      <c r="G29" t="s">
-        <v>430</v>
-      </c>
-      <c r="H29" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B30" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C30" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D30" t="s">
+        <v>398</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="F30" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>pohcheng.jpg</v>
+      </c>
+      <c r="G30" t="s">
+        <v>429</v>
+      </c>
+      <c r="H30" t="s">
         <v>400</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>401</v>
-      </c>
-      <c r="F30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>pohcheng.jpg</v>
-      </c>
-      <c r="G30" t="s">
-        <v>431</v>
-      </c>
-      <c r="H30" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B31" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C31" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D31" t="s">
+        <v>398</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="F31" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geoklan.jpg</v>
+      </c>
+      <c r="G31" t="s">
+        <v>430</v>
+      </c>
+      <c r="H31" t="s">
         <v>400</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>401</v>
-      </c>
-      <c r="F31" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>geoklan.jpg</v>
-      </c>
-      <c r="G31" t="s">
-        <v>432</v>
-      </c>
-      <c r="H31" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B32" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C32" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D32" t="s">
+        <v>398</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="F32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laichee.jpg</v>
+      </c>
+      <c r="G32" t="s">
+        <v>431</v>
+      </c>
+      <c r="H32" t="s">
         <v>400</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>401</v>
-      </c>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>laichee.jpg</v>
-      </c>
-      <c r="G32" t="s">
-        <v>433</v>
-      </c>
-      <c r="H32" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B33" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C33" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D33" t="s">
+        <v>398</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="F33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>beechoo.jpg</v>
+      </c>
+      <c r="G33" t="s">
+        <v>432</v>
+      </c>
+      <c r="H33" t="s">
         <v>400</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>401</v>
-      </c>
-      <c r="F33" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>beechoo.jpg</v>
-      </c>
-      <c r="G33" t="s">
-        <v>434</v>
-      </c>
-      <c r="H33" t="s">
-        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -5695,15 +6059,15 @@
         <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4" t="s">
         <v>201</v>
-      </c>
-      <c r="B4" t="s">
-        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -5712,12 +6076,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5962,20 +6328,23 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6001,14 +6370,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="694" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A633333-D661-4E54-B797-A99088FCAB75}"/>
+  <xr:revisionPtr revIDLastSave="696" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ECB2120-521B-4229-A269-5ACD6B1C0C8F}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="481">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -755,9 +755,6 @@
     <t>中医保健养生讲座 - 中药茶饮</t>
   </si>
   <si>
-    <t>2026年中邦第61届国庆晚宴，晚上7点至10点。（代表：陈浚纬, Bill Tan）</t>
-  </si>
-  <si>
     <t>717 商店中元会 (代表：周锦昌, Kathy, 丽菁, 丽丝和先生）</t>
   </si>
   <si>
@@ -860,9 +857,6 @@
     <t>南凤福利协会 Nam Hong Welfare Service Society · For committee members reference 仅供理事参考</t>
   </si>
   <si>
-    <t>中邦，健康之歌。 八月二十九日，早上9点30分至中午12点30分。医师梁芷维健康讲座 - 动养生，食养命。</t>
-  </si>
-  <si>
     <t>Songs of Health. Chong Pang Zone. Blk 108, Yishun Ring Road #01-301. 9.30am to 12.30pm (Representative: Physician Leong Chin Mee - Health Talk)</t>
   </si>
   <si>
@@ -1485,6 +1479,12 @@
   </si>
   <si>
     <t>Dragon Board Festival</t>
+  </si>
+  <si>
+    <t>2026年忠邦第61届国庆晚宴，晚上7点至10点。（代表：陈浚纬, Bill Tan）</t>
+  </si>
+  <si>
+    <t>忠邦，健康之歌。 八月二十九日，早上9点30分至中午12点30分。医师梁芷维健康讲座 - 动养生，食养命。</t>
   </si>
 </sst>
 </file>
@@ -1751,8 +1751,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2086,7 +2086,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -2196,7 +2196,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -2206,7 +2206,7 @@
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>30</v>
       </c>
@@ -2223,10 +2223,10 @@
         <v>136</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="12">
         <f>DATE(2026,1,1)</f>
         <v>46023</v>
@@ -2245,13 +2245,10 @@
         <v>126</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>434</v>
-      </c>
-      <c r="H2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="12">
         <f>DATE(2026,2,8)</f>
         <v>46061</v>
@@ -2270,13 +2267,10 @@
         <v>123</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>437</v>
-      </c>
-      <c r="H3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="12">
         <f>DATE(2026,2,26)</f>
         <v>46079</v>
@@ -2295,13 +2289,10 @@
         <v>133</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>438</v>
-      </c>
-      <c r="H4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="12">
         <f>DATE(2026,2,27)</f>
         <v>46080</v>
@@ -2320,13 +2311,10 @@
         <v>123</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>441</v>
-      </c>
-      <c r="H5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
         <f>DATE(2026,3,7)</f>
         <v>46088</v>
@@ -2345,13 +2333,10 @@
         <v>123</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>442</v>
-      </c>
-      <c r="H6" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
         <f>DATE(2026,3,20)</f>
         <v>46101</v>
@@ -2370,13 +2355,10 @@
         <v>126</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>439</v>
-      </c>
-      <c r="H7" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="12">
         <f>DATE(2026,3,23)</f>
         <v>46104</v>
@@ -2395,13 +2377,10 @@
         <v>123</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>445</v>
-      </c>
-      <c r="H8" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="12">
         <f>DATE(2026,3,24)</f>
         <v>46105</v>
@@ -2420,10 +2399,10 @@
         <v>123</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="12">
         <f>DATE(2026,3,27)</f>
         <v>46108</v>
@@ -2442,10 +2421,10 @@
         <v>123</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="12">
         <f>DATE(2026,4,20)</f>
         <v>46132</v>
@@ -2458,16 +2437,16 @@
         <v>132</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="12">
         <f>DATE(2026,5,4)</f>
         <v>46146</v>
@@ -2486,10 +2465,10 @@
         <v>131</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="12">
         <f>DATE(2026,5,15)</f>
         <v>46157</v>
@@ -2508,10 +2487,10 @@
         <v>133</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="12">
         <f>DATE(2026,5,24)</f>
         <v>46166</v>
@@ -2524,16 +2503,16 @@
         <v>151</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="12">
         <f>DATE(2026,5,25)</f>
         <v>46167</v>
@@ -2552,10 +2531,10 @@
         <v>123</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="12">
         <f>DATE(2026,5,29)</f>
         <v>46171</v>
@@ -2571,10 +2550,10 @@
         <v>154</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -2593,10 +2572,10 @@
         <v>156</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -2615,10 +2594,10 @@
         <v>158</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -2637,10 +2616,10 @@
         <v>160</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -2662,7 +2641,7 @@
         <v>123</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -2684,7 +2663,7 @@
         <v>123</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -2706,7 +2685,7 @@
         <v>123</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -2728,7 +2707,7 @@
         <v>126</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -2750,7 +2729,7 @@
         <v>126</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -2772,7 +2751,7 @@
         <v>123</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -2794,7 +2773,7 @@
         <v>123</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -2816,7 +2795,7 @@
         <v>126</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -2829,16 +2808,16 @@
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>123</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -2851,16 +2830,16 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>228</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -2873,16 +2852,16 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -2895,16 +2874,16 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>237</v>
+        <v>479</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -2917,16 +2896,16 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>226</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -2948,7 +2927,7 @@
         <v>126</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -2961,16 +2940,16 @@
         <v>Sat</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>272</v>
+        <v>480</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -2983,16 +2962,16 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -3005,16 +2984,16 @@
         <v>Mon</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -3027,16 +3006,16 @@
         <v>Tue</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -3049,16 +3028,16 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>227</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -3071,16 +3050,16 @@
         <v>Thu</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D39" s="16" t="s">
         <v>229</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -3093,16 +3072,16 @@
         <v>Sat</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -3124,7 +3103,7 @@
         <v>126</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -3137,16 +3116,16 @@
         <v>Mon</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D42" s="16" t="s">
         <v>230</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -3159,16 +3138,16 @@
         <v>Tue</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -3181,16 +3160,16 @@
         <v>Wed</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -3203,14 +3182,14 @@
         <v>Tue</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -3223,16 +3202,16 @@
         <v>Wed</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -3245,14 +3224,14 @@
         <v>Fri</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D47" s="11"/>
       <c r="E47" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -3274,7 +3253,7 @@
         <v>126</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -3287,16 +3266,16 @@
         <v>Fri</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>126</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="38.5" x14ac:dyDescent="0.35">
@@ -3309,16 +3288,16 @@
         <v>Fri</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -3331,16 +3310,16 @@
         <v>Sat</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>133</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -3359,10 +3338,10 @@
         <v>207</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G52" s="19"/>
     </row>
@@ -3382,10 +3361,10 @@
         <v>208</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -3404,10 +3383,10 @@
         <v>209</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -3429,7 +3408,7 @@
         <v>123</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -3451,7 +3430,7 @@
         <v>126</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -3473,7 +3452,7 @@
         <v>133</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -3486,7 +3465,7 @@
         <v>Fri</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>213</v>
@@ -3495,7 +3474,7 @@
         <v>133</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
@@ -3517,7 +3496,7 @@
         <v>123</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -3530,16 +3509,16 @@
         <v>Thu</v>
       </c>
       <c r="C60" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="D60" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="D60" s="11" t="s">
-        <v>249</v>
-      </c>
       <c r="E60" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F60" s="26" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -3561,7 +3540,7 @@
         <v>126</v>
       </c>
       <c r="F61" s="26" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -3583,7 +3562,7 @@
         <v>123</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -3602,10 +3581,10 @@
         <v>217</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -3627,7 +3606,7 @@
         <v>126</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -3646,10 +3625,10 @@
         <v>218</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -3668,10 +3647,10 @@
         <v>219</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F66" s="26" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -3690,10 +3669,10 @@
         <v>220</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -3715,7 +3694,7 @@
         <v>123</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -3728,7 +3707,7 @@
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D69" s="11" t="s">
         <v>215</v>
@@ -3737,7 +3716,7 @@
         <v>126</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -3759,7 +3738,7 @@
         <v>126</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -3781,7 +3760,7 @@
         <v>126</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -3800,10 +3779,10 @@
         <v>223</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -3825,7 +3804,7 @@
         <v>126</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -3847,7 +3826,7 @@
         <v>126</v>
       </c>
       <c r="F74" s="26" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -3869,7 +3848,7 @@
         <v>133</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
@@ -3891,7 +3870,7 @@
         <v>126</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
@@ -3913,7 +3892,7 @@
         <v>126</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
@@ -3935,7 +3914,7 @@
         <v>126</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -3957,7 +3936,7 @@
         <v>126</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -3979,7 +3958,7 @@
         <v>133</v>
       </c>
       <c r="F80" s="26" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -4206,7 +4185,7 @@
         <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>98</v>
@@ -4458,7 +4437,7 @@
         <v>111</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>94</v>
@@ -4478,7 +4457,7 @@
         <v>111</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>87</v>
@@ -4498,7 +4477,7 @@
         <v>111</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>103</v>
@@ -4518,7 +4497,7 @@
         <v>111</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>89</v>
@@ -4538,7 +4517,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>91</v>
@@ -4907,7 +4886,7 @@
         <v>61</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>29</v>
@@ -5186,839 +5165,839 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>G2&amp;H2</f>
         <v>jinhoa.jpg</v>
       </c>
       <c r="G2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F3" s="4" t="str">
         <f t="shared" ref="F3:F33" si="0">G3&amp;H3</f>
         <v>kathy.jpg</v>
       </c>
       <c r="G3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aceline.jpg</v>
       </c>
       <c r="G4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>agnes.jpg</v>
       </c>
       <c r="G5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bryan.jpg</v>
       </c>
       <c r="G6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="H6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B7" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yinyee.jpg</v>
       </c>
       <c r="G7" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H7" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D8" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>jingyi.jpg</v>
       </c>
       <c r="G8" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H8" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C9" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D9" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chihwee.jpg</v>
       </c>
       <c r="G9" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H9" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C10" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D10" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>crystal.jpg</v>
       </c>
       <c r="G10" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H10" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B11" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C11" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D11" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>peiyuen.jpg</v>
       </c>
       <c r="G11" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H11" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>doran.jpg</v>
       </c>
       <c r="G12" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H12" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B13" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C13" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D13" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>alicia.jpg</v>
       </c>
       <c r="G13" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H13" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B14" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C14" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D14" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E14" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>keongeng.jpg</v>
       </c>
       <c r="G14" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H14" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B15" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C15" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D15" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E15" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>siokteng.jpg</v>
       </c>
       <c r="G15" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H15" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B16" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C16" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D16" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E16" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>vivian.jpg</v>
       </c>
       <c r="G16" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H16" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B17" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C17" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D17" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E17" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bonteck.jpg</v>
       </c>
       <c r="G17" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H17" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B18" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C18" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D18" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E18" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chinmee.jpg</v>
       </c>
       <c r="G18" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H18" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B19" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C19" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D19" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E19" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>soonmeng.jpg</v>
       </c>
       <c r="G19" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H19" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B20" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C20" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D20" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E20" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yuehong.jpg</v>
       </c>
       <c r="G20" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H20" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B21" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C21" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D21" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E21" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>choejang.jpg</v>
       </c>
       <c r="G21" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H21" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B22" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C22" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D22" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E22" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>meichia.jpg</v>
       </c>
       <c r="G22" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H22" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B23" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C23" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D23" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E23" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>gekhee.jpg</v>
       </c>
       <c r="G23" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H23" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B24" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C24" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D24" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E24" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aimee.jpg</v>
       </c>
       <c r="G24" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H24" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B25" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C25" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D25" t="s">
+        <v>396</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="F25" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geokchin.jpg</v>
+      </c>
+      <c r="G25" t="s">
+        <v>422</v>
+      </c>
+      <c r="H25" t="s">
         <v>398</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>399</v>
-      </c>
-      <c r="F25" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>geokchin.jpg</v>
-      </c>
-      <c r="G25" t="s">
-        <v>424</v>
-      </c>
-      <c r="H25" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B26" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C26" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D26" t="s">
+        <v>396</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="F26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laysiew.jpg</v>
+      </c>
+      <c r="G26" t="s">
+        <v>423</v>
+      </c>
+      <c r="H26" t="s">
         <v>398</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>399</v>
-      </c>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>laysiew.jpg</v>
-      </c>
-      <c r="G26" t="s">
-        <v>425</v>
-      </c>
-      <c r="H26" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B27" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C27" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D27" t="s">
+        <v>396</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="F27" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>waiyee.jpg</v>
+      </c>
+      <c r="G27" t="s">
+        <v>424</v>
+      </c>
+      <c r="H27" t="s">
         <v>398</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>399</v>
-      </c>
-      <c r="F27" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>waiyee.jpg</v>
-      </c>
-      <c r="G27" t="s">
-        <v>426</v>
-      </c>
-      <c r="H27" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B28" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C28" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D28" t="s">
+        <v>396</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="F28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>carol.jpg</v>
+      </c>
+      <c r="G28" t="s">
+        <v>425</v>
+      </c>
+      <c r="H28" t="s">
         <v>398</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>399</v>
-      </c>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>carol.jpg</v>
-      </c>
-      <c r="G28" t="s">
-        <v>427</v>
-      </c>
-      <c r="H28" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B29" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C29" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D29" t="s">
+        <v>396</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="F29" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>yokewant.jpg</v>
+      </c>
+      <c r="G29" t="s">
+        <v>426</v>
+      </c>
+      <c r="H29" t="s">
         <v>398</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>399</v>
-      </c>
-      <c r="F29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>yokewant.jpg</v>
-      </c>
-      <c r="G29" t="s">
-        <v>428</v>
-      </c>
-      <c r="H29" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B30" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C30" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D30" t="s">
+        <v>396</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="F30" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>pohcheng.jpg</v>
+      </c>
+      <c r="G30" t="s">
+        <v>427</v>
+      </c>
+      <c r="H30" t="s">
         <v>398</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>399</v>
-      </c>
-      <c r="F30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>pohcheng.jpg</v>
-      </c>
-      <c r="G30" t="s">
-        <v>429</v>
-      </c>
-      <c r="H30" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B31" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C31" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D31" t="s">
+        <v>396</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="F31" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geoklan.jpg</v>
+      </c>
+      <c r="G31" t="s">
+        <v>428</v>
+      </c>
+      <c r="H31" t="s">
         <v>398</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>399</v>
-      </c>
-      <c r="F31" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>geoklan.jpg</v>
-      </c>
-      <c r="G31" t="s">
-        <v>430</v>
-      </c>
-      <c r="H31" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B32" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C32" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D32" t="s">
+        <v>396</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="F32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laichee.jpg</v>
+      </c>
+      <c r="G32" t="s">
+        <v>429</v>
+      </c>
+      <c r="H32" t="s">
         <v>398</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>399</v>
-      </c>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>laichee.jpg</v>
-      </c>
-      <c r="G32" t="s">
-        <v>431</v>
-      </c>
-      <c r="H32" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B33" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C33" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D33" t="s">
+        <v>396</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="F33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>beechoo.jpg</v>
+      </c>
+      <c r="G33" t="s">
+        <v>430</v>
+      </c>
+      <c r="H33" t="s">
         <v>398</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>399</v>
-      </c>
-      <c r="F33" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>beechoo.jpg</v>
-      </c>
-      <c r="G33" t="s">
-        <v>432</v>
-      </c>
-      <c r="H33" t="s">
-        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -6059,7 +6038,7 @@
         <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="696" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ECB2120-521B-4229-A269-5ACD6B1C0C8F}"/>
+  <xr:revisionPtr revIDLastSave="698" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41E20CBB-CF75-4B08-B819-45F9FDDFE3A2}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="479">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -293,9 +293,6 @@
     <t>张艺超</t>
   </si>
   <si>
-    <t>stanley.jpg</t>
-  </si>
-  <si>
     <t>CherKimSeah.jpg</t>
   </si>
   <si>
@@ -330,9 +327,6 @@
   </si>
   <si>
     <t>Fitri.jpg</t>
-  </si>
-  <si>
-    <t>Jie.jpg</t>
   </si>
   <si>
     <t>Peter.jpg</t>
@@ -2086,7 +2080,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -2211,7 +2205,7 @@
         <v>30</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>31</v>
@@ -2220,10 +2214,10 @@
         <v>32</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2236,16 +2230,16 @@
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2258,16 +2252,16 @@
         <v>Sun</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2280,16 +2274,16 @@
         <v>Thu</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2302,16 +2296,16 @@
         <v>Fri</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2324,16 +2318,16 @@
         <v>Sat</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2346,16 +2340,16 @@
         <v>Fri</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2368,16 +2362,16 @@
         <v>Mon</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2390,16 +2384,16 @@
         <v>Tue</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2412,16 +2406,16 @@
         <v>Fri</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -2434,16 +2428,16 @@
         <v>Mon</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -2456,16 +2450,16 @@
         <v>Mon</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -2478,16 +2472,16 @@
         <v>Fri</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -2500,16 +2494,16 @@
         <v>Sun</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -2522,16 +2516,16 @@
         <v>Mon</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -2544,16 +2538,16 @@
         <v>Fri</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -2566,16 +2560,16 @@
         <v>Sat</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -2588,16 +2582,16 @@
         <v>Sun</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -2610,16 +2604,16 @@
         <v>Mon</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -2632,16 +2626,16 @@
         <v>Fri</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -2654,16 +2648,16 @@
         <v>Sat</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -2676,16 +2670,16 @@
         <v>Sat</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -2698,16 +2692,16 @@
         <v>Fri</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -2720,16 +2714,16 @@
         <v>Fri</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -2742,16 +2736,16 @@
         <v>Fri</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -2764,16 +2758,16 @@
         <v>Sat</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -2786,16 +2780,16 @@
         <v>Sat</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -2808,16 +2802,16 @@
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -2830,16 +2824,16 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -2852,16 +2846,16 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -2874,16 +2868,16 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -2896,16 +2890,16 @@
         <v>Sun</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -2918,16 +2912,16 @@
         <v>Fri</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -2940,16 +2934,16 @@
         <v>Sat</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -2962,16 +2956,16 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -2984,16 +2978,16 @@
         <v>Mon</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -3006,16 +3000,16 @@
         <v>Tue</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -3028,16 +3022,16 @@
         <v>Thu</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -3050,16 +3044,16 @@
         <v>Thu</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -3072,16 +3066,16 @@
         <v>Sat</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -3094,16 +3088,16 @@
         <v>Sat</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -3116,16 +3110,16 @@
         <v>Mon</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -3138,16 +3132,16 @@
         <v>Tue</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -3160,16 +3154,16 @@
         <v>Wed</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -3182,14 +3176,14 @@
         <v>Tue</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="11" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -3202,16 +3196,16 @@
         <v>Wed</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -3224,14 +3218,14 @@
         <v>Fri</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D47" s="11"/>
       <c r="E47" s="11" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -3244,16 +3238,16 @@
         <v>Sun</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -3266,16 +3260,16 @@
         <v>Fri</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="38.5" x14ac:dyDescent="0.35">
@@ -3288,16 +3282,16 @@
         <v>Fri</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -3310,16 +3304,16 @@
         <v>Sat</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -3332,16 +3326,16 @@
         <v>Mon</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G52" s="19"/>
     </row>
@@ -3355,16 +3349,16 @@
         <v>Tue</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -3377,16 +3371,16 @@
         <v>Wed</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -3399,16 +3393,16 @@
         <v>Tue</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -3421,16 +3415,16 @@
         <v>Tue</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -3443,16 +3437,16 @@
         <v>Wed</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -3465,16 +3459,16 @@
         <v>Fri</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
@@ -3487,16 +3481,16 @@
         <v>Sat</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -3509,16 +3503,16 @@
         <v>Thu</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F60" s="26" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -3531,16 +3525,16 @@
         <v>Fri</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F61" s="26" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -3553,16 +3547,16 @@
         <v>Thu</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -3575,16 +3569,16 @@
         <v>Sat</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -3597,16 +3591,16 @@
         <v>Fri</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -3619,16 +3613,16 @@
         <v>Wed</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -3641,16 +3635,16 @@
         <v>Thu</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F66" s="26" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -3663,16 +3657,16 @@
         <v>Fri</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -3685,16 +3679,16 @@
         <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -3707,16 +3701,16 @@
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -3729,16 +3723,16 @@
         <v>Fri</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -3751,16 +3745,16 @@
         <v>Fri</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -3773,16 +3767,16 @@
         <v>Mon</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -3795,16 +3789,16 @@
         <v>Fri</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -3817,16 +3811,16 @@
         <v>Fri</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F74" s="26" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -3839,16 +3833,16 @@
         <v>Sat</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
@@ -3861,16 +3855,16 @@
         <v>Fri</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
@@ -3883,16 +3877,16 @@
         <v>Fri</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
@@ -3905,16 +3899,16 @@
         <v>Fri</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -3927,16 +3921,16 @@
         <v>Fri</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -3949,16 +3943,16 @@
         <v>Thu</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F80" s="26" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -4010,7 +4004,7 @@
         <v>38</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4024,7 +4018,7 @@
         <v>40</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4038,7 +4032,7 @@
         <v>42</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4052,7 +4046,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4066,7 +4060,7 @@
         <v>46</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4080,7 +4074,7 @@
         <v>48</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4094,7 +4088,7 @@
         <v>50</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4108,7 +4102,7 @@
         <v>52</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4122,7 +4116,7 @@
         <v>54</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4136,7 +4130,7 @@
         <v>56</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4148,7 +4142,7 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4160,7 +4154,7 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4174,7 +4168,7 @@
         <v>60</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4185,10 +4179,10 @@
         <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4202,7 +4196,7 @@
         <v>63</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4210,13 +4204,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>64</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4230,7 +4224,7 @@
         <v>66</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4244,7 +4238,7 @@
         <v>68</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4258,7 +4252,7 @@
         <v>70</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4272,7 +4266,7 @@
         <v>72</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4286,7 +4280,7 @@
         <v>74</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4300,7 +4294,7 @@
         <v>76</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4314,7 +4308,7 @@
         <v>78</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4328,7 +4322,7 @@
         <v>80</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4342,7 +4336,7 @@
         <v>82</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -4377,7 +4371,7 @@
         <v>24</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>21</v>
@@ -4400,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -4414,13 +4408,13 @@
         <v>48</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -4434,13 +4428,13 @@
         <v>42</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -4454,13 +4448,13 @@
         <v>46</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -4474,13 +4468,13 @@
         <v>50</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -4494,13 +4488,13 @@
         <v>56</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -4514,13 +4508,13 @@
         <v>68</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -4534,13 +4528,13 @@
         <v>78</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -4554,13 +4548,13 @@
         <v>74</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -4574,13 +4568,13 @@
         <v>72</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -4594,13 +4588,13 @@
         <v>66</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -4648,10 +4642,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -4666,15 +4660,15 @@
         <v>28</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -4687,21 +4681,21 @@
         <v>29</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>64</v>
@@ -4710,15 +4704,15 @@
         <v>29</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -4731,15 +4725,15 @@
         <v>29</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
@@ -4754,15 +4748,15 @@
         <v>29</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
@@ -4777,15 +4771,15 @@
         <v>28</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -4800,15 +4794,15 @@
         <v>29</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
@@ -4823,15 +4817,15 @@
         <v>28</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
@@ -4846,15 +4840,15 @@
         <v>29</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -4869,15 +4863,15 @@
         <v>28</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -4886,21 +4880,21 @@
         <v>61</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>29</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -4915,15 +4909,15 @@
         <v>29</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -4938,15 +4932,15 @@
         <v>29</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -4961,15 +4955,15 @@
         <v>28</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
@@ -4984,15 +4978,15 @@
         <v>29</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
@@ -5007,15 +5001,15 @@
         <v>28</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -5030,15 +5024,15 @@
         <v>29</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
@@ -5053,15 +5047,15 @@
         <v>29</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
@@ -5076,15 +5070,15 @@
         <v>28</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
@@ -5099,15 +5093,15 @@
         <v>29</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -5122,7 +5116,7 @@
         <v>29</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -5157,7 +5151,7 @@
         <v>24</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>21</v>
@@ -5165,839 +5159,839 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>G2&amp;H2</f>
         <v>jinhoa.jpg</v>
       </c>
       <c r="G2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F3" s="4" t="str">
         <f t="shared" ref="F3:F33" si="0">G3&amp;H3</f>
         <v>kathy.jpg</v>
       </c>
       <c r="G3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aceline.jpg</v>
       </c>
       <c r="G4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>agnes.jpg</v>
       </c>
       <c r="G5" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H5" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bryan.jpg</v>
       </c>
       <c r="G6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B7" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D7" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yinyee.jpg</v>
       </c>
       <c r="G7" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H7" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D8" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>jingyi.jpg</v>
       </c>
       <c r="G8" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="H8" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B9" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C9" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D9" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chihwee.jpg</v>
       </c>
       <c r="G9" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H9" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D10" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>crystal.jpg</v>
       </c>
       <c r="G10" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H10" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C11" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D11" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>peiyuen.jpg</v>
       </c>
       <c r="G11" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H11" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D12" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>doran.jpg</v>
       </c>
       <c r="G12" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B13" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C13" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D13" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>alicia.jpg</v>
       </c>
       <c r="G13" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H13" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B14" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C14" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E14" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>keongeng.jpg</v>
       </c>
       <c r="G14" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H14" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B15" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D15" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E15" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>siokteng.jpg</v>
       </c>
       <c r="G15" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B16" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D16" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E16" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>vivian.jpg</v>
       </c>
       <c r="G16" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H16" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B17" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C17" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D17" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E17" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bonteck.jpg</v>
       </c>
       <c r="G17" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H17" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B18" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C18" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D18" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E18" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chinmee.jpg</v>
       </c>
       <c r="G18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H18" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C19" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D19" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E19" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>soonmeng.jpg</v>
       </c>
       <c r="G19" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H19" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B20" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C20" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D20" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E20" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yuehong.jpg</v>
       </c>
       <c r="G20" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H20" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B21" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C21" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D21" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E21" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>choejang.jpg</v>
       </c>
       <c r="G21" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H21" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B22" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C22" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D22" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E22" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>meichia.jpg</v>
       </c>
       <c r="G22" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H22" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B23" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C23" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D23" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E23" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>gekhee.jpg</v>
       </c>
       <c r="G23" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H23" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B24" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C24" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D24" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E24" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aimee.jpg</v>
       </c>
       <c r="G24" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H24" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B25" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C25" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D25" t="s">
+        <v>394</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="F25" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geokchin.jpg</v>
+      </c>
+      <c r="G25" t="s">
+        <v>420</v>
+      </c>
+      <c r="H25" t="s">
         <v>396</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>397</v>
-      </c>
-      <c r="F25" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>geokchin.jpg</v>
-      </c>
-      <c r="G25" t="s">
-        <v>422</v>
-      </c>
-      <c r="H25" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B26" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C26" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D26" t="s">
+        <v>394</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="F26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laysiew.jpg</v>
+      </c>
+      <c r="G26" t="s">
+        <v>421</v>
+      </c>
+      <c r="H26" t="s">
         <v>396</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>397</v>
-      </c>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>laysiew.jpg</v>
-      </c>
-      <c r="G26" t="s">
-        <v>423</v>
-      </c>
-      <c r="H26" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B27" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C27" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D27" t="s">
+        <v>394</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="F27" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>waiyee.jpg</v>
+      </c>
+      <c r="G27" t="s">
+        <v>422</v>
+      </c>
+      <c r="H27" t="s">
         <v>396</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>397</v>
-      </c>
-      <c r="F27" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>waiyee.jpg</v>
-      </c>
-      <c r="G27" t="s">
-        <v>424</v>
-      </c>
-      <c r="H27" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B28" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C28" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D28" t="s">
+        <v>394</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="F28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>carol.jpg</v>
+      </c>
+      <c r="G28" t="s">
+        <v>423</v>
+      </c>
+      <c r="H28" t="s">
         <v>396</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>397</v>
-      </c>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>carol.jpg</v>
-      </c>
-      <c r="G28" t="s">
-        <v>425</v>
-      </c>
-      <c r="H28" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B29" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C29" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D29" t="s">
+        <v>394</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="F29" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>yokewant.jpg</v>
+      </c>
+      <c r="G29" t="s">
+        <v>424</v>
+      </c>
+      <c r="H29" t="s">
         <v>396</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>397</v>
-      </c>
-      <c r="F29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>yokewant.jpg</v>
-      </c>
-      <c r="G29" t="s">
-        <v>426</v>
-      </c>
-      <c r="H29" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B30" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C30" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D30" t="s">
+        <v>394</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="F30" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>pohcheng.jpg</v>
+      </c>
+      <c r="G30" t="s">
+        <v>425</v>
+      </c>
+      <c r="H30" t="s">
         <v>396</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>397</v>
-      </c>
-      <c r="F30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>pohcheng.jpg</v>
-      </c>
-      <c r="G30" t="s">
-        <v>427</v>
-      </c>
-      <c r="H30" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B31" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C31" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D31" t="s">
+        <v>394</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="F31" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geoklan.jpg</v>
+      </c>
+      <c r="G31" t="s">
+        <v>426</v>
+      </c>
+      <c r="H31" t="s">
         <v>396</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>397</v>
-      </c>
-      <c r="F31" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>geoklan.jpg</v>
-      </c>
-      <c r="G31" t="s">
-        <v>428</v>
-      </c>
-      <c r="H31" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B32" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C32" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D32" t="s">
+        <v>394</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="F32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laichee.jpg</v>
+      </c>
+      <c r="G32" t="s">
+        <v>427</v>
+      </c>
+      <c r="H32" t="s">
         <v>396</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>397</v>
-      </c>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>laichee.jpg</v>
-      </c>
-      <c r="G32" t="s">
-        <v>429</v>
-      </c>
-      <c r="H32" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B33" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C33" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D33" t="s">
+        <v>394</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="F33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>beechoo.jpg</v>
+      </c>
+      <c r="G33" t="s">
+        <v>428</v>
+      </c>
+      <c r="H33" t="s">
         <v>396</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>397</v>
-      </c>
-      <c r="F33" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>beechoo.jpg</v>
-      </c>
-      <c r="G33" t="s">
-        <v>430</v>
-      </c>
-      <c r="H33" t="s">
-        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -6038,15 +6032,15 @@
         <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="698" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41E20CBB-CF75-4B08-B819-45F9FDDFE3A2}"/>
+  <xr:revisionPtr revIDLastSave="699" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3D5B34B-BF99-4869-BBA6-B92A1FB9BEDF}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -3202,7 +3202,7 @@
         <v>271</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>260</v>
+        <v>121</v>
       </c>
       <c r="F46" s="25" t="s">
         <v>439</v>
@@ -6049,14 +6049,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6301,23 +6299,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6343,9 +6338,14 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="699" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3D5B34B-BF99-4869-BBA6-B92A1FB9BEDF}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="699" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3D5B34B-BF99-4869-BBA6-B92A1FB9BEDF}"/>
+  <xr:revisionPtr revIDLastSave="708" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B026082A-BBA7-40C6-BEA9-5947A60B6E0E}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$81</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="482">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -1479,6 +1479,15 @@
   </si>
   <si>
     <t>忠邦，健康之歌。 八月二十九日，早上9点30分至中午12点30分。医师梁芷维健康讲座 - 动养生，食养命。</t>
+  </si>
+  <si>
+    <t>Staff training by UOB : Will Writing by Mr Patrick Chang</t>
+  </si>
+  <si>
+    <t>Staff Training - Will writing</t>
+  </si>
+  <si>
+    <t>员工培训： 遗嘱规划</t>
   </si>
 </sst>
 </file>
@@ -2190,7 +2199,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -2226,7 +2235,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="13" t="str">
-        <f t="shared" ref="B2:B54" si="0">TEXT($A2,"ddd")</f>
+        <f t="shared" ref="B2:B55" si="0">TEXT($A2,"ddd")</f>
         <v>Thu</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -2798,7 +2807,7 @@
         <v>46239</v>
       </c>
       <c r="B28" s="13" t="str">
-        <f t="shared" ref="B28:B39" si="1">TEXT($A28,"ddd")</f>
+        <f t="shared" ref="B28:B40" si="1">TEXT($A28,"ddd")</f>
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
@@ -2882,68 +2891,68 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="12">
+        <f>DATE(2026,8,19)</f>
+        <v>46253</v>
+      </c>
+      <c r="B32" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Wed</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F32" s="25" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="12">
         <f>DATE(2026,8,23)</f>
         <v>46257</v>
       </c>
-      <c r="B32" s="13" t="str">
+      <c r="B33" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sun</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C33" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D33" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E33" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F32" s="25" t="s">
+      <c r="F33" s="25" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="12">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="12">
         <f>DATE(2026,8,28)</f>
         <v>46262</v>
       </c>
-      <c r="B33" s="13" t="str">
-        <f>TEXT($A33,"ddd")</f>
+      <c r="B34" s="13" t="str">
+        <f>TEXT($A34,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C34" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D34" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E34" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F33" s="25" t="s">
+      <c r="F34" s="25" t="s">
         <v>454</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="12">
-        <f>DATE(2026,8,29)</f>
-        <v>46263</v>
-      </c>
-      <c r="B34" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Sat</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>478</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="F34" s="25" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -2956,82 +2965,82 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>235</v>
+        <v>478</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>455</v>
+        <v>436</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="12">
+        <f>DATE(2026,8,29)</f>
+        <v>46263</v>
+      </c>
+      <c r="B36" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Sat</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="F36" s="25" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="12">
         <f>DATE(2026,8,31)</f>
         <v>46265</v>
       </c>
-      <c r="B36" s="13" t="str">
-        <f>TEXT($A36,"ddd")</f>
+      <c r="B37" s="13" t="str">
+        <f>TEXT($A37,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C37" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="D37" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E37" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F36" s="25" t="s">
+      <c r="F37" s="25" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="12">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="12">
         <f>DATE(2026,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="B37" s="13" t="str">
+      <c r="B38" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Tue</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C38" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D38" s="16" t="s">
         <v>236</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="F37" s="25" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="12">
-        <f>DATE(2026,9,3)</f>
-        <v>46268</v>
-      </c>
-      <c r="B38" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>Thu</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>225</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>243</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -3044,32 +3053,32 @@
         <v>Thu</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>227</v>
+        <v>253</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>225</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>243</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="12">
-        <f>DATE(2026,9,5)</f>
-        <v>46270</v>
+        <f>DATE(2026,9,3)</f>
+        <v>46268</v>
       </c>
       <c r="B40" s="13" t="str">
-        <f>TEXT($A40,"ddd")</f>
-        <v>Sat</v>
+        <f t="shared" si="1"/>
+        <v>Thu</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>237</v>
+        <v>254</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>227</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>243</v>
@@ -3084,195 +3093,195 @@
         <v>46270</v>
       </c>
       <c r="B41" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT($A41,"ddd")</f>
         <v>Sat</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>164</v>
+        <v>255</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>124</v>
+        <v>243</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="12">
+        <f>DATE(2026,9,5)</f>
+        <v>46270</v>
+      </c>
+      <c r="B42" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F42" s="25" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="12">
         <f>DATE(2026,9,7)</f>
         <v>46272</v>
       </c>
-      <c r="B42" s="13" t="str">
-        <f>TEXT($A42,"ddd")</f>
+      <c r="B43" s="13" t="str">
+        <f>TEXT($A43,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C43" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D43" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E43" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F42" s="25" t="s">
+      <c r="F43" s="25" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="12">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="12">
         <f>DATE(2026,9,8)</f>
         <v>46273</v>
       </c>
-      <c r="B43" s="13" t="str">
-        <f>TEXT($A43,"ddd")</f>
+      <c r="B44" s="13" t="str">
+        <f>TEXT($A44,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C44" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D44" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E44" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F43" s="25" t="s">
+      <c r="F44" s="25" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="12">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="12">
         <f>DATE(2026,9,9)</f>
         <v>46274</v>
       </c>
-      <c r="B44" s="13" t="str">
-        <f>TEXT($A44,"ddd")</f>
+      <c r="B45" s="13" t="str">
+        <f>TEXT($A45,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C45" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D45" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E45" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F44" s="25" t="s">
+      <c r="F45" s="25" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="12">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="12">
         <f>DATE(2026,9,15)</f>
         <v>46280</v>
       </c>
-      <c r="B45" s="13" t="str">
+      <c r="B46" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C46" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="D45" s="16"/>
-      <c r="E45" s="11" t="s">
+      <c r="D46" s="16"/>
+      <c r="E46" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="F45" s="25" t="s">
+      <c r="F46" s="25" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="12">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="12">
         <f>DATE(2026,9,16)</f>
         <v>46281</v>
       </c>
-      <c r="B46" s="13" t="str">
+      <c r="B47" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C47" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D47" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E47" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F46" s="25" t="s">
+      <c r="F47" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="12">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="12">
         <f>DATE(2026,9,18)</f>
         <v>46283</v>
       </c>
-      <c r="B47" s="13" t="str">
+      <c r="B48" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C48" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11" t="s">
+      <c r="D48" s="11"/>
+      <c r="E48" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="F47" s="25" t="s">
+      <c r="F48" s="25" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="12">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" s="12">
         <f>DATE(2026,9,20)</f>
         <v>46285</v>
       </c>
-      <c r="B48" s="13" t="str">
+      <c r="B49" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C49" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D49" s="11" t="s">
         <v>167</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F48" s="25" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49" s="12">
-        <f>DATE(2026,10,9)</f>
-        <v>46304</v>
-      </c>
-      <c r="B49" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Fri</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>247</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="38.5" x14ac:dyDescent="0.35">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="12">
         <f>DATE(2026,10,9)</f>
         <v>46304</v>
@@ -3281,449 +3290,449 @@
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C50" s="20" t="s">
+      <c r="C50" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F50" s="25" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="12">
+        <f>DATE(2026,10,9)</f>
+        <v>46304</v>
+      </c>
+      <c r="B51" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="C51" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D51" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E51" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="F50" s="25" t="s">
+      <c r="F51" s="25" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A51" s="12">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" s="12">
         <f>DATE(2026,10,10)</f>
         <v>46305</v>
       </c>
-      <c r="B51" s="13" t="str">
+      <c r="B52" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C52" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D52" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E52" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F51" s="25" t="s">
+      <c r="F52" s="25" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52" s="12">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" s="12">
         <f>DATE(2026,10,12)</f>
         <v>46307</v>
       </c>
-      <c r="B52" s="13" t="str">
+      <c r="B53" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C53" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D53" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E53" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F52" s="25" t="s">
+      <c r="F53" s="25" t="s">
         <v>469</v>
       </c>
-      <c r="G52" s="19"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" s="12">
+      <c r="G53" s="19"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54" s="12">
         <f>DATE(2026,10,13)</f>
         <v>46308</v>
       </c>
-      <c r="B53" s="13" t="str">
+      <c r="B54" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C54" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D54" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E54" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F53" s="25" t="s">
+      <c r="F54" s="25" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" s="12">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55" s="12">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
       </c>
-      <c r="B54" s="13" t="str">
+      <c r="B55" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C55" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D55" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E55" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F54" s="25" t="s">
+      <c r="F55" s="25" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A55" s="12">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56" s="12">
         <f>DATE(2026,11,3)</f>
         <v>46329</v>
       </c>
-      <c r="B55" s="13" t="str">
-        <f t="shared" ref="B55:B80" si="2">TEXT($A55,"ddd")</f>
+      <c r="B56" s="13" t="str">
+        <f t="shared" ref="B56:B81" si="2">TEXT($A56,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C56" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D56" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E56" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F55" s="25" t="s">
+      <c r="F56" s="25" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56" s="12">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" s="12">
         <f>DATE(2026,11,10)</f>
         <v>46336</v>
       </c>
-      <c r="B56" s="13" t="str">
+      <c r="B57" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Tue</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="C57" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D57" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E57" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F56" s="25" t="s">
+      <c r="F57" s="25" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A57" s="12">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58" s="12">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B57" s="13" t="str">
+      <c r="B58" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C58" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="D57" s="16" t="s">
+      <c r="D58" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E58" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F57" s="25" t="s">
+      <c r="F58" s="25" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A58" s="12">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B58" s="13" t="str">
+      <c r="B59" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C59" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D59" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E59" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F58" s="25" t="s">
+      <c r="F59" s="25" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A59" s="12">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" s="12">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B59" s="13" t="str">
+      <c r="B60" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C60" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D60" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E60" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F59" s="25" t="s">
+      <c r="F60" s="25" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A60" s="12">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" s="12">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B60" s="13" t="str">
+      <c r="B61" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C61" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D61" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E61" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="F60" s="26" t="s">
+      <c r="F61" s="26" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61" s="12">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" s="12">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B61" s="13" t="str">
+      <c r="B62" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C62" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D62" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E62" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F61" s="26" t="s">
+      <c r="F62" s="26" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A62" s="12">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" s="12">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B62" s="13" t="str">
+      <c r="B63" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C63" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D63" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E63" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F62" s="26" t="s">
+      <c r="F63" s="26" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A63" s="12">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" s="12">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
       </c>
-      <c r="B63" s="13" t="str">
+      <c r="B64" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C63" s="16" t="s">
+      <c r="C64" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D64" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E64" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="F63" s="26" t="s">
+      <c r="F64" s="26" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A64" s="12">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="12">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
       </c>
-      <c r="B64" s="13" t="str">
+      <c r="B65" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C65" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D65" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="E65" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F64" s="26" t="s">
+      <c r="F65" s="26" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A65" s="12">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="12">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B65" s="13" t="str">
+      <c r="B66" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C66" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D66" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E66" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F65" s="26" t="s">
+      <c r="F66" s="26" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A66" s="12">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B66" s="13" t="str">
+      <c r="B67" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C67" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D67" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="E66" s="11" t="s">
+      <c r="E67" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F66" s="26" t="s">
+      <c r="F67" s="26" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" s="12">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B67" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="D67" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="F67" s="26" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A68" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
       </c>
       <c r="B68" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>121</v>
+        <v>243</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>476</v>
+        <v>442</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B69" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>277</v>
+        <v>178</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B70" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>173</v>
+        <v>277</v>
       </c>
       <c r="D70" s="11" t="s">
         <v>213</v>
@@ -3737,18 +3746,18 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="12">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B71" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>124</v>
@@ -3759,62 +3768,62 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="12">
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
+      </c>
+      <c r="B72" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F72" s="26" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="12">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B72" s="13" t="str">
+      <c r="B73" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C73" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="D72" s="11" t="s">
+      <c r="D73" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="E72" s="11" t="s">
+      <c r="E73" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F72" s="26" t="s">
+      <c r="F73" s="26" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A73" s="12">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="12">
         <f>DATE(2027,8,20)</f>
         <v>46619</v>
-      </c>
-      <c r="B73" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F73" s="26" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
       </c>
       <c r="B74" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E74" s="11" t="s">
         <v>124</v>
@@ -3825,52 +3834,52 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="12">
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
+      </c>
+      <c r="B75" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F75" s="26" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B75" s="13" t="str">
+      <c r="B76" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C76" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="D76" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="E76" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F75" s="26" t="s">
+      <c r="F76" s="26" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A76" s="12">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="12">
         <f>DATE(2027,10,1)</f>
         <v>46661</v>
-      </c>
-      <c r="B76" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F76" s="26" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A77" s="12">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
       </c>
       <c r="B77" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3891,8 +3900,8 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="12">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
       </c>
       <c r="B78" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3913,8 +3922,8 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
       </c>
       <c r="B79" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3935,34 +3944,56 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="12">
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
+      </c>
+      <c r="B80" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F80" s="26" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" s="12">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B80" s="13" t="str">
+      <c r="B81" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C81" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="D80" s="16" t="s">
+      <c r="D81" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="E80" s="11" t="s">
+      <c r="E81" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F80" s="26" t="s">
+      <c r="F81" s="26" t="s">
         <v>473</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E80" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E81" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="D36" r:id="rId1" xr:uid="{DF6FA8D1-34EA-46D0-A461-22B2F51DB446}"/>
+    <hyperlink ref="D37" r:id="rId1" xr:uid="{DF6FA8D1-34EA-46D0-A461-22B2F51DB446}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6024,7 +6055,7 @@
       </c>
       <c r="B2" s="18">
         <f ca="1">TODAY()</f>
-        <v>46251</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -6049,12 +6080,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6299,20 +6332,23 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6338,14 +6374,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="708" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B026082A-BBA7-40C6-BEA9-5947A60B6E0E}"/>
+  <xr:revisionPtr revIDLastSave="716" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1412F492-67E2-487D-A1A4-400DA7A15956}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$82</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="485">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -1488,6 +1488,15 @@
   </si>
   <si>
     <t>员工培训： 遗嘱规划</t>
+  </si>
+  <si>
+    <t>[Tentative] CSR Partnership - Corporate (Will writing talk by Mr Partrick Chang)</t>
+  </si>
+  <si>
+    <t>[未确认]  企业社会责任合作 - 遗嘱规划讲座</t>
+  </si>
+  <si>
+    <t>Corporate - Wellness Talk (Will writing)</t>
   </si>
 </sst>
 </file>
@@ -2199,7 +2208,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -3420,7 +3429,7 @@
         <v>46329</v>
       </c>
       <c r="B56" s="13" t="str">
-        <f t="shared" ref="B56:B81" si="2">TEXT($A56,"ddd")</f>
+        <f t="shared" ref="B56:B82" si="2">TEXT($A56,"ddd")</f>
         <v>Tue</v>
       </c>
       <c r="C56" s="16" t="s">
@@ -3460,301 +3469,301 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="12">
+        <f>DATE(2026,11,24)</f>
+        <v>46350</v>
+      </c>
+      <c r="B58" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Tue</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F58" s="25" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" s="12">
         <f>DATE(2026,12,16)</f>
         <v>46372</v>
       </c>
-      <c r="B58" s="13" t="str">
+      <c r="B59" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C59" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="D58" s="16" t="s">
+      <c r="D59" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E59" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F58" s="25" t="s">
+      <c r="F59" s="25" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A59" s="12">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" s="12">
         <f>DATE(2027,1,1)</f>
         <v>46388</v>
       </c>
-      <c r="B59" s="13" t="str">
+      <c r="B60" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="C60" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D60" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E60" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F59" s="25" t="s">
+      <c r="F60" s="25" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A60" s="12">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" s="12">
         <f>DATE(2027,1,30)</f>
         <v>46417</v>
       </c>
-      <c r="B60" s="13" t="str">
+      <c r="B61" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C61" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D61" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E61" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F60" s="25" t="s">
+      <c r="F61" s="25" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61" s="12">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" s="12">
         <f>DATE(2027,2,18)</f>
         <v>46436</v>
       </c>
-      <c r="B61" s="13" t="str">
+      <c r="B62" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C62" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D62" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E62" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="F61" s="26" t="s">
+      <c r="F62" s="26" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A62" s="12">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" s="12">
         <f>DATE(2027,3,19)</f>
         <v>46465</v>
       </c>
-      <c r="B62" s="13" t="str">
+      <c r="B63" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C63" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D63" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E63" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F62" s="26" t="s">
+      <c r="F63" s="26" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A63" s="12">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" s="12">
         <f>DATE(2027,3,25)</f>
         <v>46471</v>
       </c>
-      <c r="B63" s="13" t="str">
+      <c r="B64" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C64" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D64" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E64" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F63" s="26" t="s">
+      <c r="F64" s="26" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A64" s="12">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="12">
         <f>DATE(2027,4,3)</f>
         <v>46480</v>
       </c>
-      <c r="B64" s="13" t="str">
+      <c r="B65" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C64" s="16" t="s">
+      <c r="C65" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D65" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="E65" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="F64" s="26" t="s">
+      <c r="F65" s="26" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A65" s="12">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="12">
         <f>DATE(2027,4,9)</f>
         <v>46486</v>
       </c>
-      <c r="B65" s="13" t="str">
+      <c r="B66" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C66" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D66" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E66" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F65" s="26" t="s">
+      <c r="F66" s="26" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A66" s="12">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="12">
         <f>DATE(2027,5,19)</f>
         <v>46526</v>
       </c>
-      <c r="B66" s="13" t="str">
+      <c r="B67" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Wed</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C67" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D67" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="E66" s="11" t="s">
+      <c r="E67" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F66" s="26" t="s">
+      <c r="F67" s="26" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" s="12">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="12">
         <f>DATE(2027,5,20)</f>
         <v>46527</v>
       </c>
-      <c r="B67" s="13" t="str">
+      <c r="B68" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C68" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D68" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="E67" s="11" t="s">
+      <c r="E68" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F67" s="26" t="s">
+      <c r="F68" s="26" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A68" s="12">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="12">
         <f>DATE(2027,5,21)</f>
         <v>46528</v>
-      </c>
-      <c r="B68" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="D68" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="F68" s="26" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A69" s="12">
-        <f>DATE(2027,5,28)</f>
-        <v>46535</v>
       </c>
       <c r="B69" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>121</v>
+        <v>243</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>476</v>
+        <v>442</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
-        <f>DATE(2027,6,11)</f>
-        <v>46549</v>
+        <f>DATE(2027,5,28)</f>
+        <v>46535</v>
       </c>
       <c r="B70" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>277</v>
+        <v>178</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="12">
-        <f>DATE(2027,7,9)</f>
-        <v>46577</v>
+        <f>DATE(2027,6,11)</f>
+        <v>46549</v>
       </c>
       <c r="B71" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>173</v>
+        <v>277</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>213</v>
@@ -3768,18 +3777,18 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="12">
-        <f>DATE(2027,7,30)</f>
-        <v>46598</v>
+        <f>DATE(2027,7,9)</f>
+        <v>46577</v>
       </c>
       <c r="B72" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>124</v>
@@ -3790,62 +3799,62 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="12">
+        <f>DATE(2027,7,30)</f>
+        <v>46598</v>
+      </c>
+      <c r="B73" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F73" s="26" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="12">
         <f>DATE(2027,8,16)</f>
         <v>46615</v>
       </c>
-      <c r="B73" s="13" t="str">
+      <c r="B74" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Mon</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C74" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="D73" s="11" t="s">
+      <c r="D74" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="E74" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F73" s="26" t="s">
+      <c r="F74" s="26" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" s="12">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="12">
         <f>DATE(2027,8,20)</f>
         <v>46619</v>
-      </c>
-      <c r="B74" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="D74" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="E74" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F74" s="26" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A75" s="12">
-        <f>DATE(2027,9,10)</f>
-        <v>46640</v>
       </c>
       <c r="B75" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Fri</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E75" s="11" t="s">
         <v>124</v>
@@ -3856,52 +3865,52 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="12">
+        <f>DATE(2027,9,10)</f>
+        <v>46640</v>
+      </c>
+      <c r="B76" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F76" s="26" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="12">
         <f>DATE(2027,9,18)</f>
         <v>46648</v>
       </c>
-      <c r="B76" s="13" t="str">
+      <c r="B77" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Sat</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C77" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D76" s="11" t="s">
+      <c r="D77" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E77" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F76" s="26" t="s">
+      <c r="F77" s="26" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A77" s="12">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" s="12">
         <f>DATE(2027,10,1)</f>
         <v>46661</v>
-      </c>
-      <c r="B77" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>Fri</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D77" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="E77" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F77" s="26" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A78" s="12">
-        <f>DATE(2027,10,15)</f>
-        <v>46675</v>
       </c>
       <c r="B78" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3922,8 +3931,8 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="12">
-        <f>DATE(2027,11,12)</f>
-        <v>46703</v>
+        <f>DATE(2027,10,15)</f>
+        <v>46675</v>
       </c>
       <c r="B79" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3944,8 +3953,8 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="12">
-        <f>DATE(2027,11,26)</f>
-        <v>46717</v>
+        <f>DATE(2027,11,12)</f>
+        <v>46703</v>
       </c>
       <c r="B80" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3966,28 +3975,50 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="12">
+        <f>DATE(2027,11,26)</f>
+        <v>46717</v>
+      </c>
+      <c r="B81" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Fri</v>
+      </c>
+      <c r="C81" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F81" s="25" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="12">
         <f>DATE(2027,12,16)</f>
         <v>46737</v>
       </c>
-      <c r="B81" s="13" t="str">
+      <c r="B82" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Thu</v>
       </c>
-      <c r="C81" s="11" t="s">
+      <c r="C82" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="D81" s="16" t="s">
+      <c r="D82" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="E81" s="11" t="s">
+      <c r="E82" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F81" s="26" t="s">
+      <c r="F82" s="26" t="s">
         <v>473</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E81" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:E82" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="2">
       <iconFilter iconSet="3Arrows"/>
     </filterColumn>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="716" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1412F492-67E2-487D-A1A4-400DA7A15956}"/>
+  <xr:revisionPtr revIDLastSave="720" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16DB86A0-1140-4522-82B8-DA52C36993E9}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -749,18 +749,12 @@
     <t>中医保健养生讲座 - 中药茶饮</t>
   </si>
   <si>
-    <t>717 商店中元会 (代表：周锦昌, Kathy, 丽菁, 丽丝和先生）</t>
-  </si>
-  <si>
     <t>华报善堂中元会 (代表：徐金声, Chi Hwee, Yan Yi, Agnes, Jin Hoa）。筹款活动包括义标。</t>
   </si>
   <si>
     <t>[日期未确认] 义顺镇商贩联合中元会歌台 (代表：徐金声, Doran, Pei Yuen）</t>
   </si>
   <si>
-    <t>义顺南旺村中元会。(代表：Doran, Bryan, 丽菁, 丽丝和先生）</t>
-  </si>
-  <si>
     <t>南凤善堂中元会晚宴（200人）</t>
   </si>
   <si>
@@ -797,9 +791,6 @@
     <t>Lunar July (ZhongYuan Festival) - YS ONE, 1 Yishun Street 23 (Representative: Bryan, 丽菁, 丽丝和先生 - all to arrive by 7pm)</t>
   </si>
   <si>
-    <t>Lunar July (ZhongYuan Festival) - 724 Yishun Street 71 (Representative: Chew Kim Cheong, Kathy, 丽菁, 丽丝和先生 - all to arrive by 7pm)</t>
-  </si>
-  <si>
     <t>Lunar July (ZhongYuan Festival) - 561 Yishun Ring Road (Representative: Cher Kim Seah,Chi Hwee, Yan Yi, Agnes - all to arrive by 7pm). Auction item included.</t>
   </si>
   <si>
@@ -818,9 +809,6 @@
     <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon dinner (200 pax) - all to arrive by 7pm</t>
   </si>
   <si>
-    <t xml:space="preserve">Lunar July (ZhongYuan Festival) - Blk 838 Yishun Street 81 (Representative: Doran, Bryan, 丽菁, 丽丝和先生 - all to arrive by 7pm) </t>
-  </si>
-  <si>
     <t>North West District Meeting and Council Appointment Ceremony 2026. 6pm-9pm. (Representative: Jin Hoa)</t>
   </si>
   <si>
@@ -1497,6 +1485,18 @@
   </si>
   <si>
     <t>Corporate - Wellness Talk (Will writing)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - 724 Yishun Street 71 (Representative: Chew Kim Cheong, Bryan, 丽菁, 丽丝和先生 - all to arrive by 7pm)</t>
+  </si>
+  <si>
+    <t>717 商店中元会 (代表：周锦昌, Bryan, 丽菁, 丽丝和先生）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunar July (ZhongYuan Festival) - Blk 838 Yishun Street 81 (Representative: Doran, Kathy, 丽菁, 丽丝和先生 - all to arrive by 7pm) </t>
+  </si>
+  <si>
+    <t>义顺南旺村中元会。(代表：Doran, Kathy, 丽菁, 丽丝和先生）</t>
   </si>
 </sst>
 </file>
@@ -2098,7 +2098,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -2235,7 +2235,7 @@
         <v>134</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2257,7 +2257,7 @@
         <v>124</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2279,7 +2279,7 @@
         <v>121</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2301,7 +2301,7 @@
         <v>131</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2323,7 +2323,7 @@
         <v>121</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2345,7 +2345,7 @@
         <v>121</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2367,7 +2367,7 @@
         <v>124</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2389,7 +2389,7 @@
         <v>121</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2411,7 +2411,7 @@
         <v>121</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2433,7 +2433,7 @@
         <v>121</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -2449,13 +2449,13 @@
         <v>130</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -2477,7 +2477,7 @@
         <v>129</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -2499,7 +2499,7 @@
         <v>131</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -2515,13 +2515,13 @@
         <v>149</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -2543,7 +2543,7 @@
         <v>121</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -2562,10 +2562,10 @@
         <v>152</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -2584,10 +2584,10 @@
         <v>154</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -2606,10 +2606,10 @@
         <v>156</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -2628,10 +2628,10 @@
         <v>158</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -2653,7 +2653,7 @@
         <v>121</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -2675,7 +2675,7 @@
         <v>121</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -2697,7 +2697,7 @@
         <v>121</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -2719,7 +2719,7 @@
         <v>124</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -2741,7 +2741,7 @@
         <v>124</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -2763,7 +2763,7 @@
         <v>121</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -2785,7 +2785,7 @@
         <v>121</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -2807,7 +2807,7 @@
         <v>124</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -2820,16 +2820,16 @@
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -2842,16 +2842,16 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>226</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -2864,16 +2864,16 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -2886,16 +2886,16 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -2908,16 +2908,16 @@
         <v>Wed</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -2930,16 +2930,16 @@
         <v>Sun</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>224</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -2961,7 +2961,7 @@
         <v>124</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -2974,16 +2974,16 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -2996,16 +2996,16 @@
         <v>Sat</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>251</v>
+        <v>481</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>235</v>
+        <v>482</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -3018,16 +3018,16 @@
         <v>Mon</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -3040,16 +3040,16 @@
         <v>Tue</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -3062,16 +3062,16 @@
         <v>Thu</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>225</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -3084,16 +3084,16 @@
         <v>Thu</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D40" s="16" t="s">
         <v>227</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -3106,16 +3106,16 @@
         <v>Sat</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -3137,7 +3137,7 @@
         <v>124</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -3150,16 +3150,16 @@
         <v>Mon</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D43" s="16" t="s">
         <v>228</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -3172,16 +3172,16 @@
         <v>Tue</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -3194,16 +3194,16 @@
         <v>Wed</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>258</v>
+        <v>483</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>238</v>
+        <v>484</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -3216,14 +3216,14 @@
         <v>Tue</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D46" s="16"/>
       <c r="E46" s="11" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -3236,16 +3236,16 @@
         <v>Wed</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E47" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -3258,14 +3258,14 @@
         <v>Fri</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D48" s="11"/>
       <c r="E48" s="11" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -3287,7 +3287,7 @@
         <v>124</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -3300,16 +3300,16 @@
         <v>Fri</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="38.5" x14ac:dyDescent="0.35">
@@ -3322,16 +3322,16 @@
         <v>Fri</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -3344,16 +3344,16 @@
         <v>Sat</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -3372,10 +3372,10 @@
         <v>205</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="G53" s="19"/>
     </row>
@@ -3395,10 +3395,10 @@
         <v>206</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -3417,10 +3417,10 @@
         <v>207</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -3442,7 +3442,7 @@
         <v>121</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -3464,7 +3464,7 @@
         <v>124</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -3477,16 +3477,16 @@
         <v>Tue</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
@@ -3508,7 +3508,7 @@
         <v>131</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -3521,7 +3521,7 @@
         <v>Fri</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>211</v>
@@ -3530,7 +3530,7 @@
         <v>131</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -3552,7 +3552,7 @@
         <v>121</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -3565,16 +3565,16 @@
         <v>Thu</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -3596,7 +3596,7 @@
         <v>124</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -3618,7 +3618,7 @@
         <v>121</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -3637,10 +3637,10 @@
         <v>215</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -3662,7 +3662,7 @@
         <v>124</v>
       </c>
       <c r="F66" s="26" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -3681,10 +3681,10 @@
         <v>216</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -3703,10 +3703,10 @@
         <v>217</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -3725,10 +3725,10 @@
         <v>218</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -3750,7 +3750,7 @@
         <v>121</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -3763,7 +3763,7 @@
         <v>Fri</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>213</v>
@@ -3772,7 +3772,7 @@
         <v>124</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -3794,7 +3794,7 @@
         <v>124</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -3816,7 +3816,7 @@
         <v>124</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -3835,10 +3835,10 @@
         <v>221</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F74" s="26" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -3860,7 +3860,7 @@
         <v>124</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
@@ -3882,7 +3882,7 @@
         <v>124</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
@@ -3904,7 +3904,7 @@
         <v>131</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
@@ -3926,7 +3926,7 @@
         <v>124</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -3948,7 +3948,7 @@
         <v>124</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -3970,7 +3970,7 @@
         <v>124</v>
       </c>
       <c r="F80" s="26" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
@@ -3983,16 +3983,16 @@
         <v>Fri</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F81" s="25" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
@@ -4014,7 +4014,7 @@
         <v>131</v>
       </c>
       <c r="F82" s="26" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -4241,7 +4241,7 @@
         <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>96</v>
@@ -4493,7 +4493,7 @@
         <v>109</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>93</v>
@@ -4513,7 +4513,7 @@
         <v>109</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>86</v>
@@ -4533,7 +4533,7 @@
         <v>109</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>101</v>
@@ -4553,7 +4553,7 @@
         <v>109</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>88</v>
@@ -4573,7 +4573,7 @@
         <v>109</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>90</v>
@@ -4942,7 +4942,7 @@
         <v>61</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>29</v>
@@ -5221,839 +5221,839 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>G2&amp;H2</f>
         <v>jinhoa.jpg</v>
       </c>
       <c r="G2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="H2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C3" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F3" s="4" t="str">
         <f t="shared" ref="F3:F33" si="0">G3&amp;H3</f>
         <v>kathy.jpg</v>
       </c>
       <c r="G3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="H3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C4" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D4" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aceline.jpg</v>
       </c>
       <c r="G4" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="H4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C5" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D5" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="F5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>agnes.jpg</v>
       </c>
       <c r="G5" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="H5" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C6" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D6" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bryan.jpg</v>
       </c>
       <c r="G6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="H6" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B7" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C7" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D7" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="F7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yinyee.jpg</v>
       </c>
       <c r="G7" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="H7" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B8" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C8" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D8" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="F8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>jingyi.jpg</v>
       </c>
       <c r="G8" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H8" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B9" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C9" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D9" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chihwee.jpg</v>
       </c>
       <c r="G9" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="H9" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B10" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C10" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D10" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="F10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>crystal.jpg</v>
       </c>
       <c r="G10" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="H10" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B11" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C11" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D11" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>peiyuen.jpg</v>
       </c>
       <c r="G11" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="H11" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B12" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C12" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D12" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="F12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>doran.jpg</v>
       </c>
       <c r="G12" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="H12" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B13" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C13" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D13" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>alicia.jpg</v>
       </c>
       <c r="G13" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="H13" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B14" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C14" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D14" t="s">
+        <v>388</v>
+      </c>
+      <c r="E14" t="s">
+        <v>389</v>
+      </c>
+      <c r="F14" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>keongeng.jpg</v>
+      </c>
+      <c r="G14" t="s">
+        <v>405</v>
+      </c>
+      <c r="H14" t="s">
         <v>392</v>
-      </c>
-      <c r="E14" t="s">
-        <v>393</v>
-      </c>
-      <c r="F14" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>keongeng.jpg</v>
-      </c>
-      <c r="G14" t="s">
-        <v>409</v>
-      </c>
-      <c r="H14" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B15" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C15" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D15" t="s">
+        <v>388</v>
+      </c>
+      <c r="E15" t="s">
+        <v>389</v>
+      </c>
+      <c r="F15" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>siokteng.jpg</v>
+      </c>
+      <c r="G15" t="s">
+        <v>406</v>
+      </c>
+      <c r="H15" t="s">
         <v>392</v>
-      </c>
-      <c r="E15" t="s">
-        <v>393</v>
-      </c>
-      <c r="F15" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>siokteng.jpg</v>
-      </c>
-      <c r="G15" t="s">
-        <v>410</v>
-      </c>
-      <c r="H15" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B16" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C16" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D16" t="s">
+        <v>388</v>
+      </c>
+      <c r="E16" t="s">
+        <v>389</v>
+      </c>
+      <c r="F16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>vivian.jpg</v>
+      </c>
+      <c r="G16" t="s">
+        <v>407</v>
+      </c>
+      <c r="H16" t="s">
         <v>392</v>
-      </c>
-      <c r="E16" t="s">
-        <v>393</v>
-      </c>
-      <c r="F16" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>vivian.jpg</v>
-      </c>
-      <c r="G16" t="s">
-        <v>411</v>
-      </c>
-      <c r="H16" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B17" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C17" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D17" t="s">
+        <v>388</v>
+      </c>
+      <c r="E17" t="s">
+        <v>389</v>
+      </c>
+      <c r="F17" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>bonteck.jpg</v>
+      </c>
+      <c r="G17" t="s">
+        <v>408</v>
+      </c>
+      <c r="H17" t="s">
         <v>392</v>
-      </c>
-      <c r="E17" t="s">
-        <v>393</v>
-      </c>
-      <c r="F17" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>bonteck.jpg</v>
-      </c>
-      <c r="G17" t="s">
-        <v>412</v>
-      </c>
-      <c r="H17" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B18" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C18" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D18" t="s">
+        <v>388</v>
+      </c>
+      <c r="E18" t="s">
+        <v>389</v>
+      </c>
+      <c r="F18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>chinmee.jpg</v>
+      </c>
+      <c r="G18" t="s">
+        <v>409</v>
+      </c>
+      <c r="H18" t="s">
         <v>392</v>
-      </c>
-      <c r="E18" t="s">
-        <v>393</v>
-      </c>
-      <c r="F18" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>chinmee.jpg</v>
-      </c>
-      <c r="G18" t="s">
-        <v>413</v>
-      </c>
-      <c r="H18" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B19" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C19" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D19" t="s">
+        <v>388</v>
+      </c>
+      <c r="E19" t="s">
+        <v>389</v>
+      </c>
+      <c r="F19" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>soonmeng.jpg</v>
+      </c>
+      <c r="G19" t="s">
+        <v>410</v>
+      </c>
+      <c r="H19" t="s">
         <v>392</v>
-      </c>
-      <c r="E19" t="s">
-        <v>393</v>
-      </c>
-      <c r="F19" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>soonmeng.jpg</v>
-      </c>
-      <c r="G19" t="s">
-        <v>414</v>
-      </c>
-      <c r="H19" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B20" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C20" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D20" t="s">
+        <v>388</v>
+      </c>
+      <c r="E20" t="s">
+        <v>389</v>
+      </c>
+      <c r="F20" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>yuehong.jpg</v>
+      </c>
+      <c r="G20" t="s">
+        <v>411</v>
+      </c>
+      <c r="H20" t="s">
         <v>392</v>
-      </c>
-      <c r="E20" t="s">
-        <v>393</v>
-      </c>
-      <c r="F20" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>yuehong.jpg</v>
-      </c>
-      <c r="G20" t="s">
-        <v>415</v>
-      </c>
-      <c r="H20" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B21" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C21" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D21" t="s">
+        <v>388</v>
+      </c>
+      <c r="E21" t="s">
+        <v>389</v>
+      </c>
+      <c r="F21" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>choejang.jpg</v>
+      </c>
+      <c r="G21" t="s">
+        <v>412</v>
+      </c>
+      <c r="H21" t="s">
         <v>392</v>
-      </c>
-      <c r="E21" t="s">
-        <v>393</v>
-      </c>
-      <c r="F21" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>choejang.jpg</v>
-      </c>
-      <c r="G21" t="s">
-        <v>416</v>
-      </c>
-      <c r="H21" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B22" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C22" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D22" t="s">
+        <v>388</v>
+      </c>
+      <c r="E22" t="s">
+        <v>389</v>
+      </c>
+      <c r="F22" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>meichia.jpg</v>
+      </c>
+      <c r="G22" t="s">
+        <v>413</v>
+      </c>
+      <c r="H22" t="s">
         <v>392</v>
-      </c>
-      <c r="E22" t="s">
-        <v>393</v>
-      </c>
-      <c r="F22" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>meichia.jpg</v>
-      </c>
-      <c r="G22" t="s">
-        <v>417</v>
-      </c>
-      <c r="H22" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B23" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C23" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D23" t="s">
+        <v>388</v>
+      </c>
+      <c r="E23" t="s">
+        <v>389</v>
+      </c>
+      <c r="F23" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>gekhee.jpg</v>
+      </c>
+      <c r="G23" t="s">
+        <v>414</v>
+      </c>
+      <c r="H23" t="s">
         <v>392</v>
-      </c>
-      <c r="E23" t="s">
-        <v>393</v>
-      </c>
-      <c r="F23" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>gekhee.jpg</v>
-      </c>
-      <c r="G23" t="s">
-        <v>418</v>
-      </c>
-      <c r="H23" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B24" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C24" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D24" t="s">
+        <v>388</v>
+      </c>
+      <c r="E24" t="s">
+        <v>389</v>
+      </c>
+      <c r="F24" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>aimee.jpg</v>
+      </c>
+      <c r="G24" t="s">
+        <v>415</v>
+      </c>
+      <c r="H24" t="s">
         <v>392</v>
-      </c>
-      <c r="E24" t="s">
-        <v>393</v>
-      </c>
-      <c r="F24" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>aimee.jpg</v>
-      </c>
-      <c r="G24" t="s">
-        <v>419</v>
-      </c>
-      <c r="H24" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B25" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C25" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D25" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F25" s="4" t="str">
         <f t="shared" si="0"/>
         <v>geokchin.jpg</v>
       </c>
       <c r="G25" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="H25" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B26" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C26" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D26" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F26" s="4" t="str">
         <f t="shared" si="0"/>
         <v>laysiew.jpg</v>
       </c>
       <c r="G26" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="H26" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B27" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C27" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D27" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F27" s="4" t="str">
         <f t="shared" si="0"/>
         <v>waiyee.jpg</v>
       </c>
       <c r="G27" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="H27" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B28" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C28" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D28" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F28" s="4" t="str">
         <f t="shared" si="0"/>
         <v>carol.jpg</v>
       </c>
       <c r="G28" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="H28" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B29" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C29" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D29" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F29" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yokewant.jpg</v>
       </c>
       <c r="G29" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="H29" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B30" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C30" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D30" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F30" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pohcheng.jpg</v>
       </c>
       <c r="G30" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H30" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B31" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C31" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D31" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F31" s="4" t="str">
         <f t="shared" si="0"/>
         <v>geoklan.jpg</v>
       </c>
       <c r="G31" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="H31" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B32" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C32" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D32" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F32" s="4" t="str">
         <f t="shared" si="0"/>
         <v>laichee.jpg</v>
       </c>
       <c r="G32" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="H32" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B33" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C33" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D33" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F33" s="4" t="str">
         <f t="shared" si="0"/>
         <v>beechoo.jpg</v>
       </c>
       <c r="G33" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="H33" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="B2" s="18">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -6094,7 +6094,7 @@
         <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -6111,14 +6111,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6363,23 +6361,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6405,9 +6400,14 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="720" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16DB86A0-1140-4522-82B8-DA52C36993E9}"/>
+  <xr:revisionPtr revIDLastSave="722" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{077009F3-421A-40E1-89F2-1FC72D6CB3DF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -779,9 +779,6 @@
     <t>[未确认] 新春晚宴 – 企业社会责任（JustCo或MS项目）二月18日或二月19日</t>
   </si>
   <si>
-    <t>Wee Guan Construction 企业社会责任（150人）</t>
-  </si>
-  <si>
     <t xml:space="preserve">Temple Dinner - 元龙聖庙（关帝聖君兴诸众神诞）(Representative: Cher Kim Seah, Agnes, Bryan, Kathy, Jin Hoa - all to arrive by 7pm). Auction item included. </t>
   </si>
   <si>
@@ -815,9 +812,6 @@
     <t>Govt. Agency Invitation</t>
   </si>
   <si>
-    <t>Wee Guan Construction CSR Mental Health Day (150 pax). 70 volunteers. Buffet, activities, goodie bag. 9am to 1pm.</t>
-  </si>
-  <si>
     <t>Building Nee Soon Together | Invitation to Dialogue Session</t>
   </si>
   <si>
@@ -1497,6 +1491,12 @@
   </si>
   <si>
     <t>义顺南旺村中元会。(代表：Doran, Kathy, 丽菁, 丽丝和先生）</t>
+  </si>
+  <si>
+    <t>Wee Guan Construction CSR Mental Health Day (120 pax). 70 volunteers. Buffet, activities, goodie bag. 9am to 1pm.</t>
+  </si>
+  <si>
+    <t>Wee Guan Construction 企业社会责任（120人）</t>
   </si>
 </sst>
 </file>
@@ -2098,7 +2098,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -2235,7 +2235,7 @@
         <v>134</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2257,7 +2257,7 @@
         <v>124</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2279,7 +2279,7 @@
         <v>121</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2301,7 +2301,7 @@
         <v>131</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2323,7 +2323,7 @@
         <v>121</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2345,7 +2345,7 @@
         <v>121</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2367,7 +2367,7 @@
         <v>124</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2389,7 +2389,7 @@
         <v>121</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2411,7 +2411,7 @@
         <v>121</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2433,7 +2433,7 @@
         <v>121</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -2449,13 +2449,13 @@
         <v>130</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -2477,7 +2477,7 @@
         <v>129</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -2499,7 +2499,7 @@
         <v>131</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -2515,13 +2515,13 @@
         <v>149</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -2543,7 +2543,7 @@
         <v>121</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -2565,7 +2565,7 @@
         <v>241</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -2587,7 +2587,7 @@
         <v>241</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -2609,7 +2609,7 @@
         <v>241</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -2631,7 +2631,7 @@
         <v>241</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -2653,7 +2653,7 @@
         <v>121</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -2675,7 +2675,7 @@
         <v>121</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -2697,7 +2697,7 @@
         <v>121</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -2719,7 +2719,7 @@
         <v>124</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -2741,7 +2741,7 @@
         <v>124</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -2763,7 +2763,7 @@
         <v>121</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -2785,7 +2785,7 @@
         <v>121</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -2807,7 +2807,7 @@
         <v>124</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -2829,7 +2829,7 @@
         <v>121</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -2842,7 +2842,7 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>226</v>
@@ -2851,7 +2851,7 @@
         <v>241</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -2864,16 +2864,16 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>241</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -2886,16 +2886,16 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -2908,16 +2908,16 @@
         <v>Wed</v>
       </c>
       <c r="C32" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="D32" s="16" t="s">
         <v>475</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>477</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -2930,7 +2930,7 @@
         <v>Sun</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>224</v>
@@ -2939,7 +2939,7 @@
         <v>241</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -2961,7 +2961,7 @@
         <v>124</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -2974,16 +2974,16 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -2996,16 +2996,16 @@
         <v>Sat</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>241</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -3018,16 +3018,16 @@
         <v>Mon</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>241</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -3040,7 +3040,7 @@
         <v>Tue</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D38" s="16" t="s">
         <v>235</v>
@@ -3049,7 +3049,7 @@
         <v>241</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -3062,7 +3062,7 @@
         <v>Thu</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>225</v>
@@ -3071,7 +3071,7 @@
         <v>241</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -3084,7 +3084,7 @@
         <v>Thu</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D40" s="16" t="s">
         <v>227</v>
@@ -3093,7 +3093,7 @@
         <v>241</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -3106,7 +3106,7 @@
         <v>Sat</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>236</v>
@@ -3115,7 +3115,7 @@
         <v>241</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -3137,7 +3137,7 @@
         <v>124</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -3150,7 +3150,7 @@
         <v>Mon</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D43" s="16" t="s">
         <v>228</v>
@@ -3159,7 +3159,7 @@
         <v>241</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -3172,7 +3172,7 @@
         <v>Tue</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D44" s="16" t="s">
         <v>237</v>
@@ -3181,7 +3181,7 @@
         <v>241</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -3194,16 +3194,16 @@
         <v>Wed</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E45" s="11" t="s">
         <v>241</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -3216,14 +3216,14 @@
         <v>Tue</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D46" s="16"/>
       <c r="E46" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -3236,16 +3236,16 @@
         <v>Wed</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E47" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -3258,14 +3258,14 @@
         <v>Fri</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D48" s="11"/>
       <c r="E48" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -3287,7 +3287,7 @@
         <v>124</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -3300,16 +3300,16 @@
         <v>Fri</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>257</v>
+        <v>483</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>245</v>
+        <v>484</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="38.5" x14ac:dyDescent="0.35">
@@ -3322,16 +3322,16 @@
         <v>Fri</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -3344,16 +3344,16 @@
         <v>Sat</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -3375,7 +3375,7 @@
         <v>241</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G53" s="19"/>
     </row>
@@ -3398,7 +3398,7 @@
         <v>241</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -3420,7 +3420,7 @@
         <v>241</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -3442,7 +3442,7 @@
         <v>121</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -3464,7 +3464,7 @@
         <v>124</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -3477,16 +3477,16 @@
         <v>Tue</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
@@ -3508,7 +3508,7 @@
         <v>131</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -3530,7 +3530,7 @@
         <v>131</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -3552,7 +3552,7 @@
         <v>121</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -3574,7 +3574,7 @@
         <v>242</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -3596,7 +3596,7 @@
         <v>124</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -3618,7 +3618,7 @@
         <v>121</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -3640,7 +3640,7 @@
         <v>242</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -3662,7 +3662,7 @@
         <v>124</v>
       </c>
       <c r="F66" s="26" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -3684,7 +3684,7 @@
         <v>241</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -3706,7 +3706,7 @@
         <v>241</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -3728,7 +3728,7 @@
         <v>241</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -3750,7 +3750,7 @@
         <v>121</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -3763,7 +3763,7 @@
         <v>Fri</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>213</v>
@@ -3772,7 +3772,7 @@
         <v>124</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -3794,7 +3794,7 @@
         <v>124</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -3816,7 +3816,7 @@
         <v>124</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -3838,7 +3838,7 @@
         <v>241</v>
       </c>
       <c r="F74" s="26" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -3860,7 +3860,7 @@
         <v>124</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
@@ -3882,7 +3882,7 @@
         <v>124</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
@@ -3904,7 +3904,7 @@
         <v>131</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
@@ -3926,7 +3926,7 @@
         <v>124</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -3948,7 +3948,7 @@
         <v>124</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -3970,7 +3970,7 @@
         <v>124</v>
       </c>
       <c r="F80" s="26" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
@@ -3983,16 +3983,16 @@
         <v>Fri</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F81" s="25" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
@@ -4014,7 +4014,7 @@
         <v>131</v>
       </c>
       <c r="F82" s="26" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -4241,7 +4241,7 @@
         <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>96</v>
@@ -4493,7 +4493,7 @@
         <v>109</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>93</v>
@@ -4513,7 +4513,7 @@
         <v>109</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>86</v>
@@ -4533,7 +4533,7 @@
         <v>109</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>101</v>
@@ -4553,7 +4553,7 @@
         <v>109</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>88</v>
@@ -4573,7 +4573,7 @@
         <v>109</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>90</v>
@@ -4942,7 +4942,7 @@
         <v>61</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>29</v>
@@ -5221,839 +5221,839 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>G2&amp;H2</f>
         <v>jinhoa.jpg</v>
       </c>
       <c r="G2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F3" s="4" t="str">
         <f t="shared" ref="F3:F33" si="0">G3&amp;H3</f>
         <v>kathy.jpg</v>
       </c>
       <c r="G3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aceline.jpg</v>
       </c>
       <c r="G4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="H4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>agnes.jpg</v>
       </c>
       <c r="G5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bryan.jpg</v>
       </c>
       <c r="G6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D7" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yinyee.jpg</v>
       </c>
       <c r="G7" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="H7" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D8" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>jingyi.jpg</v>
       </c>
       <c r="G8" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H8" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B9" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C9" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D9" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chihwee.jpg</v>
       </c>
       <c r="G9" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H9" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C10" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D10" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>crystal.jpg</v>
       </c>
       <c r="G10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H10" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C11" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D11" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>peiyuen.jpg</v>
       </c>
       <c r="G11" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H11" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C12" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D12" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>doran.jpg</v>
       </c>
       <c r="G12" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H12" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B13" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D13" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>alicia.jpg</v>
       </c>
       <c r="G13" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H13" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B14" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C14" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D14" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E14" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>keongeng.jpg</v>
       </c>
       <c r="G14" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="H14" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B15" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C15" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D15" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>siokteng.jpg</v>
       </c>
       <c r="G15" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H15" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B16" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C16" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D16" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E16" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>vivian.jpg</v>
       </c>
       <c r="G16" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B17" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C17" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D17" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bonteck.jpg</v>
       </c>
       <c r="G17" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H17" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B18" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C18" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D18" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E18" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chinmee.jpg</v>
       </c>
       <c r="G18" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H18" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B19" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C19" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D19" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E19" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>soonmeng.jpg</v>
       </c>
       <c r="G19" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H19" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B20" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C20" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D20" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E20" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yuehong.jpg</v>
       </c>
       <c r="G20" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B21" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C21" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D21" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E21" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>choejang.jpg</v>
       </c>
       <c r="G21" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H21" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B22" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C22" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D22" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E22" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>meichia.jpg</v>
       </c>
       <c r="G22" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H22" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B23" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C23" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D23" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E23" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>gekhee.jpg</v>
       </c>
       <c r="G23" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H23" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B24" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C24" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D24" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E24" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aimee.jpg</v>
       </c>
       <c r="G24" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H24" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B25" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C25" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D25" t="s">
+        <v>388</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="F25" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geokchin.jpg</v>
+      </c>
+      <c r="G25" t="s">
+        <v>414</v>
+      </c>
+      <c r="H25" t="s">
         <v>390</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="F25" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>geokchin.jpg</v>
-      </c>
-      <c r="G25" t="s">
-        <v>416</v>
-      </c>
-      <c r="H25" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B26" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C26" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D26" t="s">
+        <v>388</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="F26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laysiew.jpg</v>
+      </c>
+      <c r="G26" t="s">
+        <v>415</v>
+      </c>
+      <c r="H26" t="s">
         <v>390</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>laysiew.jpg</v>
-      </c>
-      <c r="G26" t="s">
-        <v>417</v>
-      </c>
-      <c r="H26" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B27" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C27" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D27" t="s">
+        <v>388</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="F27" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>waiyee.jpg</v>
+      </c>
+      <c r="G27" t="s">
+        <v>416</v>
+      </c>
+      <c r="H27" t="s">
         <v>390</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="F27" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>waiyee.jpg</v>
-      </c>
-      <c r="G27" t="s">
-        <v>418</v>
-      </c>
-      <c r="H27" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B28" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C28" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D28" t="s">
+        <v>388</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="F28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>carol.jpg</v>
+      </c>
+      <c r="G28" t="s">
+        <v>417</v>
+      </c>
+      <c r="H28" t="s">
         <v>390</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>carol.jpg</v>
-      </c>
-      <c r="G28" t="s">
-        <v>419</v>
-      </c>
-      <c r="H28" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B29" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C29" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D29" t="s">
+        <v>388</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="F29" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>yokewant.jpg</v>
+      </c>
+      <c r="G29" t="s">
+        <v>418</v>
+      </c>
+      <c r="H29" t="s">
         <v>390</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="F29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>yokewant.jpg</v>
-      </c>
-      <c r="G29" t="s">
-        <v>420</v>
-      </c>
-      <c r="H29" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B30" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C30" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D30" t="s">
+        <v>388</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="F30" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>pohcheng.jpg</v>
+      </c>
+      <c r="G30" t="s">
+        <v>419</v>
+      </c>
+      <c r="H30" t="s">
         <v>390</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="F30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>pohcheng.jpg</v>
-      </c>
-      <c r="G30" t="s">
-        <v>421</v>
-      </c>
-      <c r="H30" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B31" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C31" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D31" t="s">
+        <v>388</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="F31" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>geoklan.jpg</v>
+      </c>
+      <c r="G31" t="s">
+        <v>420</v>
+      </c>
+      <c r="H31" t="s">
         <v>390</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="F31" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>geoklan.jpg</v>
-      </c>
-      <c r="G31" t="s">
-        <v>422</v>
-      </c>
-      <c r="H31" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B32" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C32" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D32" t="s">
+        <v>388</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="F32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>laichee.jpg</v>
+      </c>
+      <c r="G32" t="s">
+        <v>421</v>
+      </c>
+      <c r="H32" t="s">
         <v>390</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>laichee.jpg</v>
-      </c>
-      <c r="G32" t="s">
-        <v>423</v>
-      </c>
-      <c r="H32" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B33" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C33" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D33" t="s">
+        <v>388</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="F33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>beechoo.jpg</v>
+      </c>
+      <c r="G33" t="s">
+        <v>422</v>
+      </c>
+      <c r="H33" t="s">
         <v>390</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="F33" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>beechoo.jpg</v>
-      </c>
-      <c r="G33" t="s">
-        <v>424</v>
-      </c>
-      <c r="H33" t="s">
-        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -6094,7 +6094,7 @@
         <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="722" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{077009F3-421A-40E1-89F2-1FC72D6CB3DF}"/>
+  <xr:revisionPtr revIDLastSave="730" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAB1DC0D-112A-401B-AE96-3717E8A33D39}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="486">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -530,21 +530,12 @@
     <t>摩根士丹利企业社会责任活动暨寿像拍摄</t>
   </si>
   <si>
-    <t>TFE Ration Distribution (140 pax)</t>
-  </si>
-  <si>
     <t>TFE物资派发（140人）</t>
   </si>
   <si>
-    <t>MWS Family Service Centre Family Wellness Day (Exhibition Booth)</t>
-  </si>
-  <si>
     <t>卫理公会福利服务家庭服务中心家庭健康日（展位）</t>
   </si>
   <si>
-    <t>正罡玄门 Mid-Autumn Ration (200 pax)</t>
-  </si>
-  <si>
     <t>正罡玄门中秋物资派发（200人）</t>
   </si>
   <si>
@@ -554,9 +545,6 @@
     <t>[Tentative] Sponsor a HUG Campaign (Physical Launch Closer to Christmas)</t>
   </si>
   <si>
-    <t>[Tentative] MS Project Ration Distribution (Date Unconfirmed)</t>
-  </si>
-  <si>
     <t>[Tentative] Deepavali Ang Pao Distribution (AMS Hindus)</t>
   </si>
   <si>
@@ -833,9 +821,6 @@
     <t>南凤福利协会 Nam Hong Welfare Service Society · For committee members reference 仅供理事参考</t>
   </si>
   <si>
-    <t>Songs of Health. Chong Pang Zone. Blk 108, Yishun Ring Road #01-301. 9.30am to 12.30pm (Representative: Physician Leong Chin Mee - Health Talk)</t>
-  </si>
-  <si>
     <t>Kopi Kaki session at [location TBA], 830am to 930am</t>
   </si>
   <si>
@@ -860,9 +845,6 @@
     <t>[Tentative] CSR Partnership – Corporate / School - Singapore Flyer (suggestion)</t>
   </si>
   <si>
-    <t>Nam Hong Charity Concert 2026 (Location: Tzu Chi Humanistic Youth Centre)</t>
-  </si>
-  <si>
     <t>南凤慈济慈善演唱会2026</t>
   </si>
   <si>
@@ -1493,10 +1475,31 @@
     <t>义顺南旺村中元会。(代表：Doran, Kathy, 丽菁, 丽丝和先生）</t>
   </si>
   <si>
-    <t>Wee Guan Construction CSR Mental Health Day (120 pax). 70 volunteers. Buffet, activities, goodie bag. 9am to 1pm.</t>
-  </si>
-  <si>
     <t>Wee Guan Construction 企业社会责任（120人）</t>
+  </si>
+  <si>
+    <t>TFE Ration Distribution (140 pax). (In charge: Bryan)</t>
+  </si>
+  <si>
+    <t>Songs of Health. Chong Pang Zone. Blk 108, Yishun Ring Road #01-301. 9.30am to 12.30pm (Representative: Physician Leong Chin Mee - Health Talk). (In charge: Bryan)</t>
+  </si>
+  <si>
+    <t>MWS Family Service Centre Family Wellness Day (Exhibition Booth). (In charge: Bryan)</t>
+  </si>
+  <si>
+    <t>正罡玄门 Mid-Autumn Ration (200 pax). (In charge: Bryan &amp; Chi Hwee)</t>
+  </si>
+  <si>
+    <t>Wee Guan Construction CSR Mental Health Day (120 pax). 70 volunteers. Buffet, activities, goodie bag. 9am to 1pm. (In charge: Chi Hwee, Jin Hoa)</t>
+  </si>
+  <si>
+    <t>Nam Hong Charity Concert 2026 (Location: Tzu Chi Humanistic Youth Centre). (In charge: Bryan, Chi Hwee)</t>
+  </si>
+  <si>
+    <t>[Tentative] Sponsor a HUG Campaign (Physical Launch Closer to Christmas). (In charge: Chi Hwee, Jin Hoa)</t>
+  </si>
+  <si>
+    <t>[Tentative] MS Project Ration Distribution (Date Unconfirmed). (In charge: Chi Hwee)</t>
   </si>
 </sst>
 </file>
@@ -2098,7 +2101,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -2235,7 +2238,7 @@
         <v>134</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2257,7 +2260,7 @@
         <v>124</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2279,7 +2282,7 @@
         <v>121</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2301,7 +2304,7 @@
         <v>131</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2323,7 +2326,7 @@
         <v>121</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2345,7 +2348,7 @@
         <v>121</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2367,7 +2370,7 @@
         <v>124</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2389,7 +2392,7 @@
         <v>121</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2411,7 +2414,7 @@
         <v>121</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2427,13 +2430,13 @@
         <v>128</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -2449,13 +2452,13 @@
         <v>130</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -2477,7 +2480,7 @@
         <v>129</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -2499,7 +2502,7 @@
         <v>131</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -2515,13 +2518,13 @@
         <v>149</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -2543,7 +2546,7 @@
         <v>121</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -2562,10 +2565,10 @@
         <v>152</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -2584,10 +2587,10 @@
         <v>154</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -2606,10 +2609,10 @@
         <v>156</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -2628,10 +2631,10 @@
         <v>158</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -2647,13 +2650,13 @@
         <v>128</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -2675,7 +2678,7 @@
         <v>121</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -2691,13 +2694,13 @@
         <v>128</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -2719,7 +2722,7 @@
         <v>124</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -2732,16 +2735,16 @@
         <v>Fri</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -2757,13 +2760,13 @@
         <v>128</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -2779,13 +2782,13 @@
         <v>128</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -2798,16 +2801,16 @@
         <v>Sat</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -2820,16 +2823,16 @@
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -2842,16 +2845,16 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -2864,16 +2867,16 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -2886,16 +2889,16 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -2908,16 +2911,16 @@
         <v>Wed</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -2930,16 +2933,16 @@
         <v>Sun</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -2952,16 +2955,16 @@
         <v>Fri</v>
       </c>
       <c r="C34" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>162</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>163</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -2974,16 +2977,16 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>263</v>
+        <v>479</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -2996,16 +2999,16 @@
         <v>Sat</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -3018,16 +3021,16 @@
         <v>Mon</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -3040,16 +3043,16 @@
         <v>Tue</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -3062,16 +3065,16 @@
         <v>Thu</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -3084,16 +3087,16 @@
         <v>Thu</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -3106,16 +3109,16 @@
         <v>Sat</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -3128,16 +3131,16 @@
         <v>Sat</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>164</v>
+        <v>480</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -3150,16 +3153,16 @@
         <v>Mon</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -3172,16 +3175,16 @@
         <v>Tue</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D44" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="E44" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="E44" s="11" t="s">
-        <v>241</v>
-      </c>
       <c r="F44" s="25" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -3194,16 +3197,16 @@
         <v>Wed</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -3216,14 +3219,14 @@
         <v>Tue</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D46" s="16"/>
       <c r="E46" s="11" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -3236,16 +3239,16 @@
         <v>Wed</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E47" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -3258,14 +3261,14 @@
         <v>Fri</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D48" s="11"/>
       <c r="E48" s="11" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -3278,16 +3281,16 @@
         <v>Sun</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>166</v>
+        <v>481</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -3300,16 +3303,16 @@
         <v>Fri</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="38.5" x14ac:dyDescent="0.35">
@@ -3322,16 +3325,16 @@
         <v>Fri</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -3344,16 +3347,16 @@
         <v>Sat</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>272</v>
+        <v>483</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -3366,16 +3369,16 @@
         <v>Mon</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="G53" s="19"/>
     </row>
@@ -3389,16 +3392,16 @@
         <v>Tue</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -3411,16 +3414,16 @@
         <v>Wed</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -3433,16 +3436,16 @@
         <v>Tue</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -3455,16 +3458,16 @@
         <v>Tue</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>170</v>
+        <v>485</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -3477,16 +3480,16 @@
         <v>Tue</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
@@ -3499,16 +3502,16 @@
         <v>Wed</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>169</v>
+        <v>484</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E59" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -3521,16 +3524,16 @@
         <v>Fri</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -3543,16 +3546,16 @@
         <v>Sat</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -3565,16 +3568,16 @@
         <v>Thu</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -3587,16 +3590,16 @@
         <v>Fri</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -3609,16 +3612,16 @@
         <v>Thu</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E64" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -3631,16 +3634,16 @@
         <v>Sat</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -3653,16 +3656,16 @@
         <v>Fri</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F66" s="26" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -3675,16 +3678,16 @@
         <v>Wed</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -3697,16 +3700,16 @@
         <v>Thu</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -3719,16 +3722,16 @@
         <v>Fri</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -3741,16 +3744,16 @@
         <v>Fri</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -3763,16 +3766,16 @@
         <v>Fri</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -3785,16 +3788,16 @@
         <v>Fri</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -3807,16 +3810,16 @@
         <v>Fri</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E73" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -3829,16 +3832,16 @@
         <v>Mon</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F74" s="26" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -3851,16 +3854,16 @@
         <v>Fri</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E75" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
@@ -3873,16 +3876,16 @@
         <v>Fri</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E76" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
@@ -3895,16 +3898,16 @@
         <v>Sat</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E77" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
@@ -3917,16 +3920,16 @@
         <v>Fri</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E78" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -3939,16 +3942,16 @@
         <v>Fri</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E79" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -3961,16 +3964,16 @@
         <v>Fri</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E80" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F80" s="26" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
@@ -3983,16 +3986,16 @@
         <v>Fri</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F81" s="25" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
@@ -4005,16 +4008,16 @@
         <v>Thu</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E82" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F82" s="26" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -4241,7 +4244,7 @@
         <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>96</v>
@@ -4266,7 +4269,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>64</v>
@@ -4433,7 +4436,7 @@
         <v>24</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>21</v>
@@ -4493,7 +4496,7 @@
         <v>109</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>93</v>
@@ -4513,7 +4516,7 @@
         <v>109</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>86</v>
@@ -4533,7 +4536,7 @@
         <v>109</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>101</v>
@@ -4553,7 +4556,7 @@
         <v>109</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>88</v>
@@ -4573,7 +4576,7 @@
         <v>109</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>90</v>
@@ -4704,10 +4707,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C2" s="17">
         <v>1</v>
@@ -4727,10 +4730,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C3" s="17">
         <v>2</v>
@@ -4748,16 +4751,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C4" s="17">
         <v>3</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>64</v>
@@ -4771,10 +4774,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C5" s="17">
         <v>4</v>
@@ -4792,10 +4795,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C6" s="17">
         <v>5</v>
@@ -4815,10 +4818,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C7" s="17">
         <v>1</v>
@@ -4838,10 +4841,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C8" s="17">
         <v>2</v>
@@ -4861,10 +4864,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>
@@ -4884,10 +4887,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C10" s="17">
         <v>2</v>
@@ -4907,10 +4910,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -4930,10 +4933,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -4942,7 +4945,7 @@
         <v>61</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>29</v>
@@ -4953,10 +4956,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C13" s="17">
         <v>3</v>
@@ -4976,10 +4979,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C14" s="17">
         <v>4</v>
@@ -4999,10 +5002,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C15" s="17">
         <v>1</v>
@@ -5022,10 +5025,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C16" s="17">
         <v>2</v>
@@ -5045,10 +5048,10 @@
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C17" s="17">
         <v>1</v>
@@ -5068,10 +5071,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -5091,10 +5094,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C19" s="17">
         <v>3</v>
@@ -5114,10 +5117,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C20" s="17">
         <v>1</v>
@@ -5137,10 +5140,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C21" s="17">
         <v>2</v>
@@ -5160,10 +5163,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C22" s="17">
         <v>3</v>
@@ -5213,7 +5216,7 @@
         <v>24</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>21</v>
@@ -5221,839 +5224,839 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B2" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="D2" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="E2" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>G2&amp;H2</f>
         <v>jinhoa.jpg</v>
       </c>
       <c r="G2" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="H2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B3" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C3" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="D3" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="E3" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="F3" s="4" t="str">
         <f t="shared" ref="F3:F33" si="0">G3&amp;H3</f>
         <v>kathy.jpg</v>
       </c>
       <c r="G3" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="H3" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B4" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C4" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="D4" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="E4" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="F4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aceline.jpg</v>
       </c>
       <c r="G4" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="H4" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B5" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C5" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D5" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="F5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>agnes.jpg</v>
       </c>
       <c r="G5" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="H5" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B6" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C6" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="D6" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="F6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bryan.jpg</v>
       </c>
       <c r="G6" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="H6" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B7" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C7" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="D7" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="F7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yinyee.jpg</v>
       </c>
       <c r="G7" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="H7" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B8" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C8" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="D8" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="F8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>jingyi.jpg</v>
       </c>
       <c r="G8" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="H8" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B9" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C9" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D9" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chihwee.jpg</v>
       </c>
       <c r="G9" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="H9" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B10" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C10" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="D10" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="F10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>crystal.jpg</v>
       </c>
       <c r="G10" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="H10" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B11" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C11" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="D11" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>peiyuen.jpg</v>
       </c>
       <c r="G11" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="H11" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B12" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C12" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D12" t="s">
+        <v>378</v>
+      </c>
+      <c r="F12" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>doran.jpg</v>
+      </c>
+      <c r="G12" t="s">
+        <v>395</v>
+      </c>
+      <c r="H12" t="s">
         <v>384</v>
-      </c>
-      <c r="F12" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>doran.jpg</v>
-      </c>
-      <c r="G12" t="s">
-        <v>401</v>
-      </c>
-      <c r="H12" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B13" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C13" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D13" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="F13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>alicia.jpg</v>
       </c>
       <c r="G13" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="H13" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B14" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C14" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D14" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E14" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>keongeng.jpg</v>
       </c>
       <c r="G14" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="H14" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C15" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D15" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E15" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>siokteng.jpg</v>
       </c>
       <c r="G15" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="H15" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B16" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C16" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D16" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E16" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>vivian.jpg</v>
       </c>
       <c r="G16" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="H16" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B17" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C17" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="D17" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E17" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bonteck.jpg</v>
       </c>
       <c r="G17" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="H17" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B18" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C18" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="D18" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E18" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chinmee.jpg</v>
       </c>
       <c r="G18" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="H18" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B19" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C19" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="D19" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E19" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>soonmeng.jpg</v>
       </c>
       <c r="G19" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="H19" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B20" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C20" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="D20" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E20" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yuehong.jpg</v>
       </c>
       <c r="G20" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="H20" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B21" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C21" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D21" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E21" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>choejang.jpg</v>
       </c>
       <c r="G21" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="H21" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="B22" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C22" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D22" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E22" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>meichia.jpg</v>
       </c>
       <c r="G22" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="H22" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B23" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C23" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D23" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E23" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>gekhee.jpg</v>
       </c>
       <c r="G23" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="H23" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B24" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C24" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="D24" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E24" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aimee.jpg</v>
       </c>
       <c r="G24" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="H24" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B25" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C25" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="D25" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="F25" s="4" t="str">
         <f t="shared" si="0"/>
         <v>geokchin.jpg</v>
       </c>
       <c r="G25" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="H25" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B26" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C26" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D26" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="F26" s="4" t="str">
         <f t="shared" si="0"/>
         <v>laysiew.jpg</v>
       </c>
       <c r="G26" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="H26" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B27" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C27" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D27" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="F27" s="4" t="str">
         <f t="shared" si="0"/>
         <v>waiyee.jpg</v>
       </c>
       <c r="G27" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="H27" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B28" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C28" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D28" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="F28" s="4" t="str">
         <f t="shared" si="0"/>
         <v>carol.jpg</v>
       </c>
       <c r="G28" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="H28" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="B29" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C29" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="D29" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="F29" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yokewant.jpg</v>
       </c>
       <c r="G29" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="H29" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B30" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C30" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="D30" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="F30" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pohcheng.jpg</v>
       </c>
       <c r="G30" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="H30" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="B31" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C31" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D31" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="F31" s="4" t="str">
         <f t="shared" si="0"/>
         <v>geoklan.jpg</v>
       </c>
       <c r="G31" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="H31" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B32" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C32" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D32" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="F32" s="4" t="str">
         <f t="shared" si="0"/>
         <v>laichee.jpg</v>
       </c>
       <c r="G32" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="H32" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B33" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C33" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="D33" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="F33" s="4" t="str">
         <f t="shared" si="0"/>
         <v>beechoo.jpg</v>
       </c>
       <c r="G33" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="H33" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -6094,15 +6097,15 @@
         <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B4" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -6111,12 +6114,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6361,20 +6366,23 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6400,14 +6408,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="730" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAB1DC0D-112A-401B-AE96-3717E8A33D39}"/>
+  <xr:revisionPtr revIDLastSave="736" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E226A840-5827-437B-8D62-955994946661}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -713,9 +713,6 @@
     <t>元龙聖庙（关帝聖君兴诸众神诞）(代表：徐金声, Agnes, Bryan, Kathy, Jin Hoa）。筹款活动包括义标。</t>
   </si>
   <si>
-    <t>[日期未确认] 义顺镇商贩联合中元会 (代表：徐金声, Pei Yuen, Yan Yi）。筹款活动包括义标。</t>
-  </si>
-  <si>
     <t>南凤善堂中元会 (代表：梁天城,南凤福利协会员工，晓晓）。筹款活动包括义标。</t>
   </si>
   <si>
@@ -740,9 +737,6 @@
     <t>华报善堂中元会 (代表：徐金声, Chi Hwee, Yan Yi, Agnes, Jin Hoa）。筹款活动包括义标。</t>
   </si>
   <si>
-    <t>[日期未确认] 义顺镇商贩联合中元会歌台 (代表：徐金声, Doran, Pei Yuen）</t>
-  </si>
-  <si>
     <t>南凤善堂中元会晚宴（200人）</t>
   </si>
   <si>
@@ -782,18 +776,9 @@
     <t>Lunar July (ZhongYuan Festival) - Jurong Safra Pearl Garden Restaurant (Representative: Neo Tian Siah, Kathy, Jin Hoa - all to arrive by 7pm)</t>
   </si>
   <si>
-    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Pei Yuen, Yan Yi - all to arrive by 7pm). Auction item included.</t>
-  </si>
-  <si>
-    <t>[Tentative date] Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Doran, Pei Yuen - all to arrive by 7pm)</t>
-  </si>
-  <si>
     <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon (Representative: Neo Tian Siah, NHWSS office staff, 5 front desk, 晓晓 - all to arrive by 7pm). Auction item included.</t>
   </si>
   <si>
-    <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon dinner (200 pax) - all to arrive by 7pm</t>
-  </si>
-  <si>
     <t>North West District Meeting and Council Appointment Ceremony 2026. 6pm-9pm. (Representative: Jin Hoa)</t>
   </si>
   <si>
@@ -1500,6 +1485,21 @@
   </si>
   <si>
     <t>[Tentative] MS Project Ration Distribution (Date Unconfirmed). (In charge: Chi Hwee)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon dinner for NHWSS elderly (200 pax) - all to arrive by 7pm</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Pei Yuen, Yan Yi - all to arrive by 7pm). Auction item included.</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Doran, Pei Yuen - all to arrive by 7pm)</t>
+  </si>
+  <si>
+    <t>义顺镇商贩联合中元会歌台 (代表：徐金声, Doran, Pei Yuen）</t>
+  </si>
+  <si>
+    <t>义顺镇商贩联合中元会 (代表：徐金声, Pei Yuen, Yan Yi）。筹款活动包括义标。</t>
   </si>
 </sst>
 </file>
@@ -2101,7 +2101,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -2238,7 +2238,7 @@
         <v>134</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2260,7 +2260,7 @@
         <v>124</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2282,7 +2282,7 @@
         <v>121</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2304,7 +2304,7 @@
         <v>131</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2326,7 +2326,7 @@
         <v>121</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2348,7 +2348,7 @@
         <v>121</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2370,7 +2370,7 @@
         <v>124</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2392,7 +2392,7 @@
         <v>121</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2414,7 +2414,7 @@
         <v>121</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2430,13 +2430,13 @@
         <v>128</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -2452,13 +2452,13 @@
         <v>130</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -2480,7 +2480,7 @@
         <v>129</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -2502,7 +2502,7 @@
         <v>131</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -2518,13 +2518,13 @@
         <v>149</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -2546,7 +2546,7 @@
         <v>121</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -2565,10 +2565,10 @@
         <v>152</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -2587,10 +2587,10 @@
         <v>154</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -2609,10 +2609,10 @@
         <v>156</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -2631,10 +2631,10 @@
         <v>158</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -2650,13 +2650,13 @@
         <v>128</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -2678,7 +2678,7 @@
         <v>121</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -2694,13 +2694,13 @@
         <v>128</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -2722,7 +2722,7 @@
         <v>124</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -2744,7 +2744,7 @@
         <v>124</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -2760,13 +2760,13 @@
         <v>128</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -2782,13 +2782,13 @@
         <v>128</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -2801,16 +2801,16 @@
         <v>Sat</v>
       </c>
       <c r="C27" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>226</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>227</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -2823,16 +2823,16 @@
         <v>Wed</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -2845,16 +2845,16 @@
         <v>Sat</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>222</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -2867,16 +2867,16 @@
         <v>Fri</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -2889,16 +2889,16 @@
         <v>Sat</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -2911,16 +2911,16 @@
         <v>Wed</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>129</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -2933,16 +2933,16 @@
         <v>Sun</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>220</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -2955,7 +2955,7 @@
         <v>Fri</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>162</v>
@@ -2964,7 +2964,7 @@
         <v>124</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -2977,16 +2977,16 @@
         <v>Sat</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -2999,16 +2999,16 @@
         <v>Sat</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -3021,16 +3021,16 @@
         <v>Mon</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -3043,16 +3043,16 @@
         <v>Tue</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -3065,16 +3065,16 @@
         <v>Thu</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>221</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -3087,38 +3087,38 @@
         <v>Thu</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>246</v>
+        <v>482</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>223</v>
+        <v>485</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="12">
-        <f>DATE(2026,9,5)</f>
-        <v>46270</v>
+        <f>DATE(2026,9,4)</f>
+        <v>46269</v>
       </c>
       <c r="B41" s="13" t="str">
         <f>TEXT($A41,"ddd")</f>
-        <v>Sat</v>
+        <v>Fri</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>247</v>
+        <v>483</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>232</v>
+        <v>484</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -3131,7 +3131,7 @@
         <v>Sat</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>163</v>
@@ -3140,7 +3140,7 @@
         <v>124</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -3153,16 +3153,16 @@
         <v>Mon</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -3175,16 +3175,16 @@
         <v>Tue</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>249</v>
+        <v>481</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -3197,16 +3197,16 @@
         <v>Wed</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -3219,14 +3219,14 @@
         <v>Tue</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D46" s="16"/>
       <c r="E46" s="11" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -3239,16 +3239,16 @@
         <v>Wed</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E47" s="11" t="s">
         <v>121</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -3261,14 +3261,14 @@
         <v>Fri</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D48" s="11"/>
       <c r="E48" s="11" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -3281,7 +3281,7 @@
         <v>Sun</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>164</v>
@@ -3290,7 +3290,7 @@
         <v>124</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -3303,16 +3303,16 @@
         <v>Fri</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="38.5" x14ac:dyDescent="0.35">
@@ -3325,16 +3325,16 @@
         <v>Fri</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -3347,16 +3347,16 @@
         <v>Sat</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>131</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -3375,10 +3375,10 @@
         <v>201</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="G53" s="19"/>
     </row>
@@ -3398,10 +3398,10 @@
         <v>202</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -3420,10 +3420,10 @@
         <v>203</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -3445,7 +3445,7 @@
         <v>121</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -3458,7 +3458,7 @@
         <v>Tue</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="D57" s="11" t="s">
         <v>205</v>
@@ -3467,7 +3467,7 @@
         <v>124</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -3480,16 +3480,16 @@
         <v>Tue</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
@@ -3502,7 +3502,7 @@
         <v>Wed</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="D59" s="16" t="s">
         <v>206</v>
@@ -3511,7 +3511,7 @@
         <v>131</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -3524,7 +3524,7 @@
         <v>Fri</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>207</v>
@@ -3533,7 +3533,7 @@
         <v>131</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -3555,7 +3555,7 @@
         <v>121</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -3568,16 +3568,16 @@
         <v>Thu</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -3599,7 +3599,7 @@
         <v>124</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -3621,7 +3621,7 @@
         <v>121</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -3634,16 +3634,16 @@
         <v>Sat</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D65" s="11" t="s">
         <v>211</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -3665,7 +3665,7 @@
         <v>124</v>
       </c>
       <c r="F66" s="26" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -3684,10 +3684,10 @@
         <v>212</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -3706,10 +3706,10 @@
         <v>213</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -3728,10 +3728,10 @@
         <v>214</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -3753,7 +3753,7 @@
         <v>121</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -3766,7 +3766,7 @@
         <v>Fri</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>209</v>
@@ -3775,7 +3775,7 @@
         <v>124</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -3797,7 +3797,7 @@
         <v>124</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -3819,7 +3819,7 @@
         <v>124</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -3838,10 +3838,10 @@
         <v>217</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F74" s="26" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -3863,7 +3863,7 @@
         <v>124</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
@@ -3885,7 +3885,7 @@
         <v>124</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
@@ -3907,7 +3907,7 @@
         <v>131</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
@@ -3929,7 +3929,7 @@
         <v>124</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -3951,7 +3951,7 @@
         <v>124</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -3973,7 +3973,7 @@
         <v>124</v>
       </c>
       <c r="F80" s="26" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
@@ -3986,16 +3986,16 @@
         <v>Fri</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F81" s="25" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
@@ -4017,7 +4017,7 @@
         <v>131</v>
       </c>
       <c r="F82" s="26" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -4244,7 +4244,7 @@
         <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>96</v>
@@ -4496,7 +4496,7 @@
         <v>109</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>93</v>
@@ -4516,7 +4516,7 @@
         <v>109</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>86</v>
@@ -4536,7 +4536,7 @@
         <v>109</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>101</v>
@@ -4556,7 +4556,7 @@
         <v>109</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>88</v>
@@ -4576,7 +4576,7 @@
         <v>109</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>90</v>
@@ -4945,7 +4945,7 @@
         <v>61</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>29</v>
@@ -5224,839 +5224,839 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>G2&amp;H2</f>
         <v>jinhoa.jpg</v>
       </c>
       <c r="G2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="H2" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="D3" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E3" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F3" s="4" t="str">
         <f t="shared" ref="F3:F33" si="0">G3&amp;H3</f>
         <v>kathy.jpg</v>
       </c>
       <c r="G3" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="H3" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C4" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D4" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E4" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="F4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aceline.jpg</v>
       </c>
       <c r="G4" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="H4" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C5" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="D5" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="F5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>agnes.jpg</v>
       </c>
       <c r="G5" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="H5" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B6" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C6" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="D6" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="F6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bryan.jpg</v>
       </c>
       <c r="G6" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="H6" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B7" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C7" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="D7" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="F7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yinyee.jpg</v>
       </c>
       <c r="G7" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="H7" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B8" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C8" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D8" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>jingyi.jpg</v>
       </c>
       <c r="G8" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="H8" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B9" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C9" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="D9" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="F9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chihwee.jpg</v>
       </c>
       <c r="G9" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="H9" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B10" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C10" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="D10" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="F10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>crystal.jpg</v>
       </c>
       <c r="G10" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="H10" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B11" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C11" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D11" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="F11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>peiyuen.jpg</v>
       </c>
       <c r="G11" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="H11" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B12" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C12" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D12" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="F12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>doran.jpg</v>
       </c>
       <c r="G12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H12" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B13" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C13" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D13" t="s">
+        <v>374</v>
+      </c>
+      <c r="F13" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>alicia.jpg</v>
+      </c>
+      <c r="G13" t="s">
+        <v>391</v>
+      </c>
+      <c r="H13" t="s">
         <v>379</v>
-      </c>
-      <c r="F13" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>alicia.jpg</v>
-      </c>
-      <c r="G13" t="s">
-        <v>396</v>
-      </c>
-      <c r="H13" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B14" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C14" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D14" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E14" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>keongeng.jpg</v>
       </c>
       <c r="G14" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="H14" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B15" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C15" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D15" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E15" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>siokteng.jpg</v>
       </c>
       <c r="G15" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="H15" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B16" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C16" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D16" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E16" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>vivian.jpg</v>
       </c>
       <c r="G16" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H16" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B17" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C17" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D17" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E17" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bonteck.jpg</v>
       </c>
       <c r="G17" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H17" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B18" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C18" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="D18" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E18" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chinmee.jpg</v>
       </c>
       <c r="G18" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="H18" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B19" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C19" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D19" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E19" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>soonmeng.jpg</v>
       </c>
       <c r="G19" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="H19" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B20" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C20" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D20" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E20" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yuehong.jpg</v>
       </c>
       <c r="G20" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="H20" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B21" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C21" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="D21" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E21" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>choejang.jpg</v>
       </c>
       <c r="G21" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="H21" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B22" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C22" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D22" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E22" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>meichia.jpg</v>
       </c>
       <c r="G22" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="H22" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B23" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C23" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D23" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E23" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>gekhee.jpg</v>
       </c>
       <c r="G23" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H23" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B24" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C24" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D24" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E24" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>aimee.jpg</v>
       </c>
       <c r="G24" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H24" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B25" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C25" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="D25" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F25" s="4" t="str">
         <f t="shared" si="0"/>
         <v>geokchin.jpg</v>
       </c>
       <c r="G25" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="H25" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B26" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C26" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D26" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F26" s="4" t="str">
         <f t="shared" si="0"/>
         <v>laysiew.jpg</v>
       </c>
       <c r="G26" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H26" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B27" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C27" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D27" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F27" s="4" t="str">
         <f t="shared" si="0"/>
         <v>waiyee.jpg</v>
       </c>
       <c r="G27" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H27" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B28" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C28" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D28" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F28" s="4" t="str">
         <f t="shared" si="0"/>
         <v>carol.jpg</v>
       </c>
       <c r="G28" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="H28" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B29" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C29" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D29" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F29" s="4" t="str">
         <f t="shared" si="0"/>
         <v>yokewant.jpg</v>
       </c>
       <c r="G29" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="H29" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B30" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C30" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="D30" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F30" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pohcheng.jpg</v>
       </c>
       <c r="G30" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H30" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B31" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C31" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D31" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F31" s="4" t="str">
         <f t="shared" si="0"/>
         <v>geoklan.jpg</v>
       </c>
       <c r="G31" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="H31" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B32" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C32" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D32" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F32" s="4" t="str">
         <f t="shared" si="0"/>
         <v>laichee.jpg</v>
       </c>
       <c r="G32" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="H32" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B33" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C33" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="D33" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F33" s="4" t="str">
         <f t="shared" si="0"/>
         <v>beechoo.jpg</v>
       </c>
       <c r="G33" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="H33" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -6097,7 +6097,7 @@
         <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -6114,14 +6114,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6366,23 +6364,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b731a6fc-fd02-48a8-bb42-25eb2962d7a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6408,9 +6403,14 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7399F2-0FCF-47AB-8CCA-BE20605336D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2415039C-A0B7-409A-B9B2-F0CB01DB9AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="bde74905-0e41-4c1c-a9e9-0b0ca4a779e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b731a6fc-fd02-48a8-bb42-25eb2962d7a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="736" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E226A840-5827-437B-8D62-955994946661}"/>
+  <xr:revisionPtr revIDLastSave="739" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E74AC07-4280-44EF-ABBB-F780F25DEDB9}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1490,16 +1490,16 @@
     <t>Lunar July (ZhongYuan Festival) - Nam Hong Siang Theon dinner for NHWSS elderly (200 pax) - all to arrive by 7pm</t>
   </si>
   <si>
-    <t>Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Pei Yuen, Yan Yi - all to arrive by 7pm). Auction item included.</t>
-  </si>
-  <si>
-    <t>Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Doran, Pei Yuen - all to arrive by 7pm)</t>
-  </si>
-  <si>
     <t>义顺镇商贩联合中元会歌台 (代表：徐金声, Doran, Pei Yuen）</t>
   </si>
   <si>
-    <t>义顺镇商贩联合中元会 (代表：徐金声, Pei Yuen, Yan Yi）。筹款活动包括义标。</t>
+    <t>Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road (Representative: Cher Kim Seah, Pei Yuen, Yan Yi - all to arrive by 7pm)</t>
+  </si>
+  <si>
+    <t>义顺镇商贩联合中元会 (代表：徐金声, Pei Yuen, Yan Yi)</t>
+  </si>
+  <si>
+    <t>Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road - Ge-Tai (Representative: Cher Kim Seah, Doran, Pei Yuen - all to arrive by 7pm)</t>
   </si>
 </sst>
 </file>
@@ -3087,10 +3087,10 @@
         <v>Thu</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>235</v>
@@ -3109,10 +3109,10 @@
         <v>Fri</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E41" s="11" t="s">
         <v>235</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://namhongwelfare.sharepoint.com/sites/General/Shared Documents/namhong/EXCO/Meeting Minutes/EXCO Meeting/Membership Handbook/Mobile Membership Profile/Member Handbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="739" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E74AC07-4280-44EF-ABBB-F780F25DEDB9}"/>
+  <xr:revisionPtr revIDLastSave="1621" documentId="11_A88C884250063A86F00218599B70D26268CCBE65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AD36B1C-3126-4DF4-8CAF-54ED489EA88A}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="Info" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Events'!$A$1:$E$108</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="534">
   <si>
     <t>HOW THIS WORKS</t>
   </si>
@@ -1500,6 +1500,150 @@
   </si>
   <si>
     <t>Lunar July (ZhongYuan Festival) - 104 Yishun Ring Road - Ge-Tai (Representative: Cher Kim Seah, Doran, Pei Yuen - all to arrive by 7pm)</t>
+  </si>
+  <si>
+    <t>Christmas Day (Public Holiday)</t>
+  </si>
+  <si>
+    <t>圣诞节（公共假期）</t>
+  </si>
+  <si>
+    <t>Public Holiday</t>
+  </si>
+  <si>
+    <t>Deepavali (Public Holiday)</t>
+  </si>
+  <si>
+    <t>屠妖节（公共假期）</t>
+  </si>
+  <si>
+    <t>National Day (Public Holiday)</t>
+  </si>
+  <si>
+    <t>国庆日（公共假期）</t>
+  </si>
+  <si>
+    <t>Vesak Day (Public Holiday)</t>
+  </si>
+  <si>
+    <t>卫塞节（公共假期）</t>
+  </si>
+  <si>
+    <t>Labour Day (Public Holiday)</t>
+  </si>
+  <si>
+    <t>劳动节（公共假期）</t>
+  </si>
+  <si>
+    <t>[Tentative] Hari Raya Haji (Public Holiday) - date subject to sighting of the moon</t>
+  </si>
+  <si>
+    <t>[未确认] 哈芝节（公共假期）－日期以观月为准</t>
+  </si>
+  <si>
+    <t>Public Holiday, Tentative</t>
+  </si>
+  <si>
+    <t>Good Friday (Public Holiday)</t>
+  </si>
+  <si>
+    <t>耶稣受难日（公共假期）</t>
+  </si>
+  <si>
+    <t>[Tentative] Hari Raya Puasa (Public Holiday) - date subject to sighting of the moon</t>
+  </si>
+  <si>
+    <t>[未确认] 开斋节（公共假期）－日期以观月为准</t>
+  </si>
+  <si>
+    <t>Chinese New Year Day 1 (Public Holiday)</t>
+  </si>
+  <si>
+    <t>农历新年第一天（公共假期）</t>
+  </si>
+  <si>
+    <t>Chinese New Year Day 2 (Public Holiday)</t>
+  </si>
+  <si>
+    <t>农历新年第二天（公共假期）</t>
+  </si>
+  <si>
+    <t>Public Holiday in Lieu of Chinese New Year Day 2 (falls on Sunday)</t>
+  </si>
+  <si>
+    <t>农历新年第二天补假（适逢星期日）</t>
+  </si>
+  <si>
+    <t>New Year's Day (Public Holiday)</t>
+  </si>
+  <si>
+    <t>元旦（公共假期）</t>
+  </si>
+  <si>
+    <t>Public Holiday in Lieu of Deepavali (falls on Sunday)</t>
+  </si>
+  <si>
+    <t>屠妖节补假（适逢星期日）</t>
+  </si>
+  <si>
+    <t>Public Holiday in Lieu of National Day (falls on Sunday)</t>
+  </si>
+  <si>
+    <t>国庆日补假（适逢星期日）</t>
+  </si>
+  <si>
+    <t>Public Holiday in Lieu of Vesak Day (falls on Sunday)</t>
+  </si>
+  <si>
+    <t>卫塞节补假（适逢星期日）</t>
+  </si>
+  <si>
+    <t>New Year's Day</t>
+  </si>
+  <si>
+    <t>Chinese New Year</t>
+  </si>
+  <si>
+    <t>Hari Raya Puasa</t>
+  </si>
+  <si>
+    <t>Good Friday</t>
+  </si>
+  <si>
+    <t>Labour Day</t>
+  </si>
+  <si>
+    <t>Hari Raya Haji</t>
+  </si>
+  <si>
+    <t>Vesak Day</t>
+  </si>
+  <si>
+    <t>Vesak Day in lieu</t>
+  </si>
+  <si>
+    <t>National Day</t>
+  </si>
+  <si>
+    <t>National Day in lieu</t>
+  </si>
+  <si>
+    <t>Deepavali</t>
+  </si>
+  <si>
+    <t>Deepavali in lieu</t>
+  </si>
+  <si>
+    <t>Christmas Day</t>
+  </si>
+  <si>
+    <t>CNY in lieu</t>
+  </si>
+  <si>
+    <t>Hari Raya Haji (Public Holiday) - date subject to sighting of the moon</t>
+  </si>
+  <si>
+    <t>哈芝节（公共假期）－日期以观月为准</t>
   </si>
 </sst>
 </file>
@@ -1601,7 +1745,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1709,12 +1853,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D5DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D5DD"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D5DD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D5DD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD0D5DD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D5DD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D5DD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD0D5DD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1768,6 +1949,50 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2071,7 +2296,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="525" row="7">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="7">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2211,7 +2436,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" bestFit="1" customWidth="1"/>
@@ -2242,1792 +2467,2364 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="12">
+      <c r="A2" s="32">
         <f>DATE(2026,1,1)</f>
         <v>46023</v>
       </c>
-      <c r="B2" s="13" t="str">
-        <f t="shared" ref="B2:B55" si="0">TEXT($A2,"ddd")</f>
+      <c r="B2" s="33" t="str">
+        <f>TEXT($A2,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="34" t="s">
+        <v>510</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>511</v>
+      </c>
+      <c r="E2" s="38" t="s">
+        <v>488</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="35">
+        <f>DATE(2026,1,1)</f>
+        <v>46023</v>
+      </c>
+      <c r="B3" s="36" t="str">
+        <f t="shared" ref="B3:B66" si="0">TEXT($A3,"ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="C3" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D3" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E3" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F3" s="25" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="12">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="39">
         <f>DATE(2026,2,8)</f>
         <v>46061</v>
       </c>
-      <c r="B3" s="13" t="str">
+      <c r="B4" s="40" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C4" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D4" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E4" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F4" s="25" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="12">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="43">
+        <f>DATE(2026,2,17)</f>
+        <v>46070</v>
+      </c>
+      <c r="B5" s="44" t="str">
+        <f>TEXT($A5,"ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>504</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>505</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>488</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="28">
+        <f>DATE(2026,2,18)</f>
+        <v>46071</v>
+      </c>
+      <c r="B6" s="27" t="str">
+        <f>TEXT($A6,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>506</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>507</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>488</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="35">
         <f>DATE(2026,2,26)</f>
         <v>46079</v>
       </c>
-      <c r="B4" s="13" t="str">
+      <c r="B7" s="36" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C7" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D7" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E7" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F7" s="25" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="12">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="12">
         <f>DATE(2026,2,27)</f>
         <v>46080</v>
       </c>
-      <c r="B5" s="13" t="str">
+      <c r="B8" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C8" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D8" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E8" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F8" s="25" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="12">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="12">
         <f>DATE(2026,3,7)</f>
         <v>46088</v>
       </c>
-      <c r="B6" s="13" t="str">
+      <c r="B9" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C9" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D9" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E9" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F9" s="25" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="12">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="39">
         <f>DATE(2026,3,20)</f>
         <v>46101</v>
       </c>
-      <c r="B7" s="13" t="str">
+      <c r="B10" s="40" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C10" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D10" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E10" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F10" s="25" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="12">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="28">
+        <f>DATE(2026,3,21)</f>
+        <v>46102</v>
+      </c>
+      <c r="B11" s="27" t="str">
+        <f>TEXT($A11,"ddd")</f>
+        <v>Sat</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>502</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>503</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>499</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="35">
         <f>DATE(2026,3,23)</f>
         <v>46104</v>
       </c>
-      <c r="B8" s="13" t="str">
+      <c r="B12" s="36" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C12" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D12" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E12" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F12" s="25" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="12">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="12">
         <f>DATE(2026,3,24)</f>
         <v>46105</v>
       </c>
-      <c r="B9" s="13" t="str">
+      <c r="B13" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C13" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D13" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E13" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F13" s="25" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="12">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="39">
         <f>DATE(2026,3,27)</f>
         <v>46108</v>
       </c>
-      <c r="B10" s="13" t="str">
+      <c r="B14" s="40" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C14" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D14" s="47" t="s">
         <v>227</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E14" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F14" s="25" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="12">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="28">
+        <f>DATE(2026,4,3)</f>
+        <v>46115</v>
+      </c>
+      <c r="B15" s="27" t="str">
+        <f>TEXT($A15,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>500</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>501</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>488</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="48">
         <f>DATE(2026,4,20)</f>
         <v>46132</v>
       </c>
-      <c r="B11" s="13" t="str">
+      <c r="B16" s="49" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C16" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D16" s="25" t="s">
         <v>250</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E16" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F16" s="25" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="12">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="28">
+        <f>DATE(2026,5,1)</f>
+        <v>46143</v>
+      </c>
+      <c r="B17" s="27" t="str">
+        <f>TEXT($A17,"ddd")</f>
+        <v>Fri</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>495</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>496</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>488</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="35">
         <f>DATE(2026,5,4)</f>
         <v>46146</v>
       </c>
-      <c r="B12" s="13" t="str">
+      <c r="B18" s="36" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C18" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D18" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E18" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F18" s="25" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="12">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="12">
         <f>DATE(2026,5,15)</f>
         <v>46157</v>
       </c>
-      <c r="B13" s="13" t="str">
+      <c r="B19" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C19" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D19" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E19" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F19" s="25" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="12">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="12">
         <f>DATE(2026,5,24)</f>
         <v>46166</v>
       </c>
-      <c r="B14" s="13" t="str">
+      <c r="B20" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C20" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D20" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E20" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F20" s="25" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="12">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="39">
         <f>DATE(2026,5,25)</f>
         <v>46167</v>
       </c>
-      <c r="B15" s="13" t="str">
+      <c r="B21" s="40" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C21" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D21" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E21" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="F21" s="25" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="12">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="28">
+        <f>DATE(2026,5,27)</f>
+        <v>46169</v>
+      </c>
+      <c r="B22" s="27" t="str">
+        <f>TEXT($A22,"ddd")</f>
+        <v>Wed</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>532</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>533</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>499</v>
+      </c>
+      <c r="F22" s="30" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="35">
         <f>DATE(2026,5,29)</f>
         <v>46171</v>
       </c>
-      <c r="B16" s="13" t="str">
+      <c r="B23" s="36" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C23" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D23" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E23" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="F16" s="25" t="s">
+      <c r="F23" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="12">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="39">
         <f>DATE(2026,5,30)</f>
         <v>46172</v>
       </c>
-      <c r="B17" s="13" t="str">
+      <c r="B24" s="40" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C24" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D24" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E24" s="41" t="s">
         <v>235</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="F24" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="12">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="43">
         <f>DATE(2026,5,31)</f>
         <v>46173</v>
       </c>
-      <c r="B18" s="13" t="str">
+      <c r="B25" s="44" t="str">
+        <f>TEXT($A25,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="C25" s="45" t="s">
+        <v>493</v>
+      </c>
+      <c r="D25" s="45" t="s">
+        <v>494</v>
+      </c>
+      <c r="E25" s="46" t="s">
+        <v>488</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="28">
+        <f>DATE(2026,6,1)</f>
+        <v>46174</v>
+      </c>
+      <c r="B26" s="27" t="str">
+        <f>TEXT($A26,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>516</v>
+      </c>
+      <c r="D26" s="29" t="s">
+        <v>517</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>488</v>
+      </c>
+      <c r="F26" s="30" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="35">
+        <f>DATE(2026,5,31)</f>
+        <v>46173</v>
+      </c>
+      <c r="B27" s="36" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C27" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D27" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E27" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="F27" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="12">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="12">
         <f>DATE(2026,6,1)</f>
         <v>46174</v>
       </c>
-      <c r="B19" s="13" t="str">
+      <c r="B28" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C28" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D28" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E28" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F19" s="25" t="s">
+      <c r="F28" s="25" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="12">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="12">
         <f>DATE(2026,6,12)</f>
         <v>46185</v>
       </c>
-      <c r="B20" s="13" t="str">
+      <c r="B29" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C29" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D29" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E29" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F20" s="25" t="s">
+      <c r="F29" s="25" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="12">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="12">
         <f>DATE(2026,6,13)</f>
         <v>46186</v>
       </c>
-      <c r="B21" s="13" t="str">
+      <c r="B30" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C30" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D30" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E30" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F30" s="25" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="12">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="12">
         <f>DATE(2026,6,20)</f>
         <v>46193</v>
       </c>
-      <c r="B22" s="13" t="str">
+      <c r="B31" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C31" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D31" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E31" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F22" s="25" t="s">
+      <c r="F31" s="25" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="12">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="12">
         <f>DATE(2026,7,3)</f>
         <v>46206</v>
       </c>
-      <c r="B23" s="13" t="str">
+      <c r="B32" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C32" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D32" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E32" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F23" s="25" t="s">
+      <c r="F32" s="25" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="12">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="12">
         <f>DATE(2026,7,24)</f>
         <v>46227</v>
       </c>
-      <c r="B24" s="13" t="str">
+      <c r="B33" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C33" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D33" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E33" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F24" s="25" t="s">
+      <c r="F33" s="25" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="12">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="12">
         <f>DATE(2026,7,24)</f>
         <v>46227</v>
       </c>
-      <c r="B25" s="13" t="str">
+      <c r="B34" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C34" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D34" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E34" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F25" s="25" t="s">
+      <c r="F34" s="25" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="12">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="12">
         <f>DATE(2026,7,25)</f>
         <v>46228</v>
       </c>
-      <c r="B26" s="13" t="str">
+      <c r="B35" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C35" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D35" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E35" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F26" s="25" t="s">
+      <c r="F35" s="25" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="12">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="12">
         <f>DATE(2026,8,1)</f>
         <v>46235</v>
       </c>
-      <c r="B27" s="13" t="str">
+      <c r="B36" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C36" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D36" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E36" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F27" s="25" t="s">
+      <c r="F36" s="25" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="12">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="12">
         <f>DATE(2026,8,5)</f>
         <v>46239</v>
       </c>
-      <c r="B28" s="13" t="str">
-        <f t="shared" ref="B28:B40" si="1">TEXT($A28,"ddd")</f>
+      <c r="B37" s="13" t="str">
+        <f t="shared" ref="B37:B51" si="1">TEXT($A37,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C37" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D37" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E37" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F28" s="25" t="s">
+      <c r="F37" s="25" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="12">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="39">
         <f>DATE(2026,8,8)</f>
         <v>46242</v>
       </c>
-      <c r="B29" s="13" t="str">
+      <c r="B38" s="40" t="str">
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C38" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D38" s="47" t="s">
         <v>222</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E38" s="41" t="s">
         <v>235</v>
       </c>
-      <c r="F29" s="25" t="s">
+      <c r="F38" s="25" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="12">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="43">
+        <f>DATE(2026,8,9)</f>
+        <v>46243</v>
+      </c>
+      <c r="B39" s="44" t="str">
+        <f>TEXT($A39,"ddd")</f>
+        <v>Sun</v>
+      </c>
+      <c r="C39" s="45" t="s">
+        <v>491</v>
+      </c>
+      <c r="D39" s="45" t="s">
+        <v>492</v>
+      </c>
+      <c r="E39" s="46" t="s">
+        <v>488</v>
+      </c>
+      <c r="F39" s="30" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="28">
+        <f>DATE(2026,8,10)</f>
+        <v>46244</v>
+      </c>
+      <c r="B40" s="27" t="str">
+        <f>TEXT($A40,"ddd")</f>
+        <v>Mon</v>
+      </c>
+      <c r="C40" s="29" t="s">
+        <v>514</v>
+      </c>
+      <c r="D40" s="29" t="s">
+        <v>515</v>
+      </c>
+      <c r="E40" s="42" t="s">
+        <v>488</v>
+      </c>
+      <c r="F40" s="30" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="35">
         <f>DATE(2026,8,14)</f>
         <v>46248</v>
       </c>
-      <c r="B30" s="13" t="str">
+      <c r="B41" s="36" t="str">
         <f t="shared" si="1"/>
         <v>Fri</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C41" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D41" s="50" t="s">
         <v>260</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E41" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="F30" s="25" t="s">
+      <c r="F41" s="25" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="12">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="12">
         <f>DATE(2026,8,15)</f>
         <v>46249</v>
       </c>
-      <c r="B31" s="13" t="str">
+      <c r="B42" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C42" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D42" s="16" t="s">
         <v>460</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E42" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="F31" s="25" t="s">
+      <c r="F42" s="25" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="12">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="12">
         <f>DATE(2026,8,19)</f>
         <v>46253</v>
       </c>
-      <c r="B32" s="13" t="str">
+      <c r="B43" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Wed</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C43" s="11" t="s">
         <v>462</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D43" s="16" t="s">
         <v>464</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E43" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F32" s="25" t="s">
+      <c r="F43" s="25" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="12">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="12">
         <f>DATE(2026,8,23)</f>
         <v>46257</v>
       </c>
-      <c r="B33" s="13" t="str">
+      <c r="B44" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sun</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C44" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D44" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E44" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F33" s="25" t="s">
+      <c r="F44" s="25" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="12">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="12">
         <f>DATE(2026,8,28)</f>
         <v>46262</v>
       </c>
-      <c r="B34" s="13" t="str">
-        <f>TEXT($A34,"ddd")</f>
+      <c r="B45" s="13" t="str">
+        <f>TEXT($A45,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C45" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D45" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E45" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F34" s="25" t="s">
+      <c r="F45" s="25" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="12">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="12">
         <f>DATE(2026,8,29)</f>
         <v>46263</v>
       </c>
-      <c r="B35" s="13" t="str">
+      <c r="B46" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C46" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D46" s="11" t="s">
         <v>461</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E46" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="F35" s="25" t="s">
+      <c r="F46" s="25" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="12">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="12">
         <f>DATE(2026,8,29)</f>
         <v>46263</v>
       </c>
-      <c r="B36" s="13" t="str">
+      <c r="B47" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Sat</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C47" s="11" t="s">
         <v>468</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D47" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E47" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F36" s="25" t="s">
+      <c r="F47" s="25" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="12">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="12">
         <f>DATE(2026,8,31)</f>
         <v>46265</v>
       </c>
-      <c r="B37" s="13" t="str">
-        <f>TEXT($A37,"ddd")</f>
+      <c r="B48" s="13" t="str">
+        <f>TEXT($A48,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C48" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D48" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E48" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F37" s="25" t="s">
+      <c r="F48" s="25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="12">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" s="12">
         <f>DATE(2026,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="B38" s="13" t="str">
+      <c r="B49" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Tue</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C49" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D49" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E49" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F38" s="25" t="s">
+      <c r="F49" s="25" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="12">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" s="12">
         <f>DATE(2026,9,3)</f>
         <v>46268</v>
       </c>
-      <c r="B39" s="13" t="str">
+      <c r="B50" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C50" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D50" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E50" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F39" s="25" t="s">
+      <c r="F50" s="25" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="12">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" s="12">
         <f>DATE(2026,9,3)</f>
         <v>46268</v>
       </c>
-      <c r="B40" s="13" t="str">
+      <c r="B51" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C51" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D51" s="16" t="s">
         <v>484</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E51" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F40" s="25" t="s">
+      <c r="F51" s="25" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="12">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" s="12">
         <f>DATE(2026,9,4)</f>
         <v>46269</v>
       </c>
-      <c r="B41" s="13" t="str">
-        <f>TEXT($A41,"ddd")</f>
+      <c r="B52" s="13" t="str">
+        <f>TEXT($A52,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C52" s="11" t="s">
         <v>485</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D52" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E52" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F41" s="25" t="s">
+      <c r="F52" s="25" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="12">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" s="12">
         <f>DATE(2026,9,5)</f>
         <v>46270</v>
       </c>
-      <c r="B42" s="13" t="str">
+      <c r="B53" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C53" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D53" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E53" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F42" s="25" t="s">
+      <c r="F53" s="25" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="12">
+      <c r="G53" s="19"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54" s="12">
         <f>DATE(2026,9,7)</f>
         <v>46272</v>
       </c>
-      <c r="B43" s="13" t="str">
-        <f>TEXT($A43,"ddd")</f>
+      <c r="B54" s="13" t="str">
+        <f>TEXT($A54,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C54" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D54" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E54" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F43" s="25" t="s">
+      <c r="F54" s="25" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="12">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55" s="12">
         <f>DATE(2026,9,8)</f>
         <v>46273</v>
       </c>
-      <c r="B44" s="13" t="str">
-        <f>TEXT($A44,"ddd")</f>
+      <c r="B55" s="13" t="str">
+        <f>TEXT($A55,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C55" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D55" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E55" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F44" s="25" t="s">
+      <c r="F55" s="25" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="12">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56" s="12">
         <f>DATE(2026,9,9)</f>
         <v>46274</v>
       </c>
-      <c r="B45" s="13" t="str">
-        <f>TEXT($A45,"ddd")</f>
+      <c r="B56" s="13" t="str">
+        <f>TEXT($A56,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C56" s="16" t="s">
         <v>470</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D56" s="16" t="s">
         <v>471</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E56" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F45" s="25" t="s">
+      <c r="F56" s="25" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="12">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" s="12">
         <f>DATE(2026,9,15)</f>
         <v>46280</v>
       </c>
-      <c r="B46" s="13" t="str">
+      <c r="B57" s="13" 